--- a/插件详细手册/0.性能测试报告/性能测试统计表.xlsx
+++ b/插件详细手册/0.性能测试报告/性能测试统计表.xlsx
@@ -1,11 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="23426"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="4" rupBuild="9302"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B254591-893B-43B5-A0C1-877D154B3191}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-105" yWindow="-105" windowWidth="20730" windowHeight="11760" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="地图界面" sheetId="1" r:id="rId1"/>
@@ -17,12 +16,12 @@
 </file>
 
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
     <author>作者</author>
   </authors>
   <commentList>
-    <comment ref="D87" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000001000000}">
+    <comment ref="D89" authorId="0">
       <text>
         <r>
           <rPr>
@@ -48,7 +47,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F140" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000002000000}">
+    <comment ref="F142" authorId="0">
       <text>
         <r>
           <rPr>
@@ -79,12 +78,12 @@
 </file>
 
 <file path=xl/comments2.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
     <author>作者</author>
   </authors>
   <commentList>
-    <comment ref="D40" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000001000000}">
+    <comment ref="D42" authorId="0">
       <text>
         <r>
           <rPr>
@@ -116,7 +115,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1575" uniqueCount="811">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1633" uniqueCount="839">
   <si>
     <t>行走图 - 图块同步镜像</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -3361,11 +3360,123 @@
     <t xml:space="preserve">  40.75ms</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
+  <si>
+    <t>Drill_ActorPortraitureExtend</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>战斗UI - 高级角色肖像</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>21.33ms</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>37.60ms</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>57.92ms</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>17.25ms</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>45.58ms</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>61.37ms</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Drill_SceneSelfplateM、N</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>面板 - 全自定义信息面板M、N</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">  21.54ms</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Drill_GlobalGameTimer</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>系统 - 累计游戏计时器</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">  5.07ms</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">  12.32ms</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Drill_CoreOfActionSequence</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>系统 - GIF动画序列核心</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>系统 - 截取地图工具</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">  15.20ms</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">  13.55ms</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Drill_PictureActionSequence</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>图片 - GIF动画序列</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>17.76ms</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>13.94ms</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>12.60ms</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">  131.05ms</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">  21.21ms</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>图片 - GIF动画序列（首次载入大量图片时）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -3599,21 +3710,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -3629,13 +3725,28 @@
     <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -3703,7 +3814,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -3736,26 +3847,9 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -3788,23 +3882,6 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -3980,18 +4057,18 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A2:H169"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15.6" x14ac:dyDescent="0.35"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A2:H173"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="39.6640625" style="1" customWidth="1"/>
-    <col min="2" max="2" width="38.77734375" style="1" customWidth="1"/>
-    <col min="3" max="3" width="14.77734375" style="1" customWidth="1"/>
-    <col min="4" max="8" width="12.6640625" style="1" customWidth="1"/>
+    <col min="1" max="1" width="39.625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="38.75" style="1" customWidth="1"/>
+    <col min="3" max="3" width="14.75" style="1" customWidth="1"/>
+    <col min="4" max="8" width="12.625" style="1" customWidth="1"/>
     <col min="9" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2" s="4" t="s">
         <v>44</v>
       </c>
@@ -4003,105 +4080,105 @@
       <c r="G2" s="4"/>
       <c r="H2" s="5"/>
     </row>
-    <row r="4" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="24" t="s">
         <v>57</v>
       </c>
       <c r="B4" s="24"/>
       <c r="C4" s="24"/>
-      <c r="D4" s="29" t="s">
+      <c r="D4" s="33" t="s">
         <v>55</v>
       </c>
-      <c r="E4" s="29"/>
+      <c r="E4" s="33"/>
       <c r="F4" s="11" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="5" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="24" t="s">
         <v>46</v>
       </c>
       <c r="B5" s="24"/>
       <c r="C5" s="24"/>
-      <c r="D5" s="27" t="s">
+      <c r="D5" s="31" t="s">
         <v>47</v>
       </c>
-      <c r="E5" s="27"/>
+      <c r="E5" s="31"/>
       <c r="F5" s="10" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="6" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="24" t="s">
         <v>45</v>
       </c>
       <c r="B6" s="24"/>
       <c r="C6" s="24"/>
-      <c r="D6" s="28" t="s">
+      <c r="D6" s="32" t="s">
         <v>49</v>
       </c>
-      <c r="E6" s="28"/>
+      <c r="E6" s="32"/>
       <c r="F6" s="13" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="7" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="30" t="s">
+    <row r="7" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="25" t="s">
         <v>62</v>
       </c>
-      <c r="B7" s="30"/>
-      <c r="C7" s="30"/>
-      <c r="D7" s="32" t="s">
+      <c r="B7" s="25"/>
+      <c r="C7" s="25"/>
+      <c r="D7" s="27" t="s">
         <v>51</v>
       </c>
-      <c r="E7" s="32"/>
+      <c r="E7" s="27"/>
       <c r="F7" s="12" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="8" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="30" t="s">
+    <row r="8" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="25" t="s">
         <v>63</v>
       </c>
-      <c r="B8" s="30"/>
-      <c r="C8" s="30"/>
-      <c r="D8" s="33" t="s">
+      <c r="B8" s="25"/>
+      <c r="C8" s="25"/>
+      <c r="D8" s="28" t="s">
         <v>53</v>
       </c>
-      <c r="E8" s="33"/>
+      <c r="E8" s="28"/>
       <c r="F8" s="14" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="9" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="24" t="s">
         <v>144</v>
       </c>
       <c r="B9" s="24"/>
       <c r="C9" s="24"/>
     </row>
-    <row r="10" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="24" t="s">
         <v>373</v>
       </c>
       <c r="B10" s="24"/>
       <c r="C10" s="24"/>
     </row>
-    <row r="12" spans="1:8" ht="16.2" x14ac:dyDescent="0.4">
-      <c r="A12" s="34" t="s">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A12" s="29" t="s">
         <v>343</v>
       </c>
-      <c r="B12" s="34"/>
+      <c r="B12" s="29"/>
       <c r="C12" s="8"/>
-      <c r="D12" s="31" t="s">
+      <c r="D12" s="26" t="s">
         <v>579</v>
       </c>
-      <c r="E12" s="31"/>
-      <c r="F12" s="31"/>
-      <c r="G12" s="31"/>
+      <c r="E12" s="26"/>
+      <c r="F12" s="26"/>
+      <c r="G12" s="26"/>
       <c r="H12" s="5"/>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A13" s="19" t="s">
         <v>160</v>
       </c>
@@ -4125,7 +4202,7 @@
       </c>
       <c r="H13" s="2"/>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A14" s="1" t="s">
         <v>171</v>
       </c>
@@ -4135,14 +4212,14 @@
       <c r="C14" s="1" t="s">
         <v>180</v>
       </c>
-      <c r="D14" s="26" t="s">
+      <c r="D14" s="30" t="s">
         <v>178</v>
       </c>
-      <c r="E14" s="26"/>
-      <c r="F14" s="26"/>
-      <c r="G14" s="26"/>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="E14" s="30"/>
+      <c r="F14" s="30"/>
+      <c r="G14" s="30"/>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A15" s="1" t="s">
         <v>375</v>
       </c>
@@ -4152,14 +4229,14 @@
       <c r="C15" s="1" t="s">
         <v>180</v>
       </c>
-      <c r="D15" s="26" t="s">
+      <c r="D15" s="30" t="s">
         <v>178</v>
       </c>
-      <c r="E15" s="26"/>
-      <c r="F15" s="26"/>
-      <c r="G15" s="26"/>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="E15" s="30"/>
+      <c r="F15" s="30"/>
+      <c r="G15" s="30"/>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A16" s="1" t="s">
         <v>401</v>
       </c>
@@ -4176,7 +4253,7 @@
       <c r="F16" s="24"/>
       <c r="G16" s="24"/>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A17" s="1" t="s">
         <v>377</v>
       </c>
@@ -4193,7 +4270,7 @@
       <c r="F17" s="24"/>
       <c r="G17" s="24"/>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A18" s="1" t="s">
         <v>585</v>
       </c>
@@ -4210,7 +4287,7 @@
       <c r="F18" s="24"/>
       <c r="G18" s="24"/>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A19" s="1" t="s">
         <v>581</v>
       </c>
@@ -4227,7 +4304,7 @@
       <c r="F19" s="24"/>
       <c r="G19" s="24"/>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A20" s="1" t="s">
         <v>614</v>
       </c>
@@ -4244,7 +4321,7 @@
       <c r="F20" s="24"/>
       <c r="G20" s="24"/>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A21" s="1" t="s">
         <v>616</v>
       </c>
@@ -4254,14 +4331,14 @@
       <c r="C21" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="D21" s="26" t="s">
+      <c r="D21" s="30" t="s">
         <v>178</v>
       </c>
-      <c r="E21" s="26"/>
-      <c r="F21" s="26"/>
-      <c r="G21" s="26"/>
-    </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="E21" s="30"/>
+      <c r="F21" s="30"/>
+      <c r="G21" s="30"/>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A22" s="1" t="s">
         <v>717</v>
       </c>
@@ -4271,14 +4348,14 @@
       <c r="C22" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="D22" s="25" t="s">
+      <c r="D22" s="34" t="s">
         <v>721</v>
       </c>
-      <c r="E22" s="25"/>
-      <c r="F22" s="25"/>
-      <c r="G22" s="25"/>
-    </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="E22" s="34"/>
+      <c r="F22" s="34"/>
+      <c r="G22" s="34"/>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A23" s="1" t="s">
         <v>716</v>
       </c>
@@ -4295,7 +4372,7 @@
       <c r="F23" s="24"/>
       <c r="G23" s="24"/>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A24" s="1" t="s">
         <v>738</v>
       </c>
@@ -4312,7 +4389,7 @@
       <c r="F24" s="24"/>
       <c r="G24" s="24"/>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A25" s="1" t="s">
         <v>793</v>
       </c>
@@ -4329,480 +4406,474 @@
       <c r="F25" s="24"/>
       <c r="G25" s="24"/>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A26" s="1" t="s">
+        <v>826</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>827</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D26" s="24" t="s">
+        <v>825</v>
+      </c>
+      <c r="E26" s="24"/>
+      <c r="F26" s="24"/>
+      <c r="G26" s="24"/>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A27" s="1" t="s">
         <v>172</v>
       </c>
-      <c r="B26" s="1" t="s">
+      <c r="B27" s="1" t="s">
         <v>163</v>
-      </c>
-      <c r="C26" s="1" t="s">
-        <v>179</v>
-      </c>
-      <c r="D26" s="26" t="s">
-        <v>178</v>
-      </c>
-      <c r="E26" s="26"/>
-      <c r="F26" s="26"/>
-      <c r="G26" s="26"/>
-    </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A27" s="1" t="s">
-        <v>173</v>
-      </c>
-      <c r="B27" s="1" t="s">
-        <v>164</v>
       </c>
       <c r="C27" s="1" t="s">
         <v>179</v>
       </c>
-      <c r="D27" s="26" t="s">
-        <v>182</v>
-      </c>
-      <c r="E27" s="26"/>
-      <c r="F27" s="26"/>
-      <c r="G27" s="26"/>
-    </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="D27" s="30" t="s">
+        <v>178</v>
+      </c>
+      <c r="E27" s="30"/>
+      <c r="F27" s="30"/>
+      <c r="G27" s="30"/>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A28" s="1" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>174</v>
+        <v>164</v>
       </c>
       <c r="C28" s="1" t="s">
         <v>179</v>
       </c>
-      <c r="D28" s="24" t="s">
-        <v>408</v>
-      </c>
-      <c r="E28" s="24"/>
-      <c r="F28" s="24"/>
-      <c r="G28" s="24"/>
-    </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="D28" s="30" t="s">
+        <v>182</v>
+      </c>
+      <c r="E28" s="30"/>
+      <c r="F28" s="30"/>
+      <c r="G28" s="30"/>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A29" s="1" t="s">
-        <v>165</v>
+        <v>175</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="C29" s="1" t="s">
         <v>179</v>
       </c>
-      <c r="D29" s="26" t="s">
+      <c r="D29" s="24" t="s">
+        <v>408</v>
+      </c>
+      <c r="E29" s="24"/>
+      <c r="F29" s="24"/>
+      <c r="G29" s="24"/>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A30" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="D30" s="30" t="s">
         <v>178</v>
       </c>
-      <c r="E29" s="26"/>
-      <c r="F29" s="26"/>
-      <c r="G29" s="26"/>
-    </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A30" s="1" t="s">
+      <c r="E30" s="30"/>
+      <c r="F30" s="30"/>
+      <c r="G30" s="30"/>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A31" s="1" t="s">
         <v>166</v>
       </c>
-      <c r="B30" s="1" t="s">
+      <c r="B31" s="1" t="s">
         <v>167</v>
       </c>
-      <c r="C30" s="1" t="s">
+      <c r="C31" s="1" t="s">
         <v>180</v>
       </c>
-      <c r="D30" s="24" t="s">
+      <c r="D31" s="24" t="s">
         <v>409</v>
       </c>
-      <c r="E30" s="24"/>
-      <c r="F30" s="24"/>
-      <c r="G30" s="24"/>
-    </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A31" s="1" t="s">
-        <v>177</v>
-      </c>
-      <c r="B31" s="1" t="s">
-        <v>168</v>
-      </c>
-      <c r="C31" s="1" t="s">
-        <v>181</v>
-      </c>
-      <c r="D31" s="26" t="s">
-        <v>182</v>
-      </c>
-      <c r="E31" s="26"/>
-      <c r="F31" s="26"/>
-      <c r="G31" s="26"/>
-    </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="E31" s="24"/>
+      <c r="F31" s="24"/>
+      <c r="G31" s="24"/>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A32" s="1" t="s">
-        <v>169</v>
+        <v>822</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>170</v>
+        <v>823</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>180</v>
+        <v>43</v>
       </c>
       <c r="D32" s="24" t="s">
-        <v>410</v>
+        <v>829</v>
       </c>
       <c r="E32" s="24"/>
       <c r="F32" s="24"/>
       <c r="G32" s="24"/>
     </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A33" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="C33" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="D33" s="30" t="s">
+        <v>182</v>
+      </c>
+      <c r="E33" s="30"/>
+      <c r="F33" s="30"/>
+      <c r="G33" s="30"/>
+    </row>
+    <row r="34" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A34" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="C34" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="D34" s="24" t="s">
+        <v>410</v>
+      </c>
+      <c r="E34" s="24"/>
+      <c r="F34" s="24"/>
+      <c r="G34" s="24"/>
+    </row>
+    <row r="35" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A35" s="1" t="s">
         <v>750</v>
       </c>
-      <c r="B33" s="1" t="s">
+      <c r="B35" s="1" t="s">
         <v>751</v>
       </c>
-      <c r="C33" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="D33" s="26" t="s">
+      <c r="C35" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D35" s="30" t="s">
         <v>182</v>
       </c>
-      <c r="E33" s="26"/>
-      <c r="F33" s="26"/>
-      <c r="G33" s="26"/>
-    </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A35" s="1" t="s">
+      <c r="E35" s="30"/>
+      <c r="F35" s="30"/>
+      <c r="G35" s="30"/>
+    </row>
+    <row r="37" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A37" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="B35" s="1" t="s">
+      <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="C35" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="D35" s="6" t="s">
+      <c r="C37" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D37" s="6" t="s">
         <v>393</v>
       </c>
-      <c r="E35" s="7" t="s">
+      <c r="E37" s="7" t="s">
         <v>394</v>
       </c>
-      <c r="F35" s="7" t="s">
+      <c r="F37" s="7" t="s">
         <v>392</v>
       </c>
-      <c r="G35" s="1" t="s">
+      <c r="G37" s="1" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A36" s="22" t="s">
+    <row r="38" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A38" s="22" t="s">
         <v>27</v>
       </c>
-      <c r="B36" s="22" t="s">
+      <c r="B38" s="22" t="s">
         <v>28</v>
       </c>
-      <c r="C36" s="22" t="s">
-        <v>43</v>
-      </c>
-      <c r="D36" s="15" t="s">
+      <c r="C38" s="22" t="s">
+        <v>43</v>
+      </c>
+      <c r="D38" s="15" t="s">
         <v>14</v>
       </c>
-      <c r="E36" s="15" t="s">
+      <c r="E38" s="15" t="s">
         <v>14</v>
       </c>
-      <c r="F36" s="15" t="s">
+      <c r="F38" s="15" t="s">
         <v>14</v>
       </c>
-      <c r="G36" s="15" t="s">
+      <c r="G38" s="15" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A37" s="1" t="s">
+    <row r="39" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A39" s="1" t="s">
         <v>631</v>
       </c>
-      <c r="B37" s="1" t="s">
+      <c r="B39" s="1" t="s">
         <v>632</v>
       </c>
-      <c r="C37" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="D37" s="15" t="s">
+      <c r="C39" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D39" s="15" t="s">
         <v>635</v>
       </c>
-      <c r="E37" s="15" t="s">
+      <c r="E39" s="15" t="s">
         <v>636</v>
       </c>
-      <c r="F37" s="6" t="s">
+      <c r="F39" s="6" t="s">
         <v>634</v>
       </c>
-      <c r="G37" s="7" t="s">
+      <c r="G39" s="7" t="s">
         <v>633</v>
       </c>
     </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A38" s="1" t="s">
+    <row r="40" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A40" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="B38" s="1" t="s">
+      <c r="B40" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="H38" s="1" t="s">
+      <c r="H40" s="1" t="s">
         <v>183</v>
       </c>
     </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A39" s="1" t="s">
+    <row r="41" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A41" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="B39" s="1" t="s">
+      <c r="B41" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="C39" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="D39" s="1" t="s">
+      <c r="C41" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D41" s="1" t="s">
         <v>695</v>
       </c>
-      <c r="E39" s="1" t="s">
+      <c r="E41" s="1" t="s">
         <v>696</v>
       </c>
-      <c r="F39" s="1" t="s">
+      <c r="F41" s="1" t="s">
         <v>697</v>
-      </c>
-      <c r="G39" s="1" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A40" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="B40" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="C40" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="D40" s="1" t="s">
-        <v>694</v>
-      </c>
-      <c r="E40" s="1" t="s">
-        <v>693</v>
-      </c>
-      <c r="F40" s="1" t="s">
-        <v>692</v>
-      </c>
-      <c r="G40" s="1" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A41" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="B41" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="C41" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="D41" s="1" t="s">
-        <v>689</v>
-      </c>
-      <c r="E41" s="1" t="s">
-        <v>690</v>
-      </c>
-      <c r="F41" s="1" t="s">
-        <v>691</v>
       </c>
       <c r="G41" s="1" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A42" s="1" t="s">
-        <v>36</v>
+        <v>58</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>37</v>
+        <v>59</v>
       </c>
       <c r="C42" s="1" t="s">
         <v>43</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>387</v>
+        <v>694</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>146</v>
+        <v>693</v>
       </c>
       <c r="F42" s="1" t="s">
-        <v>388</v>
+        <v>692</v>
       </c>
       <c r="G42" s="1" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A43" s="1" t="s">
-        <v>725</v>
+        <v>60</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>726</v>
+        <v>61</v>
       </c>
       <c r="C43" s="1" t="s">
         <v>43</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>729</v>
+        <v>689</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>728</v>
+        <v>690</v>
       </c>
       <c r="F43" s="1" t="s">
-        <v>727</v>
+        <v>691</v>
       </c>
       <c r="G43" s="1" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A44" s="1" t="s">
-        <v>789</v>
+        <v>36</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>790</v>
+        <v>37</v>
       </c>
       <c r="C44" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="D44" s="24" t="s">
-        <v>406</v>
-      </c>
-      <c r="E44" s="24"/>
-      <c r="F44" s="24"/>
-      <c r="G44" s="24"/>
-    </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="D44" s="1" t="s">
+        <v>387</v>
+      </c>
+      <c r="E44" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="F44" s="1" t="s">
+        <v>388</v>
+      </c>
+      <c r="G44" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A45" s="1" t="s">
-        <v>38</v>
+        <v>725</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>39</v>
+        <v>726</v>
       </c>
       <c r="C45" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="D45" s="15" t="s">
-        <v>158</v>
-      </c>
-      <c r="E45" s="15" t="s">
-        <v>159</v>
-      </c>
-      <c r="F45" s="6" t="s">
-        <v>157</v>
+      <c r="D45" s="1" t="s">
+        <v>729</v>
+      </c>
+      <c r="E45" s="1" t="s">
+        <v>728</v>
+      </c>
+      <c r="F45" s="1" t="s">
+        <v>727</v>
       </c>
       <c r="G45" s="1" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A46" s="1" t="s">
+        <v>789</v>
+      </c>
+      <c r="B46" s="1" t="s">
+        <v>790</v>
+      </c>
+      <c r="C46" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D46" s="24" t="s">
+        <v>406</v>
+      </c>
+      <c r="E46" s="24"/>
+      <c r="F46" s="24"/>
+      <c r="G46" s="24"/>
+    </row>
+    <row r="47" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A47" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="B47" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="C47" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D47" s="15" t="s">
+        <v>158</v>
+      </c>
+      <c r="E47" s="15" t="s">
+        <v>159</v>
+      </c>
+      <c r="F47" s="6" t="s">
+        <v>157</v>
+      </c>
+      <c r="G47" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="48" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A48" s="1" t="s">
         <v>622</v>
       </c>
-      <c r="B46" s="1" t="s">
+      <c r="B48" s="1" t="s">
         <v>623</v>
       </c>
-      <c r="C46" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="D46" s="6" t="s">
+      <c r="C48" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D48" s="6" t="s">
         <v>618</v>
       </c>
-      <c r="E46" s="6" t="s">
+      <c r="E48" s="6" t="s">
         <v>619</v>
       </c>
-      <c r="F46" s="6" t="s">
+      <c r="F48" s="6" t="s">
         <v>620</v>
       </c>
-      <c r="G46" s="1" t="s">
+      <c r="G48" s="1" t="s">
         <v>621</v>
       </c>
     </row>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A48" s="1" t="s">
+    <row r="50" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A50" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="B48" s="1" t="s">
+      <c r="B50" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="C48" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="D48" s="1" t="s">
+      <c r="C50" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D50" s="1" t="s">
         <v>497</v>
       </c>
-      <c r="E48" s="1" t="s">
+      <c r="E50" s="1" t="s">
         <v>498</v>
       </c>
-      <c r="F48" s="1" t="s">
+      <c r="F50" s="1" t="s">
         <v>499</v>
       </c>
-      <c r="G48" s="1" t="s">
+      <c r="G50" s="1" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="49" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A49" s="1" t="s">
+    <row r="51" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A51" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="B49" s="1" t="s">
+      <c r="B51" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="H49" s="1" t="s">
+      <c r="H51" s="1" t="s">
         <v>183</v>
       </c>
     </row>
-    <row r="50" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A50" s="1" t="s">
+    <row r="52" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A52" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="B50" s="1" t="s">
+      <c r="B52" s="1" t="s">
         <v>69</v>
-      </c>
-      <c r="C50" s="1" t="s">
-        <v>143</v>
-      </c>
-      <c r="D50" s="24" t="s">
-        <v>411</v>
-      </c>
-      <c r="E50" s="24"/>
-      <c r="F50" s="24"/>
-      <c r="G50" s="24"/>
-    </row>
-    <row r="51" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A51" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="B51" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="C51" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="D51" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="E51" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="F51" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="G51" s="1" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="52" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A52" s="1" t="s">
-        <v>151</v>
-      </c>
-      <c r="B52" s="1" t="s">
-        <v>150</v>
       </c>
       <c r="C52" s="1" t="s">
         <v>143</v>
@@ -4814,69 +4885,63 @@
       <c r="F52" s="24"/>
       <c r="G52" s="24"/>
     </row>
-    <row r="53" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A53" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B53" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="C53" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D53" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="E53" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="F53" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="G53" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="54" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A54" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="B54" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="C54" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="D54" s="24" t="s">
+        <v>411</v>
+      </c>
+      <c r="E54" s="24"/>
+      <c r="F54" s="24"/>
+      <c r="G54" s="24"/>
+    </row>
+    <row r="55" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A55" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="B53" s="1" t="s">
+      <c r="B55" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="H53" s="1" t="s">
+      <c r="H55" s="1" t="s">
         <v>183</v>
       </c>
     </row>
-    <row r="54" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A54" s="1" t="s">
+    <row r="56" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A56" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="B54" s="1" t="s">
+      <c r="B56" s="1" t="s">
         <v>22</v>
-      </c>
-      <c r="C54" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="D54" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="E54" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="F54" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="G54" s="1" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="55" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A55" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="B55" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="C55" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="D55" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="E55" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="F55" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="G55" s="1" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="56" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A56" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="B56" s="1" t="s">
-        <v>18</v>
       </c>
       <c r="C56" s="1" t="s">
         <v>43</v>
@@ -4885,7 +4950,7 @@
         <v>15</v>
       </c>
       <c r="E56" s="7" t="s">
-        <v>123</v>
+        <v>16</v>
       </c>
       <c r="F56" s="1" t="s">
         <v>17</v>
@@ -4894,505 +4959,511 @@
         <v>14</v>
       </c>
     </row>
-    <row r="57" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A57" s="1" t="s">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>10</v>
+        <v>70</v>
       </c>
       <c r="C57" s="1" t="s">
         <v>43</v>
       </c>
       <c r="D57" s="6" t="s">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="E57" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="F57" s="7" t="s">
-        <v>9</v>
+        <v>16</v>
+      </c>
+      <c r="F57" s="1" t="s">
+        <v>17</v>
       </c>
       <c r="G57" s="1" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="58" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A58" s="1" t="s">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="C58" s="1" t="s">
         <v>43</v>
       </c>
       <c r="D58" s="6" t="s">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="E58" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="F58" s="7" t="s">
-        <v>6</v>
+        <v>123</v>
+      </c>
+      <c r="F58" s="1" t="s">
+        <v>17</v>
       </c>
       <c r="G58" s="1" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="59" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A59" s="1" t="s">
-        <v>569</v>
+        <v>11</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>570</v>
+        <v>10</v>
       </c>
       <c r="C59" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="D59" s="1" t="s">
-        <v>571</v>
-      </c>
-      <c r="E59" s="1" t="s">
-        <v>572</v>
-      </c>
-      <c r="F59" s="1" t="s">
-        <v>573</v>
+      <c r="D59" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="E59" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="F59" s="7" t="s">
+        <v>9</v>
       </c>
       <c r="G59" s="1" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="60" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A60" s="1" t="s">
-        <v>40</v>
+        <v>3</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="C60" s="1" t="s">
         <v>43</v>
       </c>
       <c r="D60" s="6" t="s">
-        <v>148</v>
-      </c>
-      <c r="E60" s="6" t="s">
-        <v>149</v>
+        <v>4</v>
+      </c>
+      <c r="E60" s="7" t="s">
+        <v>5</v>
       </c>
       <c r="F60" s="7" t="s">
-        <v>147</v>
+        <v>6</v>
       </c>
       <c r="G60" s="1" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="61" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A61" s="1" t="s">
-        <v>626</v>
+        <v>569</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>627</v>
+        <v>570</v>
       </c>
       <c r="C61" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="D61" s="6" t="s">
-        <v>628</v>
-      </c>
-      <c r="E61" s="6" t="s">
-        <v>629</v>
-      </c>
-      <c r="F61" s="7" t="s">
-        <v>630</v>
+      <c r="D61" s="1" t="s">
+        <v>571</v>
+      </c>
+      <c r="E61" s="1" t="s">
+        <v>572</v>
+      </c>
+      <c r="F61" s="1" t="s">
+        <v>573</v>
       </c>
       <c r="G61" s="1" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="63" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A62" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="B62" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="C62" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D62" s="6" t="s">
+        <v>148</v>
+      </c>
+      <c r="E62" s="6" t="s">
+        <v>149</v>
+      </c>
+      <c r="F62" s="7" t="s">
+        <v>147</v>
+      </c>
+      <c r="G62" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="63" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A63" s="1" t="s">
+        <v>626</v>
+      </c>
+      <c r="B63" s="1" t="s">
+        <v>627</v>
+      </c>
+      <c r="C63" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D63" s="6" t="s">
+        <v>628</v>
+      </c>
+      <c r="E63" s="6" t="s">
+        <v>629</v>
+      </c>
+      <c r="F63" s="7" t="s">
+        <v>630</v>
+      </c>
+      <c r="G63" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="65" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A65" s="1" t="s">
         <v>556</v>
       </c>
-      <c r="B63" s="1" t="s">
+      <c r="B65" s="1" t="s">
         <v>558</v>
       </c>
-      <c r="C63" s="1" t="s">
+      <c r="C65" s="1" t="s">
         <v>143</v>
       </c>
-      <c r="D63" s="24" t="s">
+      <c r="D65" s="24" t="s">
         <v>406</v>
       </c>
-      <c r="E63" s="24"/>
-      <c r="F63" s="24"/>
-      <c r="G63" s="24"/>
-    </row>
-    <row r="64" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A64" s="1" t="s">
+      <c r="E65" s="24"/>
+      <c r="F65" s="24"/>
+      <c r="G65" s="24"/>
+    </row>
+    <row r="66" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A66" s="1" t="s">
         <v>557</v>
       </c>
-      <c r="B64" s="1" t="s">
+      <c r="B66" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="C64" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="D64" s="1" t="s">
+      <c r="C66" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D66" s="1" t="s">
         <v>140</v>
       </c>
-      <c r="E64" s="1" t="s">
+      <c r="E66" s="1" t="s">
         <v>141</v>
       </c>
-      <c r="F64" s="1" t="s">
+      <c r="F66" s="1" t="s">
         <v>142</v>
       </c>
-      <c r="G64" s="1" t="s">
+      <c r="G66" s="1" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="65" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A65" s="1" t="s">
+    <row r="67" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A67" s="1" t="s">
         <v>559</v>
       </c>
-      <c r="B65" s="1" t="s">
+      <c r="B67" s="1" t="s">
         <v>560</v>
       </c>
-      <c r="C65" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="D65" s="1" t="s">
+      <c r="C67" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D67" s="1" t="s">
         <v>561</v>
       </c>
-      <c r="E65" s="1" t="s">
+      <c r="E67" s="1" t="s">
         <v>562</v>
       </c>
-      <c r="F65" s="1" t="s">
+      <c r="F67" s="1" t="s">
         <v>563</v>
       </c>
-      <c r="G65" s="1" t="s">
+      <c r="G67" s="1" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="66" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A66" s="1" t="s">
+    <row r="68" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A68" s="1" t="s">
         <v>672</v>
       </c>
-      <c r="B66" s="1" t="s">
+      <c r="B68" s="1" t="s">
         <v>673</v>
       </c>
-      <c r="C66" s="1" t="s">
+      <c r="C68" s="1" t="s">
         <v>674</v>
       </c>
-      <c r="D66" s="24" t="s">
+      <c r="D68" s="24" t="s">
         <v>406</v>
       </c>
-      <c r="E66" s="24"/>
-      <c r="F66" s="24"/>
-      <c r="G66" s="24"/>
-    </row>
-    <row r="67" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A67" s="1" t="s">
+      <c r="E68" s="24"/>
+      <c r="F68" s="24"/>
+      <c r="G68" s="24"/>
+    </row>
+    <row r="69" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A69" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="B67" s="1" t="s">
+      <c r="B69" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="C67" s="1" t="s">
+      <c r="C69" s="1" t="s">
         <v>143</v>
       </c>
-      <c r="D67" s="24" t="s">
+      <c r="D69" s="24" t="s">
         <v>412</v>
       </c>
-      <c r="E67" s="24"/>
-      <c r="F67" s="24"/>
-      <c r="G67" s="24"/>
-    </row>
-    <row r="68" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A68" s="1" t="s">
+      <c r="E69" s="24"/>
+      <c r="F69" s="24"/>
+      <c r="G69" s="24"/>
+    </row>
+    <row r="70" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A70" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="B68" s="1" t="s">
+      <c r="B70" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="C68" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="D68" s="1" t="s">
+      <c r="C70" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D70" s="1" t="s">
         <v>396</v>
       </c>
-      <c r="E68" s="1" t="s">
+      <c r="E70" s="1" t="s">
         <v>397</v>
       </c>
-      <c r="F68" s="1" t="s">
+      <c r="F70" s="1" t="s">
         <v>390</v>
-      </c>
-      <c r="G68" s="1" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="69" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A69" s="1" t="s">
-        <v>564</v>
-      </c>
-      <c r="B69" s="1" t="s">
-        <v>565</v>
-      </c>
-      <c r="C69" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="D69" s="1" t="s">
-        <v>566</v>
-      </c>
-      <c r="E69" s="1" t="s">
-        <v>567</v>
-      </c>
-      <c r="F69" s="1" t="s">
-        <v>390</v>
-      </c>
-      <c r="G69" s="1" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="70" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A70" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="B70" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="C70" s="1" t="s">
-        <v>180</v>
-      </c>
-      <c r="D70" s="1" t="s">
-        <v>395</v>
-      </c>
-      <c r="E70" s="1" t="s">
-        <v>389</v>
-      </c>
-      <c r="F70" s="1" t="s">
-        <v>391</v>
       </c>
       <c r="G70" s="1" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="71" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A71" s="1" t="s">
-        <v>609</v>
+        <v>564</v>
       </c>
       <c r="B71" s="1" t="s">
-        <v>610</v>
+        <v>565</v>
       </c>
       <c r="C71" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="D71" s="7" t="s">
-        <v>613</v>
+      <c r="D71" s="1" t="s">
+        <v>566</v>
       </c>
       <c r="E71" s="1" t="s">
-        <v>611</v>
+        <v>567</v>
       </c>
       <c r="F71" s="1" t="s">
-        <v>612</v>
+        <v>390</v>
       </c>
       <c r="G71" s="1" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="72" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A72" s="1" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="C72" s="1" t="s">
-        <v>143</v>
-      </c>
-      <c r="D72" s="24" t="s">
-        <v>406</v>
-      </c>
-      <c r="E72" s="24"/>
-      <c r="F72" s="24"/>
-      <c r="G72" s="24"/>
-    </row>
-    <row r="73" spans="1:7" x14ac:dyDescent="0.35">
+        <v>180</v>
+      </c>
+      <c r="D72" s="1" t="s">
+        <v>395</v>
+      </c>
+      <c r="E72" s="1" t="s">
+        <v>389</v>
+      </c>
+      <c r="F72" s="1" t="s">
+        <v>391</v>
+      </c>
+      <c r="G72" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="73" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A73" s="1" t="s">
-        <v>89</v>
+        <v>609</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>90</v>
+        <v>610</v>
       </c>
       <c r="C73" s="1" t="s">
-        <v>143</v>
-      </c>
-      <c r="D73" s="1" t="s">
-        <v>568</v>
+        <v>43</v>
+      </c>
+      <c r="D73" s="7" t="s">
+        <v>613</v>
       </c>
       <c r="E73" s="1" t="s">
-        <v>390</v>
+        <v>611</v>
       </c>
       <c r="F73" s="1" t="s">
-        <v>390</v>
+        <v>612</v>
       </c>
       <c r="G73" s="1" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="74" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A74" s="1" t="s">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="B74" s="1" t="s">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="C74" s="1" t="s">
         <v>143</v>
       </c>
-      <c r="D74" s="1" t="s">
-        <v>379</v>
-      </c>
-      <c r="E74" s="1" t="s">
-        <v>145</v>
-      </c>
-      <c r="F74" s="1" t="s">
-        <v>380</v>
-      </c>
-      <c r="G74" s="1" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="75" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="D74" s="24" t="s">
+        <v>406</v>
+      </c>
+      <c r="E74" s="24"/>
+      <c r="F74" s="24"/>
+      <c r="G74" s="24"/>
+    </row>
+    <row r="75" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A75" s="1" t="s">
-        <v>574</v>
+        <v>89</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>575</v>
+        <v>90</v>
       </c>
       <c r="C75" s="1" t="s">
-        <v>43</v>
+        <v>143</v>
       </c>
       <c r="D75" s="1" t="s">
-        <v>576</v>
+        <v>568</v>
       </c>
       <c r="E75" s="1" t="s">
-        <v>577</v>
+        <v>390</v>
       </c>
       <c r="F75" s="1" t="s">
-        <v>578</v>
+        <v>390</v>
       </c>
       <c r="G75" s="1" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="76" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A76" s="1" t="s">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="B76" s="1" t="s">
-        <v>83</v>
+        <v>92</v>
       </c>
       <c r="C76" s="1" t="s">
         <v>143</v>
       </c>
       <c r="D76" s="1" t="s">
-        <v>506</v>
+        <v>379</v>
       </c>
       <c r="E76" s="1" t="s">
-        <v>507</v>
+        <v>145</v>
       </c>
       <c r="F76" s="1" t="s">
-        <v>390</v>
+        <v>380</v>
       </c>
       <c r="G76" s="1" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="77" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A77" s="1" t="s">
-        <v>152</v>
+        <v>574</v>
       </c>
       <c r="B77" s="1" t="s">
-        <v>153</v>
+        <v>575</v>
       </c>
       <c r="C77" s="1" t="s">
-        <v>143</v>
-      </c>
-      <c r="D77" s="7" t="s">
-        <v>156</v>
+        <v>43</v>
+      </c>
+      <c r="D77" s="1" t="s">
+        <v>576</v>
       </c>
       <c r="E77" s="1" t="s">
-        <v>154</v>
+        <v>577</v>
       </c>
       <c r="F77" s="1" t="s">
-        <v>155</v>
+        <v>578</v>
       </c>
       <c r="G77" s="1" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="78" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A78" s="1" t="s">
-        <v>518</v>
+        <v>82</v>
       </c>
       <c r="B78" s="1" t="s">
-        <v>517</v>
+        <v>83</v>
       </c>
       <c r="C78" s="1" t="s">
         <v>143</v>
       </c>
-      <c r="D78" s="24" t="s">
+      <c r="D78" s="1" t="s">
+        <v>506</v>
+      </c>
+      <c r="E78" s="1" t="s">
+        <v>507</v>
+      </c>
+      <c r="F78" s="1" t="s">
+        <v>390</v>
+      </c>
+      <c r="G78" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="79" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A79" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="B79" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="C79" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="D79" s="7" t="s">
+        <v>156</v>
+      </c>
+      <c r="E79" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="F79" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="G79" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="80" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A80" s="1" t="s">
+        <v>518</v>
+      </c>
+      <c r="B80" s="1" t="s">
+        <v>517</v>
+      </c>
+      <c r="C80" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="D80" s="24" t="s">
         <v>406</v>
       </c>
-      <c r="E78" s="24"/>
-      <c r="F78" s="24"/>
-      <c r="G78" s="24"/>
-    </row>
-    <row r="79" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A79" s="1" t="s">
+      <c r="E80" s="24"/>
+      <c r="F80" s="24"/>
+      <c r="G80" s="24"/>
+    </row>
+    <row r="81" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A81" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="B79" s="1" t="s">
+      <c r="B81" s="1" t="s">
         <v>85</v>
-      </c>
-      <c r="C79" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="D79" s="24" t="s">
-        <v>406</v>
-      </c>
-      <c r="E79" s="24"/>
-      <c r="F79" s="24"/>
-      <c r="G79" s="24"/>
-    </row>
-    <row r="80" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A80" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="B80" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="C80" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="D80" s="1" t="s">
-        <v>555</v>
-      </c>
-      <c r="E80" s="1" t="s">
-        <v>553</v>
-      </c>
-      <c r="F80" s="1" t="s">
-        <v>554</v>
-      </c>
-      <c r="G80" s="1" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="81" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A81" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="B81" s="1" t="s">
-        <v>378</v>
       </c>
       <c r="C81" s="1" t="s">
         <v>43</v>
@@ -5404,35 +5475,35 @@
       <c r="F81" s="24"/>
       <c r="G81" s="24"/>
     </row>
-    <row r="82" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A82" s="1" t="s">
-        <v>93</v>
+        <v>86</v>
       </c>
       <c r="B82" s="1" t="s">
-        <v>94</v>
+        <v>87</v>
       </c>
       <c r="C82" s="1" t="s">
-        <v>143</v>
+        <v>43</v>
       </c>
       <c r="D82" s="1" t="s">
-        <v>528</v>
+        <v>555</v>
       </c>
       <c r="E82" s="1" t="s">
-        <v>529</v>
+        <v>553</v>
       </c>
       <c r="F82" s="1" t="s">
-        <v>530</v>
+        <v>554</v>
       </c>
       <c r="G82" s="1" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="83" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A83" s="1" t="s">
-        <v>743</v>
+        <v>88</v>
       </c>
       <c r="B83" s="1" t="s">
-        <v>744</v>
+        <v>378</v>
       </c>
       <c r="C83" s="1" t="s">
         <v>43</v>
@@ -5444,765 +5515,771 @@
       <c r="F83" s="24"/>
       <c r="G83" s="24"/>
     </row>
-    <row r="84" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A84" s="1" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="B84" s="1" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="C84" s="1" t="s">
         <v>143</v>
       </c>
-      <c r="D84" s="24" t="s">
+      <c r="D84" s="1" t="s">
+        <v>528</v>
+      </c>
+      <c r="E84" s="1" t="s">
+        <v>529</v>
+      </c>
+      <c r="F84" s="1" t="s">
+        <v>530</v>
+      </c>
+      <c r="G84" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="85" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A85" s="1" t="s">
+        <v>743</v>
+      </c>
+      <c r="B85" s="1" t="s">
+        <v>744</v>
+      </c>
+      <c r="C85" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D85" s="24" t="s">
+        <v>406</v>
+      </c>
+      <c r="E85" s="24"/>
+      <c r="F85" s="24"/>
+      <c r="G85" s="24"/>
+    </row>
+    <row r="86" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A86" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="B86" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="C86" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="D86" s="24" t="s">
         <v>411</v>
       </c>
-      <c r="E84" s="24"/>
-      <c r="F84" s="24"/>
-      <c r="G84" s="24"/>
-    </row>
-    <row r="86" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A86" s="1" t="s">
+      <c r="E86" s="24"/>
+      <c r="F86" s="24"/>
+      <c r="G86" s="24"/>
+    </row>
+    <row r="88" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A88" s="1" t="s">
         <v>522</v>
       </c>
-      <c r="B86" s="1" t="s">
+      <c r="B88" s="1" t="s">
         <v>523</v>
       </c>
-      <c r="C86" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="D86" s="26" t="s">
+      <c r="C88" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D88" s="30" t="s">
         <v>178</v>
       </c>
-      <c r="E86" s="26"/>
-      <c r="F86" s="26"/>
-      <c r="G86" s="26"/>
-    </row>
-    <row r="87" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A87" s="1" t="s">
+      <c r="E88" s="30"/>
+      <c r="F88" s="30"/>
+      <c r="G88" s="30"/>
+    </row>
+    <row r="89" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A89" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="B87" s="1" t="s">
+      <c r="B89" s="1" t="s">
         <v>519</v>
       </c>
-      <c r="C87" s="1" t="s">
+      <c r="C89" s="1" t="s">
         <v>534</v>
       </c>
-      <c r="D87" s="7" t="s">
+      <c r="D89" s="7" t="s">
         <v>121</v>
       </c>
-      <c r="E87" s="7" t="s">
+      <c r="E89" s="7" t="s">
         <v>122</v>
       </c>
-      <c r="F87" s="1" t="s">
+      <c r="F89" s="1" t="s">
         <v>120</v>
       </c>
-      <c r="G87" s="1" t="s">
+      <c r="G89" s="1" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="88" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A88" s="1" t="s">
+    <row r="90" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A90" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="B88" s="1" t="s">
+      <c r="B90" s="1" t="s">
         <v>520</v>
-      </c>
-      <c r="C88" s="1" t="s">
-        <v>143</v>
-      </c>
-      <c r="D88" s="1" t="s">
-        <v>547</v>
-      </c>
-      <c r="E88" s="1" t="s">
-        <v>548</v>
-      </c>
-      <c r="F88" s="1" t="s">
-        <v>549</v>
-      </c>
-      <c r="G88" s="1" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="89" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A89" s="1" t="s">
-        <v>98</v>
-      </c>
-      <c r="B89" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="C89" s="1" t="s">
-        <v>535</v>
-      </c>
-      <c r="D89" s="15" t="s">
-        <v>537</v>
-      </c>
-      <c r="E89" s="15" t="s">
-        <v>542</v>
-      </c>
-      <c r="F89" s="15" t="s">
-        <v>543</v>
-      </c>
-      <c r="G89" s="15" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="90" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A90" s="1" t="s">
-        <v>525</v>
-      </c>
-      <c r="B90" s="1" t="s">
-        <v>524</v>
       </c>
       <c r="C90" s="1" t="s">
         <v>143</v>
       </c>
       <c r="D90" s="1" t="s">
-        <v>544</v>
+        <v>547</v>
       </c>
       <c r="E90" s="1" t="s">
-        <v>545</v>
+        <v>548</v>
       </c>
       <c r="F90" s="1" t="s">
-        <v>546</v>
+        <v>549</v>
       </c>
       <c r="G90" s="1" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="91" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A91" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="B91" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="C91" s="1" t="s">
+        <v>535</v>
+      </c>
+      <c r="D91" s="15" t="s">
+        <v>537</v>
+      </c>
+      <c r="E91" s="15" t="s">
+        <v>542</v>
+      </c>
+      <c r="F91" s="15" t="s">
+        <v>543</v>
+      </c>
+      <c r="G91" s="15" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="92" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A92" s="1" t="s">
+        <v>525</v>
+      </c>
+      <c r="B92" s="1" t="s">
+        <v>524</v>
+      </c>
+      <c r="C92" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="D92" s="1" t="s">
+        <v>544</v>
+      </c>
+      <c r="E92" s="1" t="s">
+        <v>545</v>
+      </c>
+      <c r="F92" s="1" t="s">
+        <v>546</v>
+      </c>
+      <c r="G92" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="93" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A93" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="B91" s="1" t="s">
+      <c r="B93" s="1" t="s">
         <v>521</v>
       </c>
-      <c r="C91" s="1" t="s">
+      <c r="C93" s="1" t="s">
         <v>143</v>
       </c>
-      <c r="D91" s="1" t="s">
+      <c r="D93" s="1" t="s">
         <v>531</v>
       </c>
-      <c r="E91" s="1" t="s">
+      <c r="E93" s="1" t="s">
         <v>532</v>
       </c>
-      <c r="F91" s="1" t="s">
+      <c r="F93" s="1" t="s">
         <v>533</v>
       </c>
-      <c r="G91" s="1" t="s">
+      <c r="G93" s="1" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="92" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A92" s="1" t="s">
+    <row r="94" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A94" s="1" t="s">
         <v>101</v>
       </c>
-      <c r="B92" s="1" t="s">
+      <c r="B94" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="C92" s="1" t="s">
+      <c r="C94" s="1" t="s">
         <v>535</v>
       </c>
-      <c r="D92" s="15" t="s">
+      <c r="D94" s="15" t="s">
         <v>541</v>
       </c>
-      <c r="E92" s="15" t="s">
+      <c r="E94" s="15" t="s">
         <v>538</v>
       </c>
-      <c r="F92" s="15" t="s">
+      <c r="F94" s="15" t="s">
         <v>539</v>
       </c>
-      <c r="G92" s="15" t="s">
+      <c r="G94" s="15" t="s">
         <v>540</v>
       </c>
     </row>
-    <row r="94" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A94" s="1" t="s">
+    <row r="96" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A96" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="B94" s="16" t="s">
+      <c r="B96" s="16" t="s">
         <v>105</v>
       </c>
-      <c r="C94" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="D94" s="6" t="s">
+      <c r="C96" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D96" s="6" t="s">
         <v>384</v>
       </c>
-      <c r="E94" s="7" t="s">
+      <c r="E96" s="7" t="s">
         <v>386</v>
       </c>
-      <c r="F94" s="1" t="s">
+      <c r="F96" s="1" t="s">
         <v>385</v>
       </c>
-      <c r="G94" s="1" t="s">
+      <c r="G96" s="1" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="95" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A95" s="1" t="s">
+    <row r="97" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A97" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="B95" s="16" t="s">
+      <c r="B97" s="16" t="s">
         <v>107</v>
       </c>
-      <c r="C95" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="D95" s="7" t="s">
+      <c r="C97" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D97" s="7" t="s">
         <v>136</v>
       </c>
-      <c r="E95" s="7" t="s">
+      <c r="E97" s="7" t="s">
         <v>137</v>
       </c>
-      <c r="F95" s="7" t="s">
+      <c r="F97" s="7" t="s">
         <v>138</v>
       </c>
-      <c r="G95" s="1" t="s">
+      <c r="G97" s="1" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="96" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A96" s="1" t="s">
+    <row r="98" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A98" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="B96" s="16" t="s">
+      <c r="B98" s="16" t="s">
         <v>109</v>
       </c>
-      <c r="C96" s="1" t="s">
+      <c r="C98" s="1" t="s">
         <v>143</v>
       </c>
-      <c r="D96" s="24" t="s">
+      <c r="D98" s="24" t="s">
         <v>406</v>
       </c>
-      <c r="E96" s="24"/>
-      <c r="F96" s="24"/>
-      <c r="G96" s="24"/>
-    </row>
-    <row r="97" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A97" s="1" t="s">
+      <c r="E98" s="24"/>
+      <c r="F98" s="24"/>
+      <c r="G98" s="24"/>
+    </row>
+    <row r="99" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A99" s="1" t="s">
         <v>110</v>
       </c>
-      <c r="B97" s="1" t="s">
+      <c r="B99" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="C97" s="1" t="s">
+      <c r="C99" s="1" t="s">
         <v>143</v>
       </c>
-      <c r="D97" s="24" t="s">
+      <c r="D99" s="24" t="s">
         <v>406</v>
       </c>
-      <c r="E97" s="24"/>
-      <c r="F97" s="24"/>
-      <c r="G97" s="24"/>
-    </row>
-    <row r="98" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A98" s="1" t="s">
+      <c r="E99" s="24"/>
+      <c r="F99" s="24"/>
+      <c r="G99" s="24"/>
+    </row>
+    <row r="100" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A100" s="1" t="s">
         <v>112</v>
       </c>
-      <c r="B98" s="16" t="s">
+      <c r="B100" s="16" t="s">
         <v>508</v>
       </c>
-      <c r="C98" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="D98" s="1" t="s">
+      <c r="C100" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D100" s="1" t="s">
         <v>510</v>
       </c>
-      <c r="E98" s="1" t="s">
+      <c r="E100" s="1" t="s">
         <v>511</v>
       </c>
-      <c r="F98" s="1" t="s">
+      <c r="F100" s="1" t="s">
         <v>512</v>
-      </c>
-      <c r="G98" s="1" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="99" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A99" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="B99" s="16" t="s">
-        <v>509</v>
-      </c>
-      <c r="C99" s="1" t="s">
-        <v>536</v>
-      </c>
-      <c r="D99" s="15" t="s">
-        <v>514</v>
-      </c>
-      <c r="E99" s="15" t="s">
-        <v>515</v>
-      </c>
-      <c r="F99" s="15" t="s">
-        <v>516</v>
-      </c>
-      <c r="G99" s="15" t="s">
-        <v>513</v>
-      </c>
-    </row>
-    <row r="100" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A100" s="1" t="s">
-        <v>527</v>
-      </c>
-      <c r="B100" s="16" t="s">
-        <v>526</v>
-      </c>
-      <c r="C100" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="D100" s="1" t="s">
-        <v>550</v>
-      </c>
-      <c r="E100" s="1" t="s">
-        <v>551</v>
-      </c>
-      <c r="F100" s="1" t="s">
-        <v>552</v>
       </c>
       <c r="G100" s="1" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="101" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A101" s="1" t="s">
-        <v>113</v>
-      </c>
-      <c r="B101" s="1" t="s">
-        <v>114</v>
+        <v>112</v>
+      </c>
+      <c r="B101" s="16" t="s">
+        <v>509</v>
       </c>
       <c r="C101" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="D101" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="E101" s="1" t="s">
-        <v>118</v>
-      </c>
-      <c r="F101" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="G101" s="1" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="102" spans="1:8" x14ac:dyDescent="0.35">
+        <v>536</v>
+      </c>
+      <c r="D101" s="15" t="s">
+        <v>514</v>
+      </c>
+      <c r="E101" s="15" t="s">
+        <v>515</v>
+      </c>
+      <c r="F101" s="15" t="s">
+        <v>516</v>
+      </c>
+      <c r="G101" s="15" t="s">
+        <v>513</v>
+      </c>
+    </row>
+    <row r="102" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A102" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="B102" s="1" t="s">
-        <v>116</v>
+        <v>527</v>
+      </c>
+      <c r="B102" s="16" t="s">
+        <v>526</v>
       </c>
       <c r="C102" s="1" t="s">
-        <v>143</v>
+        <v>43</v>
       </c>
       <c r="D102" s="1" t="s">
-        <v>381</v>
+        <v>550</v>
       </c>
       <c r="E102" s="1" t="s">
-        <v>382</v>
+        <v>551</v>
       </c>
       <c r="F102" s="1" t="s">
-        <v>383</v>
+        <v>552</v>
       </c>
       <c r="G102" s="1" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="104" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A103" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="B103" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="C103" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D103" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="E103" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="F103" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="G103" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="104" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A104" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="B104" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="C104" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="D104" s="1" t="s">
+        <v>381</v>
+      </c>
+      <c r="E104" s="1" t="s">
+        <v>382</v>
+      </c>
+      <c r="F104" s="1" t="s">
+        <v>383</v>
+      </c>
+      <c r="G104" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="106" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A106" s="1" t="s">
         <v>184</v>
       </c>
-      <c r="B104" s="1" t="s">
+      <c r="B106" s="1" t="s">
         <v>185</v>
-      </c>
-      <c r="H104" s="1" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="105" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A105" s="1" t="s">
-        <v>186</v>
-      </c>
-      <c r="B105" s="1" t="s">
-        <v>187</v>
-      </c>
-      <c r="H105" s="1" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="106" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A106" s="1" t="s">
-        <v>188</v>
-      </c>
-      <c r="B106" s="1" t="s">
-        <v>189</v>
       </c>
       <c r="H106" s="1" t="s">
         <v>183</v>
       </c>
     </row>
-    <row r="107" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="107" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A107" s="1" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="B107" s="1" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="H107" s="1" t="s">
         <v>183</v>
       </c>
     </row>
-    <row r="108" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="108" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A108" s="1" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="B108" s="1" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="H108" s="1" t="s">
         <v>183</v>
       </c>
     </row>
-    <row r="109" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="109" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A109" s="1" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="B109" s="1" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="H109" s="1" t="s">
         <v>183</v>
       </c>
     </row>
-    <row r="110" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="110" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A110" s="1" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="B110" s="1" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="H110" s="1" t="s">
         <v>183</v>
       </c>
     </row>
-    <row r="111" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="111" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A111" s="1" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="B111" s="1" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="H111" s="1" t="s">
         <v>183</v>
       </c>
     </row>
-    <row r="112" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="112" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A112" s="1" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="B112" s="1" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="H112" s="1" t="s">
         <v>183</v>
       </c>
     </row>
-    <row r="113" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="113" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A113" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="B113" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="H113" s="1" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="114" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A114" s="1" t="s">
+        <v>200</v>
+      </c>
+      <c r="B114" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="H114" s="1" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="115" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A115" s="1" t="s">
         <v>730</v>
       </c>
-      <c r="B113" s="1" t="s">
+      <c r="B115" s="1" t="s">
         <v>731</v>
       </c>
-      <c r="C113" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="D113" s="1" t="s">
+      <c r="C115" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D115" s="1" t="s">
         <v>734</v>
       </c>
-      <c r="E113" s="1" t="s">
+      <c r="E115" s="1" t="s">
         <v>733</v>
       </c>
-      <c r="F113" s="1" t="s">
+      <c r="F115" s="1" t="s">
         <v>732</v>
       </c>
-      <c r="G113" s="1" t="s">
+      <c r="G115" s="1" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="114" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A114" s="1" t="s">
+    <row r="116" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A116" s="1" t="s">
         <v>745</v>
       </c>
-      <c r="B114" s="1" t="s">
+      <c r="B116" s="1" t="s">
         <v>746</v>
       </c>
-      <c r="C114" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="D114" s="1" t="s">
+      <c r="C116" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D116" s="1" t="s">
         <v>747</v>
       </c>
-      <c r="E114" s="1" t="s">
+      <c r="E116" s="1" t="s">
         <v>748</v>
       </c>
-      <c r="F114" s="1" t="s">
+      <c r="F116" s="1" t="s">
         <v>749</v>
       </c>
-      <c r="G114" s="1" t="s">
+      <c r="G116" s="1" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="116" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A116" s="1" t="s">
+    <row r="118" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A118" s="1" t="s">
         <v>274</v>
       </c>
-      <c r="B116" s="1" t="s">
+      <c r="B118" s="1" t="s">
         <v>275</v>
-      </c>
-      <c r="H116" s="1" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="117" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A117" s="1" t="s">
-        <v>276</v>
-      </c>
-      <c r="B117" s="1" t="s">
-        <v>277</v>
-      </c>
-      <c r="H117" s="1" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="118" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A118" s="1" t="s">
-        <v>278</v>
-      </c>
-      <c r="B118" s="1" t="s">
-        <v>279</v>
       </c>
       <c r="H118" s="1" t="s">
         <v>213</v>
       </c>
     </row>
-    <row r="119" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="119" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A119" s="1" t="s">
-        <v>280</v>
+        <v>276</v>
       </c>
       <c r="B119" s="1" t="s">
-        <v>281</v>
+        <v>277</v>
       </c>
       <c r="H119" s="1" t="s">
         <v>213</v>
       </c>
     </row>
-    <row r="120" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="120" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A120" s="1" t="s">
-        <v>282</v>
+        <v>278</v>
       </c>
       <c r="B120" s="1" t="s">
-        <v>283</v>
+        <v>279</v>
       </c>
       <c r="H120" s="1" t="s">
         <v>213</v>
       </c>
     </row>
-    <row r="121" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="121" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A121" s="1" t="s">
-        <v>284</v>
+        <v>280</v>
       </c>
       <c r="B121" s="1" t="s">
-        <v>285</v>
+        <v>281</v>
       </c>
       <c r="H121" s="1" t="s">
         <v>213</v>
       </c>
     </row>
-    <row r="122" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="122" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A122" s="1" t="s">
-        <v>286</v>
+        <v>282</v>
       </c>
       <c r="B122" s="1" t="s">
-        <v>287</v>
+        <v>283</v>
       </c>
       <c r="H122" s="1" t="s">
         <v>213</v>
       </c>
     </row>
-    <row r="123" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="123" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A123" s="1" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="B123" s="1" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
       <c r="H123" s="1" t="s">
         <v>213</v>
       </c>
     </row>
-    <row r="124" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="124" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A124" s="1" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="B124" s="1" t="s">
-        <v>291</v>
+        <v>287</v>
       </c>
       <c r="H124" s="1" t="s">
         <v>213</v>
       </c>
     </row>
-    <row r="126" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="125" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A125" s="1" t="s">
+        <v>288</v>
+      </c>
+      <c r="B125" s="1" t="s">
+        <v>289</v>
+      </c>
+      <c r="H125" s="1" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="126" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A126" s="1" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="B126" s="1" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="H126" s="1" t="s">
         <v>213</v>
       </c>
     </row>
-    <row r="127" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A127" s="1" t="s">
+    <row r="128" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A128" s="1" t="s">
+        <v>292</v>
+      </c>
+      <c r="B128" s="1" t="s">
+        <v>293</v>
+      </c>
+      <c r="H128" s="1" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="129" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A129" s="1" t="s">
         <v>294</v>
       </c>
-      <c r="B127" s="1" t="s">
+      <c r="B129" s="1" t="s">
         <v>295</v>
       </c>
-      <c r="C127" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="D127" s="24" t="s">
+      <c r="C129" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D129" s="24" t="s">
         <v>715</v>
       </c>
-      <c r="E127" s="24"/>
-      <c r="F127" s="24"/>
-      <c r="G127" s="24"/>
-    </row>
-    <row r="128" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A128" s="16" t="s">
+      <c r="E129" s="24"/>
+      <c r="F129" s="24"/>
+      <c r="G129" s="24"/>
+    </row>
+    <row r="130" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A130" s="16" t="s">
         <v>296</v>
       </c>
-      <c r="B128" s="16" t="s">
+      <c r="B130" s="16" t="s">
         <v>297</v>
       </c>
-      <c r="C128" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="D128" s="26" t="s">
+      <c r="C130" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D130" s="30" t="s">
         <v>345</v>
       </c>
-      <c r="E128" s="26"/>
-      <c r="F128" s="26"/>
-      <c r="G128" s="26"/>
-    </row>
-    <row r="129" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A129" s="16" t="s">
+      <c r="E130" s="30"/>
+      <c r="F130" s="30"/>
+      <c r="G130" s="30"/>
+    </row>
+    <row r="131" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A131" s="16" t="s">
         <v>702</v>
       </c>
-      <c r="B129" s="16" t="s">
+      <c r="B131" s="16" t="s">
         <v>703</v>
       </c>
-      <c r="C129" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="D129" s="7" t="s">
+      <c r="C131" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D131" s="7" t="s">
         <v>708</v>
       </c>
-      <c r="E129" s="7" t="s">
+      <c r="E131" s="7" t="s">
         <v>709</v>
       </c>
-      <c r="F129" s="1" t="s">
+      <c r="F131" s="1" t="s">
         <v>706</v>
       </c>
-      <c r="G129" s="1" t="s">
+      <c r="G131" s="1" t="s">
         <v>707</v>
       </c>
     </row>
-    <row r="130" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A130" s="16" t="s">
+    <row r="132" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A132" s="16" t="s">
         <v>704</v>
       </c>
-      <c r="B130" s="16" t="s">
+      <c r="B132" s="16" t="s">
         <v>705</v>
       </c>
-      <c r="C130" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="D130" s="1" t="s">
+      <c r="C132" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D132" s="1" t="s">
         <v>710</v>
       </c>
-      <c r="E130" s="1" t="s">
+      <c r="E132" s="1" t="s">
         <v>711</v>
       </c>
-      <c r="F130" s="1" t="s">
+      <c r="F132" s="1" t="s">
         <v>712</v>
       </c>
-      <c r="G130" s="1" t="s">
+      <c r="G132" s="1" t="s">
         <v>707</v>
       </c>
     </row>
-    <row r="131" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A131" s="16" t="s">
+    <row r="133" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A133" s="16" t="s">
         <v>405</v>
       </c>
-      <c r="B131" s="16" t="s">
+      <c r="B133" s="16" t="s">
         <v>404</v>
       </c>
-      <c r="C131" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="D131" s="24" t="s">
+      <c r="C133" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D133" s="24" t="s">
         <v>413</v>
-      </c>
-      <c r="E131" s="24"/>
-      <c r="F131" s="24"/>
-      <c r="G131" s="24"/>
-    </row>
-    <row r="132" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A132" s="1" t="s">
-        <v>298</v>
-      </c>
-      <c r="B132" s="1" t="s">
-        <v>299</v>
-      </c>
-      <c r="C132" s="1" t="s">
-        <v>143</v>
-      </c>
-      <c r="D132" s="24" t="s">
-        <v>408</v>
-      </c>
-      <c r="E132" s="24"/>
-      <c r="F132" s="24"/>
-      <c r="G132" s="24"/>
-    </row>
-    <row r="133" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A133" s="1" t="s">
-        <v>300</v>
-      </c>
-      <c r="B133" s="1" t="s">
-        <v>301</v>
-      </c>
-      <c r="C133" s="1" t="s">
-        <v>143</v>
-      </c>
-      <c r="D133" s="24" t="s">
-        <v>408</v>
       </c>
       <c r="E133" s="24"/>
       <c r="F133" s="24"/>
       <c r="G133" s="24"/>
     </row>
-    <row r="134" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="134" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A134" s="1" t="s">
-        <v>302</v>
+        <v>298</v>
       </c>
       <c r="B134" s="1" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="C134" s="1" t="s">
         <v>143</v>
@@ -6214,238 +6291,232 @@
       <c r="F134" s="24"/>
       <c r="G134" s="24"/>
     </row>
-    <row r="136" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="135" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A135" s="1" t="s">
+        <v>300</v>
+      </c>
+      <c r="B135" s="1" t="s">
+        <v>301</v>
+      </c>
+      <c r="C135" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="D135" s="24" t="s">
+        <v>408</v>
+      </c>
+      <c r="E135" s="24"/>
+      <c r="F135" s="24"/>
+      <c r="G135" s="24"/>
+    </row>
+    <row r="136" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A136" s="1" t="s">
-        <v>605</v>
+        <v>302</v>
       </c>
       <c r="B136" s="1" t="s">
-        <v>606</v>
+        <v>303</v>
       </c>
       <c r="C136" s="1" t="s">
-        <v>43</v>
+        <v>143</v>
       </c>
       <c r="D136" s="24" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="E136" s="24"/>
       <c r="F136" s="24"/>
       <c r="G136" s="24"/>
     </row>
-    <row r="137" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A137" s="1" t="s">
+    <row r="138" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A138" s="1" t="s">
+        <v>605</v>
+      </c>
+      <c r="B138" s="1" t="s">
+        <v>606</v>
+      </c>
+      <c r="C138" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D138" s="24" t="s">
+        <v>406</v>
+      </c>
+      <c r="E138" s="24"/>
+      <c r="F138" s="24"/>
+      <c r="G138" s="24"/>
+    </row>
+    <row r="139" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A139" s="1" t="s">
         <v>607</v>
       </c>
-      <c r="B137" s="1" t="s">
+      <c r="B139" s="1" t="s">
         <v>608</v>
       </c>
-      <c r="C137" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="D137" s="24" t="s">
+      <c r="C139" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D139" s="24" t="s">
         <v>406</v>
       </c>
-      <c r="E137" s="24"/>
-      <c r="F137" s="24"/>
-      <c r="G137" s="24"/>
-    </row>
-    <row r="138" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A138" s="1" t="s">
+      <c r="E139" s="24"/>
+      <c r="F139" s="24"/>
+      <c r="G139" s="24"/>
+    </row>
+    <row r="140" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A140" s="1" t="s">
         <v>124</v>
       </c>
-      <c r="B138" s="1" t="s">
+      <c r="B140" s="1" t="s">
         <v>125</v>
       </c>
-      <c r="C138" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="D138" s="26" t="s">
+      <c r="C140" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D140" s="30" t="s">
         <v>307</v>
       </c>
-      <c r="E138" s="26"/>
-      <c r="F138" s="26"/>
-      <c r="G138" s="26"/>
-    </row>
-    <row r="139" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A139" s="1" t="s">
+      <c r="E140" s="30"/>
+      <c r="F140" s="30"/>
+      <c r="G140" s="30"/>
+    </row>
+    <row r="141" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A141" s="1" t="s">
         <v>126</v>
       </c>
-      <c r="B139" s="1" t="s">
+      <c r="B141" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="C139" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="D139" s="1" t="s">
+      <c r="C141" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D141" s="1" t="s">
         <v>130</v>
       </c>
-      <c r="E139" s="1" t="s">
+      <c r="E141" s="1" t="s">
         <v>131</v>
       </c>
-      <c r="F139" s="1" t="s">
+      <c r="F141" s="1" t="s">
         <v>132</v>
-      </c>
-      <c r="G139" s="1" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="140" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A140" s="1" t="s">
-        <v>128</v>
-      </c>
-      <c r="B140" s="1" t="s">
-        <v>129</v>
-      </c>
-      <c r="C140" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="D140" s="1" t="s">
-        <v>133</v>
-      </c>
-      <c r="E140" s="1" t="s">
-        <v>134</v>
-      </c>
-      <c r="F140" s="1" t="s">
-        <v>135</v>
-      </c>
-      <c r="G140" s="1" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="141" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A141" s="1" t="s">
-        <v>759</v>
-      </c>
-      <c r="B141" s="1" t="s">
-        <v>760</v>
-      </c>
-      <c r="C141" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="D141" s="1" t="s">
-        <v>761</v>
-      </c>
-      <c r="E141" s="1" t="s">
-        <v>762</v>
-      </c>
-      <c r="F141" s="1" t="s">
-        <v>763</v>
       </c>
       <c r="G141" s="1" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="142" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="142" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A142" s="1" t="s">
-        <v>758</v>
+        <v>128</v>
       </c>
       <c r="B142" s="1" t="s">
-        <v>764</v>
+        <v>129</v>
       </c>
       <c r="C142" s="1" t="s">
         <v>43</v>
       </c>
       <c r="D142" s="1" t="s">
-        <v>765</v>
+        <v>133</v>
       </c>
       <c r="E142" s="1" t="s">
-        <v>766</v>
+        <v>134</v>
       </c>
       <c r="F142" s="1" t="s">
-        <v>767</v>
+        <v>135</v>
       </c>
       <c r="G142" s="1" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="143" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="143" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A143" s="1" t="s">
+        <v>759</v>
+      </c>
+      <c r="B143" s="1" t="s">
+        <v>760</v>
+      </c>
+      <c r="C143" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D143" s="1" t="s">
+        <v>761</v>
+      </c>
+      <c r="E143" s="1" t="s">
+        <v>762</v>
+      </c>
+      <c r="F143" s="1" t="s">
+        <v>763</v>
+      </c>
+      <c r="G143" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="144" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A144" s="1" t="s">
+        <v>758</v>
+      </c>
+      <c r="B144" s="1" t="s">
+        <v>764</v>
+      </c>
+      <c r="C144" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D144" s="1" t="s">
+        <v>765</v>
+      </c>
+      <c r="E144" s="1" t="s">
+        <v>766</v>
+      </c>
+      <c r="F144" s="1" t="s">
+        <v>767</v>
+      </c>
+      <c r="G144" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="145" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A145" s="1" t="s">
         <v>637</v>
       </c>
-      <c r="B143" s="1" t="s">
+      <c r="B145" s="1" t="s">
         <v>638</v>
       </c>
-      <c r="C143" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="D143" s="1" t="s">
+      <c r="C145" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D145" s="1" t="s">
         <v>639</v>
       </c>
-      <c r="E143" s="1" t="s">
+      <c r="E145" s="1" t="s">
         <v>640</v>
       </c>
-      <c r="F143" s="1" t="s">
+      <c r="F145" s="1" t="s">
         <v>641</v>
       </c>
-      <c r="G143" s="1" t="s">
+      <c r="G145" s="1" t="s">
         <v>642</v>
       </c>
     </row>
-    <row r="145" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A145" s="1" t="s">
+    <row r="147" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A147" s="1" t="s">
         <v>312</v>
       </c>
-      <c r="B145" s="1" t="s">
+      <c r="B147" s="1" t="s">
         <v>314</v>
       </c>
-      <c r="C145" s="1" t="s">
+      <c r="C147" s="1" t="s">
         <v>143</v>
       </c>
-      <c r="D145" s="24" t="s">
+      <c r="D147" s="24" t="s">
         <v>788</v>
       </c>
-      <c r="E145" s="24"/>
-      <c r="F145" s="24"/>
-      <c r="G145" s="24"/>
-    </row>
-    <row r="146" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A146" s="1" t="s">
+      <c r="E147" s="24"/>
+      <c r="F147" s="24"/>
+      <c r="G147" s="24"/>
+    </row>
+    <row r="148" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A148" s="1" t="s">
         <v>315</v>
       </c>
-      <c r="B146" s="1" t="s">
+      <c r="B148" s="1" t="s">
         <v>316</v>
       </c>
-      <c r="C146" s="1" t="s">
+      <c r="C148" s="1" t="s">
         <v>671</v>
-      </c>
-      <c r="D146" s="24" t="s">
-        <v>406</v>
-      </c>
-      <c r="E146" s="24"/>
-      <c r="F146" s="24"/>
-      <c r="G146" s="24"/>
-    </row>
-    <row r="147" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A147" s="1" t="s">
-        <v>675</v>
-      </c>
-      <c r="B147" s="1" t="s">
-        <v>676</v>
-      </c>
-      <c r="C147" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="D147" s="23" t="s">
-        <v>678</v>
-      </c>
-      <c r="E147" s="23" t="s">
-        <v>679</v>
-      </c>
-      <c r="F147" s="23" t="s">
-        <v>680</v>
-      </c>
-      <c r="G147" s="1" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="148" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A148" s="1" t="s">
-        <v>786</v>
-      </c>
-      <c r="B148" s="1" t="s">
-        <v>787</v>
-      </c>
-      <c r="C148" s="1" t="s">
-        <v>143</v>
       </c>
       <c r="D148" s="24" t="s">
         <v>406</v>
@@ -6454,378 +6525,511 @@
       <c r="F148" s="24"/>
       <c r="G148" s="24"/>
     </row>
-    <row r="149" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="149" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A149" s="1" t="s">
-        <v>784</v>
+        <v>675</v>
       </c>
       <c r="B149" s="1" t="s">
-        <v>785</v>
+        <v>676</v>
       </c>
       <c r="C149" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D149" s="23" t="s">
+        <v>678</v>
+      </c>
+      <c r="E149" s="23" t="s">
+        <v>679</v>
+      </c>
+      <c r="F149" s="23" t="s">
+        <v>680</v>
+      </c>
+      <c r="G149" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="150" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A150" s="1" t="s">
+        <v>786</v>
+      </c>
+      <c r="B150" s="1" t="s">
+        <v>787</v>
+      </c>
+      <c r="C150" s="1" t="s">
         <v>143</v>
       </c>
-      <c r="D149" s="24" t="s">
+      <c r="D150" s="24" t="s">
         <v>406</v>
-      </c>
-      <c r="E149" s="24"/>
-      <c r="F149" s="24"/>
-      <c r="G149" s="24"/>
-    </row>
-    <row r="150" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A150" s="1" t="s">
-        <v>318</v>
-      </c>
-      <c r="B150" s="1" t="s">
-        <v>320</v>
-      </c>
-      <c r="C150" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="D150" s="24" t="s">
-        <v>414</v>
       </c>
       <c r="E150" s="24"/>
       <c r="F150" s="24"/>
       <c r="G150" s="24"/>
     </row>
-    <row r="151" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="151" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A151" s="1" t="s">
+        <v>784</v>
+      </c>
+      <c r="B151" s="1" t="s">
+        <v>785</v>
+      </c>
+      <c r="C151" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="D151" s="24" t="s">
+        <v>406</v>
+      </c>
+      <c r="E151" s="24"/>
+      <c r="F151" s="24"/>
+      <c r="G151" s="24"/>
+    </row>
+    <row r="152" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A152" s="1" t="s">
+        <v>318</v>
+      </c>
+      <c r="B152" s="1" t="s">
+        <v>320</v>
+      </c>
+      <c r="C152" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D152" s="24" t="s">
+        <v>414</v>
+      </c>
+      <c r="E152" s="24"/>
+      <c r="F152" s="24"/>
+      <c r="G152" s="24"/>
+    </row>
+    <row r="153" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A153" s="1" t="s">
         <v>643</v>
       </c>
-      <c r="B151" s="1" t="s">
+      <c r="B153" s="1" t="s">
         <v>644</v>
       </c>
-      <c r="C151" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="D151" s="7" t="s">
+      <c r="C153" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D153" s="7" t="s">
         <v>653</v>
       </c>
-      <c r="E151" s="7" t="s">
+      <c r="E153" s="7" t="s">
         <v>645</v>
       </c>
-      <c r="F151" s="1" t="s">
+      <c r="F153" s="1" t="s">
         <v>646</v>
       </c>
-      <c r="G151" s="1" t="s">
+      <c r="G153" s="1" t="s">
         <v>647</v>
       </c>
     </row>
-    <row r="153" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A153" s="1" t="s">
+    <row r="155" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A155" s="1" t="s">
         <v>322</v>
       </c>
-      <c r="B153" s="1" t="s">
+      <c r="B155" s="1" t="s">
         <v>324</v>
       </c>
-      <c r="H153" s="1" t="s">
+      <c r="H155" s="1" t="s">
         <v>213</v>
       </c>
     </row>
-    <row r="154" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A154" s="1" t="s">
+    <row r="156" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A156" s="1" t="s">
         <v>669</v>
       </c>
-      <c r="B154" s="1" t="s">
+      <c r="B156" s="1" t="s">
         <v>670</v>
       </c>
-      <c r="C154" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="D154" s="1" t="s">
+      <c r="C156" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D156" s="1" t="s">
         <v>682</v>
       </c>
-      <c r="E154" s="1" t="s">
+      <c r="E156" s="1" t="s">
         <v>683</v>
       </c>
-      <c r="F154" s="1" t="s">
+      <c r="F156" s="1" t="s">
         <v>684</v>
       </c>
-      <c r="G154" s="1" t="s">
+      <c r="G156" s="1" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="155" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A155" s="1" t="s">
+    <row r="157" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A157" s="1" t="s">
         <v>325</v>
       </c>
-      <c r="B155" s="1" t="s">
+      <c r="B157" s="1" t="s">
         <v>327</v>
       </c>
-      <c r="C155" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="D155" s="6" t="s">
+      <c r="C157" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D157" s="6" t="s">
         <v>348</v>
       </c>
-      <c r="E155" s="7" t="s">
+      <c r="E157" s="7" t="s">
         <v>346</v>
       </c>
-      <c r="F155" s="7" t="s">
+      <c r="F157" s="7" t="s">
         <v>347</v>
-      </c>
-      <c r="G155" s="1" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="156" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A156" s="1" t="s">
-        <v>648</v>
-      </c>
-      <c r="B156" s="1" t="s">
-        <v>649</v>
-      </c>
-      <c r="C156" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="D156" s="7" t="s">
-        <v>650</v>
-      </c>
-      <c r="E156" s="7" t="s">
-        <v>651</v>
-      </c>
-      <c r="F156" s="7" t="s">
-        <v>652</v>
-      </c>
-      <c r="G156" s="1" t="s">
-        <v>647</v>
-      </c>
-    </row>
-    <row r="157" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A157" s="1" t="s">
-        <v>657</v>
-      </c>
-      <c r="B157" s="1" t="s">
-        <v>654</v>
-      </c>
-      <c r="C157" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="D157" s="1" t="s">
-        <v>660</v>
-      </c>
-      <c r="E157" s="1" t="s">
-        <v>661</v>
-      </c>
-      <c r="F157" s="1" t="s">
-        <v>662</v>
       </c>
       <c r="G157" s="1" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="158" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="158" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A158" s="1" t="s">
-        <v>658</v>
+        <v>648</v>
       </c>
       <c r="B158" s="1" t="s">
-        <v>655</v>
+        <v>649</v>
       </c>
       <c r="C158" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="D158" s="1" t="s">
-        <v>663</v>
-      </c>
-      <c r="E158" s="1" t="s">
-        <v>664</v>
-      </c>
-      <c r="F158" s="1" t="s">
-        <v>665</v>
+      <c r="D158" s="7" t="s">
+        <v>650</v>
+      </c>
+      <c r="E158" s="7" t="s">
+        <v>651</v>
+      </c>
+      <c r="F158" s="7" t="s">
+        <v>652</v>
       </c>
       <c r="G158" s="1" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="159" spans="1:8" x14ac:dyDescent="0.35">
+        <v>647</v>
+      </c>
+    </row>
+    <row r="159" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A159" s="1" t="s">
-        <v>659</v>
+        <v>657</v>
       </c>
       <c r="B159" s="1" t="s">
-        <v>656</v>
+        <v>654</v>
       </c>
       <c r="C159" s="1" t="s">
         <v>43</v>
       </c>
       <c r="D159" s="1" t="s">
-        <v>666</v>
+        <v>660</v>
       </c>
       <c r="E159" s="1" t="s">
-        <v>667</v>
+        <v>661</v>
       </c>
       <c r="F159" s="1" t="s">
-        <v>668</v>
+        <v>662</v>
       </c>
       <c r="G159" s="1" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="160" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="160" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A160" s="1" t="s">
-        <v>752</v>
+        <v>658</v>
       </c>
       <c r="B160" s="1" t="s">
-        <v>753</v>
+        <v>655</v>
       </c>
       <c r="C160" s="1" t="s">
         <v>43</v>
       </c>
       <c r="D160" s="1" t="s">
-        <v>756</v>
+        <v>663</v>
       </c>
       <c r="E160" s="1" t="s">
-        <v>755</v>
+        <v>664</v>
       </c>
       <c r="F160" s="1" t="s">
-        <v>754</v>
+        <v>665</v>
       </c>
       <c r="G160" s="1" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="162" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="161" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A161" s="1" t="s">
+        <v>659</v>
+      </c>
+      <c r="B161" s="1" t="s">
+        <v>656</v>
+      </c>
+      <c r="C161" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D161" s="1" t="s">
+        <v>666</v>
+      </c>
+      <c r="E161" s="1" t="s">
+        <v>667</v>
+      </c>
+      <c r="F161" s="1" t="s">
+        <v>668</v>
+      </c>
+      <c r="G161" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="162" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A162" s="1" t="s">
+        <v>752</v>
+      </c>
+      <c r="B162" s="1" t="s">
+        <v>753</v>
+      </c>
+      <c r="C162" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D162" s="1" t="s">
+        <v>756</v>
+      </c>
+      <c r="E162" s="1" t="s">
+        <v>755</v>
+      </c>
+      <c r="F162" s="1" t="s">
+        <v>754</v>
+      </c>
+      <c r="G162" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="163" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A163" s="1" t="s">
+        <v>831</v>
+      </c>
+      <c r="B163" s="1" t="s">
+        <v>832</v>
+      </c>
+      <c r="C163" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D163" s="1" t="s">
+        <v>833</v>
+      </c>
+      <c r="E163" s="1" t="s">
+        <v>834</v>
+      </c>
+      <c r="F163" s="1" t="s">
+        <v>835</v>
+      </c>
+      <c r="G163" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="164" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A164" s="1" t="s">
+        <v>831</v>
+      </c>
+      <c r="B164" s="1" t="s">
+        <v>838</v>
+      </c>
+      <c r="C164" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D164" s="15" t="s">
+        <v>836</v>
+      </c>
+      <c r="E164" s="15"/>
+      <c r="F164" s="15"/>
+      <c r="G164" s="15"/>
+    </row>
+    <row r="166" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A166" s="1" t="s">
         <v>797</v>
       </c>
-      <c r="B162" s="1" t="s">
+      <c r="B166" s="1" t="s">
         <v>798</v>
       </c>
-      <c r="C162" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="D162" s="24" t="s">
+      <c r="C166" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D166" s="24" t="s">
         <v>807</v>
       </c>
-      <c r="E162" s="24"/>
-      <c r="F162" s="24"/>
-      <c r="G162" s="24"/>
-    </row>
-    <row r="163" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A163" s="1" t="s">
+      <c r="E166" s="24"/>
+      <c r="F166" s="24"/>
+      <c r="G166" s="24"/>
+    </row>
+    <row r="167" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A167" s="1" t="s">
         <v>795</v>
       </c>
-      <c r="B163" s="1" t="s">
+      <c r="B167" s="1" t="s">
         <v>796</v>
       </c>
-      <c r="C163" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="D163" s="24" t="s">
+      <c r="C167" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D167" s="24" t="s">
         <v>808</v>
       </c>
-      <c r="E163" s="24"/>
-      <c r="F163" s="24"/>
-      <c r="G163" s="24"/>
-    </row>
-    <row r="164" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A164" s="1" t="s">
+      <c r="E167" s="24"/>
+      <c r="F167" s="24"/>
+      <c r="G167" s="24"/>
+    </row>
+    <row r="168" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A168" s="1" t="s">
         <v>799</v>
       </c>
-      <c r="B164" s="1" t="s">
+      <c r="B168" s="1" t="s">
         <v>800</v>
       </c>
-      <c r="C164" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="D164" s="24" t="s">
+      <c r="C168" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D168" s="24" t="s">
         <v>808</v>
       </c>
-      <c r="E164" s="24"/>
-      <c r="F164" s="24"/>
-      <c r="G164" s="24"/>
-    </row>
-    <row r="166" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A166" s="1" t="s">
+      <c r="E168" s="24"/>
+      <c r="F168" s="24"/>
+      <c r="G168" s="24"/>
+    </row>
+    <row r="170" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A170" s="1" t="s">
         <v>330</v>
       </c>
-      <c r="B166" s="1" t="s">
+      <c r="B170" s="1" t="s">
         <v>331</v>
       </c>
-      <c r="C166" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="D166" s="26" t="s">
+      <c r="C170" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D170" s="30" t="s">
         <v>345</v>
       </c>
-      <c r="E166" s="26"/>
-      <c r="F166" s="26"/>
-      <c r="G166" s="26"/>
-    </row>
-    <row r="167" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A167" s="1" t="s">
+      <c r="E170" s="30"/>
+      <c r="F170" s="30"/>
+      <c r="G170" s="30"/>
+    </row>
+    <row r="171" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A171" s="1" t="s">
         <v>332</v>
       </c>
-      <c r="B167" s="1" t="s">
+      <c r="B171" s="1" t="s">
         <v>333</v>
       </c>
-      <c r="C167" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="D167" s="6" t="s">
+      <c r="C171" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D171" s="6" t="s">
         <v>350</v>
       </c>
-      <c r="E167" s="7" t="s">
+      <c r="E171" s="7" t="s">
         <v>351</v>
       </c>
-      <c r="F167" s="1" t="s">
+      <c r="F171" s="1" t="s">
         <v>349</v>
       </c>
-      <c r="G167" s="1" t="s">
+      <c r="G171" s="1" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="168" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A168" s="1" t="s">
+    <row r="172" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A172" s="1" t="s">
         <v>500</v>
       </c>
-      <c r="B168" s="1" t="s">
+      <c r="B172" s="1" t="s">
         <v>501</v>
       </c>
-      <c r="C168" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="D168" s="7" t="s">
+      <c r="C172" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D172" s="7" t="s">
         <v>505</v>
       </c>
-      <c r="E168" s="1" t="s">
+      <c r="E172" s="1" t="s">
         <v>504</v>
       </c>
-      <c r="F168" s="1" t="s">
+      <c r="F172" s="1" t="s">
         <v>503</v>
       </c>
-      <c r="G168" s="1" t="s">
+      <c r="G172" s="1" t="s">
         <v>502</v>
       </c>
     </row>
-    <row r="169" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A169" s="1" t="s">
+    <row r="173" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A173" s="1" t="s">
         <v>334</v>
       </c>
-      <c r="B169" s="1" t="s">
+      <c r="B173" s="1" t="s">
         <v>369</v>
       </c>
-      <c r="C169" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="D169" s="6" t="s">
+      <c r="C173" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D173" s="6" t="s">
         <v>372</v>
       </c>
-      <c r="E169" s="7" t="s">
+      <c r="E173" s="7" t="s">
         <v>370</v>
       </c>
-      <c r="F169" s="7" t="s">
+      <c r="F173" s="7" t="s">
         <v>371</v>
       </c>
-      <c r="G169" s="1" t="s">
+      <c r="G173" s="1" t="s">
         <v>14</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="67">
-    <mergeCell ref="D162:G162"/>
-    <mergeCell ref="D163:G163"/>
-    <mergeCell ref="D164:G164"/>
+  <mergeCells count="69">
+    <mergeCell ref="D150:G150"/>
+    <mergeCell ref="D151:G151"/>
+    <mergeCell ref="D147:G147"/>
+    <mergeCell ref="D98:G98"/>
+    <mergeCell ref="D99:G99"/>
+    <mergeCell ref="D86:G86"/>
+    <mergeCell ref="D88:G88"/>
+    <mergeCell ref="D16:G16"/>
+    <mergeCell ref="D68:G68"/>
+    <mergeCell ref="D18:G18"/>
+    <mergeCell ref="D22:G22"/>
+    <mergeCell ref="D23:G23"/>
+    <mergeCell ref="D24:G24"/>
+    <mergeCell ref="D19:G19"/>
+    <mergeCell ref="D20:G20"/>
+    <mergeCell ref="D21:G21"/>
+    <mergeCell ref="D54:G54"/>
+    <mergeCell ref="D30:G30"/>
+    <mergeCell ref="D31:G31"/>
+    <mergeCell ref="D33:G33"/>
+    <mergeCell ref="D34:G34"/>
+    <mergeCell ref="D14:G14"/>
+    <mergeCell ref="D25:G25"/>
+    <mergeCell ref="D170:G170"/>
+    <mergeCell ref="D152:G152"/>
+    <mergeCell ref="D140:G140"/>
+    <mergeCell ref="D69:G69"/>
+    <mergeCell ref="D130:G130"/>
+    <mergeCell ref="D129:G129"/>
+    <mergeCell ref="D148:G148"/>
+    <mergeCell ref="D138:G138"/>
+    <mergeCell ref="D139:G139"/>
+    <mergeCell ref="D74:G74"/>
+    <mergeCell ref="D134:G134"/>
+    <mergeCell ref="D135:G135"/>
+    <mergeCell ref="D136:G136"/>
+    <mergeCell ref="D133:G133"/>
+    <mergeCell ref="A4:C4"/>
+    <mergeCell ref="A6:C6"/>
+    <mergeCell ref="A5:C5"/>
+    <mergeCell ref="D5:E5"/>
+    <mergeCell ref="D6:E6"/>
+    <mergeCell ref="D4:E4"/>
+    <mergeCell ref="D15:G15"/>
+    <mergeCell ref="D17:G17"/>
+    <mergeCell ref="D46:G46"/>
+    <mergeCell ref="D81:G81"/>
     <mergeCell ref="D83:G83"/>
+    <mergeCell ref="D80:G80"/>
+    <mergeCell ref="D35:G35"/>
+    <mergeCell ref="D65:G65"/>
+    <mergeCell ref="D26:G26"/>
+    <mergeCell ref="D32:G32"/>
+    <mergeCell ref="D166:G166"/>
+    <mergeCell ref="D167:G167"/>
+    <mergeCell ref="D168:G168"/>
+    <mergeCell ref="D85:G85"/>
     <mergeCell ref="A7:C7"/>
     <mergeCell ref="A8:C8"/>
     <mergeCell ref="D12:G12"/>
@@ -6834,61 +7038,10 @@
     <mergeCell ref="A9:C9"/>
     <mergeCell ref="A10:C10"/>
     <mergeCell ref="A12:B12"/>
-    <mergeCell ref="D50:G50"/>
-    <mergeCell ref="D26:G26"/>
+    <mergeCell ref="D52:G52"/>
     <mergeCell ref="D27:G27"/>
     <mergeCell ref="D28:G28"/>
-    <mergeCell ref="D15:G15"/>
-    <mergeCell ref="D17:G17"/>
-    <mergeCell ref="D44:G44"/>
-    <mergeCell ref="D79:G79"/>
-    <mergeCell ref="D81:G81"/>
-    <mergeCell ref="D78:G78"/>
-    <mergeCell ref="D33:G33"/>
-    <mergeCell ref="A4:C4"/>
-    <mergeCell ref="A6:C6"/>
-    <mergeCell ref="A5:C5"/>
-    <mergeCell ref="D5:E5"/>
-    <mergeCell ref="D6:E6"/>
-    <mergeCell ref="D4:E4"/>
-    <mergeCell ref="D14:G14"/>
-    <mergeCell ref="D25:G25"/>
-    <mergeCell ref="D166:G166"/>
-    <mergeCell ref="D150:G150"/>
-    <mergeCell ref="D138:G138"/>
-    <mergeCell ref="D67:G67"/>
-    <mergeCell ref="D128:G128"/>
-    <mergeCell ref="D127:G127"/>
-    <mergeCell ref="D146:G146"/>
-    <mergeCell ref="D136:G136"/>
-    <mergeCell ref="D137:G137"/>
-    <mergeCell ref="D72:G72"/>
-    <mergeCell ref="D132:G132"/>
-    <mergeCell ref="D133:G133"/>
-    <mergeCell ref="D134:G134"/>
-    <mergeCell ref="D131:G131"/>
-    <mergeCell ref="D84:G84"/>
-    <mergeCell ref="D86:G86"/>
-    <mergeCell ref="D16:G16"/>
-    <mergeCell ref="D66:G66"/>
-    <mergeCell ref="D18:G18"/>
-    <mergeCell ref="D22:G22"/>
-    <mergeCell ref="D23:G23"/>
-    <mergeCell ref="D24:G24"/>
-    <mergeCell ref="D19:G19"/>
-    <mergeCell ref="D20:G20"/>
-    <mergeCell ref="D21:G21"/>
-    <mergeCell ref="D52:G52"/>
     <mergeCell ref="D29:G29"/>
-    <mergeCell ref="D30:G30"/>
-    <mergeCell ref="D31:G31"/>
-    <mergeCell ref="D32:G32"/>
-    <mergeCell ref="D63:G63"/>
-    <mergeCell ref="D148:G148"/>
-    <mergeCell ref="D149:G149"/>
-    <mergeCell ref="D145:G145"/>
-    <mergeCell ref="D96:G96"/>
-    <mergeCell ref="D97:G97"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -6898,18 +7051,18 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A2:H129"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15.6" x14ac:dyDescent="0.35"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A2:H134"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="39.6640625" style="1" customWidth="1"/>
-    <col min="2" max="2" width="38.77734375" style="1" customWidth="1"/>
-    <col min="3" max="3" width="14.77734375" style="1" customWidth="1"/>
-    <col min="4" max="8" width="12.6640625" style="1" customWidth="1"/>
+    <col min="1" max="1" width="39.625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="38.75" style="1" customWidth="1"/>
+    <col min="3" max="3" width="14.75" style="1" customWidth="1"/>
+    <col min="4" max="8" width="12.625" style="1" customWidth="1"/>
     <col min="9" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2" s="4" t="s">
         <v>44</v>
       </c>
@@ -6921,90 +7074,90 @@
       <c r="G2" s="4"/>
       <c r="H2" s="5"/>
     </row>
-    <row r="4" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="24" t="s">
         <v>202</v>
       </c>
       <c r="B4" s="24"/>
       <c r="C4" s="24"/>
-      <c r="D4" s="29" t="s">
+      <c r="D4" s="33" t="s">
         <v>55</v>
       </c>
-      <c r="E4" s="29"/>
+      <c r="E4" s="33"/>
       <c r="F4" s="17" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="5" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="24" t="s">
         <v>421</v>
       </c>
       <c r="B5" s="24"/>
       <c r="C5" s="24"/>
-      <c r="D5" s="27" t="s">
+      <c r="D5" s="31" t="s">
         <v>47</v>
       </c>
-      <c r="E5" s="27"/>
+      <c r="E5" s="31"/>
       <c r="F5" s="10" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="6" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="24"/>
       <c r="B6" s="24"/>
       <c r="C6" s="24"/>
-      <c r="D6" s="28" t="s">
+      <c r="D6" s="32" t="s">
         <v>352</v>
       </c>
-      <c r="E6" s="28"/>
+      <c r="E6" s="32"/>
       <c r="F6" s="13" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="7" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="30"/>
-      <c r="B7" s="30"/>
-      <c r="C7" s="35"/>
-      <c r="D7" s="32" t="s">
+    <row r="7" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="25"/>
+      <c r="B7" s="25"/>
+      <c r="C7" s="37"/>
+      <c r="D7" s="27" t="s">
         <v>51</v>
       </c>
-      <c r="E7" s="32"/>
+      <c r="E7" s="27"/>
       <c r="F7" s="12" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="8" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="30"/>
-      <c r="B8" s="30"/>
-      <c r="C8" s="30"/>
-      <c r="D8" s="33" t="s">
+    <row r="8" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="25"/>
+      <c r="B8" s="25"/>
+      <c r="C8" s="25"/>
+      <c r="D8" s="28" t="s">
         <v>53</v>
       </c>
-      <c r="E8" s="33"/>
+      <c r="E8" s="28"/>
       <c r="F8" s="14" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="9" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="24"/>
       <c r="B9" s="24"/>
       <c r="C9" s="24"/>
     </row>
-    <row r="11" spans="1:8" ht="16.2" x14ac:dyDescent="0.4">
-      <c r="A11" s="34" t="s">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A11" s="29" t="s">
         <v>344</v>
       </c>
-      <c r="B11" s="34"/>
+      <c r="B11" s="29"/>
       <c r="C11" s="18"/>
-      <c r="D11" s="31" t="s">
+      <c r="D11" s="26" t="s">
         <v>579</v>
       </c>
-      <c r="E11" s="31"/>
-      <c r="F11" s="31"/>
-      <c r="G11" s="31"/>
+      <c r="E11" s="26"/>
+      <c r="F11" s="26"/>
+      <c r="G11" s="26"/>
       <c r="H11" s="5"/>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A12" s="19" t="s">
         <v>160</v>
       </c>
@@ -7026,7 +7179,7 @@
       <c r="G12" s="36"/>
       <c r="H12" s="2"/>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A13" s="1" t="s">
         <v>171</v>
       </c>
@@ -7036,14 +7189,14 @@
       <c r="C13" s="1" t="s">
         <v>180</v>
       </c>
-      <c r="D13" s="26" t="s">
+      <c r="D13" s="30" t="s">
         <v>178</v>
       </c>
-      <c r="E13" s="26"/>
-      <c r="F13" s="26"/>
-      <c r="G13" s="26"/>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="E13" s="30"/>
+      <c r="F13" s="30"/>
+      <c r="G13" s="30"/>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A14" s="1" t="s">
         <v>375</v>
       </c>
@@ -7053,14 +7206,14 @@
       <c r="C14" s="1" t="s">
         <v>180</v>
       </c>
-      <c r="D14" s="26" t="s">
+      <c r="D14" s="30" t="s">
         <v>178</v>
       </c>
-      <c r="E14" s="26"/>
-      <c r="F14" s="26"/>
-      <c r="G14" s="26"/>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="E14" s="30"/>
+      <c r="F14" s="30"/>
+      <c r="G14" s="30"/>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A15" s="1" t="s">
         <v>401</v>
       </c>
@@ -7077,7 +7230,7 @@
       <c r="F15" s="24"/>
       <c r="G15" s="24"/>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A16" s="1" t="s">
         <v>377</v>
       </c>
@@ -7087,14 +7240,14 @@
       <c r="C16" s="1" t="s">
         <v>180</v>
       </c>
-      <c r="D16" s="25" t="s">
+      <c r="D16" s="34" t="s">
         <v>420</v>
       </c>
-      <c r="E16" s="25"/>
-      <c r="F16" s="25"/>
-      <c r="G16" s="25"/>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="E16" s="34"/>
+      <c r="F16" s="34"/>
+      <c r="G16" s="34"/>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A17" s="1" t="s">
         <v>585</v>
       </c>
@@ -7111,7 +7264,7 @@
       <c r="F17" s="24"/>
       <c r="G17" s="24"/>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A18" s="1" t="s">
         <v>581</v>
       </c>
@@ -7128,7 +7281,7 @@
       <c r="F18" s="24"/>
       <c r="G18" s="24"/>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A19" s="1" t="s">
         <v>614</v>
       </c>
@@ -7145,7 +7298,7 @@
       <c r="F19" s="24"/>
       <c r="G19" s="24"/>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A20" s="1" t="s">
         <v>616</v>
       </c>
@@ -7155,14 +7308,14 @@
       <c r="C20" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="D20" s="26" t="s">
+      <c r="D20" s="30" t="s">
         <v>178</v>
       </c>
-      <c r="E20" s="26"/>
-      <c r="F20" s="26"/>
-      <c r="G20" s="26"/>
-    </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="E20" s="30"/>
+      <c r="F20" s="30"/>
+      <c r="G20" s="30"/>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A21" s="1" t="s">
         <v>717</v>
       </c>
@@ -7172,14 +7325,14 @@
       <c r="C21" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="D21" s="25" t="s">
+      <c r="D21" s="34" t="s">
         <v>723</v>
       </c>
-      <c r="E21" s="25"/>
-      <c r="F21" s="25"/>
-      <c r="G21" s="25"/>
-    </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="E21" s="34"/>
+      <c r="F21" s="34"/>
+      <c r="G21" s="34"/>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A22" s="1" t="s">
         <v>716</v>
       </c>
@@ -7196,7 +7349,7 @@
       <c r="F22" s="24"/>
       <c r="G22" s="24"/>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A23" s="1" t="s">
         <v>738</v>
       </c>
@@ -7213,7 +7366,7 @@
       <c r="F23" s="24"/>
       <c r="G23" s="24"/>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A24" s="1" t="s">
         <v>793</v>
       </c>
@@ -7230,1073 +7383,1091 @@
       <c r="F24" s="24"/>
       <c r="G24" s="24"/>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A25" s="1" t="s">
+        <v>826</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>827</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D25" s="24" t="s">
+        <v>825</v>
+      </c>
+      <c r="E25" s="24"/>
+      <c r="F25" s="24"/>
+      <c r="G25" s="24"/>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A26" s="1" t="s">
         <v>172</v>
       </c>
-      <c r="B25" s="1" t="s">
+      <c r="B26" s="1" t="s">
         <v>163</v>
-      </c>
-      <c r="C25" s="1" t="s">
-        <v>179</v>
-      </c>
-      <c r="D25" s="26" t="s">
-        <v>178</v>
-      </c>
-      <c r="E25" s="26"/>
-      <c r="F25" s="26"/>
-      <c r="G25" s="26"/>
-    </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A26" s="1" t="s">
-        <v>173</v>
-      </c>
-      <c r="B26" s="1" t="s">
-        <v>164</v>
       </c>
       <c r="C26" s="1" t="s">
         <v>179</v>
       </c>
-      <c r="D26" s="26" t="s">
-        <v>182</v>
-      </c>
-      <c r="E26" s="26"/>
-      <c r="F26" s="26"/>
-      <c r="G26" s="26"/>
-    </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="D26" s="30" t="s">
+        <v>178</v>
+      </c>
+      <c r="E26" s="30"/>
+      <c r="F26" s="30"/>
+      <c r="G26" s="30"/>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A27" s="1" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>174</v>
+        <v>828</v>
       </c>
       <c r="C27" s="1" t="s">
         <v>179</v>
       </c>
-      <c r="D27" s="24" t="s">
-        <v>408</v>
-      </c>
-      <c r="E27" s="24"/>
-      <c r="F27" s="24"/>
-      <c r="G27" s="24"/>
-    </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="D27" s="30" t="s">
+        <v>182</v>
+      </c>
+      <c r="E27" s="30"/>
+      <c r="F27" s="30"/>
+      <c r="G27" s="30"/>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A28" s="1" t="s">
-        <v>165</v>
+        <v>175</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="C28" s="1" t="s">
         <v>179</v>
       </c>
-      <c r="D28" s="26" t="s">
+      <c r="D28" s="24" t="s">
+        <v>408</v>
+      </c>
+      <c r="E28" s="24"/>
+      <c r="F28" s="24"/>
+      <c r="G28" s="24"/>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A29" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="D29" s="30" t="s">
         <v>178</v>
       </c>
-      <c r="E28" s="26"/>
-      <c r="F28" s="26"/>
-      <c r="G28" s="26"/>
-    </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A29" s="1" t="s">
+      <c r="E29" s="30"/>
+      <c r="F29" s="30"/>
+      <c r="G29" s="30"/>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A30" s="1" t="s">
         <v>166</v>
       </c>
-      <c r="B29" s="1" t="s">
+      <c r="B30" s="1" t="s">
         <v>167</v>
       </c>
-      <c r="C29" s="1" t="s">
+      <c r="C30" s="1" t="s">
         <v>180</v>
       </c>
-      <c r="D29" s="24" t="s">
+      <c r="D30" s="24" t="s">
         <v>419</v>
       </c>
-      <c r="E29" s="24"/>
-      <c r="F29" s="24"/>
-      <c r="G29" s="24"/>
-    </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A30" s="1" t="s">
-        <v>177</v>
-      </c>
-      <c r="B30" s="1" t="s">
-        <v>168</v>
-      </c>
-      <c r="C30" s="1" t="s">
-        <v>181</v>
-      </c>
-      <c r="D30" s="26" t="s">
-        <v>182</v>
-      </c>
-      <c r="E30" s="26"/>
-      <c r="F30" s="26"/>
-      <c r="G30" s="26"/>
-    </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="E30" s="24"/>
+      <c r="F30" s="24"/>
+      <c r="G30" s="24"/>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A31" s="1" t="s">
-        <v>169</v>
+        <v>822</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>170</v>
+        <v>823</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>180</v>
+        <v>43</v>
       </c>
       <c r="D31" s="24" t="s">
-        <v>418</v>
+        <v>830</v>
       </c>
       <c r="E31" s="24"/>
       <c r="F31" s="24"/>
       <c r="G31" s="24"/>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A32" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="C32" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="D32" s="30" t="s">
+        <v>182</v>
+      </c>
+      <c r="E32" s="30"/>
+      <c r="F32" s="30"/>
+      <c r="G32" s="30"/>
+    </row>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A33" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="C33" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="D33" s="24" t="s">
+        <v>418</v>
+      </c>
+      <c r="E33" s="24"/>
+      <c r="F33" s="24"/>
+      <c r="G33" s="24"/>
+    </row>
+    <row r="34" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A34" s="1" t="s">
         <v>750</v>
       </c>
-      <c r="B32" s="1" t="s">
+      <c r="B34" s="1" t="s">
         <v>751</v>
       </c>
-      <c r="C32" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="D32" s="26" t="s">
+      <c r="C34" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D34" s="30" t="s">
         <v>182</v>
       </c>
-      <c r="E32" s="26"/>
-      <c r="F32" s="26"/>
-      <c r="G32" s="26"/>
-    </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A34" s="1" t="s">
+      <c r="E34" s="30"/>
+      <c r="F34" s="30"/>
+      <c r="G34" s="30"/>
+    </row>
+    <row r="36" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A36" s="1" t="s">
         <v>203</v>
       </c>
-      <c r="B34" s="1" t="s">
+      <c r="B36" s="1" t="s">
         <v>204</v>
-      </c>
-      <c r="H34" s="1" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A35" s="1" t="s">
-        <v>205</v>
-      </c>
-      <c r="B35" s="1" t="s">
-        <v>206</v>
-      </c>
-      <c r="H35" s="1" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A36" s="1" t="s">
-        <v>207</v>
-      </c>
-      <c r="B36" s="1" t="s">
-        <v>208</v>
       </c>
       <c r="H36" s="1" t="s">
         <v>213</v>
       </c>
     </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A37" s="1" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="H37" s="1" t="s">
         <v>213</v>
       </c>
     </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A38" s="1" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
       <c r="H38" s="1" t="s">
         <v>213</v>
       </c>
     </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A39" s="16" t="s">
-        <v>214</v>
-      </c>
-      <c r="B39" s="16" t="s">
-        <v>215</v>
+    <row r="39" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A39" s="1" t="s">
+        <v>209</v>
+      </c>
+      <c r="B39" s="1" t="s">
+        <v>210</v>
       </c>
       <c r="H39" s="1" t="s">
         <v>213</v>
       </c>
     </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A40" s="16" t="s">
-        <v>216</v>
-      </c>
-      <c r="B40" s="16" t="s">
-        <v>217</v>
-      </c>
-      <c r="C40" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="D40" s="37" t="s">
-        <v>417</v>
-      </c>
-      <c r="E40" s="37"/>
-      <c r="F40" s="37"/>
-      <c r="G40" s="37"/>
-    </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A40" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="B40" s="1" t="s">
+        <v>212</v>
+      </c>
+      <c r="H40" s="1" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A41" s="16" t="s">
-        <v>218</v>
+        <v>214</v>
       </c>
       <c r="B41" s="16" t="s">
-        <v>219</v>
+        <v>215</v>
       </c>
       <c r="H41" s="1" t="s">
         <v>213</v>
       </c>
     </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A42" s="16" t="s">
-        <v>220</v>
+        <v>216</v>
       </c>
       <c r="B42" s="16" t="s">
-        <v>221</v>
-      </c>
-      <c r="H42" s="1" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.35">
+        <v>217</v>
+      </c>
+      <c r="C42" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D42" s="35" t="s">
+        <v>417</v>
+      </c>
+      <c r="E42" s="35"/>
+      <c r="F42" s="35"/>
+      <c r="G42" s="35"/>
+    </row>
+    <row r="43" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A43" s="16" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
       <c r="B43" s="16" t="s">
-        <v>223</v>
+        <v>219</v>
       </c>
       <c r="H43" s="1" t="s">
         <v>213</v>
       </c>
     </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A44" s="16" t="s">
+        <v>220</v>
+      </c>
+      <c r="B44" s="16" t="s">
+        <v>221</v>
+      </c>
+      <c r="H44" s="1" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A45" s="16" t="s">
+        <v>222</v>
+      </c>
+      <c r="B45" s="16" t="s">
+        <v>223</v>
+      </c>
+      <c r="H45" s="1" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A46" s="16" t="s">
         <v>791</v>
       </c>
-      <c r="B44" s="16" t="s">
+      <c r="B46" s="16" t="s">
         <v>792</v>
       </c>
-      <c r="C44" s="1" t="s">
+      <c r="C46" s="1" t="s">
         <v>143</v>
       </c>
-      <c r="D44" s="24" t="s">
+      <c r="D46" s="24" t="s">
         <v>406</v>
       </c>
-      <c r="E44" s="24"/>
-      <c r="F44" s="24"/>
-      <c r="G44" s="24"/>
-    </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A45" s="16" t="s">
+      <c r="E46" s="24"/>
+      <c r="F46" s="24"/>
+      <c r="G46" s="24"/>
+    </row>
+    <row r="47" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A47" s="16" t="s">
         <v>224</v>
       </c>
-      <c r="B45" s="16" t="s">
+      <c r="B47" s="16" t="s">
         <v>225</v>
       </c>
-      <c r="C45" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="D45" s="15" t="s">
+      <c r="C47" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D47" s="15" t="s">
         <v>358</v>
       </c>
-      <c r="E45" s="6" t="s">
+      <c r="E47" s="6" t="s">
         <v>356</v>
       </c>
-      <c r="F45" s="7" t="s">
+      <c r="F47" s="7" t="s">
         <v>357</v>
       </c>
-      <c r="G45" s="1" t="s">
+      <c r="G47" s="1" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A46" s="1" t="s">
+    <row r="48" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A48" s="1" t="s">
         <v>624</v>
       </c>
-      <c r="B46" s="1" t="s">
+      <c r="B48" s="1" t="s">
         <v>625</v>
       </c>
-      <c r="C46" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="D46" s="6" t="s">
+      <c r="C48" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D48" s="6" t="s">
         <v>618</v>
       </c>
-      <c r="E46" s="6" t="s">
+      <c r="E48" s="6" t="s">
         <v>619</v>
       </c>
-      <c r="F46" s="6" t="s">
+      <c r="F48" s="6" t="s">
         <v>620</v>
       </c>
-      <c r="G46" s="1" t="s">
+      <c r="G48" s="1" t="s">
         <v>621</v>
       </c>
     </row>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A48" s="1" t="s">
+    <row r="50" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A50" s="1" t="s">
         <v>226</v>
       </c>
-      <c r="B48" s="1" t="s">
+      <c r="B50" s="1" t="s">
         <v>227</v>
-      </c>
-      <c r="H48" s="1" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="49" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A49" s="1" t="s">
-        <v>228</v>
-      </c>
-      <c r="B49" s="1" t="s">
-        <v>229</v>
-      </c>
-      <c r="H49" s="1" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="50" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A50" s="1" t="s">
-        <v>230</v>
-      </c>
-      <c r="B50" s="1" t="s">
-        <v>231</v>
       </c>
       <c r="H50" s="1" t="s">
         <v>213</v>
       </c>
     </row>
-    <row r="51" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A51" s="1" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="H51" s="1" t="s">
         <v>213</v>
       </c>
     </row>
-    <row r="52" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A52" s="1" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="H52" s="1" t="s">
         <v>213</v>
       </c>
     </row>
-    <row r="53" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A53" s="1" t="s">
-        <v>236</v>
+        <v>232</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>237</v>
-      </c>
-      <c r="C53" s="1" t="s">
-        <v>304</v>
-      </c>
-      <c r="D53" s="6" t="s">
-        <v>311</v>
-      </c>
-      <c r="E53" s="6" t="s">
-        <v>310</v>
-      </c>
-      <c r="F53" s="7" t="s">
-        <v>308</v>
-      </c>
-      <c r="G53" s="1" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="54" spans="1:8" x14ac:dyDescent="0.35">
+        <v>233</v>
+      </c>
+      <c r="H53" s="1" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="54" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A54" s="1" t="s">
-        <v>238</v>
+        <v>234</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="H54" s="1" t="s">
         <v>213</v>
       </c>
     </row>
-    <row r="55" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A55" s="1" t="s">
-        <v>240</v>
+        <v>236</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>241</v>
-      </c>
-      <c r="H55" s="1" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="56" spans="1:8" x14ac:dyDescent="0.35">
+        <v>237</v>
+      </c>
+      <c r="C55" s="1" t="s">
+        <v>304</v>
+      </c>
+      <c r="D55" s="6" t="s">
+        <v>311</v>
+      </c>
+      <c r="E55" s="6" t="s">
+        <v>310</v>
+      </c>
+      <c r="F55" s="7" t="s">
+        <v>308</v>
+      </c>
+      <c r="G55" s="1" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="56" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A56" s="1" t="s">
-        <v>242</v>
+        <v>238</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="H56" s="1" t="s">
         <v>213</v>
       </c>
     </row>
-    <row r="58" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A57" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="B57" s="1" t="s">
+        <v>241</v>
+      </c>
+      <c r="H57" s="1" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="58" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A58" s="1" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="H58" s="1" t="s">
         <v>213</v>
       </c>
     </row>
-    <row r="59" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A59" s="1" t="s">
-        <v>246</v>
-      </c>
-      <c r="B59" s="1" t="s">
-        <v>247</v>
-      </c>
-      <c r="H59" s="1" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="60" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A60" s="1" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>249</v>
+        <v>245</v>
       </c>
       <c r="H60" s="1" t="s">
         <v>213</v>
       </c>
     </row>
-    <row r="61" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A61" s="1" t="s">
-        <v>250</v>
+        <v>246</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>251</v>
+        <v>247</v>
       </c>
       <c r="H61" s="1" t="s">
         <v>213</v>
       </c>
     </row>
-    <row r="62" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A62" s="1" t="s">
-        <v>252</v>
+        <v>248</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>253</v>
+        <v>249</v>
       </c>
       <c r="H62" s="1" t="s">
         <v>213</v>
       </c>
     </row>
-    <row r="63" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A63" s="1" t="s">
+        <v>250</v>
+      </c>
+      <c r="B63" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="H63" s="1" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="64" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A64" s="1" t="s">
+        <v>252</v>
+      </c>
+      <c r="B64" s="1" t="s">
+        <v>253</v>
+      </c>
+      <c r="H64" s="1" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="65" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A65" s="1" t="s">
         <v>398</v>
       </c>
-      <c r="B63" s="1" t="s">
+      <c r="B65" s="1" t="s">
         <v>399</v>
       </c>
-      <c r="C63" s="1" t="s">
+      <c r="C65" s="1" t="s">
         <v>400</v>
       </c>
-      <c r="D63" s="24" t="s">
+      <c r="D65" s="24" t="s">
         <v>408</v>
       </c>
-      <c r="E63" s="24"/>
-      <c r="F63" s="24"/>
-      <c r="G63" s="24"/>
-    </row>
-    <row r="65" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A65" s="1" t="s">
+      <c r="E65" s="24"/>
+      <c r="F65" s="24"/>
+      <c r="G65" s="24"/>
+    </row>
+    <row r="67" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A67" s="1" t="s">
         <v>254</v>
       </c>
-      <c r="B65" s="1" t="s">
+      <c r="B67" s="1" t="s">
         <v>255</v>
       </c>
-      <c r="H65" s="1" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="66" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A66" s="1" t="s">
+      <c r="C67" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D67" s="7" t="s">
+        <v>815</v>
+      </c>
+      <c r="E67" s="1" t="s">
+        <v>814</v>
+      </c>
+      <c r="F67" s="1" t="s">
+        <v>813</v>
+      </c>
+      <c r="G67" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="68" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A68" s="1" t="s">
+        <v>811</v>
+      </c>
+      <c r="B68" s="1" t="s">
+        <v>812</v>
+      </c>
+      <c r="C68" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D68" s="7" t="s">
+        <v>818</v>
+      </c>
+      <c r="E68" s="7" t="s">
+        <v>817</v>
+      </c>
+      <c r="F68" s="1" t="s">
+        <v>816</v>
+      </c>
+      <c r="G68" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="69" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A69" s="1" t="s">
         <v>256</v>
       </c>
-      <c r="B66" s="1" t="s">
+      <c r="B69" s="1" t="s">
         <v>257</v>
-      </c>
-      <c r="H66" s="1" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="67" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A67" s="1" t="s">
-        <v>258</v>
-      </c>
-      <c r="B67" s="1" t="s">
-        <v>259</v>
-      </c>
-      <c r="H67" s="1" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="68" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A68" s="1" t="s">
-        <v>260</v>
-      </c>
-      <c r="B68" s="1" t="s">
-        <v>261</v>
-      </c>
-      <c r="H68" s="1" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="69" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A69" s="1" t="s">
-        <v>262</v>
-      </c>
-      <c r="B69" s="1" t="s">
-        <v>263</v>
       </c>
       <c r="H69" s="1" t="s">
         <v>213</v>
       </c>
     </row>
-    <row r="70" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A70" s="1" t="s">
-        <v>264</v>
+        <v>258</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>265</v>
+        <v>259</v>
       </c>
       <c r="H70" s="1" t="s">
         <v>213</v>
       </c>
     </row>
-    <row r="71" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A71" s="1" t="s">
-        <v>266</v>
+        <v>260</v>
       </c>
       <c r="B71" s="1" t="s">
-        <v>267</v>
+        <v>261</v>
       </c>
       <c r="H71" s="1" t="s">
         <v>213</v>
       </c>
     </row>
-    <row r="72" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A72" s="1" t="s">
-        <v>268</v>
+        <v>262</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>269</v>
+        <v>263</v>
       </c>
       <c r="H72" s="1" t="s">
         <v>213</v>
       </c>
     </row>
-    <row r="73" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A73" s="1" t="s">
-        <v>270</v>
+        <v>264</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>271</v>
+        <v>265</v>
       </c>
       <c r="H73" s="1" t="s">
         <v>213</v>
       </c>
     </row>
-    <row r="74" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A74" s="1" t="s">
-        <v>272</v>
+        <v>266</v>
       </c>
       <c r="B74" s="1" t="s">
-        <v>273</v>
+        <v>267</v>
       </c>
       <c r="H74" s="1" t="s">
         <v>213</v>
       </c>
     </row>
-    <row r="76" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A75" s="1" t="s">
+        <v>268</v>
+      </c>
+      <c r="B75" s="1" t="s">
+        <v>269</v>
+      </c>
+      <c r="H75" s="1" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="76" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A76" s="1" t="s">
-        <v>274</v>
+        <v>270</v>
       </c>
       <c r="B76" s="1" t="s">
-        <v>275</v>
+        <v>271</v>
       </c>
       <c r="H76" s="1" t="s">
         <v>213</v>
       </c>
     </row>
-    <row r="77" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A77" s="1" t="s">
-        <v>276</v>
+        <v>272</v>
       </c>
       <c r="B77" s="1" t="s">
-        <v>277</v>
+        <v>273</v>
       </c>
       <c r="H77" s="1" t="s">
         <v>213</v>
       </c>
     </row>
-    <row r="78" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A78" s="1" t="s">
-        <v>278</v>
-      </c>
-      <c r="B78" s="1" t="s">
-        <v>279</v>
-      </c>
-      <c r="H78" s="1" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="79" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A79" s="1" t="s">
-        <v>280</v>
+        <v>274</v>
       </c>
       <c r="B79" s="1" t="s">
-        <v>281</v>
+        <v>275</v>
       </c>
       <c r="H79" s="1" t="s">
         <v>213</v>
       </c>
     </row>
-    <row r="80" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A80" s="1" t="s">
-        <v>282</v>
+        <v>276</v>
       </c>
       <c r="B80" s="1" t="s">
-        <v>283</v>
+        <v>277</v>
       </c>
       <c r="H80" s="1" t="s">
         <v>213</v>
       </c>
     </row>
-    <row r="81" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A81" s="1" t="s">
-        <v>284</v>
+        <v>278</v>
       </c>
       <c r="B81" s="1" t="s">
-        <v>285</v>
+        <v>279</v>
       </c>
       <c r="H81" s="1" t="s">
         <v>213</v>
       </c>
     </row>
-    <row r="82" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A82" s="1" t="s">
-        <v>286</v>
+        <v>280</v>
       </c>
       <c r="B82" s="1" t="s">
-        <v>287</v>
+        <v>281</v>
       </c>
       <c r="H82" s="1" t="s">
         <v>213</v>
       </c>
     </row>
-    <row r="83" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A83" s="1" t="s">
-        <v>288</v>
+        <v>282</v>
       </c>
       <c r="B83" s="1" t="s">
-        <v>289</v>
+        <v>283</v>
       </c>
       <c r="H83" s="1" t="s">
         <v>213</v>
       </c>
     </row>
-    <row r="84" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A84" s="1" t="s">
-        <v>290</v>
+        <v>284</v>
       </c>
       <c r="B84" s="1" t="s">
-        <v>291</v>
+        <v>285</v>
       </c>
       <c r="H84" s="1" t="s">
         <v>213</v>
       </c>
     </row>
-    <row r="86" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A85" s="1" t="s">
+        <v>286</v>
+      </c>
+      <c r="B85" s="1" t="s">
+        <v>287</v>
+      </c>
+      <c r="H85" s="1" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="86" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A86" s="1" t="s">
-        <v>292</v>
+        <v>288</v>
       </c>
       <c r="B86" s="1" t="s">
-        <v>293</v>
+        <v>289</v>
       </c>
       <c r="H86" s="1" t="s">
         <v>213</v>
       </c>
     </row>
-    <row r="87" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A87" s="1" t="s">
+        <v>290</v>
+      </c>
+      <c r="B87" s="1" t="s">
+        <v>291</v>
+      </c>
+      <c r="H87" s="1" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="89" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A89" s="1" t="s">
+        <v>292</v>
+      </c>
+      <c r="B89" s="1" t="s">
+        <v>293</v>
+      </c>
+      <c r="H89" s="1" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="90" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A90" s="1" t="s">
         <v>294</v>
       </c>
-      <c r="B87" s="1" t="s">
+      <c r="B90" s="1" t="s">
         <v>295</v>
       </c>
-      <c r="C87" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="D87" s="24" t="s">
+      <c r="C90" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D90" s="24" t="s">
         <v>714</v>
       </c>
-      <c r="E87" s="24"/>
-      <c r="F87" s="24"/>
-      <c r="G87" s="24"/>
-    </row>
-    <row r="88" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A88" s="16" t="s">
+      <c r="E90" s="24"/>
+      <c r="F90" s="24"/>
+      <c r="G90" s="24"/>
+    </row>
+    <row r="91" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A91" s="16" t="s">
         <v>296</v>
       </c>
-      <c r="B88" s="16" t="s">
+      <c r="B91" s="16" t="s">
         <v>297</v>
       </c>
-      <c r="C88" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="D88" s="24" t="s">
+      <c r="C91" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D91" s="24" t="s">
         <v>713</v>
-      </c>
-      <c r="E88" s="24"/>
-      <c r="F88" s="24"/>
-      <c r="G88" s="24"/>
-    </row>
-    <row r="89" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A89" s="16" t="s">
-        <v>702</v>
-      </c>
-      <c r="B89" s="16" t="s">
-        <v>703</v>
-      </c>
-      <c r="C89" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="D89" s="26" t="s">
-        <v>305</v>
-      </c>
-      <c r="E89" s="26"/>
-      <c r="F89" s="26"/>
-      <c r="G89" s="26"/>
-    </row>
-    <row r="90" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A90" s="16" t="s">
-        <v>704</v>
-      </c>
-      <c r="B90" s="16" t="s">
-        <v>705</v>
-      </c>
-      <c r="C90" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="D90" s="26" t="s">
-        <v>305</v>
-      </c>
-      <c r="E90" s="26"/>
-      <c r="F90" s="26"/>
-      <c r="G90" s="26"/>
-    </row>
-    <row r="91" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A91" s="16" t="s">
-        <v>405</v>
-      </c>
-      <c r="B91" s="16" t="s">
-        <v>404</v>
-      </c>
-      <c r="C91" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="D91" s="24" t="s">
-        <v>415</v>
       </c>
       <c r="E91" s="24"/>
       <c r="F91" s="24"/>
       <c r="G91" s="24"/>
     </row>
-    <row r="92" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A92" s="1" t="s">
-        <v>298</v>
-      </c>
-      <c r="B92" s="1" t="s">
-        <v>299</v>
+    <row r="92" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A92" s="16" t="s">
+        <v>702</v>
+      </c>
+      <c r="B92" s="16" t="s">
+        <v>703</v>
       </c>
       <c r="C92" s="1" t="s">
-        <v>143</v>
-      </c>
-      <c r="D92" s="24" t="s">
-        <v>408</v>
-      </c>
-      <c r="E92" s="24"/>
-      <c r="F92" s="24"/>
-      <c r="G92" s="24"/>
-    </row>
-    <row r="93" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A93" s="1" t="s">
-        <v>300</v>
-      </c>
-      <c r="B93" s="1" t="s">
-        <v>301</v>
+        <v>43</v>
+      </c>
+      <c r="D92" s="30" t="s">
+        <v>305</v>
+      </c>
+      <c r="E92" s="30"/>
+      <c r="F92" s="30"/>
+      <c r="G92" s="30"/>
+    </row>
+    <row r="93" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A93" s="16" t="s">
+        <v>704</v>
+      </c>
+      <c r="B93" s="16" t="s">
+        <v>705</v>
       </c>
       <c r="C93" s="1" t="s">
-        <v>143</v>
-      </c>
-      <c r="D93" s="24" t="s">
-        <v>408</v>
-      </c>
-      <c r="E93" s="24"/>
-      <c r="F93" s="24"/>
-      <c r="G93" s="24"/>
-    </row>
-    <row r="94" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A94" s="1" t="s">
-        <v>302</v>
-      </c>
-      <c r="B94" s="1" t="s">
-        <v>303</v>
+        <v>43</v>
+      </c>
+      <c r="D93" s="30" t="s">
+        <v>305</v>
+      </c>
+      <c r="E93" s="30"/>
+      <c r="F93" s="30"/>
+      <c r="G93" s="30"/>
+    </row>
+    <row r="94" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A94" s="16" t="s">
+        <v>405</v>
+      </c>
+      <c r="B94" s="16" t="s">
+        <v>404</v>
       </c>
       <c r="C94" s="1" t="s">
-        <v>143</v>
+        <v>43</v>
       </c>
       <c r="D94" s="24" t="s">
-        <v>408</v>
+        <v>415</v>
       </c>
       <c r="E94" s="24"/>
       <c r="F94" s="24"/>
       <c r="G94" s="24"/>
     </row>
-    <row r="96" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A95" s="1" t="s">
+        <v>298</v>
+      </c>
+      <c r="B95" s="1" t="s">
+        <v>299</v>
+      </c>
+      <c r="C95" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="D95" s="24" t="s">
+        <v>408</v>
+      </c>
+      <c r="E95" s="24"/>
+      <c r="F95" s="24"/>
+      <c r="G95" s="24"/>
+    </row>
+    <row r="96" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A96" s="1" t="s">
+        <v>300</v>
+      </c>
+      <c r="B96" s="1" t="s">
+        <v>301</v>
+      </c>
+      <c r="C96" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="D96" s="24" t="s">
+        <v>408</v>
+      </c>
+      <c r="E96" s="24"/>
+      <c r="F96" s="24"/>
+      <c r="G96" s="24"/>
+    </row>
+    <row r="97" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A97" s="1" t="s">
+        <v>302</v>
+      </c>
+      <c r="B97" s="1" t="s">
+        <v>303</v>
+      </c>
+      <c r="C97" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="D97" s="24" t="s">
+        <v>408</v>
+      </c>
+      <c r="E97" s="24"/>
+      <c r="F97" s="24"/>
+      <c r="G97" s="24"/>
+    </row>
+    <row r="99" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A99" s="1" t="s">
         <v>605</v>
       </c>
-      <c r="B96" s="1" t="s">
+      <c r="B99" s="1" t="s">
         <v>606</v>
       </c>
-      <c r="C96" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="D96" s="26" t="s">
+      <c r="C99" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D99" s="30" t="s">
         <v>305</v>
       </c>
-      <c r="E96" s="26"/>
-      <c r="F96" s="26"/>
-      <c r="G96" s="26"/>
-    </row>
-    <row r="97" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A97" s="1" t="s">
+      <c r="E99" s="30"/>
+      <c r="F99" s="30"/>
+      <c r="G99" s="30"/>
+    </row>
+    <row r="100" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A100" s="1" t="s">
         <v>607</v>
       </c>
-      <c r="B97" s="1" t="s">
+      <c r="B100" s="1" t="s">
         <v>608</v>
       </c>
-      <c r="C97" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="D97" s="26" t="s">
+      <c r="C100" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D100" s="30" t="s">
         <v>305</v>
       </c>
-      <c r="E97" s="26"/>
-      <c r="F97" s="26"/>
-      <c r="G97" s="26"/>
-    </row>
-    <row r="98" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A98" s="1" t="s">
+      <c r="E100" s="30"/>
+      <c r="F100" s="30"/>
+      <c r="G100" s="30"/>
+    </row>
+    <row r="101" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A101" s="1" t="s">
         <v>124</v>
       </c>
-      <c r="B98" s="1" t="s">
+      <c r="B101" s="1" t="s">
         <v>125</v>
       </c>
-      <c r="C98" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="D98" s="25" t="s">
+      <c r="C101" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D101" s="34" t="s">
         <v>416</v>
       </c>
-      <c r="E98" s="25"/>
-      <c r="F98" s="25"/>
-      <c r="G98" s="25"/>
-    </row>
-    <row r="99" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A99" s="1" t="s">
+      <c r="E101" s="34"/>
+      <c r="F101" s="34"/>
+      <c r="G101" s="34"/>
+    </row>
+    <row r="102" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A102" s="1" t="s">
         <v>126</v>
       </c>
-      <c r="B99" s="1" t="s">
+      <c r="B102" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="C99" s="1" t="s">
+      <c r="C102" s="1" t="s">
         <v>304</v>
       </c>
-      <c r="D99" s="26" t="s">
+      <c r="D102" s="30" t="s">
         <v>305</v>
       </c>
-      <c r="E99" s="26"/>
-      <c r="F99" s="26"/>
-      <c r="G99" s="26"/>
-    </row>
-    <row r="100" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A100" s="1" t="s">
+      <c r="E102" s="30"/>
+      <c r="F102" s="30"/>
+      <c r="G102" s="30"/>
+    </row>
+    <row r="103" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A103" s="1" t="s">
         <v>128</v>
       </c>
-      <c r="B100" s="1" t="s">
+      <c r="B103" s="1" t="s">
         <v>129</v>
       </c>
-      <c r="C100" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="D100" s="26" t="s">
+      <c r="C103" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D103" s="30" t="s">
         <v>306</v>
       </c>
-      <c r="E100" s="26"/>
-      <c r="F100" s="26"/>
-      <c r="G100" s="26"/>
-    </row>
-    <row r="101" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A101" s="1" t="s">
+      <c r="E103" s="30"/>
+      <c r="F103" s="30"/>
+      <c r="G103" s="30"/>
+    </row>
+    <row r="104" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A104" s="1" t="s">
         <v>759</v>
       </c>
-      <c r="B101" s="1" t="s">
+      <c r="B104" s="1" t="s">
         <v>760</v>
       </c>
-      <c r="C101" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="D101" s="24" t="s">
+      <c r="C104" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D104" s="24" t="s">
         <v>768</v>
       </c>
-      <c r="E101" s="24"/>
-      <c r="F101" s="24"/>
-      <c r="G101" s="24"/>
-    </row>
-    <row r="102" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A102" s="1" t="s">
+      <c r="E104" s="24"/>
+      <c r="F104" s="24"/>
+      <c r="G104" s="24"/>
+    </row>
+    <row r="105" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A105" s="1" t="s">
         <v>758</v>
       </c>
-      <c r="B102" s="1" t="s">
+      <c r="B105" s="1" t="s">
         <v>764</v>
       </c>
-      <c r="C102" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="D102" s="24" t="s">
+      <c r="C105" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D105" s="24" t="s">
         <v>769</v>
-      </c>
-      <c r="E102" s="24"/>
-      <c r="F102" s="24"/>
-      <c r="G102" s="24"/>
-    </row>
-    <row r="103" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A103" s="1" t="s">
-        <v>637</v>
-      </c>
-      <c r="B103" s="1" t="s">
-        <v>638</v>
-      </c>
-      <c r="C103" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="D103" s="26" t="s">
-        <v>305</v>
-      </c>
-      <c r="E103" s="26"/>
-      <c r="F103" s="26"/>
-      <c r="G103" s="26"/>
-    </row>
-    <row r="105" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A105" s="1" t="s">
-        <v>312</v>
-      </c>
-      <c r="B105" s="1" t="s">
-        <v>313</v>
-      </c>
-      <c r="C105" s="1" t="s">
-        <v>143</v>
-      </c>
-      <c r="D105" s="24" t="s">
-        <v>788</v>
       </c>
       <c r="E105" s="24"/>
       <c r="F105" s="24"/>
       <c r="G105" s="24"/>
     </row>
-    <row r="106" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="106" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A106" s="1" t="s">
-        <v>328</v>
+        <v>637</v>
       </c>
       <c r="B106" s="1" t="s">
-        <v>329</v>
+        <v>638</v>
       </c>
       <c r="C106" s="1" t="s">
-        <v>671</v>
-      </c>
-      <c r="D106" s="24" t="s">
-        <v>406</v>
-      </c>
-      <c r="E106" s="24"/>
-      <c r="F106" s="24"/>
-      <c r="G106" s="24"/>
-    </row>
-    <row r="107" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A107" s="1" t="s">
-        <v>675</v>
-      </c>
-      <c r="B107" s="1" t="s">
-        <v>676</v>
-      </c>
-      <c r="C107" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="D107" s="24" t="s">
-        <v>677</v>
-      </c>
-      <c r="E107" s="24"/>
-      <c r="F107" s="24"/>
-      <c r="G107" s="24"/>
-    </row>
-    <row r="108" spans="1:7" x14ac:dyDescent="0.35">
+        <v>43</v>
+      </c>
+      <c r="D106" s="30" t="s">
+        <v>305</v>
+      </c>
+      <c r="E106" s="30"/>
+      <c r="F106" s="30"/>
+      <c r="G106" s="30"/>
+    </row>
+    <row r="108" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A108" s="1" t="s">
-        <v>786</v>
+        <v>312</v>
       </c>
       <c r="B108" s="1" t="s">
-        <v>787</v>
+        <v>313</v>
       </c>
       <c r="C108" s="1" t="s">
         <v>143</v>
       </c>
       <c r="D108" s="24" t="s">
-        <v>406</v>
+        <v>788</v>
       </c>
       <c r="E108" s="24"/>
       <c r="F108" s="24"/>
       <c r="G108" s="24"/>
     </row>
-    <row r="109" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="109" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A109" s="1" t="s">
-        <v>784</v>
+        <v>328</v>
       </c>
       <c r="B109" s="1" t="s">
-        <v>785</v>
+        <v>329</v>
       </c>
       <c r="C109" s="1" t="s">
-        <v>143</v>
+        <v>671</v>
       </c>
       <c r="D109" s="24" t="s">
         <v>406</v>
@@ -8305,343 +8476,401 @@
       <c r="F109" s="24"/>
       <c r="G109" s="24"/>
     </row>
-    <row r="110" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="110" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A110" s="1" t="s">
-        <v>317</v>
+        <v>675</v>
       </c>
       <c r="B110" s="1" t="s">
-        <v>319</v>
+        <v>676</v>
       </c>
       <c r="C110" s="1" t="s">
         <v>43</v>
       </c>
       <c r="D110" s="24" t="s">
-        <v>414</v>
+        <v>677</v>
       </c>
       <c r="E110" s="24"/>
       <c r="F110" s="24"/>
       <c r="G110" s="24"/>
     </row>
-    <row r="111" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="111" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A111" s="1" t="s">
-        <v>643</v>
+        <v>786</v>
       </c>
       <c r="B111" s="1" t="s">
-        <v>644</v>
+        <v>787</v>
       </c>
       <c r="C111" s="1" t="s">
-        <v>43</v>
+        <v>143</v>
       </c>
       <c r="D111" s="24" t="s">
-        <v>681</v>
+        <v>406</v>
       </c>
       <c r="E111" s="24"/>
       <c r="F111" s="24"/>
       <c r="G111" s="24"/>
     </row>
-    <row r="113" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="112" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A112" s="1" t="s">
+        <v>784</v>
+      </c>
+      <c r="B112" s="1" t="s">
+        <v>785</v>
+      </c>
+      <c r="C112" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="D112" s="24" t="s">
+        <v>406</v>
+      </c>
+      <c r="E112" s="24"/>
+      <c r="F112" s="24"/>
+      <c r="G112" s="24"/>
+    </row>
+    <row r="113" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A113" s="1" t="s">
-        <v>321</v>
+        <v>317</v>
       </c>
       <c r="B113" s="1" t="s">
-        <v>323</v>
-      </c>
-      <c r="H113" s="1" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="114" spans="1:8" x14ac:dyDescent="0.35">
+        <v>319</v>
+      </c>
+      <c r="C113" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D113" s="24" t="s">
+        <v>414</v>
+      </c>
+      <c r="E113" s="24"/>
+      <c r="F113" s="24"/>
+      <c r="G113" s="24"/>
+    </row>
+    <row r="114" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A114" s="1" t="s">
-        <v>669</v>
+        <v>643</v>
       </c>
       <c r="B114" s="1" t="s">
-        <v>670</v>
+        <v>644</v>
       </c>
       <c r="C114" s="1" t="s">
         <v>43</v>
       </c>
       <c r="D114" s="24" t="s">
-        <v>685</v>
+        <v>681</v>
       </c>
       <c r="E114" s="24"/>
       <c r="F114" s="24"/>
       <c r="G114" s="24"/>
     </row>
-    <row r="115" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A115" s="1" t="s">
-        <v>325</v>
-      </c>
-      <c r="B115" s="1" t="s">
-        <v>326</v>
-      </c>
-      <c r="C115" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="D115" s="6" t="s">
-        <v>348</v>
-      </c>
-      <c r="E115" s="7" t="s">
-        <v>346</v>
-      </c>
-      <c r="F115" s="7" t="s">
-        <v>347</v>
-      </c>
-      <c r="G115" s="1" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="116" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="116" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A116" s="1" t="s">
-        <v>648</v>
+        <v>321</v>
       </c>
       <c r="B116" s="1" t="s">
-        <v>649</v>
-      </c>
-      <c r="C116" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="D116" s="7" t="s">
-        <v>650</v>
-      </c>
-      <c r="E116" s="7" t="s">
-        <v>651</v>
-      </c>
-      <c r="F116" s="7" t="s">
-        <v>652</v>
-      </c>
-      <c r="G116" s="1" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="117" spans="1:8" x14ac:dyDescent="0.35">
+        <v>323</v>
+      </c>
+      <c r="H116" s="1" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="117" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A117" s="1" t="s">
-        <v>657</v>
+        <v>669</v>
       </c>
       <c r="B117" s="1" t="s">
-        <v>654</v>
+        <v>670</v>
       </c>
       <c r="C117" s="1" t="s">
         <v>43</v>
       </c>
       <c r="D117" s="24" t="s">
-        <v>687</v>
+        <v>685</v>
       </c>
       <c r="E117" s="24"/>
       <c r="F117" s="24"/>
       <c r="G117" s="24"/>
     </row>
-    <row r="118" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="118" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A118" s="1" t="s">
-        <v>658</v>
+        <v>325</v>
       </c>
       <c r="B118" s="1" t="s">
-        <v>655</v>
+        <v>326</v>
       </c>
       <c r="C118" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="D118" s="24" t="s">
-        <v>686</v>
-      </c>
-      <c r="E118" s="24"/>
-      <c r="F118" s="24"/>
-      <c r="G118" s="24"/>
-    </row>
-    <row r="119" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="D118" s="6" t="s">
+        <v>348</v>
+      </c>
+      <c r="E118" s="7" t="s">
+        <v>346</v>
+      </c>
+      <c r="F118" s="7" t="s">
+        <v>347</v>
+      </c>
+      <c r="G118" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="119" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A119" s="1" t="s">
-        <v>659</v>
+        <v>648</v>
       </c>
       <c r="B119" s="1" t="s">
-        <v>656</v>
+        <v>649</v>
       </c>
       <c r="C119" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="D119" s="24" t="s">
-        <v>688</v>
-      </c>
-      <c r="E119" s="24"/>
-      <c r="F119" s="24"/>
-      <c r="G119" s="24"/>
-    </row>
-    <row r="120" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="D119" s="7" t="s">
+        <v>650</v>
+      </c>
+      <c r="E119" s="7" t="s">
+        <v>651</v>
+      </c>
+      <c r="F119" s="7" t="s">
+        <v>652</v>
+      </c>
+      <c r="G119" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="120" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A120" s="1" t="s">
-        <v>752</v>
+        <v>657</v>
       </c>
       <c r="B120" s="1" t="s">
-        <v>753</v>
+        <v>654</v>
       </c>
       <c r="C120" s="1" t="s">
         <v>43</v>
       </c>
       <c r="D120" s="24" t="s">
-        <v>757</v>
+        <v>687</v>
       </c>
       <c r="E120" s="24"/>
       <c r="F120" s="24"/>
       <c r="G120" s="24"/>
     </row>
-    <row r="122" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="121" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A121" s="1" t="s">
+        <v>658</v>
+      </c>
+      <c r="B121" s="1" t="s">
+        <v>655</v>
+      </c>
+      <c r="C121" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D121" s="24" t="s">
+        <v>686</v>
+      </c>
+      <c r="E121" s="24"/>
+      <c r="F121" s="24"/>
+      <c r="G121" s="24"/>
+    </row>
+    <row r="122" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A122" s="1" t="s">
-        <v>797</v>
+        <v>659</v>
       </c>
       <c r="B122" s="1" t="s">
-        <v>798</v>
+        <v>656</v>
       </c>
       <c r="C122" s="1" t="s">
         <v>43</v>
       </c>
       <c r="D122" s="24" t="s">
-        <v>806</v>
+        <v>688</v>
       </c>
       <c r="E122" s="24"/>
       <c r="F122" s="24"/>
       <c r="G122" s="24"/>
     </row>
-    <row r="123" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="123" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A123" s="1" t="s">
+        <v>752</v>
+      </c>
+      <c r="B123" s="1" t="s">
+        <v>753</v>
+      </c>
+      <c r="C123" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D123" s="24" t="s">
+        <v>757</v>
+      </c>
+      <c r="E123" s="24"/>
+      <c r="F123" s="24"/>
+      <c r="G123" s="24"/>
+    </row>
+    <row r="124" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A124" s="1" t="s">
+        <v>831</v>
+      </c>
+      <c r="B124" s="1" t="s">
+        <v>832</v>
+      </c>
+      <c r="C124" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D124" s="24" t="s">
+        <v>837</v>
+      </c>
+      <c r="E124" s="24"/>
+      <c r="F124" s="24"/>
+      <c r="G124" s="24"/>
+    </row>
+    <row r="125" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A125" s="1" t="s">
+        <v>831</v>
+      </c>
+      <c r="B125" s="1" t="s">
+        <v>838</v>
+      </c>
+      <c r="C125" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D125" s="15" t="s">
+        <v>836</v>
+      </c>
+      <c r="E125" s="15"/>
+      <c r="F125" s="15"/>
+      <c r="G125" s="15"/>
+    </row>
+    <row r="127" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A127" s="1" t="s">
+        <v>797</v>
+      </c>
+      <c r="B127" s="1" t="s">
+        <v>798</v>
+      </c>
+      <c r="C127" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D127" s="24" t="s">
+        <v>806</v>
+      </c>
+      <c r="E127" s="24"/>
+      <c r="F127" s="24"/>
+      <c r="G127" s="24"/>
+    </row>
+    <row r="128" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A128" s="1" t="s">
         <v>795</v>
       </c>
-      <c r="B123" s="1" t="s">
+      <c r="B128" s="1" t="s">
         <v>796</v>
       </c>
-      <c r="C123" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="D123" s="25" t="s">
+      <c r="C128" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D128" s="34" t="s">
         <v>805</v>
       </c>
-      <c r="E123" s="25"/>
-      <c r="F123" s="25"/>
-      <c r="G123" s="25"/>
-    </row>
-    <row r="124" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A124" s="1" t="s">
+      <c r="E128" s="34"/>
+      <c r="F128" s="34"/>
+      <c r="G128" s="34"/>
+    </row>
+    <row r="129" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A129" s="1" t="s">
         <v>799</v>
       </c>
-      <c r="B124" s="1" t="s">
+      <c r="B129" s="1" t="s">
         <v>800</v>
       </c>
-      <c r="C124" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="D124" s="25" t="s">
+      <c r="C129" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D129" s="34" t="s">
         <v>804</v>
       </c>
-      <c r="E124" s="25"/>
-      <c r="F124" s="25"/>
-      <c r="G124" s="25"/>
-    </row>
-    <row r="126" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A126" s="1" t="s">
+      <c r="E129" s="34"/>
+      <c r="F129" s="34"/>
+      <c r="G129" s="34"/>
+    </row>
+    <row r="131" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A131" s="1" t="s">
         <v>335</v>
       </c>
-      <c r="B126" s="1" t="s">
+      <c r="B131" s="1" t="s">
         <v>336</v>
       </c>
-      <c r="C126" s="1" t="s">
+      <c r="C131" s="1" t="s">
         <v>359</v>
       </c>
-      <c r="D126" s="6" t="s">
+      <c r="D131" s="6" t="s">
         <v>360</v>
       </c>
-      <c r="E126" s="7" t="s">
+      <c r="E131" s="7" t="s">
         <v>361</v>
       </c>
-      <c r="F126" s="7" t="s">
+      <c r="F131" s="7" t="s">
         <v>362</v>
       </c>
-      <c r="G126" s="1" t="s">
+      <c r="G131" s="1" t="s">
         <v>363</v>
       </c>
     </row>
-    <row r="127" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A127" s="1" t="s">
+    <row r="132" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A132" s="1" t="s">
         <v>337</v>
       </c>
-      <c r="B127" s="1" t="s">
+      <c r="B132" s="1" t="s">
         <v>338</v>
       </c>
-      <c r="H127" s="1" t="s">
+      <c r="H132" s="1" t="s">
         <v>213</v>
       </c>
     </row>
-    <row r="128" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A128" s="1" t="s">
+    <row r="133" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A133" s="1" t="s">
         <v>339</v>
       </c>
-      <c r="B128" s="1" t="s">
+      <c r="B133" s="1" t="s">
         <v>340</v>
       </c>
-      <c r="C128" s="1" t="s">
+      <c r="C133" s="1" t="s">
         <v>364</v>
       </c>
-      <c r="D128" s="7" t="s">
+      <c r="D133" s="7" t="s">
         <v>365</v>
       </c>
-      <c r="E128" s="7" t="s">
+      <c r="E133" s="7" t="s">
         <v>366</v>
       </c>
-      <c r="F128" s="1" t="s">
+      <c r="F133" s="1" t="s">
         <v>367</v>
       </c>
-      <c r="G128" s="1" t="s">
+      <c r="G133" s="1" t="s">
         <v>368</v>
       </c>
     </row>
-    <row r="129" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A129" s="1" t="s">
+    <row r="134" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A134" s="1" t="s">
         <v>341</v>
       </c>
-      <c r="B129" s="1" t="s">
+      <c r="B134" s="1" t="s">
         <v>342</v>
       </c>
-      <c r="H129" s="1" t="s">
+      <c r="H134" s="1" t="s">
         <v>213</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="68">
-    <mergeCell ref="D122:G122"/>
-    <mergeCell ref="D123:G123"/>
-    <mergeCell ref="D124:G124"/>
+  <mergeCells count="71">
+    <mergeCell ref="D103:G103"/>
+    <mergeCell ref="D23:G23"/>
+    <mergeCell ref="D21:G21"/>
+    <mergeCell ref="D22:G22"/>
     <mergeCell ref="D120:G120"/>
+    <mergeCell ref="D32:G32"/>
+    <mergeCell ref="D95:G95"/>
+    <mergeCell ref="D96:G96"/>
+    <mergeCell ref="D33:G33"/>
     <mergeCell ref="D101:G101"/>
-    <mergeCell ref="D102:G102"/>
-    <mergeCell ref="D17:G17"/>
-    <mergeCell ref="D18:G18"/>
-    <mergeCell ref="D63:G63"/>
-    <mergeCell ref="D94:G94"/>
-    <mergeCell ref="D91:G91"/>
-    <mergeCell ref="D27:G27"/>
-    <mergeCell ref="D28:G28"/>
-    <mergeCell ref="D40:G40"/>
-    <mergeCell ref="D32:G32"/>
-    <mergeCell ref="D103:G103"/>
-    <mergeCell ref="D96:G96"/>
-    <mergeCell ref="D99:G99"/>
-    <mergeCell ref="D114:G114"/>
-    <mergeCell ref="D11:G11"/>
-    <mergeCell ref="D13:G13"/>
-    <mergeCell ref="D14:G14"/>
-    <mergeCell ref="D16:G16"/>
-    <mergeCell ref="D15:G15"/>
-    <mergeCell ref="F12:G12"/>
-    <mergeCell ref="D110:G110"/>
-    <mergeCell ref="D29:G29"/>
-    <mergeCell ref="D89:G89"/>
-    <mergeCell ref="D90:G90"/>
-    <mergeCell ref="D88:G88"/>
-    <mergeCell ref="D87:G87"/>
-    <mergeCell ref="D108:G108"/>
-    <mergeCell ref="D109:G109"/>
-    <mergeCell ref="D105:G105"/>
-    <mergeCell ref="D44:G44"/>
     <mergeCell ref="D25:G25"/>
-    <mergeCell ref="D26:G26"/>
-    <mergeCell ref="D19:G19"/>
-    <mergeCell ref="D20:G20"/>
-    <mergeCell ref="D97:G97"/>
+    <mergeCell ref="D31:G31"/>
+    <mergeCell ref="D100:G100"/>
     <mergeCell ref="D24:G24"/>
     <mergeCell ref="A4:C4"/>
     <mergeCell ref="D4:E4"/>
@@ -8655,21 +8884,51 @@
     <mergeCell ref="D8:E8"/>
     <mergeCell ref="A9:C9"/>
     <mergeCell ref="A11:B11"/>
-    <mergeCell ref="D119:G119"/>
-    <mergeCell ref="D106:G106"/>
-    <mergeCell ref="D107:G107"/>
-    <mergeCell ref="D111:G111"/>
-    <mergeCell ref="D100:G100"/>
-    <mergeCell ref="D23:G23"/>
-    <mergeCell ref="D21:G21"/>
-    <mergeCell ref="D22:G22"/>
+    <mergeCell ref="D99:G99"/>
+    <mergeCell ref="D102:G102"/>
     <mergeCell ref="D117:G117"/>
-    <mergeCell ref="D118:G118"/>
+    <mergeCell ref="D11:G11"/>
+    <mergeCell ref="D13:G13"/>
+    <mergeCell ref="D14:G14"/>
+    <mergeCell ref="D16:G16"/>
+    <mergeCell ref="D15:G15"/>
+    <mergeCell ref="F12:G12"/>
+    <mergeCell ref="D113:G113"/>
     <mergeCell ref="D30:G30"/>
     <mergeCell ref="D92:G92"/>
     <mergeCell ref="D93:G93"/>
-    <mergeCell ref="D31:G31"/>
-    <mergeCell ref="D98:G98"/>
+    <mergeCell ref="D91:G91"/>
+    <mergeCell ref="D90:G90"/>
+    <mergeCell ref="D111:G111"/>
+    <mergeCell ref="D17:G17"/>
+    <mergeCell ref="D18:G18"/>
+    <mergeCell ref="D65:G65"/>
+    <mergeCell ref="D97:G97"/>
+    <mergeCell ref="D94:G94"/>
+    <mergeCell ref="D28:G28"/>
+    <mergeCell ref="D29:G29"/>
+    <mergeCell ref="D42:G42"/>
+    <mergeCell ref="D34:G34"/>
+    <mergeCell ref="D46:G46"/>
+    <mergeCell ref="D26:G26"/>
+    <mergeCell ref="D27:G27"/>
+    <mergeCell ref="D19:G19"/>
+    <mergeCell ref="D20:G20"/>
+    <mergeCell ref="D127:G127"/>
+    <mergeCell ref="D128:G128"/>
+    <mergeCell ref="D129:G129"/>
+    <mergeCell ref="D123:G123"/>
+    <mergeCell ref="D104:G104"/>
+    <mergeCell ref="D105:G105"/>
+    <mergeCell ref="D106:G106"/>
+    <mergeCell ref="D112:G112"/>
+    <mergeCell ref="D108:G108"/>
+    <mergeCell ref="D122:G122"/>
+    <mergeCell ref="D109:G109"/>
+    <mergeCell ref="D110:G110"/>
+    <mergeCell ref="D114:G114"/>
+    <mergeCell ref="D121:G121"/>
+    <mergeCell ref="D124:G124"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -8679,18 +8938,18 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A2:H116"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15.6" x14ac:dyDescent="0.35"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A2:H119"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="39.6640625" style="1" customWidth="1"/>
-    <col min="2" max="2" width="38.77734375" style="1" customWidth="1"/>
-    <col min="3" max="3" width="14.77734375" style="1" customWidth="1"/>
-    <col min="4" max="8" width="12.6640625" style="1" customWidth="1"/>
+    <col min="1" max="1" width="39.625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="38.75" style="1" customWidth="1"/>
+    <col min="3" max="3" width="14.75" style="1" customWidth="1"/>
+    <col min="4" max="8" width="12.625" style="1" customWidth="1"/>
     <col min="9" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2" s="4" t="s">
         <v>44</v>
       </c>
@@ -8702,90 +8961,90 @@
       <c r="G2" s="4"/>
       <c r="H2" s="5"/>
     </row>
-    <row r="4" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="24" t="s">
         <v>202</v>
       </c>
       <c r="B4" s="24"/>
       <c r="C4" s="24"/>
-      <c r="D4" s="29" t="s">
+      <c r="D4" s="33" t="s">
         <v>55</v>
       </c>
-      <c r="E4" s="29"/>
+      <c r="E4" s="33"/>
       <c r="F4" s="20" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="5" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="24" t="s">
         <v>422</v>
       </c>
       <c r="B5" s="24"/>
       <c r="C5" s="24"/>
-      <c r="D5" s="27" t="s">
+      <c r="D5" s="31" t="s">
         <v>47</v>
       </c>
-      <c r="E5" s="27"/>
+      <c r="E5" s="31"/>
       <c r="F5" s="10" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="6" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="24"/>
       <c r="B6" s="24"/>
       <c r="C6" s="24"/>
-      <c r="D6" s="28" t="s">
+      <c r="D6" s="32" t="s">
         <v>352</v>
       </c>
-      <c r="E6" s="28"/>
+      <c r="E6" s="32"/>
       <c r="F6" s="13" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="7" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="30"/>
-      <c r="B7" s="30"/>
-      <c r="C7" s="35"/>
-      <c r="D7" s="32" t="s">
+    <row r="7" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="25"/>
+      <c r="B7" s="25"/>
+      <c r="C7" s="37"/>
+      <c r="D7" s="27" t="s">
         <v>51</v>
       </c>
-      <c r="E7" s="32"/>
+      <c r="E7" s="27"/>
       <c r="F7" s="12" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="8" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="30"/>
-      <c r="B8" s="30"/>
-      <c r="C8" s="30"/>
-      <c r="D8" s="33" t="s">
+    <row r="8" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="25"/>
+      <c r="B8" s="25"/>
+      <c r="C8" s="25"/>
+      <c r="D8" s="28" t="s">
         <v>53</v>
       </c>
-      <c r="E8" s="33"/>
+      <c r="E8" s="28"/>
       <c r="F8" s="14" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="9" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="24"/>
       <c r="B9" s="24"/>
       <c r="C9" s="24"/>
     </row>
-    <row r="11" spans="1:8" ht="16.2" x14ac:dyDescent="0.4">
-      <c r="A11" s="34" t="s">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A11" s="29" t="s">
         <v>486</v>
       </c>
-      <c r="B11" s="34"/>
+      <c r="B11" s="29"/>
       <c r="C11" s="21"/>
-      <c r="D11" s="31" t="s">
+      <c r="D11" s="26" t="s">
         <v>580</v>
       </c>
-      <c r="E11" s="31"/>
-      <c r="F11" s="31"/>
-      <c r="G11" s="31"/>
+      <c r="E11" s="26"/>
+      <c r="F11" s="26"/>
+      <c r="G11" s="26"/>
       <c r="H11" s="5"/>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A12" s="19" t="s">
         <v>160</v>
       </c>
@@ -8809,7 +9068,7 @@
       </c>
       <c r="H12" s="2"/>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A13" s="1" t="s">
         <v>171</v>
       </c>
@@ -8819,14 +9078,14 @@
       <c r="C13" s="1" t="s">
         <v>180</v>
       </c>
-      <c r="D13" s="26" t="s">
+      <c r="D13" s="30" t="s">
         <v>178</v>
       </c>
-      <c r="E13" s="26"/>
-      <c r="F13" s="26"/>
-      <c r="G13" s="26"/>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="E13" s="30"/>
+      <c r="F13" s="30"/>
+      <c r="G13" s="30"/>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A14" s="1" t="s">
         <v>375</v>
       </c>
@@ -8836,14 +9095,14 @@
       <c r="C14" s="1" t="s">
         <v>180</v>
       </c>
-      <c r="D14" s="26" t="s">
+      <c r="D14" s="30" t="s">
         <v>178</v>
       </c>
-      <c r="E14" s="26"/>
-      <c r="F14" s="26"/>
-      <c r="G14" s="26"/>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="E14" s="30"/>
+      <c r="F14" s="30"/>
+      <c r="G14" s="30"/>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A15" s="1" t="s">
         <v>401</v>
       </c>
@@ -8860,7 +9119,7 @@
       <c r="F15" s="24"/>
       <c r="G15" s="24"/>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A16" s="1" t="s">
         <v>377</v>
       </c>
@@ -8870,14 +9129,14 @@
       <c r="C16" s="1" t="s">
         <v>180</v>
       </c>
-      <c r="D16" s="25" t="s">
+      <c r="D16" s="34" t="s">
         <v>420</v>
       </c>
-      <c r="E16" s="25"/>
-      <c r="F16" s="25"/>
-      <c r="G16" s="25"/>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="E16" s="34"/>
+      <c r="F16" s="34"/>
+      <c r="G16" s="34"/>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A17" s="1" t="s">
         <v>585</v>
       </c>
@@ -8894,7 +9153,7 @@
       <c r="F17" s="24"/>
       <c r="G17" s="24"/>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A18" s="1" t="s">
         <v>581</v>
       </c>
@@ -8911,7 +9170,7 @@
       <c r="F18" s="24"/>
       <c r="G18" s="24"/>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A19" s="1" t="s">
         <v>614</v>
       </c>
@@ -8928,7 +9187,7 @@
       <c r="F19" s="24"/>
       <c r="G19" s="24"/>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A20" s="1" t="s">
         <v>616</v>
       </c>
@@ -8938,14 +9197,14 @@
       <c r="C20" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="D20" s="26" t="s">
+      <c r="D20" s="30" t="s">
         <v>178</v>
       </c>
-      <c r="E20" s="26"/>
-      <c r="F20" s="26"/>
-      <c r="G20" s="26"/>
-    </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="E20" s="30"/>
+      <c r="F20" s="30"/>
+      <c r="G20" s="30"/>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A21" s="1" t="s">
         <v>717</v>
       </c>
@@ -8962,7 +9221,7 @@
       <c r="F21" s="24"/>
       <c r="G21" s="24"/>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A22" s="1" t="s">
         <v>716</v>
       </c>
@@ -8979,7 +9238,7 @@
       <c r="F22" s="24"/>
       <c r="G22" s="24"/>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A23" s="1" t="s">
         <v>738</v>
       </c>
@@ -8996,7 +9255,7 @@
       <c r="F23" s="24"/>
       <c r="G23" s="24"/>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A24" s="1" t="s">
         <v>793</v>
       </c>
@@ -9013,361 +9272,361 @@
       <c r="F24" s="24"/>
       <c r="G24" s="24"/>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A25" s="1" t="s">
+        <v>826</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>827</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D25" s="24" t="s">
+        <v>825</v>
+      </c>
+      <c r="E25" s="24"/>
+      <c r="F25" s="24"/>
+      <c r="G25" s="24"/>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A26" s="1" t="s">
         <v>172</v>
       </c>
-      <c r="B25" s="1" t="s">
+      <c r="B26" s="1" t="s">
         <v>163</v>
-      </c>
-      <c r="C25" s="1" t="s">
-        <v>143</v>
-      </c>
-      <c r="D25" s="26" t="s">
-        <v>178</v>
-      </c>
-      <c r="E25" s="26"/>
-      <c r="F25" s="26"/>
-      <c r="G25" s="26"/>
-    </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A26" s="1" t="s">
-        <v>173</v>
-      </c>
-      <c r="B26" s="1" t="s">
-        <v>164</v>
       </c>
       <c r="C26" s="1" t="s">
         <v>143</v>
       </c>
-      <c r="D26" s="26" t="s">
-        <v>182</v>
-      </c>
-      <c r="E26" s="26"/>
-      <c r="F26" s="26"/>
-      <c r="G26" s="26"/>
-    </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="D26" s="30" t="s">
+        <v>178</v>
+      </c>
+      <c r="E26" s="30"/>
+      <c r="F26" s="30"/>
+      <c r="G26" s="30"/>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A27" s="1" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>174</v>
+        <v>164</v>
       </c>
       <c r="C27" s="1" t="s">
         <v>143</v>
       </c>
-      <c r="D27" s="24" t="s">
-        <v>408</v>
-      </c>
-      <c r="E27" s="24"/>
-      <c r="F27" s="24"/>
-      <c r="G27" s="24"/>
-    </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="D27" s="30" t="s">
+        <v>182</v>
+      </c>
+      <c r="E27" s="30"/>
+      <c r="F27" s="30"/>
+      <c r="G27" s="30"/>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A28" s="1" t="s">
-        <v>165</v>
+        <v>175</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="C28" s="1" t="s">
         <v>143</v>
       </c>
-      <c r="D28" s="26" t="s">
+      <c r="D28" s="24" t="s">
+        <v>408</v>
+      </c>
+      <c r="E28" s="24"/>
+      <c r="F28" s="24"/>
+      <c r="G28" s="24"/>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A29" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="D29" s="30" t="s">
         <v>178</v>
       </c>
-      <c r="E28" s="26"/>
-      <c r="F28" s="26"/>
-      <c r="G28" s="26"/>
-    </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A29" s="1" t="s">
+      <c r="E29" s="30"/>
+      <c r="F29" s="30"/>
+      <c r="G29" s="30"/>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A30" s="1" t="s">
         <v>166</v>
       </c>
-      <c r="B29" s="1" t="s">
+      <c r="B30" s="1" t="s">
         <v>167</v>
       </c>
-      <c r="C29" s="1" t="s">
+      <c r="C30" s="1" t="s">
         <v>180</v>
       </c>
-      <c r="D29" s="26" t="s">
+      <c r="D30" s="30" t="s">
         <v>423</v>
       </c>
-      <c r="E29" s="26"/>
-      <c r="F29" s="26"/>
-      <c r="G29" s="26"/>
-    </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A30" s="1" t="s">
-        <v>177</v>
-      </c>
-      <c r="B30" s="1" t="s">
-        <v>168</v>
-      </c>
-      <c r="C30" s="1" t="s">
-        <v>181</v>
-      </c>
-      <c r="D30" s="26" t="s">
-        <v>182</v>
-      </c>
-      <c r="E30" s="26"/>
-      <c r="F30" s="26"/>
-      <c r="G30" s="26"/>
-    </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="E30" s="30"/>
+      <c r="F30" s="30"/>
+      <c r="G30" s="30"/>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A31" s="1" t="s">
-        <v>169</v>
+        <v>822</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>170</v>
+        <v>823</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>180</v>
+        <v>43</v>
       </c>
       <c r="D31" s="24" t="s">
-        <v>418</v>
+        <v>824</v>
       </c>
       <c r="E31" s="24"/>
       <c r="F31" s="24"/>
       <c r="G31" s="24"/>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A32" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="C32" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="D32" s="30" t="s">
+        <v>182</v>
+      </c>
+      <c r="E32" s="30"/>
+      <c r="F32" s="30"/>
+      <c r="G32" s="30"/>
+    </row>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A33" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="C33" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="D33" s="24" t="s">
+        <v>418</v>
+      </c>
+      <c r="E33" s="24"/>
+      <c r="F33" s="24"/>
+      <c r="G33" s="24"/>
+    </row>
+    <row r="34" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A34" s="1" t="s">
         <v>750</v>
       </c>
-      <c r="B32" s="1" t="s">
+      <c r="B34" s="1" t="s">
         <v>751</v>
       </c>
-      <c r="C32" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="D32" s="26" t="s">
+      <c r="C34" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D34" s="30" t="s">
         <v>182</v>
       </c>
-      <c r="E32" s="26"/>
-      <c r="F32" s="26"/>
-      <c r="G32" s="26"/>
-    </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A34" s="1" t="s">
+      <c r="E34" s="30"/>
+      <c r="F34" s="30"/>
+      <c r="G34" s="30"/>
+    </row>
+    <row r="36" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A36" s="1" t="s">
         <v>274</v>
       </c>
-      <c r="B34" s="1" t="s">
+      <c r="B36" s="1" t="s">
         <v>275</v>
-      </c>
-      <c r="H34" s="1" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A35" s="1" t="s">
-        <v>276</v>
-      </c>
-      <c r="B35" s="1" t="s">
-        <v>277</v>
-      </c>
-      <c r="H35" s="1" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A36" s="1" t="s">
-        <v>278</v>
-      </c>
-      <c r="B36" s="1" t="s">
-        <v>279</v>
       </c>
       <c r="H36" s="1" t="s">
         <v>183</v>
       </c>
     </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A37" s="1" t="s">
-        <v>280</v>
+        <v>276</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>281</v>
+        <v>277</v>
       </c>
       <c r="H37" s="1" t="s">
         <v>183</v>
       </c>
     </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A38" s="1" t="s">
-        <v>282</v>
+        <v>278</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>283</v>
+        <v>279</v>
       </c>
       <c r="H38" s="1" t="s">
         <v>183</v>
       </c>
     </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A39" s="1" t="s">
-        <v>284</v>
+        <v>280</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>285</v>
+        <v>281</v>
       </c>
       <c r="H39" s="1" t="s">
         <v>183</v>
       </c>
     </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A40" s="1" t="s">
-        <v>286</v>
+        <v>282</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>287</v>
+        <v>283</v>
       </c>
       <c r="H40" s="1" t="s">
         <v>183</v>
       </c>
     </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A41" s="1" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
       <c r="H41" s="1" t="s">
         <v>183</v>
       </c>
     </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A42" s="1" t="s">
+        <v>286</v>
+      </c>
+      <c r="B42" s="1" t="s">
+        <v>287</v>
+      </c>
+      <c r="H42" s="1" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A43" s="1" t="s">
+        <v>288</v>
+      </c>
+      <c r="B43" s="1" t="s">
+        <v>289</v>
+      </c>
+      <c r="H43" s="1" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A44" s="1" t="s">
         <v>290</v>
       </c>
-      <c r="B42" s="1" t="s">
+      <c r="B44" s="1" t="s">
         <v>291</v>
       </c>
-      <c r="C42" s="1" t="s">
+      <c r="C44" s="1" t="s">
         <v>143</v>
       </c>
-      <c r="D42" s="26" t="s">
+      <c r="D44" s="30" t="s">
         <v>423</v>
       </c>
-      <c r="E42" s="26"/>
-      <c r="F42" s="26"/>
-      <c r="G42" s="26"/>
-    </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A44" s="1" t="s">
+      <c r="E44" s="30"/>
+      <c r="F44" s="30"/>
+      <c r="G44" s="30"/>
+    </row>
+    <row r="46" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A46" s="1" t="s">
         <v>292</v>
       </c>
-      <c r="B44" s="1" t="s">
+      <c r="B46" s="1" t="s">
         <v>293</v>
       </c>
-      <c r="C44" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="D44" s="26" t="s">
+      <c r="C46" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D46" s="30" t="s">
         <v>423</v>
       </c>
-      <c r="E44" s="26"/>
-      <c r="F44" s="26"/>
-      <c r="G44" s="26"/>
-    </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A45" s="1" t="s">
+      <c r="E46" s="30"/>
+      <c r="F46" s="30"/>
+      <c r="G46" s="30"/>
+    </row>
+    <row r="47" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A47" s="1" t="s">
         <v>294</v>
       </c>
-      <c r="B45" s="1" t="s">
+      <c r="B47" s="1" t="s">
         <v>295</v>
       </c>
-      <c r="C45" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="D45" s="26" t="s">
+      <c r="C47" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D47" s="30" t="s">
         <v>423</v>
       </c>
-      <c r="E45" s="26"/>
-      <c r="F45" s="26"/>
-      <c r="G45" s="26"/>
-    </row>
-    <row r="46" spans="1:8" ht="15.6" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A46" s="16" t="s">
+      <c r="E47" s="30"/>
+      <c r="F47" s="30"/>
+      <c r="G47" s="30"/>
+    </row>
+    <row r="48" spans="1:8" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A48" s="16" t="s">
         <v>296</v>
       </c>
-      <c r="B46" s="16" t="s">
+      <c r="B48" s="16" t="s">
         <v>297</v>
       </c>
-      <c r="C46" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="D46" s="26" t="s">
+      <c r="C48" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D48" s="30" t="s">
         <v>423</v>
       </c>
-      <c r="E46" s="26"/>
-      <c r="F46" s="26"/>
-      <c r="G46" s="26"/>
-    </row>
-    <row r="47" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A47" s="16" t="s">
+      <c r="E48" s="30"/>
+      <c r="F48" s="30"/>
+      <c r="G48" s="30"/>
+    </row>
+    <row r="49" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A49" s="16" t="s">
         <v>405</v>
       </c>
-      <c r="B47" s="16" t="s">
+      <c r="B49" s="16" t="s">
         <v>404</v>
       </c>
-      <c r="C47" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="D47" s="1" t="s">
+      <c r="C49" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D49" s="1" t="s">
         <v>493</v>
       </c>
-      <c r="E47" s="1" t="s">
+      <c r="E49" s="1" t="s">
         <v>492</v>
       </c>
-      <c r="F47" s="1" t="s">
+      <c r="F49" s="1" t="s">
         <v>490</v>
       </c>
-      <c r="G47" s="1" t="s">
+      <c r="G49" s="1" t="s">
         <v>491</v>
       </c>
     </row>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A48" s="1" t="s">
+    <row r="50" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A50" s="1" t="s">
         <v>298</v>
       </c>
-      <c r="B48" s="1" t="s">
+      <c r="B50" s="1" t="s">
         <v>299</v>
-      </c>
-      <c r="C48" s="1" t="s">
-        <v>143</v>
-      </c>
-      <c r="D48" s="24" t="s">
-        <v>408</v>
-      </c>
-      <c r="E48" s="24"/>
-      <c r="F48" s="24"/>
-      <c r="G48" s="24"/>
-    </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A49" s="1" t="s">
-        <v>300</v>
-      </c>
-      <c r="B49" s="1" t="s">
-        <v>301</v>
-      </c>
-      <c r="C49" s="1" t="s">
-        <v>143</v>
-      </c>
-      <c r="D49" s="24" t="s">
-        <v>408</v>
-      </c>
-      <c r="E49" s="24"/>
-      <c r="F49" s="24"/>
-      <c r="G49" s="24"/>
-    </row>
-    <row r="50" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A50" s="1" t="s">
-        <v>302</v>
-      </c>
-      <c r="B50" s="1" t="s">
-        <v>303</v>
       </c>
       <c r="C50" s="1" t="s">
         <v>143</v>
@@ -9379,114 +9638,114 @@
       <c r="F50" s="24"/>
       <c r="G50" s="24"/>
     </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A51" s="1" t="s">
+        <v>300</v>
+      </c>
+      <c r="B51" s="1" t="s">
+        <v>301</v>
+      </c>
+      <c r="C51" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="D51" s="24" t="s">
+        <v>408</v>
+      </c>
+      <c r="E51" s="24"/>
+      <c r="F51" s="24"/>
+      <c r="G51" s="24"/>
+    </row>
+    <row r="52" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A52" s="1" t="s">
+        <v>302</v>
+      </c>
+      <c r="B52" s="1" t="s">
+        <v>303</v>
+      </c>
+      <c r="C52" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="D52" s="24" t="s">
+        <v>408</v>
+      </c>
+      <c r="E52" s="24"/>
+      <c r="F52" s="24"/>
+      <c r="G52" s="24"/>
+    </row>
+    <row r="54" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A54" s="1" t="s">
         <v>124</v>
       </c>
-      <c r="B52" s="1" t="s">
+      <c r="B54" s="1" t="s">
         <v>125</v>
       </c>
-      <c r="C52" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="D52" s="26" t="s">
+      <c r="C54" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D54" s="30" t="s">
         <v>424</v>
       </c>
-      <c r="E52" s="26"/>
-      <c r="F52" s="26"/>
-      <c r="G52" s="26"/>
-    </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A53" s="1" t="s">
+      <c r="E54" s="30"/>
+      <c r="F54" s="30"/>
+      <c r="G54" s="30"/>
+    </row>
+    <row r="55" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A55" s="1" t="s">
         <v>126</v>
       </c>
-      <c r="B53" s="1" t="s">
+      <c r="B55" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="C53" s="1" t="s">
+      <c r="C55" s="1" t="s">
         <v>180</v>
       </c>
-      <c r="D53" s="26" t="s">
+      <c r="D55" s="30" t="s">
         <v>305</v>
       </c>
-      <c r="E53" s="26"/>
-      <c r="F53" s="26"/>
-      <c r="G53" s="26"/>
-    </row>
-    <row r="54" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A54" s="1" t="s">
+      <c r="E55" s="30"/>
+      <c r="F55" s="30"/>
+      <c r="G55" s="30"/>
+    </row>
+    <row r="56" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A56" s="1" t="s">
         <v>128</v>
       </c>
-      <c r="B54" s="1" t="s">
+      <c r="B56" s="1" t="s">
         <v>129</v>
       </c>
-      <c r="C54" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="D54" s="26" t="s">
+      <c r="C56" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D56" s="30" t="s">
         <v>305</v>
       </c>
-      <c r="E54" s="26"/>
-      <c r="F54" s="26"/>
-      <c r="G54" s="26"/>
-    </row>
-    <row r="56" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A56" s="1" t="s">
+      <c r="E56" s="30"/>
+      <c r="F56" s="30"/>
+      <c r="G56" s="30"/>
+    </row>
+    <row r="58" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A58" s="1" t="s">
         <v>312</v>
       </c>
-      <c r="B56" s="1" t="s">
+      <c r="B58" s="1" t="s">
         <v>313</v>
       </c>
-      <c r="C56" s="1" t="s">
+      <c r="C58" s="1" t="s">
         <v>143</v>
       </c>
-      <c r="D56" s="24" t="s">
+      <c r="D58" s="24" t="s">
         <v>788</v>
       </c>
-      <c r="E56" s="24"/>
-      <c r="F56" s="24"/>
-      <c r="G56" s="24"/>
-    </row>
-    <row r="57" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A57" s="1" t="s">
+      <c r="E58" s="24"/>
+      <c r="F58" s="24"/>
+      <c r="G58" s="24"/>
+    </row>
+    <row r="59" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A59" s="1" t="s">
         <v>315</v>
       </c>
-      <c r="B57" s="1" t="s">
+      <c r="B59" s="1" t="s">
         <v>316</v>
-      </c>
-      <c r="C57" s="1" t="s">
-        <v>143</v>
-      </c>
-      <c r="D57" s="24" t="s">
-        <v>406</v>
-      </c>
-      <c r="E57" s="24"/>
-      <c r="F57" s="24"/>
-      <c r="G57" s="24"/>
-    </row>
-    <row r="58" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A58" s="1" t="s">
-        <v>675</v>
-      </c>
-      <c r="B58" s="1" t="s">
-        <v>676</v>
-      </c>
-      <c r="C58" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="D58" s="26" t="s">
-        <v>423</v>
-      </c>
-      <c r="E58" s="26"/>
-      <c r="F58" s="26"/>
-      <c r="G58" s="26"/>
-    </row>
-    <row r="59" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A59" s="1" t="s">
-        <v>786</v>
-      </c>
-      <c r="B59" s="1" t="s">
-        <v>787</v>
       </c>
       <c r="C59" s="1" t="s">
         <v>143</v>
@@ -9498,451 +9757,451 @@
       <c r="F59" s="24"/>
       <c r="G59" s="24"/>
     </row>
-    <row r="60" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A60" s="1" t="s">
+        <v>675</v>
+      </c>
+      <c r="B60" s="1" t="s">
+        <v>676</v>
+      </c>
+      <c r="C60" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D60" s="30" t="s">
+        <v>423</v>
+      </c>
+      <c r="E60" s="30"/>
+      <c r="F60" s="30"/>
+      <c r="G60" s="30"/>
+    </row>
+    <row r="61" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A61" s="1" t="s">
+        <v>786</v>
+      </c>
+      <c r="B61" s="1" t="s">
+        <v>787</v>
+      </c>
+      <c r="C61" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="D61" s="24" t="s">
+        <v>406</v>
+      </c>
+      <c r="E61" s="24"/>
+      <c r="F61" s="24"/>
+      <c r="G61" s="24"/>
+    </row>
+    <row r="62" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A62" s="1" t="s">
         <v>784</v>
       </c>
-      <c r="B60" s="1" t="s">
+      <c r="B62" s="1" t="s">
         <v>785</v>
       </c>
-      <c r="C60" s="1" t="s">
+      <c r="C62" s="1" t="s">
         <v>143</v>
       </c>
-      <c r="D60" s="24" t="s">
+      <c r="D62" s="24" t="s">
         <v>406</v>
       </c>
-      <c r="E60" s="24"/>
-      <c r="F60" s="24"/>
-      <c r="G60" s="24"/>
-    </row>
-    <row r="61" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A61" s="1" t="s">
+      <c r="E62" s="24"/>
+      <c r="F62" s="24"/>
+      <c r="G62" s="24"/>
+    </row>
+    <row r="63" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A63" s="1" t="s">
         <v>317</v>
       </c>
-      <c r="B61" s="1" t="s">
+      <c r="B63" s="1" t="s">
         <v>319</v>
       </c>
-      <c r="C61" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="D61" s="26" t="s">
+      <c r="C63" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D63" s="30" t="s">
         <v>423</v>
       </c>
-      <c r="E61" s="26"/>
-      <c r="F61" s="26"/>
-      <c r="G61" s="26"/>
-    </row>
-    <row r="62" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A62" s="1" t="s">
+      <c r="E63" s="30"/>
+      <c r="F63" s="30"/>
+      <c r="G63" s="30"/>
+    </row>
+    <row r="64" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A64" s="1" t="s">
         <v>643</v>
       </c>
-      <c r="B62" s="1" t="s">
+      <c r="B64" s="1" t="s">
         <v>644</v>
       </c>
-      <c r="C62" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="D62" s="26" t="s">
+      <c r="C64" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D64" s="30" t="s">
         <v>423</v>
       </c>
-      <c r="E62" s="26"/>
-      <c r="F62" s="26"/>
-      <c r="G62" s="26"/>
-    </row>
-    <row r="64" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A64" s="1" t="s">
+      <c r="E64" s="30"/>
+      <c r="F64" s="30"/>
+      <c r="G64" s="30"/>
+    </row>
+    <row r="66" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A66" s="1" t="s">
         <v>321</v>
       </c>
-      <c r="B64" s="1" t="s">
+      <c r="B66" s="1" t="s">
         <v>323</v>
       </c>
-      <c r="C64" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="D64" s="26" t="s">
+      <c r="C66" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D66" s="30" t="s">
         <v>423</v>
       </c>
-      <c r="E64" s="26"/>
-      <c r="F64" s="26"/>
-      <c r="G64" s="26"/>
-    </row>
-    <row r="65" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A65" s="1" t="s">
+      <c r="E66" s="30"/>
+      <c r="F66" s="30"/>
+      <c r="G66" s="30"/>
+    </row>
+    <row r="67" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A67" s="1" t="s">
         <v>325</v>
       </c>
-      <c r="B65" s="1" t="s">
+      <c r="B67" s="1" t="s">
         <v>326</v>
       </c>
-      <c r="C65" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="D65" s="26" t="s">
+      <c r="C67" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D67" s="30" t="s">
         <v>423</v>
       </c>
-      <c r="E65" s="26"/>
-      <c r="F65" s="26"/>
-      <c r="G65" s="26"/>
-    </row>
-    <row r="67" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A67" s="1" t="s">
+      <c r="E67" s="30"/>
+      <c r="F67" s="30"/>
+      <c r="G67" s="30"/>
+    </row>
+    <row r="69" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A69" s="1" t="s">
         <v>593</v>
       </c>
-      <c r="B67" s="1" t="s">
+      <c r="B69" s="1" t="s">
         <v>592</v>
       </c>
-      <c r="C67" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="D67" s="24" t="s">
+      <c r="C69" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D69" s="24" t="s">
         <v>406</v>
-      </c>
-      <c r="E67" s="24"/>
-      <c r="F67" s="24"/>
-      <c r="G67" s="24"/>
-    </row>
-    <row r="68" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A68" s="1" t="s">
-        <v>797</v>
-      </c>
-      <c r="B68" s="1" t="s">
-        <v>798</v>
-      </c>
-      <c r="C68" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="D68" s="24" t="s">
-        <v>801</v>
-      </c>
-      <c r="E68" s="24"/>
-      <c r="F68" s="24"/>
-      <c r="G68" s="24"/>
-    </row>
-    <row r="69" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A69" s="1" t="s">
-        <v>795</v>
-      </c>
-      <c r="B69" s="1" t="s">
-        <v>796</v>
-      </c>
-      <c r="C69" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="D69" s="24" t="s">
-        <v>802</v>
       </c>
       <c r="E69" s="24"/>
       <c r="F69" s="24"/>
       <c r="G69" s="24"/>
     </row>
-    <row r="70" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A70" s="1" t="s">
-        <v>799</v>
+        <v>797</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>800</v>
+        <v>798</v>
       </c>
       <c r="C70" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="D70" s="25" t="s">
-        <v>803</v>
-      </c>
-      <c r="E70" s="25"/>
-      <c r="F70" s="25"/>
-      <c r="G70" s="25"/>
-    </row>
-    <row r="71" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="D70" s="24" t="s">
+        <v>801</v>
+      </c>
+      <c r="E70" s="24"/>
+      <c r="F70" s="24"/>
+      <c r="G70" s="24"/>
+    </row>
+    <row r="71" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A71" s="1" t="s">
-        <v>425</v>
+        <v>795</v>
       </c>
       <c r="B71" s="1" t="s">
-        <v>426</v>
+        <v>796</v>
       </c>
       <c r="C71" s="1" t="s">
         <v>43</v>
       </c>
       <c r="D71" s="24" t="s">
-        <v>601</v>
+        <v>802</v>
       </c>
       <c r="E71" s="24"/>
       <c r="F71" s="24"/>
       <c r="G71" s="24"/>
     </row>
-    <row r="72" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A72" s="1" t="s">
-        <v>427</v>
+        <v>799</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>428</v>
+        <v>800</v>
       </c>
       <c r="C72" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="D72" s="24" t="s">
-        <v>600</v>
-      </c>
-      <c r="E72" s="24"/>
-      <c r="F72" s="24"/>
-      <c r="G72" s="24"/>
-    </row>
-    <row r="73" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="D72" s="34" t="s">
+        <v>803</v>
+      </c>
+      <c r="E72" s="34"/>
+      <c r="F72" s="34"/>
+      <c r="G72" s="34"/>
+    </row>
+    <row r="73" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A73" s="1" t="s">
-        <v>429</v>
+        <v>425</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>430</v>
+        <v>426</v>
       </c>
       <c r="C73" s="1" t="s">
         <v>43</v>
       </c>
       <c r="D73" s="24" t="s">
-        <v>598</v>
+        <v>601</v>
       </c>
       <c r="E73" s="24"/>
       <c r="F73" s="24"/>
       <c r="G73" s="24"/>
     </row>
-    <row r="74" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A74" s="1" t="s">
-        <v>431</v>
+        <v>427</v>
       </c>
       <c r="B74" s="1" t="s">
-        <v>432</v>
+        <v>428</v>
       </c>
       <c r="C74" s="1" t="s">
         <v>43</v>
       </c>
       <c r="D74" s="24" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="E74" s="24"/>
       <c r="F74" s="24"/>
       <c r="G74" s="24"/>
     </row>
-    <row r="75" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A75" s="1" t="s">
-        <v>433</v>
+        <v>429</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>434</v>
+        <v>430</v>
       </c>
       <c r="C75" s="1" t="s">
         <v>43</v>
       </c>
       <c r="D75" s="24" t="s">
-        <v>602</v>
+        <v>598</v>
       </c>
       <c r="E75" s="24"/>
       <c r="F75" s="24"/>
       <c r="G75" s="24"/>
     </row>
-    <row r="77" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A76" s="1" t="s">
+        <v>431</v>
+      </c>
+      <c r="B76" s="1" t="s">
+        <v>432</v>
+      </c>
+      <c r="C76" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D76" s="24" t="s">
+        <v>599</v>
+      </c>
+      <c r="E76" s="24"/>
+      <c r="F76" s="24"/>
+      <c r="G76" s="24"/>
+    </row>
+    <row r="77" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A77" s="1" t="s">
+        <v>433</v>
+      </c>
+      <c r="B77" s="1" t="s">
+        <v>434</v>
+      </c>
+      <c r="C77" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D77" s="24" t="s">
+        <v>602</v>
+      </c>
+      <c r="E77" s="24"/>
+      <c r="F77" s="24"/>
+      <c r="G77" s="24"/>
+    </row>
+    <row r="79" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A79" s="1" t="s">
         <v>735</v>
       </c>
-      <c r="B77" s="1" t="s">
+      <c r="B79" s="1" t="s">
         <v>736</v>
       </c>
-      <c r="C77" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="D77" s="25" t="s">
+      <c r="C79" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D79" s="34" t="s">
         <v>737</v>
       </c>
-      <c r="E77" s="25"/>
-      <c r="F77" s="25"/>
-      <c r="G77" s="25"/>
-    </row>
-    <row r="78" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A78" s="1" t="s">
+      <c r="E79" s="34"/>
+      <c r="F79" s="34"/>
+      <c r="G79" s="34"/>
+    </row>
+    <row r="80" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A80" s="1" t="s">
         <v>435</v>
       </c>
-      <c r="B78" s="1" t="s">
+      <c r="B80" s="1" t="s">
         <v>436</v>
-      </c>
-      <c r="H78" s="1" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="79" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A79" s="1" t="s">
-        <v>437</v>
-      </c>
-      <c r="B79" s="1" t="s">
-        <v>438</v>
-      </c>
-      <c r="H79" s="1" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="80" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A80" s="1" t="s">
-        <v>439</v>
-      </c>
-      <c r="B80" s="1" t="s">
-        <v>440</v>
       </c>
       <c r="H80" s="1" t="s">
         <v>183</v>
       </c>
     </row>
-    <row r="81" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A81" s="1" t="s">
-        <v>441</v>
+        <v>437</v>
       </c>
       <c r="B81" s="1" t="s">
-        <v>442</v>
+        <v>438</v>
       </c>
       <c r="H81" s="1" t="s">
         <v>183</v>
       </c>
     </row>
-    <row r="82" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A82" s="1" t="s">
-        <v>443</v>
+        <v>439</v>
       </c>
       <c r="B82" s="1" t="s">
-        <v>444</v>
+        <v>440</v>
       </c>
       <c r="H82" s="1" t="s">
         <v>183</v>
       </c>
     </row>
-    <row r="83" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A83" s="1" t="s">
+        <v>441</v>
+      </c>
+      <c r="B83" s="1" t="s">
+        <v>442</v>
+      </c>
+      <c r="H83" s="1" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="84" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A84" s="1" t="s">
+        <v>443</v>
+      </c>
+      <c r="B84" s="1" t="s">
+        <v>444</v>
+      </c>
+      <c r="H84" s="1" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="85" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A85" s="1" t="s">
         <v>445</v>
       </c>
-      <c r="B83" s="1" t="s">
+      <c r="B85" s="1" t="s">
         <v>446</v>
       </c>
-      <c r="C83" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="D83" s="24" t="s">
+      <c r="C85" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D85" s="24" t="s">
         <v>594</v>
       </c>
-      <c r="E83" s="24"/>
-      <c r="F83" s="24"/>
-      <c r="G83" s="24"/>
-    </row>
-    <row r="84" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A84" s="1" t="s">
+      <c r="E85" s="24"/>
+      <c r="F85" s="24"/>
+      <c r="G85" s="24"/>
+    </row>
+    <row r="86" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A86" s="1" t="s">
         <v>595</v>
       </c>
-      <c r="B84" s="1" t="s">
+      <c r="B86" s="1" t="s">
         <v>596</v>
       </c>
-      <c r="C84" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="D84" s="24" t="s">
+      <c r="C86" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D86" s="24" t="s">
         <v>597</v>
       </c>
-      <c r="E84" s="24"/>
-      <c r="F84" s="24"/>
-      <c r="G84" s="24"/>
-    </row>
-    <row r="85" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A85" s="1" t="s">
+      <c r="E86" s="24"/>
+      <c r="F86" s="24"/>
+      <c r="G86" s="24"/>
+    </row>
+    <row r="87" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A87" s="1" t="s">
         <v>447</v>
       </c>
-      <c r="B85" s="1" t="s">
+      <c r="B87" s="1" t="s">
         <v>448</v>
-      </c>
-      <c r="H85" s="1" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="86" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A86" s="1" t="s">
-        <v>449</v>
-      </c>
-      <c r="B86" s="1" t="s">
-        <v>450</v>
-      </c>
-      <c r="H86" s="1" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="87" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A87" s="1" t="s">
-        <v>451</v>
-      </c>
-      <c r="B87" s="1" t="s">
-        <v>452</v>
       </c>
       <c r="H87" s="1" t="s">
         <v>183</v>
       </c>
     </row>
-    <row r="88" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A88" s="1" t="s">
-        <v>453</v>
+        <v>449</v>
       </c>
       <c r="B88" s="1" t="s">
-        <v>454</v>
+        <v>450</v>
       </c>
       <c r="H88" s="1" t="s">
         <v>183</v>
       </c>
     </row>
-    <row r="89" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A89" s="1" t="s">
+        <v>451</v>
+      </c>
+      <c r="B89" s="1" t="s">
+        <v>452</v>
+      </c>
+      <c r="H89" s="1" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="90" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A90" s="1" t="s">
+        <v>453</v>
+      </c>
+      <c r="B90" s="1" t="s">
+        <v>454</v>
+      </c>
+      <c r="H90" s="1" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="91" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A91" s="1" t="s">
         <v>770</v>
       </c>
-      <c r="B89" s="1" t="s">
+      <c r="B91" s="1" t="s">
         <v>774</v>
       </c>
-      <c r="C89" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="D89" s="24" t="s">
+      <c r="C91" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D91" s="24" t="s">
         <v>586</v>
-      </c>
-      <c r="E89" s="24"/>
-      <c r="F89" s="24"/>
-      <c r="G89" s="24"/>
-    </row>
-    <row r="90" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A90" s="1" t="s">
-        <v>772</v>
-      </c>
-      <c r="B90" s="1" t="s">
-        <v>773</v>
-      </c>
-      <c r="C90" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="D90" s="24" t="s">
-        <v>587</v>
-      </c>
-      <c r="E90" s="24"/>
-      <c r="F90" s="24"/>
-      <c r="G90" s="24"/>
-    </row>
-    <row r="91" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A91" s="1" t="s">
-        <v>775</v>
-      </c>
-      <c r="B91" s="1" t="s">
-        <v>776</v>
-      </c>
-      <c r="C91" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="D91" s="24" t="s">
-        <v>588</v>
       </c>
       <c r="E91" s="24"/>
       <c r="F91" s="24"/>
       <c r="G91" s="24"/>
     </row>
-    <row r="92" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A92" s="1" t="s">
-        <v>777</v>
+        <v>772</v>
       </c>
       <c r="B92" s="1" t="s">
-        <v>778</v>
+        <v>773</v>
       </c>
       <c r="C92" s="1" t="s">
         <v>43</v>
@@ -9954,390 +10213,444 @@
       <c r="F92" s="24"/>
       <c r="G92" s="24"/>
     </row>
-    <row r="93" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A93" s="1" t="s">
-        <v>771</v>
+        <v>775</v>
       </c>
       <c r="B93" s="1" t="s">
-        <v>779</v>
+        <v>776</v>
       </c>
       <c r="C93" s="1" t="s">
         <v>43</v>
       </c>
       <c r="D93" s="24" t="s">
-        <v>783</v>
+        <v>588</v>
       </c>
       <c r="E93" s="24"/>
       <c r="F93" s="24"/>
       <c r="G93" s="24"/>
     </row>
-    <row r="94" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A94" s="1" t="s">
-        <v>780</v>
+        <v>777</v>
       </c>
       <c r="B94" s="1" t="s">
-        <v>781</v>
+        <v>778</v>
       </c>
       <c r="C94" s="1" t="s">
         <v>43</v>
       </c>
       <c r="D94" s="24" t="s">
-        <v>782</v>
+        <v>587</v>
       </c>
       <c r="E94" s="24"/>
       <c r="F94" s="24"/>
       <c r="G94" s="24"/>
     </row>
-    <row r="96" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A95" s="1" t="s">
+        <v>771</v>
+      </c>
+      <c r="B95" s="1" t="s">
+        <v>779</v>
+      </c>
+      <c r="C95" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D95" s="24" t="s">
+        <v>783</v>
+      </c>
+      <c r="E95" s="24"/>
+      <c r="F95" s="24"/>
+      <c r="G95" s="24"/>
+    </row>
+    <row r="96" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A96" s="1" t="s">
+        <v>780</v>
+      </c>
+      <c r="B96" s="1" t="s">
+        <v>781</v>
+      </c>
+      <c r="C96" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D96" s="24" t="s">
+        <v>782</v>
+      </c>
+      <c r="E96" s="24"/>
+      <c r="F96" s="24"/>
+      <c r="G96" s="24"/>
+    </row>
+    <row r="97" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A97" s="1" t="s">
+        <v>819</v>
+      </c>
+      <c r="B97" s="1" t="s">
+        <v>820</v>
+      </c>
+      <c r="C97" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D97" s="24" t="s">
+        <v>821</v>
+      </c>
+      <c r="E97" s="24"/>
+      <c r="F97" s="24"/>
+      <c r="G97" s="24"/>
+    </row>
+    <row r="99" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A99" s="1" t="s">
         <v>455</v>
       </c>
-      <c r="B96" s="1" t="s">
+      <c r="B99" s="1" t="s">
         <v>456</v>
-      </c>
-      <c r="H96" s="1" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="97" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A97" s="1" t="s">
-        <v>457</v>
-      </c>
-      <c r="B97" s="1" t="s">
-        <v>458</v>
-      </c>
-      <c r="H97" s="1" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="98" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A98" s="1" t="s">
-        <v>700</v>
-      </c>
-      <c r="B98" s="1" t="s">
-        <v>701</v>
-      </c>
-      <c r="H98" s="1" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="99" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A99" s="1" t="s">
-        <v>699</v>
-      </c>
-      <c r="B99" s="1" t="s">
-        <v>698</v>
       </c>
       <c r="H99" s="1" t="s">
         <v>183</v>
       </c>
     </row>
-    <row r="100" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A100" s="1" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="B100" s="1" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="H100" s="1" t="s">
         <v>183</v>
       </c>
     </row>
-    <row r="101" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A101" s="1" t="s">
+        <v>700</v>
+      </c>
+      <c r="B101" s="1" t="s">
+        <v>701</v>
+      </c>
+      <c r="H101" s="1" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="102" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A102" s="1" t="s">
+        <v>699</v>
+      </c>
+      <c r="B102" s="1" t="s">
+        <v>698</v>
+      </c>
+      <c r="H102" s="1" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="103" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A103" s="1" t="s">
+        <v>459</v>
+      </c>
+      <c r="B103" s="1" t="s">
+        <v>460</v>
+      </c>
+      <c r="H103" s="1" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="104" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A104" s="1" t="s">
         <v>461</v>
       </c>
-      <c r="B101" s="1" t="s">
+      <c r="B104" s="1" t="s">
         <v>462</v>
       </c>
-      <c r="C101" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="D101" s="24" t="s">
+      <c r="C104" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D104" s="24" t="s">
         <v>406</v>
       </c>
-      <c r="E101" s="24"/>
-      <c r="F101" s="24"/>
-      <c r="G101" s="24"/>
-    </row>
-    <row r="102" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A102" s="1" t="s">
+      <c r="E104" s="24"/>
+      <c r="F104" s="24"/>
+      <c r="G104" s="24"/>
+    </row>
+    <row r="105" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A105" s="1" t="s">
         <v>463</v>
       </c>
-      <c r="B102" s="1" t="s">
+      <c r="B105" s="1" t="s">
         <v>464</v>
       </c>
-      <c r="C102" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="D102" s="25" t="s">
+      <c r="C105" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D105" s="34" t="s">
         <v>810</v>
       </c>
-      <c r="E102" s="25"/>
-      <c r="F102" s="25"/>
-      <c r="G102" s="25"/>
-    </row>
-    <row r="104" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A104" s="1" t="s">
+      <c r="E105" s="34"/>
+      <c r="F105" s="34"/>
+      <c r="G105" s="34"/>
+    </row>
+    <row r="107" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A107" s="1" t="s">
         <v>478</v>
       </c>
-      <c r="B104" s="1" t="s">
+      <c r="B107" s="1" t="s">
         <v>479</v>
       </c>
-      <c r="C104" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="D104" s="37" t="s">
+      <c r="C107" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D107" s="35" t="s">
         <v>496</v>
       </c>
-      <c r="E104" s="37" t="s">
+      <c r="E107" s="35" t="s">
         <v>495</v>
       </c>
-      <c r="F104" s="37" t="s">
+      <c r="F107" s="35" t="s">
         <v>309</v>
       </c>
-      <c r="G104" s="37" t="s">
+      <c r="G107" s="35" t="s">
         <v>491</v>
       </c>
     </row>
-    <row r="105" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A105" s="16" t="s">
+    <row r="108" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A108" s="16" t="s">
         <v>465</v>
       </c>
-      <c r="B105" s="16" t="s">
+      <c r="B108" s="16" t="s">
         <v>466</v>
       </c>
-      <c r="H105" s="1" t="s">
+      <c r="H108" s="1" t="s">
         <v>183</v>
       </c>
     </row>
-    <row r="106" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A106" s="16" t="s">
+    <row r="109" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A109" s="16" t="s">
         <v>467</v>
       </c>
-      <c r="B106" s="16" t="s">
+      <c r="B109" s="16" t="s">
         <v>468</v>
       </c>
-      <c r="C106" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="D106" s="24" t="s">
+      <c r="C109" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D109" s="24" t="s">
         <v>601</v>
-      </c>
-      <c r="E106" s="24"/>
-      <c r="F106" s="24"/>
-      <c r="G106" s="24"/>
-    </row>
-    <row r="107" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A107" s="16" t="s">
-        <v>469</v>
-      </c>
-      <c r="B107" s="16" t="s">
-        <v>470</v>
-      </c>
-      <c r="C107" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="D107" s="24" t="s">
-        <v>600</v>
-      </c>
-      <c r="E107" s="24"/>
-      <c r="F107" s="24"/>
-      <c r="G107" s="24"/>
-    </row>
-    <row r="108" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A108" s="16" t="s">
-        <v>471</v>
-      </c>
-      <c r="B108" s="16" t="s">
-        <v>472</v>
-      </c>
-      <c r="C108" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="D108" s="24" t="s">
-        <v>598</v>
-      </c>
-      <c r="E108" s="24"/>
-      <c r="F108" s="24"/>
-      <c r="G108" s="24"/>
-    </row>
-    <row r="109" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A109" s="16" t="s">
-        <v>473</v>
-      </c>
-      <c r="B109" s="16" t="s">
-        <v>474</v>
-      </c>
-      <c r="C109" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="D109" s="24" t="s">
-        <v>599</v>
       </c>
       <c r="E109" s="24"/>
       <c r="F109" s="24"/>
       <c r="G109" s="24"/>
     </row>
-    <row r="110" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="110" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A110" s="16" t="s">
-        <v>475</v>
+        <v>469</v>
       </c>
       <c r="B110" s="16" t="s">
-        <v>476</v>
-      </c>
-      <c r="H110" s="1" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="111" spans="1:8" x14ac:dyDescent="0.35">
+        <v>470</v>
+      </c>
+      <c r="C110" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D110" s="24" t="s">
+        <v>600</v>
+      </c>
+      <c r="E110" s="24"/>
+      <c r="F110" s="24"/>
+      <c r="G110" s="24"/>
+    </row>
+    <row r="111" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A111" s="16" t="s">
-        <v>589</v>
+        <v>471</v>
       </c>
       <c r="B111" s="16" t="s">
-        <v>477</v>
+        <v>472</v>
       </c>
       <c r="C111" s="1" t="s">
         <v>43</v>
       </c>
       <c r="D111" s="24" t="s">
-        <v>590</v>
+        <v>598</v>
       </c>
       <c r="E111" s="24"/>
       <c r="F111" s="24"/>
       <c r="G111" s="24"/>
     </row>
-    <row r="112" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="112" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A112" s="16" t="s">
+        <v>473</v>
+      </c>
+      <c r="B112" s="16" t="s">
+        <v>474</v>
+      </c>
+      <c r="C112" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D112" s="24" t="s">
+        <v>599</v>
+      </c>
+      <c r="E112" s="24"/>
+      <c r="F112" s="24"/>
+      <c r="G112" s="24"/>
+    </row>
+    <row r="113" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A113" s="16" t="s">
+        <v>475</v>
+      </c>
+      <c r="B113" s="16" t="s">
+        <v>476</v>
+      </c>
+      <c r="H113" s="1" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="114" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A114" s="16" t="s">
+        <v>589</v>
+      </c>
+      <c r="B114" s="16" t="s">
+        <v>477</v>
+      </c>
+      <c r="C114" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D114" s="24" t="s">
+        <v>590</v>
+      </c>
+      <c r="E114" s="24"/>
+      <c r="F114" s="24"/>
+      <c r="G114" s="24"/>
+    </row>
+    <row r="115" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A115" s="16" t="s">
         <v>603</v>
       </c>
-      <c r="B112" s="16" t="s">
+      <c r="B115" s="16" t="s">
         <v>604</v>
       </c>
-      <c r="H112" s="1" t="s">
+      <c r="H115" s="1" t="s">
         <v>183</v>
       </c>
     </row>
-    <row r="114" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A114" s="1" t="s">
+    <row r="117" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A117" s="1" t="s">
         <v>480</v>
       </c>
-      <c r="B114" s="1" t="s">
+      <c r="B117" s="1" t="s">
         <v>481</v>
       </c>
-      <c r="H114" s="1" t="s">
+      <c r="H117" s="1" t="s">
         <v>183</v>
       </c>
     </row>
-    <row r="115" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A115" s="1" t="s">
+    <row r="118" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A118" s="1" t="s">
         <v>482</v>
       </c>
-      <c r="B115" s="1" t="s">
+      <c r="B118" s="1" t="s">
         <v>483</v>
       </c>
-      <c r="C115" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="D115" s="24" t="s">
+      <c r="C118" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D118" s="24" t="s">
         <v>809</v>
       </c>
-      <c r="E115" s="24"/>
-      <c r="F115" s="24"/>
-      <c r="G115" s="24"/>
-    </row>
-    <row r="116" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A116" s="1" t="s">
+      <c r="E118" s="24"/>
+      <c r="F118" s="24"/>
+      <c r="G118" s="24"/>
+    </row>
+    <row r="119" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A119" s="1" t="s">
         <v>484</v>
       </c>
-      <c r="B116" s="1" t="s">
+      <c r="B119" s="1" t="s">
         <v>485</v>
       </c>
-      <c r="H116" s="1" t="s">
+      <c r="H119" s="1" t="s">
         <v>183</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="79">
-    <mergeCell ref="D115:G115"/>
-    <mergeCell ref="D102:G102"/>
-    <mergeCell ref="A11:B11"/>
-    <mergeCell ref="D11:G11"/>
-    <mergeCell ref="D24:G24"/>
-    <mergeCell ref="D68:G68"/>
+  <mergeCells count="82">
+    <mergeCell ref="D114:G114"/>
+    <mergeCell ref="D92:G92"/>
+    <mergeCell ref="D93:G93"/>
+    <mergeCell ref="D104:G104"/>
+    <mergeCell ref="D107:G107"/>
+    <mergeCell ref="D109:G109"/>
+    <mergeCell ref="D110:G110"/>
+    <mergeCell ref="D111:G111"/>
+    <mergeCell ref="D112:G112"/>
+    <mergeCell ref="D94:G94"/>
+    <mergeCell ref="D95:G95"/>
+    <mergeCell ref="D96:G96"/>
+    <mergeCell ref="D97:G97"/>
+    <mergeCell ref="D59:G59"/>
+    <mergeCell ref="D58:G58"/>
     <mergeCell ref="D69:G69"/>
-    <mergeCell ref="A7:C7"/>
-    <mergeCell ref="D7:E7"/>
-    <mergeCell ref="A8:C8"/>
-    <mergeCell ref="D8:E8"/>
-    <mergeCell ref="A9:C9"/>
+    <mergeCell ref="D48:G48"/>
+    <mergeCell ref="D50:G50"/>
+    <mergeCell ref="D51:G51"/>
+    <mergeCell ref="D52:G52"/>
+    <mergeCell ref="D54:G54"/>
+    <mergeCell ref="D73:G73"/>
+    <mergeCell ref="D61:G61"/>
+    <mergeCell ref="D62:G62"/>
+    <mergeCell ref="D64:G64"/>
+    <mergeCell ref="D60:G60"/>
+    <mergeCell ref="D72:G72"/>
+    <mergeCell ref="D86:G86"/>
+    <mergeCell ref="D67:G67"/>
+    <mergeCell ref="D66:G66"/>
+    <mergeCell ref="D44:G44"/>
+    <mergeCell ref="D47:G47"/>
+    <mergeCell ref="D46:G46"/>
+    <mergeCell ref="D79:G79"/>
+    <mergeCell ref="D85:G85"/>
+    <mergeCell ref="D75:G75"/>
+    <mergeCell ref="D74:G74"/>
+    <mergeCell ref="D76:G76"/>
+    <mergeCell ref="D77:G77"/>
+    <mergeCell ref="D55:G55"/>
+    <mergeCell ref="D56:G56"/>
+    <mergeCell ref="D63:G63"/>
+    <mergeCell ref="D23:G23"/>
+    <mergeCell ref="D22:G22"/>
+    <mergeCell ref="D21:G21"/>
+    <mergeCell ref="D34:G34"/>
+    <mergeCell ref="D20:G20"/>
+    <mergeCell ref="D27:G27"/>
+    <mergeCell ref="D28:G28"/>
+    <mergeCell ref="D29:G29"/>
+    <mergeCell ref="D30:G30"/>
+    <mergeCell ref="D32:G32"/>
+    <mergeCell ref="D33:G33"/>
+    <mergeCell ref="D31:G31"/>
+    <mergeCell ref="D25:G25"/>
     <mergeCell ref="A4:C4"/>
     <mergeCell ref="D4:E4"/>
     <mergeCell ref="A5:C5"/>
     <mergeCell ref="D5:E5"/>
     <mergeCell ref="A6:C6"/>
     <mergeCell ref="D6:E6"/>
-    <mergeCell ref="D89:G89"/>
+    <mergeCell ref="A7:C7"/>
+    <mergeCell ref="D7:E7"/>
+    <mergeCell ref="A8:C8"/>
+    <mergeCell ref="D8:E8"/>
+    <mergeCell ref="A9:C9"/>
+    <mergeCell ref="D118:G118"/>
+    <mergeCell ref="D105:G105"/>
+    <mergeCell ref="A11:B11"/>
+    <mergeCell ref="D11:G11"/>
+    <mergeCell ref="D24:G24"/>
+    <mergeCell ref="D70:G70"/>
+    <mergeCell ref="D71:G71"/>
+    <mergeCell ref="D91:G91"/>
     <mergeCell ref="D13:G13"/>
     <mergeCell ref="D14:G14"/>
     <mergeCell ref="D15:G15"/>
     <mergeCell ref="D16:G16"/>
-    <mergeCell ref="D25:G25"/>
+    <mergeCell ref="D26:G26"/>
     <mergeCell ref="D17:G17"/>
     <mergeCell ref="D18:G18"/>
     <mergeCell ref="D19:G19"/>
-    <mergeCell ref="D23:G23"/>
-    <mergeCell ref="D22:G22"/>
-    <mergeCell ref="D21:G21"/>
-    <mergeCell ref="D32:G32"/>
-    <mergeCell ref="D20:G20"/>
-    <mergeCell ref="D26:G26"/>
-    <mergeCell ref="D70:G70"/>
-    <mergeCell ref="D84:G84"/>
-    <mergeCell ref="D65:G65"/>
-    <mergeCell ref="D64:G64"/>
-    <mergeCell ref="D42:G42"/>
-    <mergeCell ref="D45:G45"/>
-    <mergeCell ref="D44:G44"/>
-    <mergeCell ref="D77:G77"/>
-    <mergeCell ref="D83:G83"/>
-    <mergeCell ref="D27:G27"/>
-    <mergeCell ref="D28:G28"/>
-    <mergeCell ref="D29:G29"/>
-    <mergeCell ref="D30:G30"/>
-    <mergeCell ref="D31:G31"/>
-    <mergeCell ref="D73:G73"/>
-    <mergeCell ref="D72:G72"/>
-    <mergeCell ref="D74:G74"/>
-    <mergeCell ref="D75:G75"/>
-    <mergeCell ref="D53:G53"/>
-    <mergeCell ref="D54:G54"/>
-    <mergeCell ref="D61:G61"/>
-    <mergeCell ref="D71:G71"/>
-    <mergeCell ref="D59:G59"/>
-    <mergeCell ref="D60:G60"/>
-    <mergeCell ref="D62:G62"/>
-    <mergeCell ref="D58:G58"/>
-    <mergeCell ref="D57:G57"/>
-    <mergeCell ref="D56:G56"/>
-    <mergeCell ref="D67:G67"/>
-    <mergeCell ref="D46:G46"/>
-    <mergeCell ref="D48:G48"/>
-    <mergeCell ref="D49:G49"/>
-    <mergeCell ref="D50:G50"/>
-    <mergeCell ref="D52:G52"/>
-    <mergeCell ref="D111:G111"/>
-    <mergeCell ref="D90:G90"/>
-    <mergeCell ref="D91:G91"/>
-    <mergeCell ref="D101:G101"/>
-    <mergeCell ref="D104:G104"/>
-    <mergeCell ref="D106:G106"/>
-    <mergeCell ref="D107:G107"/>
-    <mergeCell ref="D108:G108"/>
-    <mergeCell ref="D109:G109"/>
-    <mergeCell ref="D92:G92"/>
-    <mergeCell ref="D93:G93"/>
-    <mergeCell ref="D94:G94"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/插件详细手册/0.性能测试报告/性能测试统计表.xlsx
+++ b/插件详细手册/0.性能测试报告/性能测试统计表.xlsx
@@ -1,10 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="4" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="23801"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AB2D869A-E59B-49B0-AD39-DAB1060F2E1F}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="-105" windowWidth="20730" windowHeight="11760" activeTab="1"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="地图界面" sheetId="1" r:id="rId1"/>
@@ -16,12 +17,12 @@
 </file>
 
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author>作者</author>
   </authors>
   <commentList>
-    <comment ref="D89" authorId="0">
+    <comment ref="D89" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000001000000}">
       <text>
         <r>
           <rPr>
@@ -47,7 +48,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F142" authorId="0">
+    <comment ref="F142" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000002000000}">
       <text>
         <r>
           <rPr>
@@ -78,12 +79,12 @@
 </file>
 
 <file path=xl/comments2.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author>作者</author>
   </authors>
   <commentList>
-    <comment ref="D42" authorId="0">
+    <comment ref="D42" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000001000000}">
       <text>
         <r>
           <rPr>
@@ -115,7 +116,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1633" uniqueCount="839">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1638" uniqueCount="843">
   <si>
     <t>行走图 - 图块同步镜像</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -1409,18 +1410,10 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>MOG_PictureEffects</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>图片 - 事件头顶图片 + 动态图片效果</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>图片 - 事件头顶图片 + 动态图片效果</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>Drill_PictureFilter</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -3470,13 +3463,37 @@
   </si>
   <si>
     <t>图片 - GIF动画序列（首次载入大量图片时）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Drill_PictureThumbtack</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>图片 - 图片图钉</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>11.36ms</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>9.72ms</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>6.83ms</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">  9.51ms</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -3814,7 +3831,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -3847,9 +3864,26 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -3882,6 +3916,23 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -4057,18 +4108,18 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A2:H173"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15.6" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="39.625" style="1" customWidth="1"/>
-    <col min="2" max="2" width="38.75" style="1" customWidth="1"/>
-    <col min="3" max="3" width="14.75" style="1" customWidth="1"/>
-    <col min="4" max="8" width="12.625" style="1" customWidth="1"/>
+    <col min="1" max="1" width="39.6640625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="41.44140625" style="1" customWidth="1"/>
+    <col min="3" max="3" width="14.77734375" style="1" customWidth="1"/>
+    <col min="4" max="8" width="12.6640625" style="1" customWidth="1"/>
     <col min="9" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A2" s="4" t="s">
         <v>44</v>
       </c>
@@ -4080,7 +4131,7 @@
       <c r="G2" s="4"/>
       <c r="H2" s="5"/>
     </row>
-    <row r="4" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="24" t="s">
         <v>57</v>
       </c>
@@ -4094,7 +4145,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="5" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="24" t="s">
         <v>46</v>
       </c>
@@ -4108,7 +4159,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="6" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="24" t="s">
         <v>45</v>
       </c>
@@ -4122,7 +4173,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="7" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="25" t="s">
         <v>62</v>
       </c>
@@ -4136,7 +4187,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="8" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="25" t="s">
         <v>63</v>
       </c>
@@ -4150,35 +4201,35 @@
         <v>54</v>
       </c>
     </row>
-    <row r="9" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="24" t="s">
         <v>144</v>
       </c>
       <c r="B9" s="24"/>
       <c r="C9" s="24"/>
     </row>
-    <row r="10" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="24" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="B10" s="24"/>
       <c r="C10" s="24"/>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:8" ht="16.2" x14ac:dyDescent="0.4">
       <c r="A12" s="29" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="B12" s="29"/>
       <c r="C12" s="8"/>
       <c r="D12" s="26" t="s">
-        <v>579</v>
+        <v>577</v>
       </c>
       <c r="E12" s="26"/>
       <c r="F12" s="26"/>
       <c r="G12" s="26"/>
       <c r="H12" s="5"/>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A13" s="19" t="s">
         <v>160</v>
       </c>
@@ -4202,7 +4253,7 @@
       </c>
       <c r="H13" s="2"/>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A14" s="1" t="s">
         <v>171</v>
       </c>
@@ -4219,12 +4270,12 @@
       <c r="F14" s="30"/>
       <c r="G14" s="30"/>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A15" s="1" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>180</v>
@@ -4236,97 +4287,97 @@
       <c r="F15" s="30"/>
       <c r="G15" s="30"/>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A16" s="1" t="s">
+        <v>399</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>400</v>
+      </c>
+      <c r="C16" s="1" t="s">
         <v>401</v>
       </c>
-      <c r="B16" s="1" t="s">
-        <v>402</v>
-      </c>
-      <c r="C16" s="1" t="s">
-        <v>403</v>
-      </c>
       <c r="D16" s="24" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="E16" s="24"/>
       <c r="F16" s="24"/>
       <c r="G16" s="24"/>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A17" s="1" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>180</v>
       </c>
       <c r="D17" s="24" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="E17" s="24"/>
       <c r="F17" s="24"/>
       <c r="G17" s="24"/>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A18" s="1" t="s">
-        <v>585</v>
+        <v>583</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>143</v>
       </c>
       <c r="D18" s="24" t="s">
-        <v>591</v>
+        <v>589</v>
       </c>
       <c r="E18" s="24"/>
       <c r="F18" s="24"/>
       <c r="G18" s="24"/>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A19" s="1" t="s">
+        <v>579</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>580</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D19" s="24" t="s">
         <v>581</v>
-      </c>
-      <c r="B19" s="1" t="s">
-        <v>582</v>
-      </c>
-      <c r="C19" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="D19" s="24" t="s">
-        <v>583</v>
       </c>
       <c r="E19" s="24"/>
       <c r="F19" s="24"/>
       <c r="G19" s="24"/>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A20" s="1" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>615</v>
+        <v>613</v>
       </c>
       <c r="C20" s="1" t="s">
         <v>143</v>
       </c>
       <c r="D20" s="24" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="E20" s="24"/>
       <c r="F20" s="24"/>
       <c r="G20" s="24"/>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A21" s="1" t="s">
-        <v>616</v>
+        <v>614</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>617</v>
+        <v>615</v>
       </c>
       <c r="C21" s="1" t="s">
         <v>43</v>
@@ -4338,92 +4389,92 @@
       <c r="F21" s="30"/>
       <c r="G21" s="30"/>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A22" s="1" t="s">
-        <v>717</v>
+        <v>715</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>718</v>
+        <v>716</v>
       </c>
       <c r="C22" s="1" t="s">
         <v>43</v>
       </c>
       <c r="D22" s="34" t="s">
-        <v>721</v>
+        <v>719</v>
       </c>
       <c r="E22" s="34"/>
       <c r="F22" s="34"/>
       <c r="G22" s="34"/>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A23" s="1" t="s">
-        <v>716</v>
+        <v>714</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>719</v>
+        <v>717</v>
       </c>
       <c r="C23" s="1" t="s">
         <v>43</v>
       </c>
       <c r="D23" s="24" t="s">
-        <v>720</v>
+        <v>718</v>
       </c>
       <c r="E23" s="24"/>
       <c r="F23" s="24"/>
       <c r="G23" s="24"/>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A24" s="1" t="s">
-        <v>738</v>
+        <v>736</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>739</v>
+        <v>737</v>
       </c>
       <c r="C24" s="1" t="s">
         <v>43</v>
       </c>
       <c r="D24" s="24" t="s">
-        <v>724</v>
+        <v>722</v>
       </c>
       <c r="E24" s="24"/>
       <c r="F24" s="24"/>
       <c r="G24" s="24"/>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A25" s="1" t="s">
-        <v>793</v>
+        <v>791</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>794</v>
+        <v>792</v>
       </c>
       <c r="C25" s="1" t="s">
         <v>143</v>
       </c>
       <c r="D25" s="24" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="E25" s="24"/>
       <c r="F25" s="24"/>
       <c r="G25" s="24"/>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A26" s="1" t="s">
-        <v>826</v>
+        <v>824</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>827</v>
+        <v>825</v>
       </c>
       <c r="C26" s="1" t="s">
         <v>43</v>
       </c>
       <c r="D26" s="24" t="s">
-        <v>825</v>
+        <v>823</v>
       </c>
       <c r="E26" s="24"/>
       <c r="F26" s="24"/>
       <c r="G26" s="24"/>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A27" s="1" t="s">
         <v>172</v>
       </c>
@@ -4440,7 +4491,7 @@
       <c r="F27" s="30"/>
       <c r="G27" s="30"/>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A28" s="1" t="s">
         <v>173</v>
       </c>
@@ -4457,7 +4508,7 @@
       <c r="F28" s="30"/>
       <c r="G28" s="30"/>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A29" s="1" t="s">
         <v>175</v>
       </c>
@@ -4468,13 +4519,13 @@
         <v>179</v>
       </c>
       <c r="D29" s="24" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="E29" s="24"/>
       <c r="F29" s="24"/>
       <c r="G29" s="24"/>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A30" s="1" t="s">
         <v>165</v>
       </c>
@@ -4491,7 +4542,7 @@
       <c r="F30" s="30"/>
       <c r="G30" s="30"/>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A31" s="1" t="s">
         <v>166</v>
       </c>
@@ -4502,30 +4553,30 @@
         <v>180</v>
       </c>
       <c r="D31" s="24" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="E31" s="24"/>
       <c r="F31" s="24"/>
       <c r="G31" s="24"/>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A32" s="1" t="s">
-        <v>822</v>
+        <v>820</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>823</v>
+        <v>821</v>
       </c>
       <c r="C32" s="1" t="s">
         <v>43</v>
       </c>
       <c r="D32" s="24" t="s">
-        <v>829</v>
+        <v>827</v>
       </c>
       <c r="E32" s="24"/>
       <c r="F32" s="24"/>
       <c r="G32" s="24"/>
     </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A33" s="1" t="s">
         <v>177</v>
       </c>
@@ -4542,7 +4593,7 @@
       <c r="F33" s="30"/>
       <c r="G33" s="30"/>
     </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A34" s="1" t="s">
         <v>169</v>
       </c>
@@ -4553,18 +4604,18 @@
         <v>180</v>
       </c>
       <c r="D34" s="24" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="E34" s="24"/>
       <c r="F34" s="24"/>
       <c r="G34" s="24"/>
     </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A35" s="1" t="s">
-        <v>750</v>
+        <v>748</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>751</v>
+        <v>749</v>
       </c>
       <c r="C35" s="1" t="s">
         <v>43</v>
@@ -4576,7 +4627,7 @@
       <c r="F35" s="30"/>
       <c r="G35" s="30"/>
     </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A37" s="1" t="s">
         <v>30</v>
       </c>
@@ -4587,19 +4638,19 @@
         <v>43</v>
       </c>
       <c r="D37" s="6" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="E37" s="7" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="F37" s="7" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="G37" s="1" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A38" s="22" t="s">
         <v>27</v>
       </c>
@@ -4622,30 +4673,30 @@
         <v>29</v>
       </c>
     </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A39" s="1" t="s">
+        <v>629</v>
+      </c>
+      <c r="B39" s="1" t="s">
+        <v>630</v>
+      </c>
+      <c r="C39" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D39" s="15" t="s">
+        <v>633</v>
+      </c>
+      <c r="E39" s="15" t="s">
+        <v>634</v>
+      </c>
+      <c r="F39" s="6" t="s">
+        <v>632</v>
+      </c>
+      <c r="G39" s="7" t="s">
         <v>631</v>
       </c>
-      <c r="B39" s="1" t="s">
-        <v>632</v>
-      </c>
-      <c r="C39" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="D39" s="15" t="s">
-        <v>635</v>
-      </c>
-      <c r="E39" s="15" t="s">
-        <v>636</v>
-      </c>
-      <c r="F39" s="6" t="s">
-        <v>634</v>
-      </c>
-      <c r="G39" s="7" t="s">
-        <v>633</v>
-      </c>
-    </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.3">
+    </row>
+    <row r="40" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A40" s="1" t="s">
         <v>32</v>
       </c>
@@ -4656,7 +4707,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A41" s="1" t="s">
         <v>34</v>
       </c>
@@ -4667,19 +4718,19 @@
         <v>43</v>
       </c>
       <c r="D41" s="1" t="s">
+        <v>693</v>
+      </c>
+      <c r="E41" s="1" t="s">
+        <v>694</v>
+      </c>
+      <c r="F41" s="1" t="s">
         <v>695</v>
-      </c>
-      <c r="E41" s="1" t="s">
-        <v>696</v>
-      </c>
-      <c r="F41" s="1" t="s">
-        <v>697</v>
       </c>
       <c r="G41" s="1" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A42" s="1" t="s">
         <v>58</v>
       </c>
@@ -4690,19 +4741,19 @@
         <v>43</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>694</v>
+        <v>692</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>693</v>
+        <v>691</v>
       </c>
       <c r="F42" s="1" t="s">
-        <v>692</v>
+        <v>690</v>
       </c>
       <c r="G42" s="1" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A43" s="1" t="s">
         <v>60</v>
       </c>
@@ -4713,19 +4764,19 @@
         <v>43</v>
       </c>
       <c r="D43" s="1" t="s">
+        <v>687</v>
+      </c>
+      <c r="E43" s="1" t="s">
+        <v>688</v>
+      </c>
+      <c r="F43" s="1" t="s">
         <v>689</v>
-      </c>
-      <c r="E43" s="1" t="s">
-        <v>690</v>
-      </c>
-      <c r="F43" s="1" t="s">
-        <v>691</v>
       </c>
       <c r="G43" s="1" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A44" s="1" t="s">
         <v>36</v>
       </c>
@@ -4736,59 +4787,59 @@
         <v>43</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="E44" s="1" t="s">
         <v>146</v>
       </c>
       <c r="F44" s="1" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="G44" s="1" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A45" s="1" t="s">
+        <v>723</v>
+      </c>
+      <c r="B45" s="1" t="s">
+        <v>724</v>
+      </c>
+      <c r="C45" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D45" s="1" t="s">
+        <v>727</v>
+      </c>
+      <c r="E45" s="1" t="s">
+        <v>726</v>
+      </c>
+      <c r="F45" s="1" t="s">
         <v>725</v>
-      </c>
-      <c r="B45" s="1" t="s">
-        <v>726</v>
-      </c>
-      <c r="C45" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="D45" s="1" t="s">
-        <v>729</v>
-      </c>
-      <c r="E45" s="1" t="s">
-        <v>728</v>
-      </c>
-      <c r="F45" s="1" t="s">
-        <v>727</v>
       </c>
       <c r="G45" s="1" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A46" s="1" t="s">
-        <v>789</v>
+        <v>787</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>790</v>
+        <v>788</v>
       </c>
       <c r="C46" s="1" t="s">
         <v>43</v>
       </c>
       <c r="D46" s="24" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="E46" s="24"/>
       <c r="F46" s="24"/>
       <c r="G46" s="24"/>
     </row>
-    <row r="47" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A47" s="1" t="s">
         <v>38</v>
       </c>
@@ -4811,30 +4862,30 @@
         <v>14</v>
       </c>
     </row>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A48" s="1" t="s">
-        <v>622</v>
+        <v>620</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>623</v>
+        <v>621</v>
       </c>
       <c r="C48" s="1" t="s">
         <v>43</v>
       </c>
       <c r="D48" s="6" t="s">
+        <v>616</v>
+      </c>
+      <c r="E48" s="6" t="s">
+        <v>617</v>
+      </c>
+      <c r="F48" s="6" t="s">
         <v>618</v>
       </c>
-      <c r="E48" s="6" t="s">
+      <c r="G48" s="1" t="s">
         <v>619</v>
       </c>
-      <c r="F48" s="6" t="s">
-        <v>620</v>
-      </c>
-      <c r="G48" s="1" t="s">
-        <v>621</v>
-      </c>
-    </row>
-    <row r="50" spans="1:8" x14ac:dyDescent="0.3">
+    </row>
+    <row r="50" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A50" s="1" t="s">
         <v>64</v>
       </c>
@@ -4845,19 +4896,19 @@
         <v>43</v>
       </c>
       <c r="D50" s="1" t="s">
+        <v>495</v>
+      </c>
+      <c r="E50" s="1" t="s">
+        <v>496</v>
+      </c>
+      <c r="F50" s="1" t="s">
         <v>497</v>
-      </c>
-      <c r="E50" s="1" t="s">
-        <v>498</v>
-      </c>
-      <c r="F50" s="1" t="s">
-        <v>499</v>
       </c>
       <c r="G50" s="1" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="51" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A51" s="1" t="s">
         <v>66</v>
       </c>
@@ -4868,7 +4919,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="52" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A52" s="1" t="s">
         <v>68</v>
       </c>
@@ -4879,13 +4930,13 @@
         <v>143</v>
       </c>
       <c r="D52" s="24" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="E52" s="24"/>
       <c r="F52" s="24"/>
       <c r="G52" s="24"/>
     </row>
-    <row r="53" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A53" s="1" t="s">
         <v>26</v>
       </c>
@@ -4908,7 +4959,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="54" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A54" s="1" t="s">
         <v>151</v>
       </c>
@@ -4919,13 +4970,13 @@
         <v>143</v>
       </c>
       <c r="D54" s="24" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="E54" s="24"/>
       <c r="F54" s="24"/>
       <c r="G54" s="24"/>
     </row>
-    <row r="55" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A55" s="1" t="s">
         <v>71</v>
       </c>
@@ -4936,7 +4987,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="56" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A56" s="1" t="s">
         <v>21</v>
       </c>
@@ -4959,7 +5010,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="57" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A57" s="1" t="s">
         <v>19</v>
       </c>
@@ -4982,7 +5033,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="58" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A58" s="1" t="s">
         <v>20</v>
       </c>
@@ -5005,7 +5056,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="59" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A59" s="1" t="s">
         <v>11</v>
       </c>
@@ -5028,7 +5079,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="60" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A60" s="1" t="s">
         <v>3</v>
       </c>
@@ -5051,30 +5102,30 @@
         <v>14</v>
       </c>
     </row>
-    <row r="61" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A61" s="1" t="s">
+        <v>567</v>
+      </c>
+      <c r="B61" s="1" t="s">
+        <v>568</v>
+      </c>
+      <c r="C61" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D61" s="1" t="s">
         <v>569</v>
       </c>
-      <c r="B61" s="1" t="s">
+      <c r="E61" s="1" t="s">
         <v>570</v>
       </c>
-      <c r="C61" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="D61" s="1" t="s">
+      <c r="F61" s="1" t="s">
         <v>571</v>
-      </c>
-      <c r="E61" s="1" t="s">
-        <v>572</v>
-      </c>
-      <c r="F61" s="1" t="s">
-        <v>573</v>
       </c>
       <c r="G61" s="1" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="62" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A62" s="1" t="s">
         <v>40</v>
       </c>
@@ -5097,49 +5148,49 @@
         <v>14</v>
       </c>
     </row>
-    <row r="63" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A63" s="1" t="s">
+        <v>624</v>
+      </c>
+      <c r="B63" s="1" t="s">
+        <v>625</v>
+      </c>
+      <c r="C63" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D63" s="6" t="s">
         <v>626</v>
       </c>
-      <c r="B63" s="1" t="s">
+      <c r="E63" s="6" t="s">
         <v>627</v>
       </c>
-      <c r="C63" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="D63" s="6" t="s">
+      <c r="F63" s="7" t="s">
         <v>628</v>
-      </c>
-      <c r="E63" s="6" t="s">
-        <v>629</v>
-      </c>
-      <c r="F63" s="7" t="s">
-        <v>630</v>
       </c>
       <c r="G63" s="1" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="65" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A65" s="1" t="s">
+        <v>554</v>
+      </c>
+      <c r="B65" s="1" t="s">
         <v>556</v>
-      </c>
-      <c r="B65" s="1" t="s">
-        <v>558</v>
       </c>
       <c r="C65" s="1" t="s">
         <v>143</v>
       </c>
       <c r="D65" s="24" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="E65" s="24"/>
       <c r="F65" s="24"/>
       <c r="G65" s="24"/>
     </row>
-    <row r="66" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A66" s="1" t="s">
-        <v>557</v>
+        <v>555</v>
       </c>
       <c r="B66" s="1" t="s">
         <v>139</v>
@@ -5160,47 +5211,47 @@
         <v>14</v>
       </c>
     </row>
-    <row r="67" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A67" s="1" t="s">
+        <v>557</v>
+      </c>
+      <c r="B67" s="1" t="s">
+        <v>558</v>
+      </c>
+      <c r="C67" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D67" s="1" t="s">
         <v>559</v>
       </c>
-      <c r="B67" s="1" t="s">
+      <c r="E67" s="1" t="s">
         <v>560</v>
       </c>
-      <c r="C67" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="D67" s="1" t="s">
+      <c r="F67" s="1" t="s">
         <v>561</v>
-      </c>
-      <c r="E67" s="1" t="s">
-        <v>562</v>
-      </c>
-      <c r="F67" s="1" t="s">
-        <v>563</v>
       </c>
       <c r="G67" s="1" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="68" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A68" s="1" t="s">
+        <v>670</v>
+      </c>
+      <c r="B68" s="1" t="s">
+        <v>671</v>
+      </c>
+      <c r="C68" s="1" t="s">
         <v>672</v>
       </c>
-      <c r="B68" s="1" t="s">
-        <v>673</v>
-      </c>
-      <c r="C68" s="1" t="s">
-        <v>674</v>
-      </c>
       <c r="D68" s="24" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="E68" s="24"/>
       <c r="F68" s="24"/>
       <c r="G68" s="24"/>
     </row>
-    <row r="69" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A69" s="1" t="s">
         <v>74</v>
       </c>
@@ -5211,13 +5262,13 @@
         <v>143</v>
       </c>
       <c r="D69" s="24" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="E69" s="24"/>
       <c r="F69" s="24"/>
       <c r="G69" s="24"/>
     </row>
-    <row r="70" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A70" s="1" t="s">
         <v>76</v>
       </c>
@@ -5228,42 +5279,42 @@
         <v>43</v>
       </c>
       <c r="D70" s="1" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="E70" s="1" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="F70" s="1" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="G70" s="1" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="71" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A71" s="1" t="s">
+        <v>562</v>
+      </c>
+      <c r="B71" s="1" t="s">
+        <v>563</v>
+      </c>
+      <c r="C71" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D71" s="1" t="s">
         <v>564</v>
       </c>
-      <c r="B71" s="1" t="s">
+      <c r="E71" s="1" t="s">
         <v>565</v>
       </c>
-      <c r="C71" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="D71" s="1" t="s">
-        <v>566</v>
-      </c>
-      <c r="E71" s="1" t="s">
-        <v>567</v>
-      </c>
       <c r="F71" s="1" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="G71" s="1" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="72" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A72" s="1" t="s">
         <v>78</v>
       </c>
@@ -5274,42 +5325,42 @@
         <v>180</v>
       </c>
       <c r="D72" s="1" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="E72" s="1" t="s">
+        <v>387</v>
+      </c>
+      <c r="F72" s="1" t="s">
         <v>389</v>
-      </c>
-      <c r="F72" s="1" t="s">
-        <v>391</v>
       </c>
       <c r="G72" s="1" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="73" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A73" s="1" t="s">
+        <v>607</v>
+      </c>
+      <c r="B73" s="1" t="s">
+        <v>608</v>
+      </c>
+      <c r="C73" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D73" s="7" t="s">
+        <v>611</v>
+      </c>
+      <c r="E73" s="1" t="s">
         <v>609</v>
       </c>
-      <c r="B73" s="1" t="s">
+      <c r="F73" s="1" t="s">
         <v>610</v>
-      </c>
-      <c r="C73" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="D73" s="7" t="s">
-        <v>613</v>
-      </c>
-      <c r="E73" s="1" t="s">
-        <v>611</v>
-      </c>
-      <c r="F73" s="1" t="s">
-        <v>612</v>
       </c>
       <c r="G73" s="1" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="74" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A74" s="1" t="s">
         <v>80</v>
       </c>
@@ -5320,13 +5371,13 @@
         <v>143</v>
       </c>
       <c r="D74" s="24" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="E74" s="24"/>
       <c r="F74" s="24"/>
       <c r="G74" s="24"/>
     </row>
-    <row r="75" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A75" s="1" t="s">
         <v>89</v>
       </c>
@@ -5337,19 +5388,19 @@
         <v>143</v>
       </c>
       <c r="D75" s="1" t="s">
-        <v>568</v>
+        <v>566</v>
       </c>
       <c r="E75" s="1" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="F75" s="1" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="G75" s="1" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="76" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A76" s="1" t="s">
         <v>91</v>
       </c>
@@ -5360,42 +5411,42 @@
         <v>143</v>
       </c>
       <c r="D76" s="1" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="E76" s="1" t="s">
         <v>145</v>
       </c>
       <c r="F76" s="1" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="G76" s="1" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="77" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A77" s="1" t="s">
+        <v>572</v>
+      </c>
+      <c r="B77" s="1" t="s">
+        <v>573</v>
+      </c>
+      <c r="C77" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D77" s="1" t="s">
         <v>574</v>
       </c>
-      <c r="B77" s="1" t="s">
+      <c r="E77" s="1" t="s">
         <v>575</v>
       </c>
-      <c r="C77" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="D77" s="1" t="s">
+      <c r="F77" s="1" t="s">
         <v>576</v>
-      </c>
-      <c r="E77" s="1" t="s">
-        <v>577</v>
-      </c>
-      <c r="F77" s="1" t="s">
-        <v>578</v>
       </c>
       <c r="G77" s="1" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="78" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A78" s="1" t="s">
         <v>82</v>
       </c>
@@ -5406,19 +5457,19 @@
         <v>143</v>
       </c>
       <c r="D78" s="1" t="s">
-        <v>506</v>
+        <v>504</v>
       </c>
       <c r="E78" s="1" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
       <c r="F78" s="1" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="G78" s="1" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="79" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A79" s="1" t="s">
         <v>152</v>
       </c>
@@ -5441,24 +5492,24 @@
         <v>14</v>
       </c>
     </row>
-    <row r="80" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A80" s="1" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="B80" s="1" t="s">
-        <v>517</v>
+        <v>515</v>
       </c>
       <c r="C80" s="1" t="s">
         <v>143</v>
       </c>
       <c r="D80" s="24" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="E80" s="24"/>
       <c r="F80" s="24"/>
       <c r="G80" s="24"/>
     </row>
-    <row r="81" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A81" s="1" t="s">
         <v>84</v>
       </c>
@@ -5469,13 +5520,13 @@
         <v>43</v>
       </c>
       <c r="D81" s="24" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="E81" s="24"/>
       <c r="F81" s="24"/>
       <c r="G81" s="24"/>
     </row>
-    <row r="82" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A82" s="1" t="s">
         <v>86</v>
       </c>
@@ -5486,36 +5537,36 @@
         <v>43</v>
       </c>
       <c r="D82" s="1" t="s">
-        <v>555</v>
+        <v>553</v>
       </c>
       <c r="E82" s="1" t="s">
-        <v>553</v>
+        <v>551</v>
       </c>
       <c r="F82" s="1" t="s">
-        <v>554</v>
+        <v>552</v>
       </c>
       <c r="G82" s="1" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="83" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A83" s="1" t="s">
         <v>88</v>
       </c>
       <c r="B83" s="1" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="C83" s="1" t="s">
         <v>43</v>
       </c>
       <c r="D83" s="24" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="E83" s="24"/>
       <c r="F83" s="24"/>
       <c r="G83" s="24"/>
     </row>
-    <row r="84" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A84" s="1" t="s">
         <v>93</v>
       </c>
@@ -5526,36 +5577,36 @@
         <v>143</v>
       </c>
       <c r="D84" s="1" t="s">
+        <v>526</v>
+      </c>
+      <c r="E84" s="1" t="s">
+        <v>527</v>
+      </c>
+      <c r="F84" s="1" t="s">
         <v>528</v>
-      </c>
-      <c r="E84" s="1" t="s">
-        <v>529</v>
-      </c>
-      <c r="F84" s="1" t="s">
-        <v>530</v>
       </c>
       <c r="G84" s="1" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="85" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A85" s="1" t="s">
-        <v>743</v>
+        <v>741</v>
       </c>
       <c r="B85" s="1" t="s">
-        <v>744</v>
+        <v>742</v>
       </c>
       <c r="C85" s="1" t="s">
         <v>43</v>
       </c>
       <c r="D85" s="24" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="E85" s="24"/>
       <c r="F85" s="24"/>
       <c r="G85" s="24"/>
     </row>
-    <row r="86" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A86" s="1" t="s">
         <v>95</v>
       </c>
@@ -5566,18 +5617,18 @@
         <v>143</v>
       </c>
       <c r="D86" s="24" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="E86" s="24"/>
       <c r="F86" s="24"/>
       <c r="G86" s="24"/>
     </row>
-    <row r="88" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A88" s="1" t="s">
-        <v>522</v>
+        <v>520</v>
       </c>
       <c r="B88" s="1" t="s">
-        <v>523</v>
+        <v>521</v>
       </c>
       <c r="C88" s="1" t="s">
         <v>43</v>
@@ -5589,15 +5640,15 @@
       <c r="F88" s="30"/>
       <c r="G88" s="30"/>
     </row>
-    <row r="89" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A89" s="1" t="s">
         <v>103</v>
       </c>
       <c r="B89" s="1" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="C89" s="1" t="s">
-        <v>534</v>
+        <v>532</v>
       </c>
       <c r="D89" s="7" t="s">
         <v>121</v>
@@ -5612,30 +5663,30 @@
         <v>14</v>
       </c>
     </row>
-    <row r="90" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A90" s="1" t="s">
         <v>97</v>
       </c>
       <c r="B90" s="1" t="s">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="C90" s="1" t="s">
         <v>143</v>
       </c>
       <c r="D90" s="1" t="s">
+        <v>545</v>
+      </c>
+      <c r="E90" s="1" t="s">
+        <v>546</v>
+      </c>
+      <c r="F90" s="1" t="s">
         <v>547</v>
-      </c>
-      <c r="E90" s="1" t="s">
-        <v>548</v>
-      </c>
-      <c r="F90" s="1" t="s">
-        <v>549</v>
       </c>
       <c r="G90" s="1" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="91" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A91" s="1" t="s">
         <v>98</v>
       </c>
@@ -5643,68 +5694,68 @@
         <v>99</v>
       </c>
       <c r="C91" s="1" t="s">
+        <v>533</v>
+      </c>
+      <c r="D91" s="15" t="s">
         <v>535</v>
       </c>
-      <c r="D91" s="15" t="s">
-        <v>537</v>
-      </c>
       <c r="E91" s="15" t="s">
-        <v>542</v>
+        <v>540</v>
       </c>
       <c r="F91" s="15" t="s">
-        <v>543</v>
+        <v>541</v>
       </c>
       <c r="G91" s="15" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="92" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A92" s="1" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="B92" s="1" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="C92" s="1" t="s">
         <v>143</v>
       </c>
       <c r="D92" s="1" t="s">
+        <v>542</v>
+      </c>
+      <c r="E92" s="1" t="s">
+        <v>543</v>
+      </c>
+      <c r="F92" s="1" t="s">
         <v>544</v>
-      </c>
-      <c r="E92" s="1" t="s">
-        <v>545</v>
-      </c>
-      <c r="F92" s="1" t="s">
-        <v>546</v>
       </c>
       <c r="G92" s="1" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="93" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A93" s="1" t="s">
         <v>100</v>
       </c>
       <c r="B93" s="1" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="C93" s="1" t="s">
         <v>143</v>
       </c>
       <c r="D93" s="1" t="s">
+        <v>529</v>
+      </c>
+      <c r="E93" s="1" t="s">
+        <v>530</v>
+      </c>
+      <c r="F93" s="1" t="s">
         <v>531</v>
-      </c>
-      <c r="E93" s="1" t="s">
-        <v>532</v>
-      </c>
-      <c r="F93" s="1" t="s">
-        <v>533</v>
       </c>
       <c r="G93" s="1" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="94" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A94" s="1" t="s">
         <v>101</v>
       </c>
@@ -5712,22 +5763,22 @@
         <v>102</v>
       </c>
       <c r="C94" s="1" t="s">
-        <v>535</v>
+        <v>533</v>
       </c>
       <c r="D94" s="15" t="s">
-        <v>541</v>
+        <v>539</v>
       </c>
       <c r="E94" s="15" t="s">
+        <v>536</v>
+      </c>
+      <c r="F94" s="15" t="s">
+        <v>537</v>
+      </c>
+      <c r="G94" s="15" t="s">
         <v>538</v>
       </c>
-      <c r="F94" s="15" t="s">
-        <v>539</v>
-      </c>
-      <c r="G94" s="15" t="s">
-        <v>540</v>
-      </c>
-    </row>
-    <row r="96" spans="1:7" x14ac:dyDescent="0.3">
+    </row>
+    <row r="96" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A96" s="1" t="s">
         <v>104</v>
       </c>
@@ -5738,19 +5789,19 @@
         <v>43</v>
       </c>
       <c r="D96" s="6" t="s">
+        <v>382</v>
+      </c>
+      <c r="E96" s="7" t="s">
         <v>384</v>
       </c>
-      <c r="E96" s="7" t="s">
-        <v>386</v>
-      </c>
       <c r="F96" s="1" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="G96" s="1" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="97" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A97" s="1" t="s">
         <v>106</v>
       </c>
@@ -5773,7 +5824,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="98" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A98" s="1" t="s">
         <v>108</v>
       </c>
@@ -5784,13 +5835,13 @@
         <v>143</v>
       </c>
       <c r="D98" s="24" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="E98" s="24"/>
       <c r="F98" s="24"/>
       <c r="G98" s="24"/>
     </row>
-    <row r="99" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A99" s="1" t="s">
         <v>110</v>
       </c>
@@ -5801,82 +5852,82 @@
         <v>143</v>
       </c>
       <c r="D99" s="24" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="E99" s="24"/>
       <c r="F99" s="24"/>
       <c r="G99" s="24"/>
     </row>
-    <row r="100" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A100" s="1" t="s">
         <v>112</v>
       </c>
       <c r="B100" s="16" t="s">
+        <v>506</v>
+      </c>
+      <c r="C100" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D100" s="1" t="s">
         <v>508</v>
       </c>
-      <c r="C100" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="D100" s="1" t="s">
+      <c r="E100" s="1" t="s">
+        <v>509</v>
+      </c>
+      <c r="F100" s="1" t="s">
         <v>510</v>
-      </c>
-      <c r="E100" s="1" t="s">
-        <v>511</v>
-      </c>
-      <c r="F100" s="1" t="s">
-        <v>512</v>
       </c>
       <c r="G100" s="1" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="101" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A101" s="1" t="s">
         <v>112</v>
       </c>
       <c r="B101" s="16" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
       <c r="C101" s="1" t="s">
-        <v>536</v>
+        <v>534</v>
       </c>
       <c r="D101" s="15" t="s">
+        <v>512</v>
+      </c>
+      <c r="E101" s="15" t="s">
+        <v>513</v>
+      </c>
+      <c r="F101" s="15" t="s">
         <v>514</v>
       </c>
-      <c r="E101" s="15" t="s">
-        <v>515</v>
-      </c>
-      <c r="F101" s="15" t="s">
-        <v>516</v>
-      </c>
       <c r="G101" s="15" t="s">
-        <v>513</v>
-      </c>
-    </row>
-    <row r="102" spans="1:8" x14ac:dyDescent="0.3">
+        <v>511</v>
+      </c>
+    </row>
+    <row r="102" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A102" s="1" t="s">
-        <v>527</v>
+        <v>525</v>
       </c>
       <c r="B102" s="16" t="s">
-        <v>526</v>
+        <v>524</v>
       </c>
       <c r="C102" s="1" t="s">
         <v>43</v>
       </c>
       <c r="D102" s="1" t="s">
+        <v>548</v>
+      </c>
+      <c r="E102" s="1" t="s">
+        <v>549</v>
+      </c>
+      <c r="F102" s="1" t="s">
         <v>550</v>
-      </c>
-      <c r="E102" s="1" t="s">
-        <v>551</v>
-      </c>
-      <c r="F102" s="1" t="s">
-        <v>552</v>
       </c>
       <c r="G102" s="1" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="103" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A103" s="1" t="s">
         <v>113</v>
       </c>
@@ -5899,7 +5950,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="104" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A104" s="1" t="s">
         <v>115</v>
       </c>
@@ -5910,19 +5961,19 @@
         <v>143</v>
       </c>
       <c r="D104" s="1" t="s">
+        <v>379</v>
+      </c>
+      <c r="E104" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="F104" s="1" t="s">
         <v>381</v>
-      </c>
-      <c r="E104" s="1" t="s">
-        <v>382</v>
-      </c>
-      <c r="F104" s="1" t="s">
-        <v>383</v>
       </c>
       <c r="G104" s="1" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="106" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A106" s="1" t="s">
         <v>184</v>
       </c>
@@ -5933,7 +5984,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="107" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A107" s="1" t="s">
         <v>186</v>
       </c>
@@ -5944,7 +5995,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="108" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A108" s="1" t="s">
         <v>188</v>
       </c>
@@ -5955,7 +6006,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="109" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A109" s="1" t="s">
         <v>190</v>
       </c>
@@ -5966,7 +6017,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="110" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A110" s="1" t="s">
         <v>192</v>
       </c>
@@ -5977,7 +6028,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="111" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A111" s="1" t="s">
         <v>194</v>
       </c>
@@ -5988,7 +6039,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="112" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A112" s="1" t="s">
         <v>196</v>
       </c>
@@ -5999,7 +6050,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="113" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A113" s="1" t="s">
         <v>198</v>
       </c>
@@ -6010,7 +6061,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="114" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A114" s="1" t="s">
         <v>200</v>
       </c>
@@ -6021,53 +6072,53 @@
         <v>183</v>
       </c>
     </row>
-    <row r="115" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A115" s="1" t="s">
+        <v>728</v>
+      </c>
+      <c r="B115" s="1" t="s">
+        <v>729</v>
+      </c>
+      <c r="C115" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D115" s="1" t="s">
+        <v>732</v>
+      </c>
+      <c r="E115" s="1" t="s">
+        <v>731</v>
+      </c>
+      <c r="F115" s="1" t="s">
         <v>730</v>
-      </c>
-      <c r="B115" s="1" t="s">
-        <v>731</v>
-      </c>
-      <c r="C115" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="D115" s="1" t="s">
-        <v>734</v>
-      </c>
-      <c r="E115" s="1" t="s">
-        <v>733</v>
-      </c>
-      <c r="F115" s="1" t="s">
-        <v>732</v>
       </c>
       <c r="G115" s="1" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="116" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A116" s="1" t="s">
+        <v>743</v>
+      </c>
+      <c r="B116" s="1" t="s">
+        <v>744</v>
+      </c>
+      <c r="C116" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D116" s="1" t="s">
         <v>745</v>
       </c>
-      <c r="B116" s="1" t="s">
+      <c r="E116" s="1" t="s">
         <v>746</v>
       </c>
-      <c r="C116" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="D116" s="1" t="s">
+      <c r="F116" s="1" t="s">
         <v>747</v>
-      </c>
-      <c r="E116" s="1" t="s">
-        <v>748</v>
-      </c>
-      <c r="F116" s="1" t="s">
-        <v>749</v>
       </c>
       <c r="G116" s="1" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="118" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A118" s="1" t="s">
         <v>274</v>
       </c>
@@ -6078,7 +6129,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="119" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A119" s="1" t="s">
         <v>276</v>
       </c>
@@ -6089,7 +6140,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="120" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A120" s="1" t="s">
         <v>278</v>
       </c>
@@ -6100,7 +6151,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="121" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A121" s="1" t="s">
         <v>280</v>
       </c>
@@ -6111,7 +6162,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="122" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A122" s="1" t="s">
         <v>282</v>
       </c>
@@ -6122,7 +6173,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="123" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A123" s="1" t="s">
         <v>284</v>
       </c>
@@ -6133,7 +6184,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="124" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A124" s="1" t="s">
         <v>286</v>
       </c>
@@ -6144,7 +6195,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="125" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A125" s="1" t="s">
         <v>288</v>
       </c>
@@ -6155,7 +6206,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="126" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A126" s="1" t="s">
         <v>290</v>
       </c>
@@ -6166,7 +6217,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="128" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A128" s="1" t="s">
         <v>292</v>
       </c>
@@ -6177,7 +6228,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="129" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A129" s="1" t="s">
         <v>294</v>
       </c>
@@ -6188,13 +6239,13 @@
         <v>43</v>
       </c>
       <c r="D129" s="24" t="s">
-        <v>715</v>
+        <v>713</v>
       </c>
       <c r="E129" s="24"/>
       <c r="F129" s="24"/>
       <c r="G129" s="24"/>
     </row>
-    <row r="130" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A130" s="16" t="s">
         <v>296</v>
       </c>
@@ -6205,76 +6256,76 @@
         <v>43</v>
       </c>
       <c r="D130" s="30" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="E130" s="30"/>
       <c r="F130" s="30"/>
       <c r="G130" s="30"/>
     </row>
-    <row r="131" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A131" s="16" t="s">
+        <v>700</v>
+      </c>
+      <c r="B131" s="16" t="s">
+        <v>701</v>
+      </c>
+      <c r="C131" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D131" s="7" t="s">
+        <v>706</v>
+      </c>
+      <c r="E131" s="7" t="s">
+        <v>707</v>
+      </c>
+      <c r="F131" s="1" t="s">
+        <v>704</v>
+      </c>
+      <c r="G131" s="1" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="132" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A132" s="16" t="s">
         <v>702</v>
       </c>
-      <c r="B131" s="16" t="s">
+      <c r="B132" s="16" t="s">
         <v>703</v>
       </c>
-      <c r="C131" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="D131" s="7" t="s">
+      <c r="C132" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D132" s="1" t="s">
         <v>708</v>
       </c>
-      <c r="E131" s="7" t="s">
+      <c r="E132" s="1" t="s">
         <v>709</v>
       </c>
-      <c r="F131" s="1" t="s">
-        <v>706</v>
-      </c>
-      <c r="G131" s="1" t="s">
-        <v>707</v>
-      </c>
-    </row>
-    <row r="132" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A132" s="16" t="s">
-        <v>704</v>
-      </c>
-      <c r="B132" s="16" t="s">
+      <c r="F132" s="1" t="s">
+        <v>710</v>
+      </c>
+      <c r="G132" s="1" t="s">
         <v>705</v>
       </c>
-      <c r="C132" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="D132" s="1" t="s">
-        <v>710</v>
-      </c>
-      <c r="E132" s="1" t="s">
-        <v>711</v>
-      </c>
-      <c r="F132" s="1" t="s">
-        <v>712</v>
-      </c>
-      <c r="G132" s="1" t="s">
-        <v>707</v>
-      </c>
-    </row>
-    <row r="133" spans="1:7" x14ac:dyDescent="0.3">
+    </row>
+    <row r="133" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A133" s="16" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="B133" s="16" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="C133" s="1" t="s">
         <v>43</v>
       </c>
       <c r="D133" s="24" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="E133" s="24"/>
       <c r="F133" s="24"/>
       <c r="G133" s="24"/>
     </row>
-    <row r="134" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A134" s="1" t="s">
         <v>298</v>
       </c>
@@ -6285,13 +6336,13 @@
         <v>143</v>
       </c>
       <c r="D134" s="24" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="E134" s="24"/>
       <c r="F134" s="24"/>
       <c r="G134" s="24"/>
     </row>
-    <row r="135" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A135" s="1" t="s">
         <v>300</v>
       </c>
@@ -6302,13 +6353,13 @@
         <v>143</v>
       </c>
       <c r="D135" s="24" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="E135" s="24"/>
       <c r="F135" s="24"/>
       <c r="G135" s="24"/>
     </row>
-    <row r="136" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A136" s="1" t="s">
         <v>302</v>
       </c>
@@ -6319,47 +6370,47 @@
         <v>143</v>
       </c>
       <c r="D136" s="24" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="E136" s="24"/>
       <c r="F136" s="24"/>
       <c r="G136" s="24"/>
     </row>
-    <row r="138" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A138" s="1" t="s">
-        <v>605</v>
+        <v>603</v>
       </c>
       <c r="B138" s="1" t="s">
-        <v>606</v>
+        <v>604</v>
       </c>
       <c r="C138" s="1" t="s">
         <v>43</v>
       </c>
       <c r="D138" s="24" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="E138" s="24"/>
       <c r="F138" s="24"/>
       <c r="G138" s="24"/>
     </row>
-    <row r="139" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A139" s="1" t="s">
-        <v>607</v>
+        <v>605</v>
       </c>
       <c r="B139" s="1" t="s">
-        <v>608</v>
+        <v>606</v>
       </c>
       <c r="C139" s="1" t="s">
         <v>43</v>
       </c>
       <c r="D139" s="24" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="E139" s="24"/>
       <c r="F139" s="24"/>
       <c r="G139" s="24"/>
     </row>
-    <row r="140" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A140" s="1" t="s">
         <v>124</v>
       </c>
@@ -6376,7 +6427,7 @@
       <c r="F140" s="30"/>
       <c r="G140" s="30"/>
     </row>
-    <row r="141" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A141" s="1" t="s">
         <v>126</v>
       </c>
@@ -6399,7 +6450,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="142" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A142" s="1" t="s">
         <v>128</v>
       </c>
@@ -6422,76 +6473,76 @@
         <v>14</v>
       </c>
     </row>
-    <row r="143" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A143" s="1" t="s">
+        <v>757</v>
+      </c>
+      <c r="B143" s="1" t="s">
+        <v>758</v>
+      </c>
+      <c r="C143" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D143" s="1" t="s">
         <v>759</v>
       </c>
-      <c r="B143" s="1" t="s">
+      <c r="E143" s="1" t="s">
         <v>760</v>
       </c>
-      <c r="C143" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="D143" s="1" t="s">
+      <c r="F143" s="1" t="s">
         <v>761</v>
-      </c>
-      <c r="E143" s="1" t="s">
-        <v>762</v>
-      </c>
-      <c r="F143" s="1" t="s">
-        <v>763</v>
       </c>
       <c r="G143" s="1" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="144" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A144" s="1" t="s">
-        <v>758</v>
+        <v>756</v>
       </c>
       <c r="B144" s="1" t="s">
+        <v>762</v>
+      </c>
+      <c r="C144" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D144" s="1" t="s">
+        <v>763</v>
+      </c>
+      <c r="E144" s="1" t="s">
         <v>764</v>
       </c>
-      <c r="C144" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="D144" s="1" t="s">
+      <c r="F144" s="1" t="s">
         <v>765</v>
-      </c>
-      <c r="E144" s="1" t="s">
-        <v>766</v>
-      </c>
-      <c r="F144" s="1" t="s">
-        <v>767</v>
       </c>
       <c r="G144" s="1" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="145" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A145" s="1" t="s">
+        <v>635</v>
+      </c>
+      <c r="B145" s="1" t="s">
+        <v>636</v>
+      </c>
+      <c r="C145" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D145" s="1" t="s">
         <v>637</v>
       </c>
-      <c r="B145" s="1" t="s">
+      <c r="E145" s="1" t="s">
         <v>638</v>
       </c>
-      <c r="C145" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="D145" s="1" t="s">
+      <c r="F145" s="1" t="s">
         <v>639</v>
       </c>
-      <c r="E145" s="1" t="s">
+      <c r="G145" s="1" t="s">
         <v>640</v>
       </c>
-      <c r="F145" s="1" t="s">
-        <v>641</v>
-      </c>
-      <c r="G145" s="1" t="s">
-        <v>642</v>
-      </c>
-    </row>
-    <row r="147" spans="1:8" x14ac:dyDescent="0.3">
+    </row>
+    <row r="147" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A147" s="1" t="s">
         <v>312</v>
       </c>
@@ -6502,13 +6553,13 @@
         <v>143</v>
       </c>
       <c r="D147" s="24" t="s">
-        <v>788</v>
+        <v>786</v>
       </c>
       <c r="E147" s="24"/>
       <c r="F147" s="24"/>
       <c r="G147" s="24"/>
     </row>
-    <row r="148" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A148" s="1" t="s">
         <v>315</v>
       </c>
@@ -6516,73 +6567,73 @@
         <v>316</v>
       </c>
       <c r="C148" s="1" t="s">
-        <v>671</v>
+        <v>669</v>
       </c>
       <c r="D148" s="24" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="E148" s="24"/>
       <c r="F148" s="24"/>
       <c r="G148" s="24"/>
     </row>
-    <row r="149" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A149" s="1" t="s">
-        <v>675</v>
+        <v>673</v>
       </c>
       <c r="B149" s="1" t="s">
+        <v>674</v>
+      </c>
+      <c r="C149" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D149" s="23" t="s">
         <v>676</v>
       </c>
-      <c r="C149" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="D149" s="23" t="s">
+      <c r="E149" s="23" t="s">
+        <v>677</v>
+      </c>
+      <c r="F149" s="23" t="s">
         <v>678</v>
-      </c>
-      <c r="E149" s="23" t="s">
-        <v>679</v>
-      </c>
-      <c r="F149" s="23" t="s">
-        <v>680</v>
       </c>
       <c r="G149" s="1" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="150" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A150" s="1" t="s">
-        <v>786</v>
+        <v>784</v>
       </c>
       <c r="B150" s="1" t="s">
-        <v>787</v>
+        <v>785</v>
       </c>
       <c r="C150" s="1" t="s">
         <v>143</v>
       </c>
       <c r="D150" s="24" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="E150" s="24"/>
       <c r="F150" s="24"/>
       <c r="G150" s="24"/>
     </row>
-    <row r="151" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A151" s="1" t="s">
-        <v>784</v>
+        <v>782</v>
       </c>
       <c r="B151" s="1" t="s">
-        <v>785</v>
+        <v>783</v>
       </c>
       <c r="C151" s="1" t="s">
         <v>143</v>
       </c>
       <c r="D151" s="24" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="E151" s="24"/>
       <c r="F151" s="24"/>
       <c r="G151" s="24"/>
     </row>
-    <row r="152" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A152" s="1" t="s">
         <v>318</v>
       </c>
@@ -6593,233 +6644,239 @@
         <v>43</v>
       </c>
       <c r="D152" s="24" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="E152" s="24"/>
       <c r="F152" s="24"/>
       <c r="G152" s="24"/>
     </row>
-    <row r="153" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A153" s="1" t="s">
+        <v>641</v>
+      </c>
+      <c r="B153" s="1" t="s">
+        <v>642</v>
+      </c>
+      <c r="C153" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D153" s="7" t="s">
+        <v>651</v>
+      </c>
+      <c r="E153" s="7" t="s">
         <v>643</v>
       </c>
-      <c r="B153" s="1" t="s">
+      <c r="F153" s="1" t="s">
         <v>644</v>
       </c>
-      <c r="C153" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="D153" s="7" t="s">
-        <v>653</v>
-      </c>
-      <c r="E153" s="7" t="s">
+      <c r="G153" s="1" t="s">
         <v>645</v>
       </c>
-      <c r="F153" s="1" t="s">
-        <v>646</v>
-      </c>
-      <c r="G153" s="1" t="s">
-        <v>647</v>
-      </c>
-    </row>
-    <row r="155" spans="1:8" x14ac:dyDescent="0.3">
+    </row>
+    <row r="155" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A155" s="1" t="s">
-        <v>322</v>
+        <v>667</v>
       </c>
       <c r="B155" s="1" t="s">
-        <v>324</v>
-      </c>
-      <c r="H155" s="1" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="156" spans="1:8" x14ac:dyDescent="0.3">
+        <v>668</v>
+      </c>
+      <c r="C155" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D155" s="1" t="s">
+        <v>680</v>
+      </c>
+      <c r="E155" s="1" t="s">
+        <v>681</v>
+      </c>
+      <c r="F155" s="1" t="s">
+        <v>682</v>
+      </c>
+      <c r="G155" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="156" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A156" s="1" t="s">
-        <v>669</v>
+        <v>323</v>
       </c>
       <c r="B156" s="1" t="s">
-        <v>670</v>
+        <v>325</v>
       </c>
       <c r="C156" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="D156" s="1" t="s">
-        <v>682</v>
-      </c>
-      <c r="E156" s="1" t="s">
-        <v>683</v>
-      </c>
-      <c r="F156" s="1" t="s">
-        <v>684</v>
+      <c r="D156" s="6" t="s">
+        <v>346</v>
+      </c>
+      <c r="E156" s="7" t="s">
+        <v>344</v>
+      </c>
+      <c r="F156" s="7" t="s">
+        <v>345</v>
       </c>
       <c r="G156" s="1" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="157" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A157" s="1" t="s">
-        <v>325</v>
+        <v>646</v>
       </c>
       <c r="B157" s="1" t="s">
-        <v>327</v>
+        <v>647</v>
       </c>
       <c r="C157" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="D157" s="6" t="s">
-        <v>348</v>
+      <c r="D157" s="7" t="s">
+        <v>648</v>
       </c>
       <c r="E157" s="7" t="s">
-        <v>346</v>
+        <v>649</v>
       </c>
       <c r="F157" s="7" t="s">
-        <v>347</v>
+        <v>650</v>
       </c>
       <c r="G157" s="1" t="s">
+        <v>645</v>
+      </c>
+    </row>
+    <row r="158" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A158" s="1" t="s">
+        <v>655</v>
+      </c>
+      <c r="B158" s="1" t="s">
+        <v>652</v>
+      </c>
+      <c r="C158" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D158" s="1" t="s">
+        <v>658</v>
+      </c>
+      <c r="E158" s="1" t="s">
+        <v>659</v>
+      </c>
+      <c r="F158" s="1" t="s">
+        <v>660</v>
+      </c>
+      <c r="G158" s="1" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="158" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A158" s="1" t="s">
-        <v>648</v>
-      </c>
-      <c r="B158" s="1" t="s">
-        <v>649</v>
-      </c>
-      <c r="C158" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="D158" s="7" t="s">
-        <v>650</v>
-      </c>
-      <c r="E158" s="7" t="s">
-        <v>651</v>
-      </c>
-      <c r="F158" s="7" t="s">
-        <v>652</v>
-      </c>
-      <c r="G158" s="1" t="s">
-        <v>647</v>
-      </c>
-    </row>
-    <row r="159" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A159" s="1" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="B159" s="1" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="C159" s="1" t="s">
         <v>43</v>
       </c>
       <c r="D159" s="1" t="s">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="E159" s="1" t="s">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="F159" s="1" t="s">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="G159" s="1" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="160" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A160" s="1" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="B160" s="1" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="C160" s="1" t="s">
         <v>43</v>
       </c>
       <c r="D160" s="1" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="E160" s="1" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="F160" s="1" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="G160" s="1" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="161" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A161" s="1" t="s">
-        <v>659</v>
+        <v>750</v>
       </c>
       <c r="B161" s="1" t="s">
-        <v>656</v>
+        <v>751</v>
       </c>
       <c r="C161" s="1" t="s">
         <v>43</v>
       </c>
       <c r="D161" s="1" t="s">
-        <v>666</v>
+        <v>754</v>
       </c>
       <c r="E161" s="1" t="s">
-        <v>667</v>
+        <v>753</v>
       </c>
       <c r="F161" s="1" t="s">
-        <v>668</v>
+        <v>752</v>
       </c>
       <c r="G161" s="1" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="162" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A162" s="1" t="s">
-        <v>752</v>
+        <v>829</v>
       </c>
       <c r="B162" s="1" t="s">
-        <v>753</v>
+        <v>830</v>
       </c>
       <c r="C162" s="1" t="s">
         <v>43</v>
       </c>
       <c r="D162" s="1" t="s">
-        <v>756</v>
+        <v>831</v>
       </c>
       <c r="E162" s="1" t="s">
-        <v>755</v>
+        <v>832</v>
       </c>
       <c r="F162" s="1" t="s">
-        <v>754</v>
+        <v>833</v>
       </c>
       <c r="G162" s="1" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="163" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A163" s="1" t="s">
-        <v>831</v>
+        <v>829</v>
       </c>
       <c r="B163" s="1" t="s">
-        <v>832</v>
+        <v>836</v>
       </c>
       <c r="C163" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="D163" s="1" t="s">
-        <v>833</v>
-      </c>
-      <c r="E163" s="1" t="s">
+      <c r="D163" s="15" t="s">
         <v>834</v>
       </c>
-      <c r="F163" s="1" t="s">
-        <v>835</v>
-      </c>
-      <c r="G163" s="1" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="164" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="E163" s="15"/>
+      <c r="F163" s="15"/>
+      <c r="G163" s="15"/>
+    </row>
+    <row r="164" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A164" s="1" t="s">
-        <v>831</v>
+        <v>837</v>
       </c>
       <c r="B164" s="1" t="s">
         <v>838</v>
@@ -6827,145 +6884,151 @@
       <c r="C164" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="D164" s="15" t="s">
-        <v>836</v>
-      </c>
-      <c r="E164" s="15"/>
-      <c r="F164" s="15"/>
-      <c r="G164" s="15"/>
-    </row>
-    <row r="166" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="D164" s="1" t="s">
+        <v>839</v>
+      </c>
+      <c r="E164" s="1" t="s">
+        <v>840</v>
+      </c>
+      <c r="F164" s="1" t="s">
+        <v>841</v>
+      </c>
+      <c r="G164" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="166" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A166" s="1" t="s">
-        <v>797</v>
+        <v>795</v>
       </c>
       <c r="B166" s="1" t="s">
-        <v>798</v>
+        <v>796</v>
       </c>
       <c r="C166" s="1" t="s">
         <v>43</v>
       </c>
       <c r="D166" s="24" t="s">
-        <v>807</v>
+        <v>805</v>
       </c>
       <c r="E166" s="24"/>
       <c r="F166" s="24"/>
       <c r="G166" s="24"/>
     </row>
-    <row r="167" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A167" s="1" t="s">
-        <v>795</v>
+        <v>793</v>
       </c>
       <c r="B167" s="1" t="s">
-        <v>796</v>
+        <v>794</v>
       </c>
       <c r="C167" s="1" t="s">
         <v>43</v>
       </c>
       <c r="D167" s="24" t="s">
-        <v>808</v>
+        <v>806</v>
       </c>
       <c r="E167" s="24"/>
       <c r="F167" s="24"/>
       <c r="G167" s="24"/>
     </row>
-    <row r="168" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A168" s="1" t="s">
-        <v>799</v>
+        <v>797</v>
       </c>
       <c r="B168" s="1" t="s">
-        <v>800</v>
+        <v>798</v>
       </c>
       <c r="C168" s="1" t="s">
         <v>43</v>
       </c>
       <c r="D168" s="24" t="s">
-        <v>808</v>
+        <v>806</v>
       </c>
       <c r="E168" s="24"/>
       <c r="F168" s="24"/>
       <c r="G168" s="24"/>
     </row>
-    <row r="170" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A170" s="1" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="B170" s="1" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="C170" s="1" t="s">
         <v>43</v>
       </c>
       <c r="D170" s="30" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="E170" s="30"/>
       <c r="F170" s="30"/>
       <c r="G170" s="30"/>
     </row>
-    <row r="171" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A171" s="1" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="B171" s="1" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="C171" s="1" t="s">
         <v>43</v>
       </c>
       <c r="D171" s="6" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="E171" s="7" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="F171" s="1" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="G171" s="1" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="172" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A172" s="1" t="s">
+        <v>498</v>
+      </c>
+      <c r="B172" s="1" t="s">
+        <v>499</v>
+      </c>
+      <c r="C172" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D172" s="7" t="s">
+        <v>503</v>
+      </c>
+      <c r="E172" s="1" t="s">
+        <v>502</v>
+      </c>
+      <c r="F172" s="1" t="s">
+        <v>501</v>
+      </c>
+      <c r="G172" s="1" t="s">
         <v>500</v>
       </c>
-      <c r="B172" s="1" t="s">
-        <v>501</v>
-      </c>
-      <c r="C172" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="D172" s="7" t="s">
-        <v>505</v>
-      </c>
-      <c r="E172" s="1" t="s">
-        <v>504</v>
-      </c>
-      <c r="F172" s="1" t="s">
-        <v>503</v>
-      </c>
-      <c r="G172" s="1" t="s">
-        <v>502</v>
-      </c>
-    </row>
-    <row r="173" spans="1:7" x14ac:dyDescent="0.3">
+    </row>
+    <row r="173" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A173" s="1" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="B173" s="1" t="s">
+        <v>367</v>
+      </c>
+      <c r="C173" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D173" s="6" t="s">
+        <v>370</v>
+      </c>
+      <c r="E173" s="7" t="s">
+        <v>368</v>
+      </c>
+      <c r="F173" s="7" t="s">
         <v>369</v>
-      </c>
-      <c r="C173" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="D173" s="6" t="s">
-        <v>372</v>
-      </c>
-      <c r="E173" s="7" t="s">
-        <v>370</v>
-      </c>
-      <c r="F173" s="7" t="s">
-        <v>371</v>
       </c>
       <c r="G173" s="1" t="s">
         <v>14</v>
@@ -7051,18 +7114,18 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A2:H134"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15.6" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="39.625" style="1" customWidth="1"/>
-    <col min="2" max="2" width="38.75" style="1" customWidth="1"/>
-    <col min="3" max="3" width="14.75" style="1" customWidth="1"/>
-    <col min="4" max="8" width="12.625" style="1" customWidth="1"/>
+    <col min="1" max="1" width="39.6640625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="40.88671875" style="1" customWidth="1"/>
+    <col min="3" max="3" width="14.77734375" style="1" customWidth="1"/>
+    <col min="4" max="8" width="12.6640625" style="1" customWidth="1"/>
     <col min="9" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A2" s="4" t="s">
         <v>44</v>
       </c>
@@ -7074,7 +7137,7 @@
       <c r="G2" s="4"/>
       <c r="H2" s="5"/>
     </row>
-    <row r="4" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="24" t="s">
         <v>202</v>
       </c>
@@ -7088,9 +7151,9 @@
         <v>56</v>
       </c>
     </row>
-    <row r="5" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="24" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="B5" s="24"/>
       <c r="C5" s="24"/>
@@ -7102,19 +7165,19 @@
         <v>48</v>
       </c>
     </row>
-    <row r="6" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="24"/>
       <c r="B6" s="24"/>
       <c r="C6" s="24"/>
       <c r="D6" s="32" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="E6" s="32"/>
       <c r="F6" s="13" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="7" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="25"/>
       <c r="B7" s="25"/>
       <c r="C7" s="37"/>
@@ -7126,7 +7189,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="8" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="25"/>
       <c r="B8" s="25"/>
       <c r="C8" s="25"/>
@@ -7138,26 +7201,26 @@
         <v>54</v>
       </c>
     </row>
-    <row r="9" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="24"/>
       <c r="B9" s="24"/>
       <c r="C9" s="24"/>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:8" ht="16.2" x14ac:dyDescent="0.4">
       <c r="A11" s="29" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="B11" s="29"/>
       <c r="C11" s="18"/>
       <c r="D11" s="26" t="s">
-        <v>579</v>
+        <v>577</v>
       </c>
       <c r="E11" s="26"/>
       <c r="F11" s="26"/>
       <c r="G11" s="26"/>
       <c r="H11" s="5"/>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A12" s="19" t="s">
         <v>160</v>
       </c>
@@ -7168,18 +7231,18 @@
         <v>42</v>
       </c>
       <c r="D12" s="3" t="s">
+        <v>351</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>352</v>
+      </c>
+      <c r="F12" s="36" t="s">
         <v>353</v>
-      </c>
-      <c r="E12" s="3" t="s">
-        <v>354</v>
-      </c>
-      <c r="F12" s="36" t="s">
-        <v>355</v>
       </c>
       <c r="G12" s="36"/>
       <c r="H12" s="2"/>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A13" s="1" t="s">
         <v>171</v>
       </c>
@@ -7196,12 +7259,12 @@
       <c r="F13" s="30"/>
       <c r="G13" s="30"/>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A14" s="1" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>180</v>
@@ -7213,97 +7276,97 @@
       <c r="F14" s="30"/>
       <c r="G14" s="30"/>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A15" s="1" t="s">
+        <v>399</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>400</v>
+      </c>
+      <c r="C15" s="1" t="s">
         <v>401</v>
       </c>
-      <c r="B15" s="1" t="s">
-        <v>402</v>
-      </c>
-      <c r="C15" s="1" t="s">
-        <v>403</v>
-      </c>
       <c r="D15" s="24" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="E15" s="24"/>
       <c r="F15" s="24"/>
       <c r="G15" s="24"/>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A16" s="1" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>180</v>
       </c>
       <c r="D16" s="34" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="E16" s="34"/>
       <c r="F16" s="34"/>
       <c r="G16" s="34"/>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A17" s="1" t="s">
-        <v>585</v>
+        <v>583</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>143</v>
       </c>
       <c r="D17" s="24" t="s">
-        <v>591</v>
+        <v>589</v>
       </c>
       <c r="E17" s="24"/>
       <c r="F17" s="24"/>
       <c r="G17" s="24"/>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A18" s="1" t="s">
+        <v>579</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>580</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D18" s="24" t="s">
         <v>581</v>
-      </c>
-      <c r="B18" s="1" t="s">
-        <v>582</v>
-      </c>
-      <c r="C18" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="D18" s="24" t="s">
-        <v>583</v>
       </c>
       <c r="E18" s="24"/>
       <c r="F18" s="24"/>
       <c r="G18" s="24"/>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A19" s="1" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>615</v>
+        <v>613</v>
       </c>
       <c r="C19" s="1" t="s">
         <v>143</v>
       </c>
       <c r="D19" s="24" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="E19" s="24"/>
       <c r="F19" s="24"/>
       <c r="G19" s="24"/>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A20" s="1" t="s">
-        <v>616</v>
+        <v>614</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>617</v>
+        <v>615</v>
       </c>
       <c r="C20" s="1" t="s">
         <v>43</v>
@@ -7315,92 +7378,92 @@
       <c r="F20" s="30"/>
       <c r="G20" s="30"/>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A21" s="1" t="s">
-        <v>717</v>
+        <v>715</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>718</v>
+        <v>716</v>
       </c>
       <c r="C21" s="1" t="s">
         <v>43</v>
       </c>
       <c r="D21" s="34" t="s">
-        <v>723</v>
+        <v>721</v>
       </c>
       <c r="E21" s="34"/>
       <c r="F21" s="34"/>
       <c r="G21" s="34"/>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A22" s="1" t="s">
-        <v>716</v>
+        <v>714</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>719</v>
+        <v>717</v>
       </c>
       <c r="C22" s="1" t="s">
         <v>43</v>
       </c>
       <c r="D22" s="24" t="s">
-        <v>722</v>
+        <v>720</v>
       </c>
       <c r="E22" s="24"/>
       <c r="F22" s="24"/>
       <c r="G22" s="24"/>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A23" s="1" t="s">
-        <v>738</v>
+        <v>736</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>739</v>
+        <v>737</v>
       </c>
       <c r="C23" s="1" t="s">
         <v>43</v>
       </c>
       <c r="D23" s="24" t="s">
-        <v>724</v>
+        <v>722</v>
       </c>
       <c r="E23" s="24"/>
       <c r="F23" s="24"/>
       <c r="G23" s="24"/>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A24" s="1" t="s">
-        <v>793</v>
+        <v>791</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>794</v>
+        <v>792</v>
       </c>
       <c r="C24" s="1" t="s">
         <v>143</v>
       </c>
       <c r="D24" s="24" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="E24" s="24"/>
       <c r="F24" s="24"/>
       <c r="G24" s="24"/>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A25" s="1" t="s">
-        <v>826</v>
+        <v>824</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>827</v>
+        <v>825</v>
       </c>
       <c r="C25" s="1" t="s">
         <v>43</v>
       </c>
       <c r="D25" s="24" t="s">
-        <v>825</v>
+        <v>823</v>
       </c>
       <c r="E25" s="24"/>
       <c r="F25" s="24"/>
       <c r="G25" s="24"/>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A26" s="1" t="s">
         <v>172</v>
       </c>
@@ -7417,12 +7480,12 @@
       <c r="F26" s="30"/>
       <c r="G26" s="30"/>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A27" s="1" t="s">
         <v>173</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>828</v>
+        <v>826</v>
       </c>
       <c r="C27" s="1" t="s">
         <v>179</v>
@@ -7434,7 +7497,7 @@
       <c r="F27" s="30"/>
       <c r="G27" s="30"/>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A28" s="1" t="s">
         <v>175</v>
       </c>
@@ -7445,13 +7508,13 @@
         <v>179</v>
       </c>
       <c r="D28" s="24" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="E28" s="24"/>
       <c r="F28" s="24"/>
       <c r="G28" s="24"/>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A29" s="1" t="s">
         <v>165</v>
       </c>
@@ -7468,7 +7531,7 @@
       <c r="F29" s="30"/>
       <c r="G29" s="30"/>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A30" s="1" t="s">
         <v>166</v>
       </c>
@@ -7479,30 +7542,30 @@
         <v>180</v>
       </c>
       <c r="D30" s="24" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="E30" s="24"/>
       <c r="F30" s="24"/>
       <c r="G30" s="24"/>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A31" s="1" t="s">
-        <v>822</v>
+        <v>820</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>823</v>
+        <v>821</v>
       </c>
       <c r="C31" s="1" t="s">
         <v>43</v>
       </c>
       <c r="D31" s="24" t="s">
-        <v>830</v>
+        <v>828</v>
       </c>
       <c r="E31" s="24"/>
       <c r="F31" s="24"/>
       <c r="G31" s="24"/>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A32" s="1" t="s">
         <v>177</v>
       </c>
@@ -7519,7 +7582,7 @@
       <c r="F32" s="30"/>
       <c r="G32" s="30"/>
     </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A33" s="1" t="s">
         <v>169</v>
       </c>
@@ -7530,18 +7593,18 @@
         <v>180</v>
       </c>
       <c r="D33" s="24" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="E33" s="24"/>
       <c r="F33" s="24"/>
       <c r="G33" s="24"/>
     </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A34" s="1" t="s">
-        <v>750</v>
+        <v>748</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>751</v>
+        <v>749</v>
       </c>
       <c r="C34" s="1" t="s">
         <v>43</v>
@@ -7553,7 +7616,7 @@
       <c r="F34" s="30"/>
       <c r="G34" s="30"/>
     </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A36" s="1" t="s">
         <v>203</v>
       </c>
@@ -7564,7 +7627,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A37" s="1" t="s">
         <v>205</v>
       </c>
@@ -7575,7 +7638,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A38" s="1" t="s">
         <v>207</v>
       </c>
@@ -7586,7 +7649,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A39" s="1" t="s">
         <v>209</v>
       </c>
@@ -7597,7 +7660,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A40" s="1" t="s">
         <v>211</v>
       </c>
@@ -7608,7 +7671,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A41" s="16" t="s">
         <v>214</v>
       </c>
@@ -7619,7 +7682,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A42" s="16" t="s">
         <v>216</v>
       </c>
@@ -7630,13 +7693,13 @@
         <v>43</v>
       </c>
       <c r="D42" s="35" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="E42" s="35"/>
       <c r="F42" s="35"/>
       <c r="G42" s="35"/>
     </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A43" s="16" t="s">
         <v>218</v>
       </c>
@@ -7647,7 +7710,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A44" s="16" t="s">
         <v>220</v>
       </c>
@@ -7658,7 +7721,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A45" s="16" t="s">
         <v>222</v>
       </c>
@@ -7669,24 +7732,24 @@
         <v>213</v>
       </c>
     </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A46" s="16" t="s">
-        <v>791</v>
+        <v>789</v>
       </c>
       <c r="B46" s="16" t="s">
-        <v>792</v>
+        <v>790</v>
       </c>
       <c r="C46" s="1" t="s">
         <v>143</v>
       </c>
       <c r="D46" s="24" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="E46" s="24"/>
       <c r="F46" s="24"/>
       <c r="G46" s="24"/>
     </row>
-    <row r="47" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A47" s="16" t="s">
         <v>224</v>
       </c>
@@ -7697,42 +7760,42 @@
         <v>43</v>
       </c>
       <c r="D47" s="15" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="E47" s="6" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="F47" s="7" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="G47" s="1" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A48" s="1" t="s">
-        <v>624</v>
+        <v>622</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>625</v>
+        <v>623</v>
       </c>
       <c r="C48" s="1" t="s">
         <v>43</v>
       </c>
       <c r="D48" s="6" t="s">
+        <v>616</v>
+      </c>
+      <c r="E48" s="6" t="s">
+        <v>617</v>
+      </c>
+      <c r="F48" s="6" t="s">
         <v>618</v>
       </c>
-      <c r="E48" s="6" t="s">
+      <c r="G48" s="1" t="s">
         <v>619</v>
       </c>
-      <c r="F48" s="6" t="s">
-        <v>620</v>
-      </c>
-      <c r="G48" s="1" t="s">
-        <v>621</v>
-      </c>
-    </row>
-    <row r="50" spans="1:8" x14ac:dyDescent="0.3">
+    </row>
+    <row r="50" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A50" s="1" t="s">
         <v>226</v>
       </c>
@@ -7743,7 +7806,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="51" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A51" s="1" t="s">
         <v>228</v>
       </c>
@@ -7754,7 +7817,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="52" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A52" s="1" t="s">
         <v>230</v>
       </c>
@@ -7765,7 +7828,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="53" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A53" s="1" t="s">
         <v>232</v>
       </c>
@@ -7776,7 +7839,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="54" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A54" s="1" t="s">
         <v>234</v>
       </c>
@@ -7787,7 +7850,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="55" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A55" s="1" t="s">
         <v>236</v>
       </c>
@@ -7810,7 +7873,7 @@
         <v>309</v>
       </c>
     </row>
-    <row r="56" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A56" s="1" t="s">
         <v>238</v>
       </c>
@@ -7821,7 +7884,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="57" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A57" s="1" t="s">
         <v>240</v>
       </c>
@@ -7832,7 +7895,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="58" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A58" s="1" t="s">
         <v>242</v>
       </c>
@@ -7843,7 +7906,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="60" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A60" s="1" t="s">
         <v>244</v>
       </c>
@@ -7854,7 +7917,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="61" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A61" s="1" t="s">
         <v>246</v>
       </c>
@@ -7865,7 +7928,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="62" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A62" s="1" t="s">
         <v>248</v>
       </c>
@@ -7876,7 +7939,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="63" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A63" s="1" t="s">
         <v>250</v>
       </c>
@@ -7887,7 +7950,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="64" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A64" s="1" t="s">
         <v>252</v>
       </c>
@@ -7898,24 +7961,24 @@
         <v>213</v>
       </c>
     </row>
-    <row r="65" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A65" s="1" t="s">
+        <v>396</v>
+      </c>
+      <c r="B65" s="1" t="s">
+        <v>397</v>
+      </c>
+      <c r="C65" s="1" t="s">
         <v>398</v>
       </c>
-      <c r="B65" s="1" t="s">
-        <v>399</v>
-      </c>
-      <c r="C65" s="1" t="s">
-        <v>400</v>
-      </c>
       <c r="D65" s="24" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="E65" s="24"/>
       <c r="F65" s="24"/>
       <c r="G65" s="24"/>
     </row>
-    <row r="67" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A67" s="1" t="s">
         <v>254</v>
       </c>
@@ -7926,42 +7989,42 @@
         <v>43</v>
       </c>
       <c r="D67" s="7" t="s">
-        <v>815</v>
+        <v>813</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>814</v>
+        <v>812</v>
       </c>
       <c r="F67" s="1" t="s">
-        <v>813</v>
+        <v>811</v>
       </c>
       <c r="G67" s="1" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="68" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A68" s="1" t="s">
-        <v>811</v>
+        <v>809</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>812</v>
+        <v>810</v>
       </c>
       <c r="C68" s="1" t="s">
         <v>43</v>
       </c>
       <c r="D68" s="7" t="s">
-        <v>818</v>
+        <v>816</v>
       </c>
       <c r="E68" s="7" t="s">
-        <v>817</v>
+        <v>815</v>
       </c>
       <c r="F68" s="1" t="s">
-        <v>816</v>
+        <v>814</v>
       </c>
       <c r="G68" s="1" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="69" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A69" s="1" t="s">
         <v>256</v>
       </c>
@@ -7972,7 +8035,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="70" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A70" s="1" t="s">
         <v>258</v>
       </c>
@@ -7983,7 +8046,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="71" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A71" s="1" t="s">
         <v>260</v>
       </c>
@@ -7994,7 +8057,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="72" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A72" s="1" t="s">
         <v>262</v>
       </c>
@@ -8005,7 +8068,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="73" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A73" s="1" t="s">
         <v>264</v>
       </c>
@@ -8016,7 +8079,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="74" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A74" s="1" t="s">
         <v>266</v>
       </c>
@@ -8027,7 +8090,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="75" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A75" s="1" t="s">
         <v>268</v>
       </c>
@@ -8038,7 +8101,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="76" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A76" s="1" t="s">
         <v>270</v>
       </c>
@@ -8049,7 +8112,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="77" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A77" s="1" t="s">
         <v>272</v>
       </c>
@@ -8060,7 +8123,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="79" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A79" s="1" t="s">
         <v>274</v>
       </c>
@@ -8071,7 +8134,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="80" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A80" s="1" t="s">
         <v>276</v>
       </c>
@@ -8082,7 +8145,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="81" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A81" s="1" t="s">
         <v>278</v>
       </c>
@@ -8093,7 +8156,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="82" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A82" s="1" t="s">
         <v>280</v>
       </c>
@@ -8104,7 +8167,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="83" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A83" s="1" t="s">
         <v>282</v>
       </c>
@@ -8115,7 +8178,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="84" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A84" s="1" t="s">
         <v>284</v>
       </c>
@@ -8126,7 +8189,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="85" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A85" s="1" t="s">
         <v>286</v>
       </c>
@@ -8137,7 +8200,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="86" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A86" s="1" t="s">
         <v>288</v>
       </c>
@@ -8148,7 +8211,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="87" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A87" s="1" t="s">
         <v>290</v>
       </c>
@@ -8159,7 +8222,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="89" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A89" s="1" t="s">
         <v>292</v>
       </c>
@@ -8170,7 +8233,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="90" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A90" s="1" t="s">
         <v>294</v>
       </c>
@@ -8181,13 +8244,13 @@
         <v>43</v>
       </c>
       <c r="D90" s="24" t="s">
-        <v>714</v>
+        <v>712</v>
       </c>
       <c r="E90" s="24"/>
       <c r="F90" s="24"/>
       <c r="G90" s="24"/>
     </row>
-    <row r="91" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A91" s="16" t="s">
         <v>296</v>
       </c>
@@ -8198,18 +8261,18 @@
         <v>43</v>
       </c>
       <c r="D91" s="24" t="s">
-        <v>713</v>
+        <v>711</v>
       </c>
       <c r="E91" s="24"/>
       <c r="F91" s="24"/>
       <c r="G91" s="24"/>
     </row>
-    <row r="92" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A92" s="16" t="s">
-        <v>702</v>
+        <v>700</v>
       </c>
       <c r="B92" s="16" t="s">
-        <v>703</v>
+        <v>701</v>
       </c>
       <c r="C92" s="1" t="s">
         <v>43</v>
@@ -8221,12 +8284,12 @@
       <c r="F92" s="30"/>
       <c r="G92" s="30"/>
     </row>
-    <row r="93" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A93" s="16" t="s">
-        <v>704</v>
+        <v>702</v>
       </c>
       <c r="B93" s="16" t="s">
-        <v>705</v>
+        <v>703</v>
       </c>
       <c r="C93" s="1" t="s">
         <v>43</v>
@@ -8238,24 +8301,24 @@
       <c r="F93" s="30"/>
       <c r="G93" s="30"/>
     </row>
-    <row r="94" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A94" s="16" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="B94" s="16" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="C94" s="1" t="s">
         <v>43</v>
       </c>
       <c r="D94" s="24" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="E94" s="24"/>
       <c r="F94" s="24"/>
       <c r="G94" s="24"/>
     </row>
-    <row r="95" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A95" s="1" t="s">
         <v>298</v>
       </c>
@@ -8266,13 +8329,13 @@
         <v>143</v>
       </c>
       <c r="D95" s="24" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="E95" s="24"/>
       <c r="F95" s="24"/>
       <c r="G95" s="24"/>
     </row>
-    <row r="96" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A96" s="1" t="s">
         <v>300</v>
       </c>
@@ -8283,13 +8346,13 @@
         <v>143</v>
       </c>
       <c r="D96" s="24" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="E96" s="24"/>
       <c r="F96" s="24"/>
       <c r="G96" s="24"/>
     </row>
-    <row r="97" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A97" s="1" t="s">
         <v>302</v>
       </c>
@@ -8300,18 +8363,18 @@
         <v>143</v>
       </c>
       <c r="D97" s="24" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="E97" s="24"/>
       <c r="F97" s="24"/>
       <c r="G97" s="24"/>
     </row>
-    <row r="99" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A99" s="1" t="s">
-        <v>605</v>
+        <v>603</v>
       </c>
       <c r="B99" s="1" t="s">
-        <v>606</v>
+        <v>604</v>
       </c>
       <c r="C99" s="1" t="s">
         <v>43</v>
@@ -8323,12 +8386,12 @@
       <c r="F99" s="30"/>
       <c r="G99" s="30"/>
     </row>
-    <row r="100" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A100" s="1" t="s">
-        <v>607</v>
+        <v>605</v>
       </c>
       <c r="B100" s="1" t="s">
-        <v>608</v>
+        <v>606</v>
       </c>
       <c r="C100" s="1" t="s">
         <v>43</v>
@@ -8340,7 +8403,7 @@
       <c r="F100" s="30"/>
       <c r="G100" s="30"/>
     </row>
-    <row r="101" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A101" s="1" t="s">
         <v>124</v>
       </c>
@@ -8351,13 +8414,13 @@
         <v>43</v>
       </c>
       <c r="D101" s="34" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="E101" s="34"/>
       <c r="F101" s="34"/>
       <c r="G101" s="34"/>
     </row>
-    <row r="102" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A102" s="1" t="s">
         <v>126</v>
       </c>
@@ -8374,7 +8437,7 @@
       <c r="F102" s="30"/>
       <c r="G102" s="30"/>
     </row>
-    <row r="103" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A103" s="1" t="s">
         <v>128</v>
       </c>
@@ -8391,46 +8454,46 @@
       <c r="F103" s="30"/>
       <c r="G103" s="30"/>
     </row>
-    <row r="104" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A104" s="1" t="s">
-        <v>759</v>
+        <v>757</v>
       </c>
       <c r="B104" s="1" t="s">
-        <v>760</v>
+        <v>758</v>
       </c>
       <c r="C104" s="1" t="s">
         <v>43</v>
       </c>
       <c r="D104" s="24" t="s">
-        <v>768</v>
+        <v>766</v>
       </c>
       <c r="E104" s="24"/>
       <c r="F104" s="24"/>
       <c r="G104" s="24"/>
     </row>
-    <row r="105" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A105" s="1" t="s">
-        <v>758</v>
+        <v>756</v>
       </c>
       <c r="B105" s="1" t="s">
-        <v>764</v>
+        <v>762</v>
       </c>
       <c r="C105" s="1" t="s">
         <v>43</v>
       </c>
       <c r="D105" s="24" t="s">
-        <v>769</v>
+        <v>767</v>
       </c>
       <c r="E105" s="24"/>
       <c r="F105" s="24"/>
       <c r="G105" s="24"/>
     </row>
-    <row r="106" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A106" s="1" t="s">
-        <v>637</v>
+        <v>635</v>
       </c>
       <c r="B106" s="1" t="s">
-        <v>638</v>
+        <v>636</v>
       </c>
       <c r="C106" s="1" t="s">
         <v>43</v>
@@ -8442,7 +8505,7 @@
       <c r="F106" s="30"/>
       <c r="G106" s="30"/>
     </row>
-    <row r="108" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A108" s="1" t="s">
         <v>312</v>
       </c>
@@ -8453,81 +8516,81 @@
         <v>143</v>
       </c>
       <c r="D108" s="24" t="s">
-        <v>788</v>
+        <v>786</v>
       </c>
       <c r="E108" s="24"/>
       <c r="F108" s="24"/>
       <c r="G108" s="24"/>
     </row>
-    <row r="109" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A109" s="1" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="B109" s="1" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="C109" s="1" t="s">
-        <v>671</v>
+        <v>669</v>
       </c>
       <c r="D109" s="24" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="E109" s="24"/>
       <c r="F109" s="24"/>
       <c r="G109" s="24"/>
     </row>
-    <row r="110" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A110" s="1" t="s">
+        <v>673</v>
+      </c>
+      <c r="B110" s="1" t="s">
+        <v>674</v>
+      </c>
+      <c r="C110" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D110" s="24" t="s">
         <v>675</v>
-      </c>
-      <c r="B110" s="1" t="s">
-        <v>676</v>
-      </c>
-      <c r="C110" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="D110" s="24" t="s">
-        <v>677</v>
       </c>
       <c r="E110" s="24"/>
       <c r="F110" s="24"/>
       <c r="G110" s="24"/>
     </row>
-    <row r="111" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A111" s="1" t="s">
-        <v>786</v>
+        <v>784</v>
       </c>
       <c r="B111" s="1" t="s">
-        <v>787</v>
+        <v>785</v>
       </c>
       <c r="C111" s="1" t="s">
         <v>143</v>
       </c>
       <c r="D111" s="24" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="E111" s="24"/>
       <c r="F111" s="24"/>
       <c r="G111" s="24"/>
     </row>
-    <row r="112" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A112" s="1" t="s">
-        <v>784</v>
+        <v>782</v>
       </c>
       <c r="B112" s="1" t="s">
-        <v>785</v>
+        <v>783</v>
       </c>
       <c r="C112" s="1" t="s">
         <v>143</v>
       </c>
       <c r="D112" s="24" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="E112" s="24"/>
       <c r="F112" s="24"/>
       <c r="G112" s="24"/>
     </row>
-    <row r="113" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A113" s="1" t="s">
         <v>317</v>
       </c>
@@ -8538,126 +8601,132 @@
         <v>43</v>
       </c>
       <c r="D113" s="24" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="E113" s="24"/>
       <c r="F113" s="24"/>
       <c r="G113" s="24"/>
     </row>
-    <row r="114" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A114" s="1" t="s">
-        <v>643</v>
+        <v>641</v>
       </c>
       <c r="B114" s="1" t="s">
-        <v>644</v>
+        <v>642</v>
       </c>
       <c r="C114" s="1" t="s">
         <v>43</v>
       </c>
       <c r="D114" s="24" t="s">
-        <v>681</v>
+        <v>679</v>
       </c>
       <c r="E114" s="24"/>
       <c r="F114" s="24"/>
       <c r="G114" s="24"/>
     </row>
-    <row r="116" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A116" s="1" t="s">
-        <v>321</v>
+        <v>667</v>
       </c>
       <c r="B116" s="1" t="s">
+        <v>668</v>
+      </c>
+      <c r="C116" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D116" s="24" t="s">
+        <v>683</v>
+      </c>
+      <c r="E116" s="24"/>
+      <c r="F116" s="24"/>
+      <c r="G116" s="24"/>
+    </row>
+    <row r="117" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A117" s="1" t="s">
         <v>323</v>
       </c>
-      <c r="H116" s="1" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="117" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A117" s="1" t="s">
-        <v>669</v>
-      </c>
       <c r="B117" s="1" t="s">
-        <v>670</v>
+        <v>324</v>
       </c>
       <c r="C117" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="D117" s="24" t="s">
-        <v>685</v>
-      </c>
-      <c r="E117" s="24"/>
-      <c r="F117" s="24"/>
-      <c r="G117" s="24"/>
-    </row>
-    <row r="118" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="D117" s="6" t="s">
+        <v>346</v>
+      </c>
+      <c r="E117" s="7" t="s">
+        <v>344</v>
+      </c>
+      <c r="F117" s="7" t="s">
+        <v>345</v>
+      </c>
+      <c r="G117" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="118" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A118" s="1" t="s">
-        <v>325</v>
+        <v>646</v>
       </c>
       <c r="B118" s="1" t="s">
-        <v>326</v>
+        <v>647</v>
       </c>
       <c r="C118" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="D118" s="6" t="s">
-        <v>348</v>
+      <c r="D118" s="7" t="s">
+        <v>648</v>
       </c>
       <c r="E118" s="7" t="s">
-        <v>346</v>
+        <v>649</v>
       </c>
       <c r="F118" s="7" t="s">
-        <v>347</v>
+        <v>650</v>
       </c>
       <c r="G118" s="1" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="119" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A119" s="1" t="s">
-        <v>648</v>
+        <v>655</v>
       </c>
       <c r="B119" s="1" t="s">
-        <v>649</v>
+        <v>652</v>
       </c>
       <c r="C119" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="D119" s="7" t="s">
-        <v>650</v>
-      </c>
-      <c r="E119" s="7" t="s">
-        <v>651</v>
-      </c>
-      <c r="F119" s="7" t="s">
-        <v>652</v>
-      </c>
-      <c r="G119" s="1" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="120" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="D119" s="24" t="s">
+        <v>685</v>
+      </c>
+      <c r="E119" s="24"/>
+      <c r="F119" s="24"/>
+      <c r="G119" s="24"/>
+    </row>
+    <row r="120" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A120" s="1" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="B120" s="1" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="C120" s="1" t="s">
         <v>43</v>
       </c>
       <c r="D120" s="24" t="s">
-        <v>687</v>
+        <v>684</v>
       </c>
       <c r="E120" s="24"/>
       <c r="F120" s="24"/>
       <c r="G120" s="24"/>
     </row>
-    <row r="121" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A121" s="1" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="B121" s="1" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="C121" s="1" t="s">
         <v>43</v>
@@ -8669,60 +8738,60 @@
       <c r="F121" s="24"/>
       <c r="G121" s="24"/>
     </row>
-    <row r="122" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A122" s="1" t="s">
-        <v>659</v>
+        <v>750</v>
       </c>
       <c r="B122" s="1" t="s">
-        <v>656</v>
+        <v>751</v>
       </c>
       <c r="C122" s="1" t="s">
         <v>43</v>
       </c>
       <c r="D122" s="24" t="s">
-        <v>688</v>
+        <v>755</v>
       </c>
       <c r="E122" s="24"/>
       <c r="F122" s="24"/>
       <c r="G122" s="24"/>
     </row>
-    <row r="123" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A123" s="1" t="s">
-        <v>752</v>
+        <v>829</v>
       </c>
       <c r="B123" s="1" t="s">
-        <v>753</v>
+        <v>830</v>
       </c>
       <c r="C123" s="1" t="s">
         <v>43</v>
       </c>
       <c r="D123" s="24" t="s">
-        <v>757</v>
+        <v>835</v>
       </c>
       <c r="E123" s="24"/>
       <c r="F123" s="24"/>
       <c r="G123" s="24"/>
     </row>
-    <row r="124" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A124" s="1" t="s">
-        <v>831</v>
+        <v>829</v>
       </c>
       <c r="B124" s="1" t="s">
-        <v>832</v>
+        <v>836</v>
       </c>
       <c r="C124" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="D124" s="24" t="s">
+      <c r="D124" s="15" t="s">
+        <v>834</v>
+      </c>
+      <c r="E124" s="15"/>
+      <c r="F124" s="15"/>
+      <c r="G124" s="15"/>
+    </row>
+    <row r="125" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A125" s="1" t="s">
         <v>837</v>
-      </c>
-      <c r="E124" s="24"/>
-      <c r="F124" s="24"/>
-      <c r="G124" s="24"/>
-    </row>
-    <row r="125" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A125" s="1" t="s">
-        <v>831</v>
       </c>
       <c r="B125" s="1" t="s">
         <v>838</v>
@@ -8730,139 +8799,139 @@
       <c r="C125" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="D125" s="15" t="s">
-        <v>836</v>
-      </c>
-      <c r="E125" s="15"/>
-      <c r="F125" s="15"/>
-      <c r="G125" s="15"/>
-    </row>
-    <row r="127" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="D125" s="24" t="s">
+        <v>842</v>
+      </c>
+      <c r="E125" s="24"/>
+      <c r="F125" s="24"/>
+      <c r="G125" s="24"/>
+    </row>
+    <row r="127" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A127" s="1" t="s">
-        <v>797</v>
+        <v>795</v>
       </c>
       <c r="B127" s="1" t="s">
-        <v>798</v>
+        <v>796</v>
       </c>
       <c r="C127" s="1" t="s">
         <v>43</v>
       </c>
       <c r="D127" s="24" t="s">
-        <v>806</v>
+        <v>804</v>
       </c>
       <c r="E127" s="24"/>
       <c r="F127" s="24"/>
       <c r="G127" s="24"/>
     </row>
-    <row r="128" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A128" s="1" t="s">
-        <v>795</v>
+        <v>793</v>
       </c>
       <c r="B128" s="1" t="s">
-        <v>796</v>
+        <v>794</v>
       </c>
       <c r="C128" s="1" t="s">
         <v>43</v>
       </c>
       <c r="D128" s="34" t="s">
-        <v>805</v>
+        <v>803</v>
       </c>
       <c r="E128" s="34"/>
       <c r="F128" s="34"/>
       <c r="G128" s="34"/>
     </row>
-    <row r="129" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A129" s="1" t="s">
-        <v>799</v>
+        <v>797</v>
       </c>
       <c r="B129" s="1" t="s">
-        <v>800</v>
+        <v>798</v>
       </c>
       <c r="C129" s="1" t="s">
         <v>43</v>
       </c>
       <c r="D129" s="34" t="s">
-        <v>804</v>
+        <v>802</v>
       </c>
       <c r="E129" s="34"/>
       <c r="F129" s="34"/>
       <c r="G129" s="34"/>
     </row>
-    <row r="131" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A131" s="1" t="s">
+        <v>333</v>
+      </c>
+      <c r="B131" s="1" t="s">
+        <v>334</v>
+      </c>
+      <c r="C131" s="1" t="s">
+        <v>357</v>
+      </c>
+      <c r="D131" s="6" t="s">
+        <v>358</v>
+      </c>
+      <c r="E131" s="7" t="s">
+        <v>359</v>
+      </c>
+      <c r="F131" s="7" t="s">
+        <v>360</v>
+      </c>
+      <c r="G131" s="1" t="s">
+        <v>361</v>
+      </c>
+      <c r="H131" s="1" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="132" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A132" s="1" t="s">
         <v>335</v>
       </c>
-      <c r="B131" s="1" t="s">
+      <c r="B132" s="1" t="s">
         <v>336</v>
       </c>
-      <c r="C131" s="1" t="s">
-        <v>359</v>
-      </c>
-      <c r="D131" s="6" t="s">
-        <v>360</v>
-      </c>
-      <c r="E131" s="7" t="s">
-        <v>361</v>
-      </c>
-      <c r="F131" s="7" t="s">
+    </row>
+    <row r="133" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A133" s="1" t="s">
+        <v>337</v>
+      </c>
+      <c r="B133" s="1" t="s">
+        <v>338</v>
+      </c>
+      <c r="C133" s="1" t="s">
         <v>362</v>
       </c>
-      <c r="G131" s="1" t="s">
+      <c r="D133" s="7" t="s">
         <v>363</v>
       </c>
-    </row>
-    <row r="132" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A132" s="1" t="s">
-        <v>337</v>
-      </c>
-      <c r="B132" s="1" t="s">
-        <v>338</v>
-      </c>
-      <c r="H132" s="1" t="s">
+      <c r="E133" s="7" t="s">
+        <v>364</v>
+      </c>
+      <c r="F133" s="1" t="s">
+        <v>365</v>
+      </c>
+      <c r="G133" s="1" t="s">
+        <v>366</v>
+      </c>
+      <c r="H133" s="1" t="s">
         <v>213</v>
       </c>
     </row>
-    <row r="133" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A133" s="1" t="s">
+    <row r="134" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A134" s="1" t="s">
         <v>339</v>
       </c>
-      <c r="B133" s="1" t="s">
+      <c r="B134" s="1" t="s">
         <v>340</v>
       </c>
-      <c r="C133" s="1" t="s">
-        <v>364</v>
-      </c>
-      <c r="D133" s="7" t="s">
-        <v>365</v>
-      </c>
-      <c r="E133" s="7" t="s">
-        <v>366</v>
-      </c>
-      <c r="F133" s="1" t="s">
-        <v>367</v>
-      </c>
-      <c r="G133" s="1" t="s">
-        <v>368</v>
-      </c>
-    </row>
-    <row r="134" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A134" s="1" t="s">
-        <v>341</v>
-      </c>
-      <c r="B134" s="1" t="s">
-        <v>342</v>
-      </c>
-      <c r="H134" s="1" t="s">
-        <v>213</v>
-      </c>
     </row>
   </sheetData>
-  <mergeCells count="71">
+  <mergeCells count="72">
     <mergeCell ref="D103:G103"/>
     <mergeCell ref="D23:G23"/>
     <mergeCell ref="D21:G21"/>
     <mergeCell ref="D22:G22"/>
-    <mergeCell ref="D120:G120"/>
+    <mergeCell ref="D119:G119"/>
     <mergeCell ref="D32:G32"/>
     <mergeCell ref="D95:G95"/>
     <mergeCell ref="D96:G96"/>
@@ -8872,6 +8941,7 @@
     <mergeCell ref="D31:G31"/>
     <mergeCell ref="D100:G100"/>
     <mergeCell ref="D24:G24"/>
+    <mergeCell ref="D111:G111"/>
     <mergeCell ref="A4:C4"/>
     <mergeCell ref="D4:E4"/>
     <mergeCell ref="A5:C5"/>
@@ -8886,7 +8956,7 @@
     <mergeCell ref="A11:B11"/>
     <mergeCell ref="D99:G99"/>
     <mergeCell ref="D102:G102"/>
-    <mergeCell ref="D117:G117"/>
+    <mergeCell ref="D116:G116"/>
     <mergeCell ref="D11:G11"/>
     <mergeCell ref="D13:G13"/>
     <mergeCell ref="D14:G14"/>
@@ -8899,7 +8969,6 @@
     <mergeCell ref="D93:G93"/>
     <mergeCell ref="D91:G91"/>
     <mergeCell ref="D90:G90"/>
-    <mergeCell ref="D111:G111"/>
     <mergeCell ref="D17:G17"/>
     <mergeCell ref="D18:G18"/>
     <mergeCell ref="D65:G65"/>
@@ -8917,18 +8986,19 @@
     <mergeCell ref="D127:G127"/>
     <mergeCell ref="D128:G128"/>
     <mergeCell ref="D129:G129"/>
-    <mergeCell ref="D123:G123"/>
+    <mergeCell ref="D122:G122"/>
     <mergeCell ref="D104:G104"/>
     <mergeCell ref="D105:G105"/>
     <mergeCell ref="D106:G106"/>
     <mergeCell ref="D112:G112"/>
     <mergeCell ref="D108:G108"/>
-    <mergeCell ref="D122:G122"/>
+    <mergeCell ref="D121:G121"/>
     <mergeCell ref="D109:G109"/>
     <mergeCell ref="D110:G110"/>
     <mergeCell ref="D114:G114"/>
-    <mergeCell ref="D121:G121"/>
-    <mergeCell ref="D124:G124"/>
+    <mergeCell ref="D120:G120"/>
+    <mergeCell ref="D123:G123"/>
+    <mergeCell ref="D125:G125"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -8938,18 +9008,18 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A2:H119"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15.6" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="39.625" style="1" customWidth="1"/>
-    <col min="2" max="2" width="38.75" style="1" customWidth="1"/>
-    <col min="3" max="3" width="14.75" style="1" customWidth="1"/>
-    <col min="4" max="8" width="12.625" style="1" customWidth="1"/>
+    <col min="1" max="1" width="39.6640625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="38.77734375" style="1" customWidth="1"/>
+    <col min="3" max="3" width="14.77734375" style="1" customWidth="1"/>
+    <col min="4" max="8" width="12.6640625" style="1" customWidth="1"/>
     <col min="9" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A2" s="4" t="s">
         <v>44</v>
       </c>
@@ -8961,7 +9031,7 @@
       <c r="G2" s="4"/>
       <c r="H2" s="5"/>
     </row>
-    <row r="4" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="24" t="s">
         <v>202</v>
       </c>
@@ -8975,9 +9045,9 @@
         <v>56</v>
       </c>
     </row>
-    <row r="5" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="24" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="B5" s="24"/>
       <c r="C5" s="24"/>
@@ -8989,19 +9059,19 @@
         <v>48</v>
       </c>
     </row>
-    <row r="6" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="24"/>
       <c r="B6" s="24"/>
       <c r="C6" s="24"/>
       <c r="D6" s="32" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="E6" s="32"/>
       <c r="F6" s="13" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="7" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="25"/>
       <c r="B7" s="25"/>
       <c r="C7" s="37"/>
@@ -9013,7 +9083,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="8" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="25"/>
       <c r="B8" s="25"/>
       <c r="C8" s="25"/>
@@ -9025,26 +9095,26 @@
         <v>54</v>
       </c>
     </row>
-    <row r="9" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="24"/>
       <c r="B9" s="24"/>
       <c r="C9" s="24"/>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:8" ht="16.2" x14ac:dyDescent="0.4">
       <c r="A11" s="29" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="B11" s="29"/>
       <c r="C11" s="21"/>
       <c r="D11" s="26" t="s">
-        <v>580</v>
+        <v>578</v>
       </c>
       <c r="E11" s="26"/>
       <c r="F11" s="26"/>
       <c r="G11" s="26"/>
       <c r="H11" s="5"/>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A12" s="19" t="s">
         <v>160</v>
       </c>
@@ -9055,20 +9125,20 @@
         <v>42</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>494</v>
+        <v>492</v>
       </c>
       <c r="E12" s="3" t="s">
+        <v>485</v>
+      </c>
+      <c r="F12" s="3" t="s">
+        <v>486</v>
+      </c>
+      <c r="G12" s="3" t="s">
         <v>487</v>
       </c>
-      <c r="F12" s="3" t="s">
-        <v>488</v>
-      </c>
-      <c r="G12" s="3" t="s">
-        <v>489</v>
-      </c>
       <c r="H12" s="2"/>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A13" s="1" t="s">
         <v>171</v>
       </c>
@@ -9085,12 +9155,12 @@
       <c r="F13" s="30"/>
       <c r="G13" s="30"/>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A14" s="1" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>180</v>
@@ -9102,97 +9172,97 @@
       <c r="F14" s="30"/>
       <c r="G14" s="30"/>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A15" s="1" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>143</v>
       </c>
       <c r="D15" s="24" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="E15" s="24"/>
       <c r="F15" s="24"/>
       <c r="G15" s="24"/>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A16" s="1" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>180</v>
       </c>
       <c r="D16" s="34" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="E16" s="34"/>
       <c r="F16" s="34"/>
       <c r="G16" s="34"/>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A17" s="1" t="s">
-        <v>585</v>
+        <v>583</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>143</v>
       </c>
       <c r="D17" s="24" t="s">
-        <v>591</v>
+        <v>589</v>
       </c>
       <c r="E17" s="24"/>
       <c r="F17" s="24"/>
       <c r="G17" s="24"/>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A18" s="1" t="s">
+        <v>579</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>580</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D18" s="24" t="s">
         <v>581</v>
-      </c>
-      <c r="B18" s="1" t="s">
-        <v>582</v>
-      </c>
-      <c r="C18" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="D18" s="24" t="s">
-        <v>583</v>
       </c>
       <c r="E18" s="24"/>
       <c r="F18" s="24"/>
       <c r="G18" s="24"/>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A19" s="1" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>615</v>
+        <v>613</v>
       </c>
       <c r="C19" s="1" t="s">
         <v>143</v>
       </c>
       <c r="D19" s="24" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="E19" s="24"/>
       <c r="F19" s="24"/>
       <c r="G19" s="24"/>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A20" s="1" t="s">
-        <v>616</v>
+        <v>614</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>617</v>
+        <v>615</v>
       </c>
       <c r="C20" s="1" t="s">
         <v>43</v>
@@ -9204,92 +9274,92 @@
       <c r="F20" s="30"/>
       <c r="G20" s="30"/>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A21" s="1" t="s">
-        <v>717</v>
+        <v>715</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>718</v>
+        <v>716</v>
       </c>
       <c r="C21" s="1" t="s">
         <v>43</v>
       </c>
       <c r="D21" s="24" t="s">
-        <v>742</v>
+        <v>740</v>
       </c>
       <c r="E21" s="24"/>
       <c r="F21" s="24"/>
       <c r="G21" s="24"/>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A22" s="1" t="s">
-        <v>716</v>
+        <v>714</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>719</v>
+        <v>717</v>
       </c>
       <c r="C22" s="1" t="s">
         <v>43</v>
       </c>
       <c r="D22" s="24" t="s">
-        <v>741</v>
+        <v>739</v>
       </c>
       <c r="E22" s="24"/>
       <c r="F22" s="24"/>
       <c r="G22" s="24"/>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A23" s="1" t="s">
+        <v>736</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>737</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D23" s="24" t="s">
         <v>738</v>
-      </c>
-      <c r="B23" s="1" t="s">
-        <v>739</v>
-      </c>
-      <c r="C23" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="D23" s="24" t="s">
-        <v>740</v>
       </c>
       <c r="E23" s="24"/>
       <c r="F23" s="24"/>
       <c r="G23" s="24"/>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A24" s="1" t="s">
-        <v>793</v>
+        <v>791</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>794</v>
+        <v>792</v>
       </c>
       <c r="C24" s="1" t="s">
         <v>143</v>
       </c>
       <c r="D24" s="24" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="E24" s="24"/>
       <c r="F24" s="24"/>
       <c r="G24" s="24"/>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A25" s="1" t="s">
-        <v>826</v>
+        <v>824</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>827</v>
+        <v>825</v>
       </c>
       <c r="C25" s="1" t="s">
         <v>43</v>
       </c>
       <c r="D25" s="24" t="s">
-        <v>825</v>
+        <v>823</v>
       </c>
       <c r="E25" s="24"/>
       <c r="F25" s="24"/>
       <c r="G25" s="24"/>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A26" s="1" t="s">
         <v>172</v>
       </c>
@@ -9306,7 +9376,7 @@
       <c r="F26" s="30"/>
       <c r="G26" s="30"/>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A27" s="1" t="s">
         <v>173</v>
       </c>
@@ -9323,7 +9393,7 @@
       <c r="F27" s="30"/>
       <c r="G27" s="30"/>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A28" s="1" t="s">
         <v>175</v>
       </c>
@@ -9334,13 +9404,13 @@
         <v>143</v>
       </c>
       <c r="D28" s="24" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="E28" s="24"/>
       <c r="F28" s="24"/>
       <c r="G28" s="24"/>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A29" s="1" t="s">
         <v>165</v>
       </c>
@@ -9357,7 +9427,7 @@
       <c r="F29" s="30"/>
       <c r="G29" s="30"/>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A30" s="1" t="s">
         <v>166</v>
       </c>
@@ -9368,30 +9438,30 @@
         <v>180</v>
       </c>
       <c r="D30" s="30" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="E30" s="30"/>
       <c r="F30" s="30"/>
       <c r="G30" s="30"/>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A31" s="1" t="s">
+        <v>820</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>821</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D31" s="24" t="s">
         <v>822</v>
-      </c>
-      <c r="B31" s="1" t="s">
-        <v>823</v>
-      </c>
-      <c r="C31" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="D31" s="24" t="s">
-        <v>824</v>
       </c>
       <c r="E31" s="24"/>
       <c r="F31" s="24"/>
       <c r="G31" s="24"/>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A32" s="1" t="s">
         <v>177</v>
       </c>
@@ -9408,7 +9478,7 @@
       <c r="F32" s="30"/>
       <c r="G32" s="30"/>
     </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A33" s="1" t="s">
         <v>169</v>
       </c>
@@ -9419,18 +9489,18 @@
         <v>180</v>
       </c>
       <c r="D33" s="24" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="E33" s="24"/>
       <c r="F33" s="24"/>
       <c r="G33" s="24"/>
     </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A34" s="1" t="s">
-        <v>750</v>
+        <v>748</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>751</v>
+        <v>749</v>
       </c>
       <c r="C34" s="1" t="s">
         <v>43</v>
@@ -9442,7 +9512,7 @@
       <c r="F34" s="30"/>
       <c r="G34" s="30"/>
     </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A36" s="1" t="s">
         <v>274</v>
       </c>
@@ -9453,7 +9523,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A37" s="1" t="s">
         <v>276</v>
       </c>
@@ -9464,7 +9534,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A38" s="1" t="s">
         <v>278</v>
       </c>
@@ -9475,7 +9545,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A39" s="1" t="s">
         <v>280</v>
       </c>
@@ -9486,7 +9556,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A40" s="1" t="s">
         <v>282</v>
       </c>
@@ -9497,7 +9567,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A41" s="1" t="s">
         <v>284</v>
       </c>
@@ -9508,7 +9578,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A42" s="1" t="s">
         <v>286</v>
       </c>
@@ -9519,7 +9589,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A43" s="1" t="s">
         <v>288</v>
       </c>
@@ -9530,7 +9600,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A44" s="1" t="s">
         <v>290</v>
       </c>
@@ -9541,13 +9611,13 @@
         <v>143</v>
       </c>
       <c r="D44" s="30" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="E44" s="30"/>
       <c r="F44" s="30"/>
       <c r="G44" s="30"/>
     </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A46" s="1" t="s">
         <v>292</v>
       </c>
@@ -9558,13 +9628,13 @@
         <v>43</v>
       </c>
       <c r="D46" s="30" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="E46" s="30"/>
       <c r="F46" s="30"/>
       <c r="G46" s="30"/>
     </row>
-    <row r="47" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A47" s="1" t="s">
         <v>294</v>
       </c>
@@ -9575,13 +9645,13 @@
         <v>43</v>
       </c>
       <c r="D47" s="30" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="E47" s="30"/>
       <c r="F47" s="30"/>
       <c r="G47" s="30"/>
     </row>
-    <row r="48" spans="1:8" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:8" ht="15.6" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A48" s="16" t="s">
         <v>296</v>
       </c>
@@ -9592,36 +9662,36 @@
         <v>43</v>
       </c>
       <c r="D48" s="30" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="E48" s="30"/>
       <c r="F48" s="30"/>
       <c r="G48" s="30"/>
     </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A49" s="16" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="B49" s="16" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="C49" s="1" t="s">
         <v>43</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>493</v>
+        <v>491</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="F49" s="1" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="G49" s="1" t="s">
-        <v>491</v>
-      </c>
-    </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.3">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A50" s="1" t="s">
         <v>298</v>
       </c>
@@ -9632,13 +9702,13 @@
         <v>143</v>
       </c>
       <c r="D50" s="24" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="E50" s="24"/>
       <c r="F50" s="24"/>
       <c r="G50" s="24"/>
     </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A51" s="1" t="s">
         <v>300</v>
       </c>
@@ -9649,13 +9719,13 @@
         <v>143</v>
       </c>
       <c r="D51" s="24" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="E51" s="24"/>
       <c r="F51" s="24"/>
       <c r="G51" s="24"/>
     </row>
-    <row r="52" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A52" s="1" t="s">
         <v>302</v>
       </c>
@@ -9666,13 +9736,13 @@
         <v>143</v>
       </c>
       <c r="D52" s="24" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="E52" s="24"/>
       <c r="F52" s="24"/>
       <c r="G52" s="24"/>
     </row>
-    <row r="54" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A54" s="1" t="s">
         <v>124</v>
       </c>
@@ -9683,13 +9753,13 @@
         <v>43</v>
       </c>
       <c r="D54" s="30" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="E54" s="30"/>
       <c r="F54" s="30"/>
       <c r="G54" s="30"/>
     </row>
-    <row r="55" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A55" s="1" t="s">
         <v>126</v>
       </c>
@@ -9706,7 +9776,7 @@
       <c r="F55" s="30"/>
       <c r="G55" s="30"/>
     </row>
-    <row r="56" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A56" s="1" t="s">
         <v>128</v>
       </c>
@@ -9723,7 +9793,7 @@
       <c r="F56" s="30"/>
       <c r="G56" s="30"/>
     </row>
-    <row r="58" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A58" s="1" t="s">
         <v>312</v>
       </c>
@@ -9734,13 +9804,13 @@
         <v>143</v>
       </c>
       <c r="D58" s="24" t="s">
-        <v>788</v>
+        <v>786</v>
       </c>
       <c r="E58" s="24"/>
       <c r="F58" s="24"/>
       <c r="G58" s="24"/>
     </row>
-    <row r="59" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A59" s="1" t="s">
         <v>315</v>
       </c>
@@ -9751,64 +9821,64 @@
         <v>143</v>
       </c>
       <c r="D59" s="24" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="E59" s="24"/>
       <c r="F59" s="24"/>
       <c r="G59" s="24"/>
     </row>
-    <row r="60" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A60" s="1" t="s">
-        <v>675</v>
+        <v>673</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>676</v>
+        <v>674</v>
       </c>
       <c r="C60" s="1" t="s">
         <v>43</v>
       </c>
       <c r="D60" s="30" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="E60" s="30"/>
       <c r="F60" s="30"/>
       <c r="G60" s="30"/>
     </row>
-    <row r="61" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A61" s="1" t="s">
-        <v>786</v>
+        <v>784</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>787</v>
+        <v>785</v>
       </c>
       <c r="C61" s="1" t="s">
         <v>143</v>
       </c>
       <c r="D61" s="24" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="E61" s="24"/>
       <c r="F61" s="24"/>
       <c r="G61" s="24"/>
     </row>
-    <row r="62" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A62" s="1" t="s">
-        <v>784</v>
+        <v>782</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>785</v>
+        <v>783</v>
       </c>
       <c r="C62" s="1" t="s">
         <v>143</v>
       </c>
       <c r="D62" s="24" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="E62" s="24"/>
       <c r="F62" s="24"/>
       <c r="G62" s="24"/>
     </row>
-    <row r="63" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A63" s="1" t="s">
         <v>317</v>
       </c>
@@ -9819,749 +9889,749 @@
         <v>43</v>
       </c>
       <c r="D63" s="30" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="E63" s="30"/>
       <c r="F63" s="30"/>
       <c r="G63" s="30"/>
     </row>
-    <row r="64" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A64" s="1" t="s">
-        <v>643</v>
+        <v>641</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>644</v>
+        <v>642</v>
       </c>
       <c r="C64" s="1" t="s">
         <v>43</v>
       </c>
       <c r="D64" s="30" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="E64" s="30"/>
       <c r="F64" s="30"/>
       <c r="G64" s="30"/>
     </row>
-    <row r="66" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A66" s="1" t="s">
         <v>321</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="C66" s="1" t="s">
         <v>43</v>
       </c>
       <c r="D66" s="30" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="E66" s="30"/>
       <c r="F66" s="30"/>
       <c r="G66" s="30"/>
     </row>
-    <row r="67" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A67" s="1" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="C67" s="1" t="s">
         <v>43</v>
       </c>
       <c r="D67" s="30" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="E67" s="30"/>
       <c r="F67" s="30"/>
       <c r="G67" s="30"/>
     </row>
-    <row r="69" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A69" s="1" t="s">
-        <v>593</v>
+        <v>591</v>
       </c>
       <c r="B69" s="1" t="s">
-        <v>592</v>
+        <v>590</v>
       </c>
       <c r="C69" s="1" t="s">
         <v>43</v>
       </c>
       <c r="D69" s="24" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="E69" s="24"/>
       <c r="F69" s="24"/>
       <c r="G69" s="24"/>
     </row>
-    <row r="70" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A70" s="1" t="s">
-        <v>797</v>
+        <v>795</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>798</v>
+        <v>796</v>
       </c>
       <c r="C70" s="1" t="s">
         <v>43</v>
       </c>
       <c r="D70" s="24" t="s">
-        <v>801</v>
+        <v>799</v>
       </c>
       <c r="E70" s="24"/>
       <c r="F70" s="24"/>
       <c r="G70" s="24"/>
     </row>
-    <row r="71" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A71" s="1" t="s">
-        <v>795</v>
+        <v>793</v>
       </c>
       <c r="B71" s="1" t="s">
-        <v>796</v>
+        <v>794</v>
       </c>
       <c r="C71" s="1" t="s">
         <v>43</v>
       </c>
       <c r="D71" s="24" t="s">
-        <v>802</v>
+        <v>800</v>
       </c>
       <c r="E71" s="24"/>
       <c r="F71" s="24"/>
       <c r="G71" s="24"/>
     </row>
-    <row r="72" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A72" s="1" t="s">
-        <v>799</v>
+        <v>797</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>800</v>
+        <v>798</v>
       </c>
       <c r="C72" s="1" t="s">
         <v>43</v>
       </c>
       <c r="D72" s="34" t="s">
-        <v>803</v>
+        <v>801</v>
       </c>
       <c r="E72" s="34"/>
       <c r="F72" s="34"/>
       <c r="G72" s="34"/>
     </row>
-    <row r="73" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A73" s="1" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="C73" s="1" t="s">
         <v>43</v>
       </c>
       <c r="D73" s="24" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="E73" s="24"/>
       <c r="F73" s="24"/>
       <c r="G73" s="24"/>
     </row>
-    <row r="74" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A74" s="1" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="B74" s="1" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="C74" s="1" t="s">
         <v>43</v>
       </c>
       <c r="D74" s="24" t="s">
-        <v>600</v>
+        <v>598</v>
       </c>
       <c r="E74" s="24"/>
       <c r="F74" s="24"/>
       <c r="G74" s="24"/>
     </row>
-    <row r="75" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A75" s="1" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="C75" s="1" t="s">
         <v>43</v>
       </c>
       <c r="D75" s="24" t="s">
-        <v>598</v>
+        <v>596</v>
       </c>
       <c r="E75" s="24"/>
       <c r="F75" s="24"/>
       <c r="G75" s="24"/>
     </row>
-    <row r="76" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A76" s="1" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="B76" s="1" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="C76" s="1" t="s">
         <v>43</v>
       </c>
       <c r="D76" s="24" t="s">
-        <v>599</v>
+        <v>597</v>
       </c>
       <c r="E76" s="24"/>
       <c r="F76" s="24"/>
       <c r="G76" s="24"/>
     </row>
-    <row r="77" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A77" s="1" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="B77" s="1" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="C77" s="1" t="s">
         <v>43</v>
       </c>
       <c r="D77" s="24" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="E77" s="24"/>
       <c r="F77" s="24"/>
       <c r="G77" s="24"/>
     </row>
-    <row r="79" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A79" s="1" t="s">
+        <v>733</v>
+      </c>
+      <c r="B79" s="1" t="s">
+        <v>734</v>
+      </c>
+      <c r="C79" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D79" s="34" t="s">
         <v>735</v>
-      </c>
-      <c r="B79" s="1" t="s">
-        <v>736</v>
-      </c>
-      <c r="C79" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="D79" s="34" t="s">
-        <v>737</v>
       </c>
       <c r="E79" s="34"/>
       <c r="F79" s="34"/>
       <c r="G79" s="34"/>
     </row>
-    <row r="80" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A80" s="1" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="B80" s="1" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="H80" s="1" t="s">
         <v>183</v>
       </c>
     </row>
-    <row r="81" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A81" s="1" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="B81" s="1" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="H81" s="1" t="s">
         <v>183</v>
       </c>
     </row>
-    <row r="82" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A82" s="1" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="B82" s="1" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="H82" s="1" t="s">
         <v>183</v>
       </c>
     </row>
-    <row r="83" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A83" s="1" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="B83" s="1" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="H83" s="1" t="s">
         <v>183</v>
       </c>
     </row>
-    <row r="84" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A84" s="1" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="B84" s="1" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="H84" s="1" t="s">
         <v>183</v>
       </c>
     </row>
-    <row r="85" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A85" s="1" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="B85" s="1" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="C85" s="1" t="s">
         <v>43</v>
       </c>
       <c r="D85" s="24" t="s">
-        <v>594</v>
+        <v>592</v>
       </c>
       <c r="E85" s="24"/>
       <c r="F85" s="24"/>
       <c r="G85" s="24"/>
     </row>
-    <row r="86" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A86" s="1" t="s">
+        <v>593</v>
+      </c>
+      <c r="B86" s="1" t="s">
+        <v>594</v>
+      </c>
+      <c r="C86" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D86" s="24" t="s">
         <v>595</v>
-      </c>
-      <c r="B86" s="1" t="s">
-        <v>596</v>
-      </c>
-      <c r="C86" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="D86" s="24" t="s">
-        <v>597</v>
       </c>
       <c r="E86" s="24"/>
       <c r="F86" s="24"/>
       <c r="G86" s="24"/>
     </row>
-    <row r="87" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A87" s="1" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="B87" s="1" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="H87" s="1" t="s">
         <v>183</v>
       </c>
     </row>
-    <row r="88" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A88" s="1" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="B88" s="1" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="H88" s="1" t="s">
         <v>183</v>
       </c>
     </row>
-    <row r="89" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A89" s="1" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="B89" s="1" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="H89" s="1" t="s">
         <v>183</v>
       </c>
     </row>
-    <row r="90" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A90" s="1" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="B90" s="1" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="H90" s="1" t="s">
         <v>183</v>
       </c>
     </row>
-    <row r="91" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A91" s="1" t="s">
-        <v>770</v>
+        <v>768</v>
       </c>
       <c r="B91" s="1" t="s">
-        <v>774</v>
+        <v>772</v>
       </c>
       <c r="C91" s="1" t="s">
         <v>43</v>
       </c>
       <c r="D91" s="24" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="E91" s="24"/>
       <c r="F91" s="24"/>
       <c r="G91" s="24"/>
     </row>
-    <row r="92" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A92" s="1" t="s">
-        <v>772</v>
+        <v>770</v>
       </c>
       <c r="B92" s="1" t="s">
-        <v>773</v>
+        <v>771</v>
       </c>
       <c r="C92" s="1" t="s">
         <v>43</v>
       </c>
       <c r="D92" s="24" t="s">
-        <v>587</v>
+        <v>585</v>
       </c>
       <c r="E92" s="24"/>
       <c r="F92" s="24"/>
       <c r="G92" s="24"/>
     </row>
-    <row r="93" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A93" s="1" t="s">
-        <v>775</v>
+        <v>773</v>
       </c>
       <c r="B93" s="1" t="s">
-        <v>776</v>
+        <v>774</v>
       </c>
       <c r="C93" s="1" t="s">
         <v>43</v>
       </c>
       <c r="D93" s="24" t="s">
-        <v>588</v>
+        <v>586</v>
       </c>
       <c r="E93" s="24"/>
       <c r="F93" s="24"/>
       <c r="G93" s="24"/>
     </row>
-    <row r="94" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A94" s="1" t="s">
-        <v>777</v>
+        <v>775</v>
       </c>
       <c r="B94" s="1" t="s">
-        <v>778</v>
+        <v>776</v>
       </c>
       <c r="C94" s="1" t="s">
         <v>43</v>
       </c>
       <c r="D94" s="24" t="s">
-        <v>587</v>
+        <v>585</v>
       </c>
       <c r="E94" s="24"/>
       <c r="F94" s="24"/>
       <c r="G94" s="24"/>
     </row>
-    <row r="95" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A95" s="1" t="s">
-        <v>771</v>
+        <v>769</v>
       </c>
       <c r="B95" s="1" t="s">
-        <v>779</v>
+        <v>777</v>
       </c>
       <c r="C95" s="1" t="s">
         <v>43</v>
       </c>
       <c r="D95" s="24" t="s">
-        <v>783</v>
+        <v>781</v>
       </c>
       <c r="E95" s="24"/>
       <c r="F95" s="24"/>
       <c r="G95" s="24"/>
     </row>
-    <row r="96" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A96" s="1" t="s">
+        <v>778</v>
+      </c>
+      <c r="B96" s="1" t="s">
+        <v>779</v>
+      </c>
+      <c r="C96" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D96" s="24" t="s">
         <v>780</v>
-      </c>
-      <c r="B96" s="1" t="s">
-        <v>781</v>
-      </c>
-      <c r="C96" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="D96" s="24" t="s">
-        <v>782</v>
       </c>
       <c r="E96" s="24"/>
       <c r="F96" s="24"/>
       <c r="G96" s="24"/>
     </row>
-    <row r="97" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A97" s="1" t="s">
+        <v>817</v>
+      </c>
+      <c r="B97" s="1" t="s">
+        <v>818</v>
+      </c>
+      <c r="C97" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D97" s="24" t="s">
         <v>819</v>
-      </c>
-      <c r="B97" s="1" t="s">
-        <v>820</v>
-      </c>
-      <c r="C97" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="D97" s="24" t="s">
-        <v>821</v>
       </c>
       <c r="E97" s="24"/>
       <c r="F97" s="24"/>
       <c r="G97" s="24"/>
     </row>
-    <row r="99" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A99" s="1" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="B99" s="1" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="H99" s="1" t="s">
         <v>183</v>
       </c>
     </row>
-    <row r="100" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A100" s="1" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="B100" s="1" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="H100" s="1" t="s">
         <v>183</v>
       </c>
     </row>
-    <row r="101" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A101" s="1" t="s">
-        <v>700</v>
+        <v>698</v>
       </c>
       <c r="B101" s="1" t="s">
-        <v>701</v>
+        <v>699</v>
       </c>
       <c r="H101" s="1" t="s">
         <v>183</v>
       </c>
     </row>
-    <row r="102" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A102" s="1" t="s">
-        <v>699</v>
+        <v>697</v>
       </c>
       <c r="B102" s="1" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="H102" s="1" t="s">
         <v>183</v>
       </c>
     </row>
-    <row r="103" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A103" s="1" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="B103" s="1" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="H103" s="1" t="s">
         <v>183</v>
       </c>
     </row>
-    <row r="104" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A104" s="1" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="B104" s="1" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="C104" s="1" t="s">
         <v>43</v>
       </c>
       <c r="D104" s="24" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="E104" s="24"/>
       <c r="F104" s="24"/>
       <c r="G104" s="24"/>
     </row>
-    <row r="105" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A105" s="1" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="B105" s="1" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="C105" s="1" t="s">
         <v>43</v>
       </c>
       <c r="D105" s="34" t="s">
-        <v>810</v>
+        <v>808</v>
       </c>
       <c r="E105" s="34"/>
       <c r="F105" s="34"/>
       <c r="G105" s="34"/>
     </row>
-    <row r="107" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A107" s="1" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="B107" s="1" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="C107" s="1" t="s">
         <v>43</v>
       </c>
       <c r="D107" s="35" t="s">
-        <v>496</v>
+        <v>494</v>
       </c>
       <c r="E107" s="35" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="F107" s="35" t="s">
         <v>309</v>
       </c>
       <c r="G107" s="35" t="s">
-        <v>491</v>
-      </c>
-    </row>
-    <row r="108" spans="1:8" x14ac:dyDescent="0.3">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="108" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A108" s="16" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="B108" s="16" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="H108" s="1" t="s">
         <v>183</v>
       </c>
     </row>
-    <row r="109" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A109" s="16" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="B109" s="16" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="C109" s="1" t="s">
         <v>43</v>
       </c>
       <c r="D109" s="24" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="E109" s="24"/>
       <c r="F109" s="24"/>
       <c r="G109" s="24"/>
     </row>
-    <row r="110" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A110" s="16" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="B110" s="16" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="C110" s="1" t="s">
         <v>43</v>
       </c>
       <c r="D110" s="24" t="s">
-        <v>600</v>
+        <v>598</v>
       </c>
       <c r="E110" s="24"/>
       <c r="F110" s="24"/>
       <c r="G110" s="24"/>
     </row>
-    <row r="111" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A111" s="16" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="B111" s="16" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="C111" s="1" t="s">
         <v>43</v>
       </c>
       <c r="D111" s="24" t="s">
-        <v>598</v>
+        <v>596</v>
       </c>
       <c r="E111" s="24"/>
       <c r="F111" s="24"/>
       <c r="G111" s="24"/>
     </row>
-    <row r="112" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A112" s="16" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="B112" s="16" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="C112" s="1" t="s">
         <v>43</v>
       </c>
       <c r="D112" s="24" t="s">
-        <v>599</v>
+        <v>597</v>
       </c>
       <c r="E112" s="24"/>
       <c r="F112" s="24"/>
       <c r="G112" s="24"/>
     </row>
-    <row r="113" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A113" s="16" t="s">
-        <v>475</v>
+        <v>473</v>
       </c>
       <c r="B113" s="16" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="H113" s="1" t="s">
         <v>183</v>
       </c>
     </row>
-    <row r="114" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A114" s="16" t="s">
-        <v>589</v>
+        <v>587</v>
       </c>
       <c r="B114" s="16" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="C114" s="1" t="s">
         <v>43</v>
       </c>
       <c r="D114" s="24" t="s">
-        <v>590</v>
+        <v>588</v>
       </c>
       <c r="E114" s="24"/>
       <c r="F114" s="24"/>
       <c r="G114" s="24"/>
     </row>
-    <row r="115" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A115" s="16" t="s">
-        <v>603</v>
+        <v>601</v>
       </c>
       <c r="B115" s="16" t="s">
-        <v>604</v>
+        <v>602</v>
       </c>
       <c r="H115" s="1" t="s">
         <v>183</v>
       </c>
     </row>
-    <row r="117" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A117" s="1" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="B117" s="1" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="H117" s="1" t="s">
         <v>183</v>
       </c>
     </row>
-    <row r="118" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A118" s="1" t="s">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="B118" s="1" t="s">
-        <v>483</v>
+        <v>481</v>
       </c>
       <c r="C118" s="1" t="s">
         <v>43</v>
       </c>
       <c r="D118" s="24" t="s">
-        <v>809</v>
+        <v>807</v>
       </c>
       <c r="E118" s="24"/>
       <c r="F118" s="24"/>
       <c r="G118" s="24"/>
     </row>
-    <row r="119" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A119" s="1" t="s">
-        <v>484</v>
+        <v>482</v>
       </c>
       <c r="B119" s="1" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="H119" s="1" t="s">
         <v>183</v>
@@ -10590,7 +10660,6 @@
     <mergeCell ref="D51:G51"/>
     <mergeCell ref="D52:G52"/>
     <mergeCell ref="D54:G54"/>
-    <mergeCell ref="D73:G73"/>
     <mergeCell ref="D61:G61"/>
     <mergeCell ref="D62:G62"/>
     <mergeCell ref="D64:G64"/>
@@ -10611,6 +10680,7 @@
     <mergeCell ref="D55:G55"/>
     <mergeCell ref="D56:G56"/>
     <mergeCell ref="D63:G63"/>
+    <mergeCell ref="D73:G73"/>
     <mergeCell ref="D23:G23"/>
     <mergeCell ref="D22:G22"/>
     <mergeCell ref="D21:G21"/>

--- a/插件详细手册/0.性能测试报告/性能测试统计表.xlsx
+++ b/插件详细手册/0.性能测试报告/性能测试统计表.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="23801"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AB2D869A-E59B-49B0-AD39-DAB1060F2E1F}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CE35BC23-6B30-4C5D-B673-7E30D29F8E8A}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="地图界面" sheetId="1" r:id="rId1"/>
@@ -22,7 +22,7 @@
     <author>作者</author>
   </authors>
   <commentList>
-    <comment ref="D89" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000001000000}">
+    <comment ref="D91" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000001000000}">
       <text>
         <r>
           <rPr>
@@ -48,7 +48,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F142" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000002000000}">
+    <comment ref="F144" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000002000000}">
       <text>
         <r>
           <rPr>
@@ -116,7 +116,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1638" uniqueCount="843">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1652" uniqueCount="852">
   <si>
     <t>行走图 - 图块同步镜像</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -3487,6 +3487,42 @@
   </si>
   <si>
     <t xml:space="preserve">  9.51ms</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Drill_EventActionSequence</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>行走图 - GIF动画序列</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Drill_EventActionSequenceAutomation</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>行走图 - GIF动画序列自动化</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>18.16ms</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>12.29ms</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>9.52ms</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>8.20ms</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>5ms以下</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -3653,7 +3689,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="38">
+  <cellXfs count="39">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -3727,6 +3763,24 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -3742,28 +3796,13 @@
     <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -4109,7 +4148,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A2:H173"/>
+  <dimension ref="A2:H175"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15.6" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="39.6640625" style="1" customWidth="1"/>
@@ -4132,101 +4171,101 @@
       <c r="H2" s="5"/>
     </row>
     <row r="4" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="24" t="s">
+      <c r="A4" s="25" t="s">
         <v>57</v>
       </c>
-      <c r="B4" s="24"/>
-      <c r="C4" s="24"/>
-      <c r="D4" s="33" t="s">
+      <c r="B4" s="25"/>
+      <c r="C4" s="25"/>
+      <c r="D4" s="30" t="s">
         <v>55</v>
       </c>
-      <c r="E4" s="33"/>
+      <c r="E4" s="30"/>
       <c r="F4" s="11" t="s">
         <v>56</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="24" t="s">
+      <c r="A5" s="25" t="s">
         <v>46</v>
       </c>
-      <c r="B5" s="24"/>
-      <c r="C5" s="24"/>
-      <c r="D5" s="31" t="s">
+      <c r="B5" s="25"/>
+      <c r="C5" s="25"/>
+      <c r="D5" s="28" t="s">
         <v>47</v>
       </c>
-      <c r="E5" s="31"/>
+      <c r="E5" s="28"/>
       <c r="F5" s="10" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="24" t="s">
+      <c r="A6" s="25" t="s">
         <v>45</v>
       </c>
-      <c r="B6" s="24"/>
-      <c r="C6" s="24"/>
-      <c r="D6" s="32" t="s">
+      <c r="B6" s="25"/>
+      <c r="C6" s="25"/>
+      <c r="D6" s="29" t="s">
         <v>49</v>
       </c>
-      <c r="E6" s="32"/>
+      <c r="E6" s="29"/>
       <c r="F6" s="13" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="25" t="s">
+      <c r="A7" s="31" t="s">
         <v>62</v>
       </c>
-      <c r="B7" s="25"/>
-      <c r="C7" s="25"/>
-      <c r="D7" s="27" t="s">
+      <c r="B7" s="31"/>
+      <c r="C7" s="31"/>
+      <c r="D7" s="33" t="s">
         <v>51</v>
       </c>
-      <c r="E7" s="27"/>
+      <c r="E7" s="33"/>
       <c r="F7" s="12" t="s">
         <v>52</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="25" t="s">
+      <c r="A8" s="31" t="s">
         <v>63</v>
       </c>
-      <c r="B8" s="25"/>
-      <c r="C8" s="25"/>
-      <c r="D8" s="28" t="s">
+      <c r="B8" s="31"/>
+      <c r="C8" s="31"/>
+      <c r="D8" s="34" t="s">
         <v>53</v>
       </c>
-      <c r="E8" s="28"/>
+      <c r="E8" s="34"/>
       <c r="F8" s="14" t="s">
         <v>54</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="24" t="s">
+      <c r="A9" s="25" t="s">
         <v>144</v>
       </c>
-      <c r="B9" s="24"/>
-      <c r="C9" s="24"/>
+      <c r="B9" s="25"/>
+      <c r="C9" s="25"/>
     </row>
     <row r="10" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="24" t="s">
+      <c r="A10" s="25" t="s">
         <v>371</v>
       </c>
-      <c r="B10" s="24"/>
-      <c r="C10" s="24"/>
+      <c r="B10" s="25"/>
+      <c r="C10" s="25"/>
     </row>
     <row r="12" spans="1:8" ht="16.2" x14ac:dyDescent="0.4">
-      <c r="A12" s="29" t="s">
+      <c r="A12" s="35" t="s">
         <v>341</v>
       </c>
-      <c r="B12" s="29"/>
+      <c r="B12" s="35"/>
       <c r="C12" s="8"/>
-      <c r="D12" s="26" t="s">
+      <c r="D12" s="32" t="s">
         <v>577</v>
       </c>
-      <c r="E12" s="26"/>
-      <c r="F12" s="26"/>
-      <c r="G12" s="26"/>
+      <c r="E12" s="32"/>
+      <c r="F12" s="32"/>
+      <c r="G12" s="32"/>
       <c r="H12" s="5"/>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.35">
@@ -4263,12 +4302,12 @@
       <c r="C14" s="1" t="s">
         <v>180</v>
       </c>
-      <c r="D14" s="30" t="s">
+      <c r="D14" s="26" t="s">
         <v>178</v>
       </c>
-      <c r="E14" s="30"/>
-      <c r="F14" s="30"/>
-      <c r="G14" s="30"/>
+      <c r="E14" s="26"/>
+      <c r="F14" s="26"/>
+      <c r="G14" s="26"/>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A15" s="1" t="s">
@@ -4280,12 +4319,12 @@
       <c r="C15" s="1" t="s">
         <v>180</v>
       </c>
-      <c r="D15" s="30" t="s">
+      <c r="D15" s="26" t="s">
         <v>178</v>
       </c>
-      <c r="E15" s="30"/>
-      <c r="F15" s="30"/>
-      <c r="G15" s="30"/>
+      <c r="E15" s="26"/>
+      <c r="F15" s="26"/>
+      <c r="G15" s="26"/>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A16" s="1" t="s">
@@ -4297,12 +4336,12 @@
       <c r="C16" s="1" t="s">
         <v>401</v>
       </c>
-      <c r="D16" s="24" t="s">
+      <c r="D16" s="25" t="s">
         <v>404</v>
       </c>
-      <c r="E16" s="24"/>
-      <c r="F16" s="24"/>
-      <c r="G16" s="24"/>
+      <c r="E16" s="25"/>
+      <c r="F16" s="25"/>
+      <c r="G16" s="25"/>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A17" s="1" t="s">
@@ -4314,12 +4353,12 @@
       <c r="C17" s="1" t="s">
         <v>180</v>
       </c>
-      <c r="D17" s="24" t="s">
+      <c r="D17" s="25" t="s">
         <v>405</v>
       </c>
-      <c r="E17" s="24"/>
-      <c r="F17" s="24"/>
-      <c r="G17" s="24"/>
+      <c r="E17" s="25"/>
+      <c r="F17" s="25"/>
+      <c r="G17" s="25"/>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A18" s="1" t="s">
@@ -4331,12 +4370,12 @@
       <c r="C18" s="1" t="s">
         <v>143</v>
       </c>
-      <c r="D18" s="24" t="s">
+      <c r="D18" s="25" t="s">
         <v>589</v>
       </c>
-      <c r="E18" s="24"/>
-      <c r="F18" s="24"/>
-      <c r="G18" s="24"/>
+      <c r="E18" s="25"/>
+      <c r="F18" s="25"/>
+      <c r="G18" s="25"/>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A19" s="1" t="s">
@@ -4348,12 +4387,12 @@
       <c r="C19" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="D19" s="24" t="s">
+      <c r="D19" s="25" t="s">
         <v>581</v>
       </c>
-      <c r="E19" s="24"/>
-      <c r="F19" s="24"/>
-      <c r="G19" s="24"/>
+      <c r="E19" s="25"/>
+      <c r="F19" s="25"/>
+      <c r="G19" s="25"/>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A20" s="1" t="s">
@@ -4365,12 +4404,12 @@
       <c r="C20" s="1" t="s">
         <v>143</v>
       </c>
-      <c r="D20" s="24" t="s">
+      <c r="D20" s="25" t="s">
         <v>404</v>
       </c>
-      <c r="E20" s="24"/>
-      <c r="F20" s="24"/>
-      <c r="G20" s="24"/>
+      <c r="E20" s="25"/>
+      <c r="F20" s="25"/>
+      <c r="G20" s="25"/>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A21" s="1" t="s">
@@ -4382,12 +4421,12 @@
       <c r="C21" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="D21" s="30" t="s">
+      <c r="D21" s="26" t="s">
         <v>178</v>
       </c>
-      <c r="E21" s="30"/>
-      <c r="F21" s="30"/>
-      <c r="G21" s="30"/>
+      <c r="E21" s="26"/>
+      <c r="F21" s="26"/>
+      <c r="G21" s="26"/>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A22" s="1" t="s">
@@ -4399,12 +4438,12 @@
       <c r="C22" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="D22" s="34" t="s">
+      <c r="D22" s="27" t="s">
         <v>719</v>
       </c>
-      <c r="E22" s="34"/>
-      <c r="F22" s="34"/>
-      <c r="G22" s="34"/>
+      <c r="E22" s="27"/>
+      <c r="F22" s="27"/>
+      <c r="G22" s="27"/>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A23" s="1" t="s">
@@ -4416,12 +4455,12 @@
       <c r="C23" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="D23" s="24" t="s">
+      <c r="D23" s="25" t="s">
         <v>718</v>
       </c>
-      <c r="E23" s="24"/>
-      <c r="F23" s="24"/>
-      <c r="G23" s="24"/>
+      <c r="E23" s="25"/>
+      <c r="F23" s="25"/>
+      <c r="G23" s="25"/>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A24" s="1" t="s">
@@ -4433,12 +4472,12 @@
       <c r="C24" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="D24" s="24" t="s">
+      <c r="D24" s="25" t="s">
         <v>722</v>
       </c>
-      <c r="E24" s="24"/>
-      <c r="F24" s="24"/>
-      <c r="G24" s="24"/>
+      <c r="E24" s="25"/>
+      <c r="F24" s="25"/>
+      <c r="G24" s="25"/>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A25" s="1" t="s">
@@ -4450,12 +4489,12 @@
       <c r="C25" s="1" t="s">
         <v>143</v>
       </c>
-      <c r="D25" s="24" t="s">
+      <c r="D25" s="25" t="s">
         <v>404</v>
       </c>
-      <c r="E25" s="24"/>
-      <c r="F25" s="24"/>
-      <c r="G25" s="24"/>
+      <c r="E25" s="25"/>
+      <c r="F25" s="25"/>
+      <c r="G25" s="25"/>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A26" s="1" t="s">
@@ -4467,12 +4506,12 @@
       <c r="C26" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="D26" s="24" t="s">
+      <c r="D26" s="25" t="s">
         <v>823</v>
       </c>
-      <c r="E26" s="24"/>
-      <c r="F26" s="24"/>
-      <c r="G26" s="24"/>
+      <c r="E26" s="25"/>
+      <c r="F26" s="25"/>
+      <c r="G26" s="25"/>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A27" s="1" t="s">
@@ -4484,12 +4523,12 @@
       <c r="C27" s="1" t="s">
         <v>179</v>
       </c>
-      <c r="D27" s="30" t="s">
+      <c r="D27" s="26" t="s">
         <v>178</v>
       </c>
-      <c r="E27" s="30"/>
-      <c r="F27" s="30"/>
-      <c r="G27" s="30"/>
+      <c r="E27" s="26"/>
+      <c r="F27" s="26"/>
+      <c r="G27" s="26"/>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A28" s="1" t="s">
@@ -4501,12 +4540,12 @@
       <c r="C28" s="1" t="s">
         <v>179</v>
       </c>
-      <c r="D28" s="30" t="s">
+      <c r="D28" s="26" t="s">
         <v>182</v>
       </c>
-      <c r="E28" s="30"/>
-      <c r="F28" s="30"/>
-      <c r="G28" s="30"/>
+      <c r="E28" s="26"/>
+      <c r="F28" s="26"/>
+      <c r="G28" s="26"/>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A29" s="1" t="s">
@@ -4518,12 +4557,12 @@
       <c r="C29" s="1" t="s">
         <v>179</v>
       </c>
-      <c r="D29" s="24" t="s">
+      <c r="D29" s="25" t="s">
         <v>406</v>
       </c>
-      <c r="E29" s="24"/>
-      <c r="F29" s="24"/>
-      <c r="G29" s="24"/>
+      <c r="E29" s="25"/>
+      <c r="F29" s="25"/>
+      <c r="G29" s="25"/>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A30" s="1" t="s">
@@ -4535,12 +4574,12 @@
       <c r="C30" s="1" t="s">
         <v>179</v>
       </c>
-      <c r="D30" s="30" t="s">
+      <c r="D30" s="26" t="s">
         <v>178</v>
       </c>
-      <c r="E30" s="30"/>
-      <c r="F30" s="30"/>
-      <c r="G30" s="30"/>
+      <c r="E30" s="26"/>
+      <c r="F30" s="26"/>
+      <c r="G30" s="26"/>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A31" s="1" t="s">
@@ -4552,12 +4591,12 @@
       <c r="C31" s="1" t="s">
         <v>180</v>
       </c>
-      <c r="D31" s="24" t="s">
+      <c r="D31" s="25" t="s">
         <v>407</v>
       </c>
-      <c r="E31" s="24"/>
-      <c r="F31" s="24"/>
-      <c r="G31" s="24"/>
+      <c r="E31" s="25"/>
+      <c r="F31" s="25"/>
+      <c r="G31" s="25"/>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A32" s="1" t="s">
@@ -4569,12 +4608,12 @@
       <c r="C32" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="D32" s="24" t="s">
+      <c r="D32" s="25" t="s">
         <v>827</v>
       </c>
-      <c r="E32" s="24"/>
-      <c r="F32" s="24"/>
-      <c r="G32" s="24"/>
+      <c r="E32" s="25"/>
+      <c r="F32" s="25"/>
+      <c r="G32" s="25"/>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A33" s="1" t="s">
@@ -4586,12 +4625,12 @@
       <c r="C33" s="1" t="s">
         <v>181</v>
       </c>
-      <c r="D33" s="30" t="s">
+      <c r="D33" s="26" t="s">
         <v>182</v>
       </c>
-      <c r="E33" s="30"/>
-      <c r="F33" s="30"/>
-      <c r="G33" s="30"/>
+      <c r="E33" s="26"/>
+      <c r="F33" s="26"/>
+      <c r="G33" s="26"/>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A34" s="1" t="s">
@@ -4603,12 +4642,12 @@
       <c r="C34" s="1" t="s">
         <v>180</v>
       </c>
-      <c r="D34" s="24" t="s">
+      <c r="D34" s="25" t="s">
         <v>408</v>
       </c>
-      <c r="E34" s="24"/>
-      <c r="F34" s="24"/>
-      <c r="G34" s="24"/>
+      <c r="E34" s="25"/>
+      <c r="F34" s="25"/>
+      <c r="G34" s="25"/>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A35" s="1" t="s">
@@ -4620,12 +4659,12 @@
       <c r="C35" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="D35" s="30" t="s">
+      <c r="D35" s="26" t="s">
         <v>182</v>
       </c>
-      <c r="E35" s="30"/>
-      <c r="F35" s="30"/>
-      <c r="G35" s="30"/>
+      <c r="E35" s="26"/>
+      <c r="F35" s="26"/>
+      <c r="G35" s="26"/>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A37" s="1" t="s">
@@ -4832,12 +4871,12 @@
       <c r="C46" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="D46" s="24" t="s">
+      <c r="D46" s="25" t="s">
         <v>404</v>
       </c>
-      <c r="E46" s="24"/>
-      <c r="F46" s="24"/>
-      <c r="G46" s="24"/>
+      <c r="E46" s="25"/>
+      <c r="F46" s="25"/>
+      <c r="G46" s="25"/>
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A47" s="1" t="s">
@@ -4929,12 +4968,12 @@
       <c r="C52" s="1" t="s">
         <v>143</v>
       </c>
-      <c r="D52" s="24" t="s">
+      <c r="D52" s="25" t="s">
         <v>409</v>
       </c>
-      <c r="E52" s="24"/>
-      <c r="F52" s="24"/>
-      <c r="G52" s="24"/>
+      <c r="E52" s="25"/>
+      <c r="F52" s="25"/>
+      <c r="G52" s="25"/>
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A53" s="1" t="s">
@@ -4969,42 +5008,54 @@
       <c r="C54" s="1" t="s">
         <v>143</v>
       </c>
-      <c r="D54" s="24" t="s">
-        <v>409</v>
-      </c>
-      <c r="E54" s="24"/>
-      <c r="F54" s="24"/>
-      <c r="G54" s="24"/>
+      <c r="D54" s="25" t="s">
+        <v>404</v>
+      </c>
+      <c r="E54" s="25"/>
+      <c r="F54" s="25"/>
+      <c r="G54" s="25"/>
     </row>
     <row r="55" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A55" s="1" t="s">
-        <v>71</v>
+        <v>843</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="H55" s="1" t="s">
-        <v>183</v>
+        <v>844</v>
+      </c>
+      <c r="C55" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D55" s="24" t="s">
+        <v>847</v>
+      </c>
+      <c r="E55" s="24" t="s">
+        <v>848</v>
+      </c>
+      <c r="F55" s="24" t="s">
+        <v>849</v>
+      </c>
+      <c r="G55" s="1" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="56" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A56" s="1" t="s">
-        <v>21</v>
+        <v>845</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>22</v>
+        <v>846</v>
       </c>
       <c r="C56" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="D56" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="E56" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="F56" s="1" t="s">
-        <v>17</v>
+      <c r="D56" s="24" t="s">
+        <v>850</v>
+      </c>
+      <c r="E56" s="24" t="s">
+        <v>851</v>
+      </c>
+      <c r="F56" s="24" t="s">
+        <v>851</v>
       </c>
       <c r="G56" s="1" t="s">
         <v>14</v>
@@ -5012,33 +5063,21 @@
     </row>
     <row r="57" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A57" s="1" t="s">
-        <v>19</v>
+        <v>71</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="C57" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="D57" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="E57" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="F57" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="G57" s="1" t="s">
-        <v>14</v>
+        <v>72</v>
+      </c>
+      <c r="H57" s="1" t="s">
+        <v>183</v>
       </c>
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A58" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="C58" s="1" t="s">
         <v>43</v>
@@ -5047,7 +5086,7 @@
         <v>15</v>
       </c>
       <c r="E58" s="7" t="s">
-        <v>123</v>
+        <v>16</v>
       </c>
       <c r="F58" s="1" t="s">
         <v>17</v>
@@ -5058,22 +5097,22 @@
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A59" s="1" t="s">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>10</v>
+        <v>70</v>
       </c>
       <c r="C59" s="1" t="s">
         <v>43</v>
       </c>
       <c r="D59" s="6" t="s">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="E59" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="F59" s="7" t="s">
-        <v>9</v>
+        <v>16</v>
+      </c>
+      <c r="F59" s="1" t="s">
+        <v>17</v>
       </c>
       <c r="G59" s="1" t="s">
         <v>14</v>
@@ -5081,22 +5120,22 @@
     </row>
     <row r="60" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A60" s="1" t="s">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="C60" s="1" t="s">
         <v>43</v>
       </c>
       <c r="D60" s="6" t="s">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="E60" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="F60" s="7" t="s">
-        <v>6</v>
+        <v>123</v>
+      </c>
+      <c r="F60" s="1" t="s">
+        <v>17</v>
       </c>
       <c r="G60" s="1" t="s">
         <v>14</v>
@@ -5104,22 +5143,22 @@
     </row>
     <row r="61" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A61" s="1" t="s">
-        <v>567</v>
+        <v>11</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>568</v>
+        <v>10</v>
       </c>
       <c r="C61" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="D61" s="1" t="s">
-        <v>569</v>
-      </c>
-      <c r="E61" s="1" t="s">
-        <v>570</v>
-      </c>
-      <c r="F61" s="1" t="s">
-        <v>571</v>
+      <c r="D61" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="E61" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="F61" s="7" t="s">
+        <v>9</v>
       </c>
       <c r="G61" s="1" t="s">
         <v>14</v>
@@ -5127,22 +5166,22 @@
     </row>
     <row r="62" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A62" s="1" t="s">
-        <v>40</v>
+        <v>3</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="C62" s="1" t="s">
         <v>43</v>
       </c>
       <c r="D62" s="6" t="s">
-        <v>148</v>
-      </c>
-      <c r="E62" s="6" t="s">
-        <v>149</v>
+        <v>4</v>
+      </c>
+      <c r="E62" s="7" t="s">
+        <v>5</v>
       </c>
       <c r="F62" s="7" t="s">
-        <v>147</v>
+        <v>6</v>
       </c>
       <c r="G62" s="1" t="s">
         <v>14</v>
@@ -5150,188 +5189,188 @@
     </row>
     <row r="63" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A63" s="1" t="s">
-        <v>624</v>
+        <v>567</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>625</v>
+        <v>568</v>
       </c>
       <c r="C63" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="D63" s="6" t="s">
-        <v>626</v>
-      </c>
-      <c r="E63" s="6" t="s">
-        <v>627</v>
-      </c>
-      <c r="F63" s="7" t="s">
-        <v>628</v>
+      <c r="D63" s="1" t="s">
+        <v>569</v>
+      </c>
+      <c r="E63" s="1" t="s">
+        <v>570</v>
+      </c>
+      <c r="F63" s="1" t="s">
+        <v>571</v>
       </c>
       <c r="G63" s="1" t="s">
         <v>14</v>
       </c>
     </row>
+    <row r="64" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A64" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="B64" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="C64" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D64" s="6" t="s">
+        <v>148</v>
+      </c>
+      <c r="E64" s="6" t="s">
+        <v>149</v>
+      </c>
+      <c r="F64" s="7" t="s">
+        <v>147</v>
+      </c>
+      <c r="G64" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A65" s="1" t="s">
-        <v>554</v>
+        <v>624</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>556</v>
+        <v>625</v>
       </c>
       <c r="C65" s="1" t="s">
-        <v>143</v>
-      </c>
-      <c r="D65" s="24" t="s">
-        <v>404</v>
-      </c>
-      <c r="E65" s="24"/>
-      <c r="F65" s="24"/>
-      <c r="G65" s="24"/>
-    </row>
-    <row r="66" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A66" s="1" t="s">
-        <v>555</v>
-      </c>
-      <c r="B66" s="1" t="s">
-        <v>139</v>
-      </c>
-      <c r="C66" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="D66" s="1" t="s">
-        <v>140</v>
-      </c>
-      <c r="E66" s="1" t="s">
-        <v>141</v>
-      </c>
-      <c r="F66" s="1" t="s">
-        <v>142</v>
-      </c>
-      <c r="G66" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D65" s="6" t="s">
+        <v>626</v>
+      </c>
+      <c r="E65" s="6" t="s">
+        <v>627</v>
+      </c>
+      <c r="F65" s="7" t="s">
+        <v>628</v>
+      </c>
+      <c r="G65" s="1" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A67" s="1" t="s">
-        <v>557</v>
+        <v>554</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="C67" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="D67" s="1" t="s">
-        <v>559</v>
-      </c>
-      <c r="E67" s="1" t="s">
-        <v>560</v>
-      </c>
-      <c r="F67" s="1" t="s">
-        <v>561</v>
-      </c>
-      <c r="G67" s="1" t="s">
-        <v>14</v>
-      </c>
+        <v>143</v>
+      </c>
+      <c r="D67" s="25" t="s">
+        <v>404</v>
+      </c>
+      <c r="E67" s="25"/>
+      <c r="F67" s="25"/>
+      <c r="G67" s="25"/>
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A68" s="1" t="s">
-        <v>670</v>
+        <v>555</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>671</v>
+        <v>139</v>
       </c>
       <c r="C68" s="1" t="s">
-        <v>672</v>
-      </c>
-      <c r="D68" s="24" t="s">
-        <v>404</v>
-      </c>
-      <c r="E68" s="24"/>
-      <c r="F68" s="24"/>
-      <c r="G68" s="24"/>
+        <v>43</v>
+      </c>
+      <c r="D68" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="E68" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="F68" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="G68" s="1" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A69" s="1" t="s">
-        <v>74</v>
+        <v>557</v>
       </c>
       <c r="B69" s="1" t="s">
-        <v>75</v>
+        <v>558</v>
       </c>
       <c r="C69" s="1" t="s">
-        <v>143</v>
-      </c>
-      <c r="D69" s="24" t="s">
-        <v>410</v>
-      </c>
-      <c r="E69" s="24"/>
-      <c r="F69" s="24"/>
-      <c r="G69" s="24"/>
+        <v>43</v>
+      </c>
+      <c r="D69" s="1" t="s">
+        <v>559</v>
+      </c>
+      <c r="E69" s="1" t="s">
+        <v>560</v>
+      </c>
+      <c r="F69" s="1" t="s">
+        <v>561</v>
+      </c>
+      <c r="G69" s="1" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A70" s="1" t="s">
-        <v>76</v>
+        <v>670</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>77</v>
+        <v>671</v>
       </c>
       <c r="C70" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="D70" s="1" t="s">
-        <v>394</v>
-      </c>
-      <c r="E70" s="1" t="s">
-        <v>395</v>
-      </c>
-      <c r="F70" s="1" t="s">
-        <v>388</v>
-      </c>
-      <c r="G70" s="1" t="s">
-        <v>14</v>
-      </c>
+        <v>672</v>
+      </c>
+      <c r="D70" s="25" t="s">
+        <v>404</v>
+      </c>
+      <c r="E70" s="25"/>
+      <c r="F70" s="25"/>
+      <c r="G70" s="25"/>
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A71" s="1" t="s">
-        <v>562</v>
+        <v>74</v>
       </c>
       <c r="B71" s="1" t="s">
-        <v>563</v>
+        <v>75</v>
       </c>
       <c r="C71" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="D71" s="1" t="s">
-        <v>564</v>
-      </c>
-      <c r="E71" s="1" t="s">
-        <v>565</v>
-      </c>
-      <c r="F71" s="1" t="s">
-        <v>388</v>
-      </c>
-      <c r="G71" s="1" t="s">
-        <v>14</v>
-      </c>
+        <v>143</v>
+      </c>
+      <c r="D71" s="25" t="s">
+        <v>410</v>
+      </c>
+      <c r="E71" s="25"/>
+      <c r="F71" s="25"/>
+      <c r="G71" s="25"/>
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A72" s="1" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="C72" s="1" t="s">
-        <v>180</v>
+        <v>43</v>
       </c>
       <c r="D72" s="1" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="E72" s="1" t="s">
-        <v>387</v>
+        <v>395</v>
       </c>
       <c r="F72" s="1" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="G72" s="1" t="s">
         <v>14</v>
@@ -5339,22 +5378,22 @@
     </row>
     <row r="73" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A73" s="1" t="s">
-        <v>607</v>
+        <v>562</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>608</v>
+        <v>563</v>
       </c>
       <c r="C73" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="D73" s="7" t="s">
-        <v>611</v>
+      <c r="D73" s="1" t="s">
+        <v>564</v>
       </c>
       <c r="E73" s="1" t="s">
-        <v>609</v>
+        <v>565</v>
       </c>
       <c r="F73" s="1" t="s">
-        <v>610</v>
+        <v>388</v>
       </c>
       <c r="G73" s="1" t="s">
         <v>14</v>
@@ -5362,39 +5401,45 @@
     </row>
     <row r="74" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A74" s="1" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="B74" s="1" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="C74" s="1" t="s">
-        <v>143</v>
-      </c>
-      <c r="D74" s="24" t="s">
-        <v>404</v>
-      </c>
-      <c r="E74" s="24"/>
-      <c r="F74" s="24"/>
-      <c r="G74" s="24"/>
+        <v>180</v>
+      </c>
+      <c r="D74" s="1" t="s">
+        <v>393</v>
+      </c>
+      <c r="E74" s="1" t="s">
+        <v>387</v>
+      </c>
+      <c r="F74" s="1" t="s">
+        <v>389</v>
+      </c>
+      <c r="G74" s="1" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="75" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A75" s="1" t="s">
-        <v>89</v>
+        <v>607</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>90</v>
+        <v>608</v>
       </c>
       <c r="C75" s="1" t="s">
-        <v>143</v>
-      </c>
-      <c r="D75" s="1" t="s">
-        <v>566</v>
+        <v>43</v>
+      </c>
+      <c r="D75" s="7" t="s">
+        <v>611</v>
       </c>
       <c r="E75" s="1" t="s">
-        <v>388</v>
+        <v>609</v>
       </c>
       <c r="F75" s="1" t="s">
-        <v>388</v>
+        <v>610</v>
       </c>
       <c r="G75" s="1" t="s">
         <v>14</v>
@@ -5402,45 +5447,39 @@
     </row>
     <row r="76" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A76" s="1" t="s">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="B76" s="1" t="s">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="C76" s="1" t="s">
         <v>143</v>
       </c>
-      <c r="D76" s="1" t="s">
-        <v>377</v>
-      </c>
-      <c r="E76" s="1" t="s">
-        <v>145</v>
-      </c>
-      <c r="F76" s="1" t="s">
-        <v>378</v>
-      </c>
-      <c r="G76" s="1" t="s">
-        <v>14</v>
-      </c>
+      <c r="D76" s="25" t="s">
+        <v>404</v>
+      </c>
+      <c r="E76" s="25"/>
+      <c r="F76" s="25"/>
+      <c r="G76" s="25"/>
     </row>
     <row r="77" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A77" s="1" t="s">
-        <v>572</v>
+        <v>89</v>
       </c>
       <c r="B77" s="1" t="s">
-        <v>573</v>
+        <v>90</v>
       </c>
       <c r="C77" s="1" t="s">
-        <v>43</v>
+        <v>143</v>
       </c>
       <c r="D77" s="1" t="s">
-        <v>574</v>
+        <v>566</v>
       </c>
       <c r="E77" s="1" t="s">
-        <v>575</v>
+        <v>388</v>
       </c>
       <c r="F77" s="1" t="s">
-        <v>576</v>
+        <v>388</v>
       </c>
       <c r="G77" s="1" t="s">
         <v>14</v>
@@ -5448,22 +5487,22 @@
     </row>
     <row r="78" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A78" s="1" t="s">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="B78" s="1" t="s">
-        <v>83</v>
+        <v>92</v>
       </c>
       <c r="C78" s="1" t="s">
         <v>143</v>
       </c>
       <c r="D78" s="1" t="s">
-        <v>504</v>
+        <v>377</v>
       </c>
       <c r="E78" s="1" t="s">
-        <v>505</v>
+        <v>145</v>
       </c>
       <c r="F78" s="1" t="s">
-        <v>388</v>
+        <v>378</v>
       </c>
       <c r="G78" s="1" t="s">
         <v>14</v>
@@ -5471,22 +5510,22 @@
     </row>
     <row r="79" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A79" s="1" t="s">
-        <v>152</v>
+        <v>572</v>
       </c>
       <c r="B79" s="1" t="s">
-        <v>153</v>
+        <v>573</v>
       </c>
       <c r="C79" s="1" t="s">
-        <v>143</v>
-      </c>
-      <c r="D79" s="7" t="s">
-        <v>156</v>
+        <v>43</v>
+      </c>
+      <c r="D79" s="1" t="s">
+        <v>574</v>
       </c>
       <c r="E79" s="1" t="s">
-        <v>154</v>
+        <v>575</v>
       </c>
       <c r="F79" s="1" t="s">
-        <v>155</v>
+        <v>576</v>
       </c>
       <c r="G79" s="1" t="s">
         <v>14</v>
@@ -5494,96 +5533,102 @@
     </row>
     <row r="80" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A80" s="1" t="s">
-        <v>516</v>
+        <v>82</v>
       </c>
       <c r="B80" s="1" t="s">
-        <v>515</v>
+        <v>83</v>
       </c>
       <c r="C80" s="1" t="s">
         <v>143</v>
       </c>
-      <c r="D80" s="24" t="s">
-        <v>404</v>
-      </c>
-      <c r="E80" s="24"/>
-      <c r="F80" s="24"/>
-      <c r="G80" s="24"/>
+      <c r="D80" s="1" t="s">
+        <v>504</v>
+      </c>
+      <c r="E80" s="1" t="s">
+        <v>505</v>
+      </c>
+      <c r="F80" s="1" t="s">
+        <v>388</v>
+      </c>
+      <c r="G80" s="1" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A81" s="1" t="s">
-        <v>84</v>
+        <v>152</v>
       </c>
       <c r="B81" s="1" t="s">
-        <v>85</v>
+        <v>153</v>
       </c>
       <c r="C81" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="D81" s="24" t="s">
-        <v>404</v>
-      </c>
-      <c r="E81" s="24"/>
-      <c r="F81" s="24"/>
-      <c r="G81" s="24"/>
+        <v>143</v>
+      </c>
+      <c r="D81" s="7" t="s">
+        <v>156</v>
+      </c>
+      <c r="E81" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="F81" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="G81" s="1" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="82" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A82" s="1" t="s">
-        <v>86</v>
+        <v>516</v>
       </c>
       <c r="B82" s="1" t="s">
-        <v>87</v>
+        <v>515</v>
       </c>
       <c r="C82" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="D82" s="1" t="s">
-        <v>553</v>
-      </c>
-      <c r="E82" s="1" t="s">
-        <v>551</v>
-      </c>
-      <c r="F82" s="1" t="s">
-        <v>552</v>
-      </c>
-      <c r="G82" s="1" t="s">
-        <v>14</v>
-      </c>
+        <v>143</v>
+      </c>
+      <c r="D82" s="25" t="s">
+        <v>404</v>
+      </c>
+      <c r="E82" s="25"/>
+      <c r="F82" s="25"/>
+      <c r="G82" s="25"/>
     </row>
     <row r="83" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A83" s="1" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="B83" s="1" t="s">
-        <v>376</v>
+        <v>85</v>
       </c>
       <c r="C83" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="D83" s="24" t="s">
+      <c r="D83" s="25" t="s">
         <v>404</v>
       </c>
-      <c r="E83" s="24"/>
-      <c r="F83" s="24"/>
-      <c r="G83" s="24"/>
+      <c r="E83" s="25"/>
+      <c r="F83" s="25"/>
+      <c r="G83" s="25"/>
     </row>
     <row r="84" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A84" s="1" t="s">
-        <v>93</v>
+        <v>86</v>
       </c>
       <c r="B84" s="1" t="s">
-        <v>94</v>
+        <v>87</v>
       </c>
       <c r="C84" s="1" t="s">
-        <v>143</v>
+        <v>43</v>
       </c>
       <c r="D84" s="1" t="s">
-        <v>526</v>
+        <v>553</v>
       </c>
       <c r="E84" s="1" t="s">
-        <v>527</v>
+        <v>551</v>
       </c>
       <c r="F84" s="1" t="s">
-        <v>528</v>
+        <v>552</v>
       </c>
       <c r="G84" s="1" t="s">
         <v>14</v>
@@ -5591,142 +5636,136 @@
     </row>
     <row r="85" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A85" s="1" t="s">
-        <v>741</v>
+        <v>88</v>
       </c>
       <c r="B85" s="1" t="s">
-        <v>742</v>
+        <v>376</v>
       </c>
       <c r="C85" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="D85" s="24" t="s">
+      <c r="D85" s="25" t="s">
         <v>404</v>
       </c>
-      <c r="E85" s="24"/>
-      <c r="F85" s="24"/>
-      <c r="G85" s="24"/>
+      <c r="E85" s="25"/>
+      <c r="F85" s="25"/>
+      <c r="G85" s="25"/>
     </row>
     <row r="86" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A86" s="1" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="B86" s="1" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="C86" s="1" t="s">
         <v>143</v>
       </c>
-      <c r="D86" s="24" t="s">
-        <v>409</v>
-      </c>
-      <c r="E86" s="24"/>
-      <c r="F86" s="24"/>
-      <c r="G86" s="24"/>
+      <c r="D86" s="1" t="s">
+        <v>526</v>
+      </c>
+      <c r="E86" s="1" t="s">
+        <v>527</v>
+      </c>
+      <c r="F86" s="1" t="s">
+        <v>528</v>
+      </c>
+      <c r="G86" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="87" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A87" s="1" t="s">
+        <v>741</v>
+      </c>
+      <c r="B87" s="1" t="s">
+        <v>742</v>
+      </c>
+      <c r="C87" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D87" s="25" t="s">
+        <v>404</v>
+      </c>
+      <c r="E87" s="25"/>
+      <c r="F87" s="25"/>
+      <c r="G87" s="25"/>
     </row>
     <row r="88" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A88" s="1" t="s">
-        <v>520</v>
+        <v>95</v>
       </c>
       <c r="B88" s="1" t="s">
-        <v>521</v>
+        <v>96</v>
       </c>
       <c r="C88" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="D88" s="30" t="s">
-        <v>178</v>
-      </c>
-      <c r="E88" s="30"/>
-      <c r="F88" s="30"/>
-      <c r="G88" s="30"/>
-    </row>
-    <row r="89" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A89" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="B89" s="1" t="s">
-        <v>517</v>
-      </c>
-      <c r="C89" s="1" t="s">
-        <v>532</v>
-      </c>
-      <c r="D89" s="7" t="s">
-        <v>121</v>
-      </c>
-      <c r="E89" s="7" t="s">
-        <v>122</v>
-      </c>
-      <c r="F89" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="G89" s="1" t="s">
-        <v>14</v>
-      </c>
+        <v>143</v>
+      </c>
+      <c r="D88" s="25" t="s">
+        <v>409</v>
+      </c>
+      <c r="E88" s="25"/>
+      <c r="F88" s="25"/>
+      <c r="G88" s="25"/>
     </row>
     <row r="90" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A90" s="1" t="s">
-        <v>97</v>
+        <v>520</v>
       </c>
       <c r="B90" s="1" t="s">
-        <v>518</v>
+        <v>521</v>
       </c>
       <c r="C90" s="1" t="s">
-        <v>143</v>
-      </c>
-      <c r="D90" s="1" t="s">
-        <v>545</v>
-      </c>
-      <c r="E90" s="1" t="s">
-        <v>546</v>
-      </c>
-      <c r="F90" s="1" t="s">
-        <v>547</v>
-      </c>
-      <c r="G90" s="1" t="s">
-        <v>14</v>
-      </c>
+        <v>43</v>
+      </c>
+      <c r="D90" s="26" t="s">
+        <v>178</v>
+      </c>
+      <c r="E90" s="26"/>
+      <c r="F90" s="26"/>
+      <c r="G90" s="26"/>
     </row>
     <row r="91" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A91" s="1" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="B91" s="1" t="s">
-        <v>99</v>
+        <v>517</v>
       </c>
       <c r="C91" s="1" t="s">
-        <v>533</v>
-      </c>
-      <c r="D91" s="15" t="s">
-        <v>535</v>
-      </c>
-      <c r="E91" s="15" t="s">
-        <v>540</v>
-      </c>
-      <c r="F91" s="15" t="s">
-        <v>541</v>
-      </c>
-      <c r="G91" s="15" t="s">
+        <v>532</v>
+      </c>
+      <c r="D91" s="7" t="s">
+        <v>121</v>
+      </c>
+      <c r="E91" s="7" t="s">
+        <v>122</v>
+      </c>
+      <c r="F91" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="G91" s="1" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="92" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A92" s="1" t="s">
-        <v>523</v>
+        <v>97</v>
       </c>
       <c r="B92" s="1" t="s">
-        <v>522</v>
+        <v>518</v>
       </c>
       <c r="C92" s="1" t="s">
         <v>143</v>
       </c>
       <c r="D92" s="1" t="s">
-        <v>542</v>
+        <v>545</v>
       </c>
       <c r="E92" s="1" t="s">
-        <v>543</v>
+        <v>546</v>
       </c>
       <c r="F92" s="1" t="s">
-        <v>544</v>
+        <v>547</v>
       </c>
       <c r="G92" s="1" t="s">
         <v>14</v>
@@ -5734,194 +5773,194 @@
     </row>
     <row r="93" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A93" s="1" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="B93" s="1" t="s">
-        <v>519</v>
+        <v>99</v>
       </c>
       <c r="C93" s="1" t="s">
-        <v>143</v>
-      </c>
-      <c r="D93" s="1" t="s">
-        <v>529</v>
-      </c>
-      <c r="E93" s="1" t="s">
-        <v>530</v>
-      </c>
-      <c r="F93" s="1" t="s">
-        <v>531</v>
-      </c>
-      <c r="G93" s="1" t="s">
+        <v>533</v>
+      </c>
+      <c r="D93" s="15" t="s">
+        <v>535</v>
+      </c>
+      <c r="E93" s="15" t="s">
+        <v>540</v>
+      </c>
+      <c r="F93" s="15" t="s">
+        <v>541</v>
+      </c>
+      <c r="G93" s="15" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="94" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A94" s="1" t="s">
-        <v>101</v>
+        <v>523</v>
       </c>
       <c r="B94" s="1" t="s">
-        <v>102</v>
+        <v>522</v>
       </c>
       <c r="C94" s="1" t="s">
-        <v>533</v>
-      </c>
-      <c r="D94" s="15" t="s">
-        <v>539</v>
-      </c>
-      <c r="E94" s="15" t="s">
-        <v>536</v>
-      </c>
-      <c r="F94" s="15" t="s">
-        <v>537</v>
-      </c>
-      <c r="G94" s="15" t="s">
-        <v>538</v>
+        <v>143</v>
+      </c>
+      <c r="D94" s="1" t="s">
+        <v>542</v>
+      </c>
+      <c r="E94" s="1" t="s">
+        <v>543</v>
+      </c>
+      <c r="F94" s="1" t="s">
+        <v>544</v>
+      </c>
+      <c r="G94" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="95" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A95" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="B95" s="1" t="s">
+        <v>519</v>
+      </c>
+      <c r="C95" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="D95" s="1" t="s">
+        <v>529</v>
+      </c>
+      <c r="E95" s="1" t="s">
+        <v>530</v>
+      </c>
+      <c r="F95" s="1" t="s">
+        <v>531</v>
+      </c>
+      <c r="G95" s="1" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="96" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A96" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="B96" s="16" t="s">
-        <v>105</v>
+        <v>101</v>
+      </c>
+      <c r="B96" s="1" t="s">
+        <v>102</v>
       </c>
       <c r="C96" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="D96" s="6" t="s">
-        <v>382</v>
-      </c>
-      <c r="E96" s="7" t="s">
-        <v>384</v>
-      </c>
-      <c r="F96" s="1" t="s">
-        <v>383</v>
-      </c>
-      <c r="G96" s="1" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="97" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A97" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="B97" s="16" t="s">
-        <v>107</v>
-      </c>
-      <c r="C97" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="D97" s="7" t="s">
-        <v>136</v>
-      </c>
-      <c r="E97" s="7" t="s">
-        <v>137</v>
-      </c>
-      <c r="F97" s="7" t="s">
-        <v>138</v>
-      </c>
-      <c r="G97" s="1" t="s">
-        <v>14</v>
+        <v>533</v>
+      </c>
+      <c r="D96" s="15" t="s">
+        <v>539</v>
+      </c>
+      <c r="E96" s="15" t="s">
+        <v>536</v>
+      </c>
+      <c r="F96" s="15" t="s">
+        <v>537</v>
+      </c>
+      <c r="G96" s="15" t="s">
+        <v>538</v>
       </c>
     </row>
     <row r="98" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A98" s="1" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="B98" s="16" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="C98" s="1" t="s">
-        <v>143</v>
-      </c>
-      <c r="D98" s="24" t="s">
-        <v>404</v>
-      </c>
-      <c r="E98" s="24"/>
-      <c r="F98" s="24"/>
-      <c r="G98" s="24"/>
+        <v>43</v>
+      </c>
+      <c r="D98" s="6" t="s">
+        <v>382</v>
+      </c>
+      <c r="E98" s="7" t="s">
+        <v>384</v>
+      </c>
+      <c r="F98" s="1" t="s">
+        <v>383</v>
+      </c>
+      <c r="G98" s="1" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="99" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A99" s="1" t="s">
-        <v>110</v>
-      </c>
-      <c r="B99" s="1" t="s">
-        <v>111</v>
+        <v>106</v>
+      </c>
+      <c r="B99" s="16" t="s">
+        <v>107</v>
       </c>
       <c r="C99" s="1" t="s">
-        <v>143</v>
-      </c>
-      <c r="D99" s="24" t="s">
-        <v>404</v>
-      </c>
-      <c r="E99" s="24"/>
-      <c r="F99" s="24"/>
-      <c r="G99" s="24"/>
+        <v>43</v>
+      </c>
+      <c r="D99" s="7" t="s">
+        <v>136</v>
+      </c>
+      <c r="E99" s="7" t="s">
+        <v>137</v>
+      </c>
+      <c r="F99" s="7" t="s">
+        <v>138</v>
+      </c>
+      <c r="G99" s="1" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="100" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A100" s="1" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="B100" s="16" t="s">
-        <v>506</v>
+        <v>109</v>
       </c>
       <c r="C100" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="D100" s="1" t="s">
-        <v>508</v>
-      </c>
-      <c r="E100" s="1" t="s">
-        <v>509</v>
-      </c>
-      <c r="F100" s="1" t="s">
-        <v>510</v>
-      </c>
-      <c r="G100" s="1" t="s">
-        <v>14</v>
-      </c>
+        <v>143</v>
+      </c>
+      <c r="D100" s="25" t="s">
+        <v>404</v>
+      </c>
+      <c r="E100" s="25"/>
+      <c r="F100" s="25"/>
+      <c r="G100" s="25"/>
     </row>
     <row r="101" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A101" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="B101" s="16" t="s">
-        <v>507</v>
+        <v>110</v>
+      </c>
+      <c r="B101" s="1" t="s">
+        <v>111</v>
       </c>
       <c r="C101" s="1" t="s">
-        <v>534</v>
-      </c>
-      <c r="D101" s="15" t="s">
-        <v>512</v>
-      </c>
-      <c r="E101" s="15" t="s">
-        <v>513</v>
-      </c>
-      <c r="F101" s="15" t="s">
-        <v>514</v>
-      </c>
-      <c r="G101" s="15" t="s">
-        <v>511</v>
-      </c>
+        <v>143</v>
+      </c>
+      <c r="D101" s="25" t="s">
+        <v>404</v>
+      </c>
+      <c r="E101" s="25"/>
+      <c r="F101" s="25"/>
+      <c r="G101" s="25"/>
     </row>
     <row r="102" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A102" s="1" t="s">
-        <v>525</v>
+        <v>112</v>
       </c>
       <c r="B102" s="16" t="s">
-        <v>524</v>
+        <v>506</v>
       </c>
       <c r="C102" s="1" t="s">
         <v>43</v>
       </c>
       <c r="D102" s="1" t="s">
-        <v>548</v>
+        <v>508</v>
       </c>
       <c r="E102" s="1" t="s">
-        <v>549</v>
+        <v>509</v>
       </c>
       <c r="F102" s="1" t="s">
-        <v>550</v>
+        <v>510</v>
       </c>
       <c r="G102" s="1" t="s">
         <v>14</v>
@@ -5929,78 +5968,102 @@
     </row>
     <row r="103" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A103" s="1" t="s">
-        <v>113</v>
-      </c>
-      <c r="B103" s="1" t="s">
-        <v>114</v>
+        <v>112</v>
+      </c>
+      <c r="B103" s="16" t="s">
+        <v>507</v>
       </c>
       <c r="C103" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="D103" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="E103" s="1" t="s">
-        <v>118</v>
-      </c>
-      <c r="F103" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="G103" s="1" t="s">
-        <v>14</v>
+        <v>534</v>
+      </c>
+      <c r="D103" s="15" t="s">
+        <v>512</v>
+      </c>
+      <c r="E103" s="15" t="s">
+        <v>513</v>
+      </c>
+      <c r="F103" s="15" t="s">
+        <v>514</v>
+      </c>
+      <c r="G103" s="15" t="s">
+        <v>511</v>
       </c>
     </row>
     <row r="104" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A104" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="B104" s="1" t="s">
-        <v>116</v>
+        <v>525</v>
+      </c>
+      <c r="B104" s="16" t="s">
+        <v>524</v>
       </c>
       <c r="C104" s="1" t="s">
-        <v>143</v>
+        <v>43</v>
       </c>
       <c r="D104" s="1" t="s">
-        <v>379</v>
+        <v>548</v>
       </c>
       <c r="E104" s="1" t="s">
-        <v>380</v>
+        <v>549</v>
       </c>
       <c r="F104" s="1" t="s">
-        <v>381</v>
+        <v>550</v>
       </c>
       <c r="G104" s="1" t="s">
         <v>14</v>
       </c>
     </row>
+    <row r="105" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A105" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="B105" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="C105" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D105" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="E105" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="F105" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="G105" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
     <row r="106" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A106" s="1" t="s">
-        <v>184</v>
+        <v>115</v>
       </c>
       <c r="B106" s="1" t="s">
-        <v>185</v>
-      </c>
-      <c r="H106" s="1" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="107" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A107" s="1" t="s">
-        <v>186</v>
-      </c>
-      <c r="B107" s="1" t="s">
-        <v>187</v>
-      </c>
-      <c r="H107" s="1" t="s">
-        <v>183</v>
+        <v>116</v>
+      </c>
+      <c r="C106" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="D106" s="1" t="s">
+        <v>379</v>
+      </c>
+      <c r="E106" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="F106" s="1" t="s">
+        <v>381</v>
+      </c>
+      <c r="G106" s="1" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="108" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A108" s="1" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="B108" s="1" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="H108" s="1" t="s">
         <v>183</v>
@@ -6008,10 +6071,10 @@
     </row>
     <row r="109" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A109" s="1" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="B109" s="1" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="H109" s="1" t="s">
         <v>183</v>
@@ -6019,10 +6082,10 @@
     </row>
     <row r="110" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A110" s="1" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="B110" s="1" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="H110" s="1" t="s">
         <v>183</v>
@@ -6030,10 +6093,10 @@
     </row>
     <row r="111" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A111" s="1" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="B111" s="1" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="H111" s="1" t="s">
         <v>183</v>
@@ -6041,10 +6104,10 @@
     </row>
     <row r="112" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A112" s="1" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="B112" s="1" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="H112" s="1" t="s">
         <v>183</v>
@@ -6052,10 +6115,10 @@
     </row>
     <row r="113" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A113" s="1" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="B113" s="1" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="H113" s="1" t="s">
         <v>183</v>
@@ -6063,10 +6126,10 @@
     </row>
     <row r="114" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A114" s="1" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="B114" s="1" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="H114" s="1" t="s">
         <v>183</v>
@@ -6074,78 +6137,78 @@
     </row>
     <row r="115" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A115" s="1" t="s">
-        <v>728</v>
+        <v>198</v>
       </c>
       <c r="B115" s="1" t="s">
-        <v>729</v>
-      </c>
-      <c r="C115" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="D115" s="1" t="s">
-        <v>732</v>
-      </c>
-      <c r="E115" s="1" t="s">
-        <v>731</v>
-      </c>
-      <c r="F115" s="1" t="s">
-        <v>730</v>
-      </c>
-      <c r="G115" s="1" t="s">
-        <v>14</v>
+        <v>199</v>
+      </c>
+      <c r="H115" s="1" t="s">
+        <v>183</v>
       </c>
     </row>
     <row r="116" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A116" s="1" t="s">
-        <v>743</v>
+        <v>200</v>
       </c>
       <c r="B116" s="1" t="s">
-        <v>744</v>
-      </c>
-      <c r="C116" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="D116" s="1" t="s">
-        <v>745</v>
-      </c>
-      <c r="E116" s="1" t="s">
-        <v>746</v>
-      </c>
-      <c r="F116" s="1" t="s">
-        <v>747</v>
-      </c>
-      <c r="G116" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="H116" s="1" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="117" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A117" s="1" t="s">
+        <v>728</v>
+      </c>
+      <c r="B117" s="1" t="s">
+        <v>729</v>
+      </c>
+      <c r="C117" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D117" s="1" t="s">
+        <v>732</v>
+      </c>
+      <c r="E117" s="1" t="s">
+        <v>731</v>
+      </c>
+      <c r="F117" s="1" t="s">
+        <v>730</v>
+      </c>
+      <c r="G117" s="1" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="118" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A118" s="1" t="s">
-        <v>274</v>
+        <v>743</v>
       </c>
       <c r="B118" s="1" t="s">
-        <v>275</v>
-      </c>
-      <c r="H118" s="1" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="119" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A119" s="1" t="s">
-        <v>276</v>
-      </c>
-      <c r="B119" s="1" t="s">
-        <v>277</v>
-      </c>
-      <c r="H119" s="1" t="s">
-        <v>213</v>
+        <v>744</v>
+      </c>
+      <c r="C118" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D118" s="1" t="s">
+        <v>745</v>
+      </c>
+      <c r="E118" s="1" t="s">
+        <v>746</v>
+      </c>
+      <c r="F118" s="1" t="s">
+        <v>747</v>
+      </c>
+      <c r="G118" s="1" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="120" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A120" s="1" t="s">
-        <v>278</v>
+        <v>274</v>
       </c>
       <c r="B120" s="1" t="s">
-        <v>279</v>
+        <v>275</v>
       </c>
       <c r="H120" s="1" t="s">
         <v>213</v>
@@ -6153,10 +6216,10 @@
     </row>
     <row r="121" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A121" s="1" t="s">
-        <v>280</v>
+        <v>276</v>
       </c>
       <c r="B121" s="1" t="s">
-        <v>281</v>
+        <v>277</v>
       </c>
       <c r="H121" s="1" t="s">
         <v>213</v>
@@ -6164,10 +6227,10 @@
     </row>
     <row r="122" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A122" s="1" t="s">
-        <v>282</v>
+        <v>278</v>
       </c>
       <c r="B122" s="1" t="s">
-        <v>283</v>
+        <v>279</v>
       </c>
       <c r="H122" s="1" t="s">
         <v>213</v>
@@ -6175,10 +6238,10 @@
     </row>
     <row r="123" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A123" s="1" t="s">
-        <v>284</v>
+        <v>280</v>
       </c>
       <c r="B123" s="1" t="s">
-        <v>285</v>
+        <v>281</v>
       </c>
       <c r="H123" s="1" t="s">
         <v>213</v>
@@ -6186,10 +6249,10 @@
     </row>
     <row r="124" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A124" s="1" t="s">
-        <v>286</v>
+        <v>282</v>
       </c>
       <c r="B124" s="1" t="s">
-        <v>287</v>
+        <v>283</v>
       </c>
       <c r="H124" s="1" t="s">
         <v>213</v>
@@ -6197,10 +6260,10 @@
     </row>
     <row r="125" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A125" s="1" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="B125" s="1" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
       <c r="H125" s="1" t="s">
         <v>213</v>
@@ -6208,312 +6271,288 @@
     </row>
     <row r="126" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A126" s="1" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="B126" s="1" t="s">
-        <v>291</v>
+        <v>287</v>
       </c>
       <c r="H126" s="1" t="s">
         <v>213</v>
       </c>
     </row>
+    <row r="127" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A127" s="1" t="s">
+        <v>288</v>
+      </c>
+      <c r="B127" s="1" t="s">
+        <v>289</v>
+      </c>
+      <c r="H127" s="1" t="s">
+        <v>213</v>
+      </c>
+    </row>
     <row r="128" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A128" s="1" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="B128" s="1" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="H128" s="1" t="s">
         <v>213</v>
       </c>
     </row>
-    <row r="129" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A129" s="1" t="s">
+    <row r="130" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A130" s="1" t="s">
+        <v>292</v>
+      </c>
+      <c r="B130" s="1" t="s">
+        <v>293</v>
+      </c>
+      <c r="H130" s="1" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="131" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A131" s="1" t="s">
         <v>294</v>
       </c>
-      <c r="B129" s="1" t="s">
+      <c r="B131" s="1" t="s">
         <v>295</v>
       </c>
-      <c r="C129" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="D129" s="24" t="s">
+      <c r="C131" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D131" s="25" t="s">
         <v>713</v>
       </c>
-      <c r="E129" s="24"/>
-      <c r="F129" s="24"/>
-      <c r="G129" s="24"/>
-    </row>
-    <row r="130" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A130" s="16" t="s">
+      <c r="E131" s="25"/>
+      <c r="F131" s="25"/>
+      <c r="G131" s="25"/>
+    </row>
+    <row r="132" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A132" s="16" t="s">
         <v>296</v>
       </c>
-      <c r="B130" s="16" t="s">
+      <c r="B132" s="16" t="s">
         <v>297</v>
       </c>
-      <c r="C130" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="D130" s="30" t="s">
+      <c r="C132" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D132" s="26" t="s">
         <v>343</v>
       </c>
-      <c r="E130" s="30"/>
-      <c r="F130" s="30"/>
-      <c r="G130" s="30"/>
-    </row>
-    <row r="131" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A131" s="16" t="s">
+      <c r="E132" s="26"/>
+      <c r="F132" s="26"/>
+      <c r="G132" s="26"/>
+    </row>
+    <row r="133" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A133" s="16" t="s">
         <v>700</v>
       </c>
-      <c r="B131" s="16" t="s">
+      <c r="B133" s="16" t="s">
         <v>701</v>
       </c>
-      <c r="C131" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="D131" s="7" t="s">
+      <c r="C133" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D133" s="7" t="s">
         <v>706</v>
       </c>
-      <c r="E131" s="7" t="s">
+      <c r="E133" s="7" t="s">
         <v>707</v>
       </c>
-      <c r="F131" s="1" t="s">
+      <c r="F133" s="1" t="s">
         <v>704</v>
       </c>
-      <c r="G131" s="1" t="s">
+      <c r="G133" s="1" t="s">
         <v>705</v>
       </c>
     </row>
-    <row r="132" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A132" s="16" t="s">
+    <row r="134" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A134" s="16" t="s">
         <v>702</v>
       </c>
-      <c r="B132" s="16" t="s">
+      <c r="B134" s="16" t="s">
         <v>703</v>
       </c>
-      <c r="C132" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="D132" s="1" t="s">
+      <c r="C134" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D134" s="1" t="s">
         <v>708</v>
       </c>
-      <c r="E132" s="1" t="s">
+      <c r="E134" s="1" t="s">
         <v>709</v>
       </c>
-      <c r="F132" s="1" t="s">
+      <c r="F134" s="1" t="s">
         <v>710</v>
       </c>
-      <c r="G132" s="1" t="s">
+      <c r="G134" s="1" t="s">
         <v>705</v>
       </c>
     </row>
-    <row r="133" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A133" s="16" t="s">
+    <row r="135" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A135" s="16" t="s">
         <v>403</v>
       </c>
-      <c r="B133" s="16" t="s">
+      <c r="B135" s="16" t="s">
         <v>402</v>
       </c>
-      <c r="C133" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="D133" s="24" t="s">
+      <c r="C135" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D135" s="25" t="s">
         <v>411</v>
       </c>
-      <c r="E133" s="24"/>
-      <c r="F133" s="24"/>
-      <c r="G133" s="24"/>
-    </row>
-    <row r="134" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A134" s="1" t="s">
+      <c r="E135" s="25"/>
+      <c r="F135" s="25"/>
+      <c r="G135" s="25"/>
+    </row>
+    <row r="136" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A136" s="1" t="s">
         <v>298</v>
       </c>
-      <c r="B134" s="1" t="s">
+      <c r="B136" s="1" t="s">
         <v>299</v>
-      </c>
-      <c r="C134" s="1" t="s">
-        <v>143</v>
-      </c>
-      <c r="D134" s="24" t="s">
-        <v>406</v>
-      </c>
-      <c r="E134" s="24"/>
-      <c r="F134" s="24"/>
-      <c r="G134" s="24"/>
-    </row>
-    <row r="135" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A135" s="1" t="s">
-        <v>300</v>
-      </c>
-      <c r="B135" s="1" t="s">
-        <v>301</v>
-      </c>
-      <c r="C135" s="1" t="s">
-        <v>143</v>
-      </c>
-      <c r="D135" s="24" t="s">
-        <v>406</v>
-      </c>
-      <c r="E135" s="24"/>
-      <c r="F135" s="24"/>
-      <c r="G135" s="24"/>
-    </row>
-    <row r="136" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A136" s="1" t="s">
-        <v>302</v>
-      </c>
-      <c r="B136" s="1" t="s">
-        <v>303</v>
       </c>
       <c r="C136" s="1" t="s">
         <v>143</v>
       </c>
-      <c r="D136" s="24" t="s">
+      <c r="D136" s="25" t="s">
         <v>406</v>
       </c>
-      <c r="E136" s="24"/>
-      <c r="F136" s="24"/>
-      <c r="G136" s="24"/>
-    </row>
-    <row r="138" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="E136" s="25"/>
+      <c r="F136" s="25"/>
+      <c r="G136" s="25"/>
+    </row>
+    <row r="137" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A137" s="1" t="s">
+        <v>300</v>
+      </c>
+      <c r="B137" s="1" t="s">
+        <v>301</v>
+      </c>
+      <c r="C137" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="D137" s="25" t="s">
+        <v>406</v>
+      </c>
+      <c r="E137" s="25"/>
+      <c r="F137" s="25"/>
+      <c r="G137" s="25"/>
+    </row>
+    <row r="138" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A138" s="1" t="s">
+        <v>302</v>
+      </c>
+      <c r="B138" s="1" t="s">
+        <v>303</v>
+      </c>
+      <c r="C138" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="D138" s="25" t="s">
+        <v>406</v>
+      </c>
+      <c r="E138" s="25"/>
+      <c r="F138" s="25"/>
+      <c r="G138" s="25"/>
+    </row>
+    <row r="140" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A140" s="1" t="s">
         <v>603</v>
       </c>
-      <c r="B138" s="1" t="s">
+      <c r="B140" s="1" t="s">
         <v>604</v>
       </c>
-      <c r="C138" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="D138" s="24" t="s">
+      <c r="C140" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D140" s="25" t="s">
         <v>404</v>
       </c>
-      <c r="E138" s="24"/>
-      <c r="F138" s="24"/>
-      <c r="G138" s="24"/>
-    </row>
-    <row r="139" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A139" s="1" t="s">
+      <c r="E140" s="25"/>
+      <c r="F140" s="25"/>
+      <c r="G140" s="25"/>
+    </row>
+    <row r="141" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A141" s="1" t="s">
         <v>605</v>
       </c>
-      <c r="B139" s="1" t="s">
+      <c r="B141" s="1" t="s">
         <v>606</v>
       </c>
-      <c r="C139" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="D139" s="24" t="s">
+      <c r="C141" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D141" s="25" t="s">
         <v>404</v>
       </c>
-      <c r="E139" s="24"/>
-      <c r="F139" s="24"/>
-      <c r="G139" s="24"/>
-    </row>
-    <row r="140" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A140" s="1" t="s">
+      <c r="E141" s="25"/>
+      <c r="F141" s="25"/>
+      <c r="G141" s="25"/>
+    </row>
+    <row r="142" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A142" s="1" t="s">
         <v>124</v>
       </c>
-      <c r="B140" s="1" t="s">
+      <c r="B142" s="1" t="s">
         <v>125</v>
       </c>
-      <c r="C140" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="D140" s="30" t="s">
+      <c r="C142" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D142" s="26" t="s">
         <v>307</v>
       </c>
-      <c r="E140" s="30"/>
-      <c r="F140" s="30"/>
-      <c r="G140" s="30"/>
-    </row>
-    <row r="141" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A141" s="1" t="s">
+      <c r="E142" s="26"/>
+      <c r="F142" s="26"/>
+      <c r="G142" s="26"/>
+    </row>
+    <row r="143" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A143" s="1" t="s">
         <v>126</v>
       </c>
-      <c r="B141" s="1" t="s">
+      <c r="B143" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="C141" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="D141" s="1" t="s">
+      <c r="C143" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D143" s="1" t="s">
         <v>130</v>
       </c>
-      <c r="E141" s="1" t="s">
+      <c r="E143" s="1" t="s">
         <v>131</v>
       </c>
-      <c r="F141" s="1" t="s">
+      <c r="F143" s="1" t="s">
         <v>132</v>
-      </c>
-      <c r="G141" s="1" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="142" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A142" s="1" t="s">
-        <v>128</v>
-      </c>
-      <c r="B142" s="1" t="s">
-        <v>129</v>
-      </c>
-      <c r="C142" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="D142" s="1" t="s">
-        <v>133</v>
-      </c>
-      <c r="E142" s="1" t="s">
-        <v>134</v>
-      </c>
-      <c r="F142" s="1" t="s">
-        <v>135</v>
-      </c>
-      <c r="G142" s="1" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="143" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A143" s="1" t="s">
-        <v>757</v>
-      </c>
-      <c r="B143" s="1" t="s">
-        <v>758</v>
-      </c>
-      <c r="C143" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="D143" s="1" t="s">
-        <v>759</v>
-      </c>
-      <c r="E143" s="1" t="s">
-        <v>760</v>
-      </c>
-      <c r="F143" s="1" t="s">
-        <v>761</v>
       </c>
       <c r="G143" s="1" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="144" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="144" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A144" s="1" t="s">
-        <v>756</v>
+        <v>128</v>
       </c>
       <c r="B144" s="1" t="s">
-        <v>762</v>
+        <v>129</v>
       </c>
       <c r="C144" s="1" t="s">
         <v>43</v>
       </c>
       <c r="D144" s="1" t="s">
-        <v>763</v>
+        <v>133</v>
       </c>
       <c r="E144" s="1" t="s">
-        <v>764</v>
+        <v>134</v>
       </c>
       <c r="F144" s="1" t="s">
-        <v>765</v>
+        <v>135</v>
       </c>
       <c r="G144" s="1" t="s">
         <v>14</v>
@@ -6521,245 +6560,245 @@
     </row>
     <row r="145" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A145" s="1" t="s">
-        <v>635</v>
+        <v>757</v>
       </c>
       <c r="B145" s="1" t="s">
-        <v>636</v>
+        <v>758</v>
       </c>
       <c r="C145" s="1" t="s">
         <v>43</v>
       </c>
       <c r="D145" s="1" t="s">
-        <v>637</v>
+        <v>759</v>
       </c>
       <c r="E145" s="1" t="s">
-        <v>638</v>
+        <v>760</v>
       </c>
       <c r="F145" s="1" t="s">
-        <v>639</v>
+        <v>761</v>
       </c>
       <c r="G145" s="1" t="s">
-        <v>640</v>
+        <v>14</v>
+      </c>
+    </row>
+    <row r="146" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A146" s="1" t="s">
+        <v>756</v>
+      </c>
+      <c r="B146" s="1" t="s">
+        <v>762</v>
+      </c>
+      <c r="C146" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D146" s="1" t="s">
+        <v>763</v>
+      </c>
+      <c r="E146" s="1" t="s">
+        <v>764</v>
+      </c>
+      <c r="F146" s="1" t="s">
+        <v>765</v>
+      </c>
+      <c r="G146" s="1" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="147" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A147" s="1" t="s">
-        <v>312</v>
+        <v>635</v>
       </c>
       <c r="B147" s="1" t="s">
-        <v>314</v>
+        <v>636</v>
       </c>
       <c r="C147" s="1" t="s">
-        <v>143</v>
-      </c>
-      <c r="D147" s="24" t="s">
-        <v>786</v>
-      </c>
-      <c r="E147" s="24"/>
-      <c r="F147" s="24"/>
-      <c r="G147" s="24"/>
-    </row>
-    <row r="148" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A148" s="1" t="s">
-        <v>315</v>
-      </c>
-      <c r="B148" s="1" t="s">
-        <v>316</v>
-      </c>
-      <c r="C148" s="1" t="s">
-        <v>669</v>
-      </c>
-      <c r="D148" s="24" t="s">
-        <v>404</v>
-      </c>
-      <c r="E148" s="24"/>
-      <c r="F148" s="24"/>
-      <c r="G148" s="24"/>
+        <v>43</v>
+      </c>
+      <c r="D147" s="1" t="s">
+        <v>637</v>
+      </c>
+      <c r="E147" s="1" t="s">
+        <v>638</v>
+      </c>
+      <c r="F147" s="1" t="s">
+        <v>639</v>
+      </c>
+      <c r="G147" s="1" t="s">
+        <v>640</v>
+      </c>
     </row>
     <row r="149" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A149" s="1" t="s">
-        <v>673</v>
+        <v>312</v>
       </c>
       <c r="B149" s="1" t="s">
-        <v>674</v>
+        <v>314</v>
       </c>
       <c r="C149" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="D149" s="23" t="s">
-        <v>676</v>
-      </c>
-      <c r="E149" s="23" t="s">
-        <v>677</v>
-      </c>
-      <c r="F149" s="23" t="s">
-        <v>678</v>
-      </c>
-      <c r="G149" s="1" t="s">
-        <v>14</v>
-      </c>
+        <v>143</v>
+      </c>
+      <c r="D149" s="25" t="s">
+        <v>786</v>
+      </c>
+      <c r="E149" s="25"/>
+      <c r="F149" s="25"/>
+      <c r="G149" s="25"/>
     </row>
     <row r="150" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A150" s="1" t="s">
-        <v>784</v>
+        <v>315</v>
       </c>
       <c r="B150" s="1" t="s">
-        <v>785</v>
+        <v>316</v>
       </c>
       <c r="C150" s="1" t="s">
-        <v>143</v>
-      </c>
-      <c r="D150" s="24" t="s">
+        <v>669</v>
+      </c>
+      <c r="D150" s="25" t="s">
         <v>404</v>
       </c>
-      <c r="E150" s="24"/>
-      <c r="F150" s="24"/>
-      <c r="G150" s="24"/>
+      <c r="E150" s="25"/>
+      <c r="F150" s="25"/>
+      <c r="G150" s="25"/>
     </row>
     <row r="151" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A151" s="1" t="s">
-        <v>782</v>
+        <v>673</v>
       </c>
       <c r="B151" s="1" t="s">
-        <v>783</v>
+        <v>674</v>
       </c>
       <c r="C151" s="1" t="s">
-        <v>143</v>
-      </c>
-      <c r="D151" s="24" t="s">
-        <v>404</v>
-      </c>
-      <c r="E151" s="24"/>
-      <c r="F151" s="24"/>
-      <c r="G151" s="24"/>
+        <v>43</v>
+      </c>
+      <c r="D151" s="23" t="s">
+        <v>676</v>
+      </c>
+      <c r="E151" s="23" t="s">
+        <v>677</v>
+      </c>
+      <c r="F151" s="23" t="s">
+        <v>678</v>
+      </c>
+      <c r="G151" s="1" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="152" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A152" s="1" t="s">
-        <v>318</v>
+        <v>784</v>
       </c>
       <c r="B152" s="1" t="s">
-        <v>320</v>
+        <v>785</v>
       </c>
       <c r="C152" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="D152" s="24" t="s">
-        <v>412</v>
-      </c>
-      <c r="E152" s="24"/>
-      <c r="F152" s="24"/>
-      <c r="G152" s="24"/>
+        <v>143</v>
+      </c>
+      <c r="D152" s="25" t="s">
+        <v>404</v>
+      </c>
+      <c r="E152" s="25"/>
+      <c r="F152" s="25"/>
+      <c r="G152" s="25"/>
     </row>
     <row r="153" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A153" s="1" t="s">
-        <v>641</v>
+        <v>782</v>
       </c>
       <c r="B153" s="1" t="s">
-        <v>642</v>
+        <v>783</v>
       </c>
       <c r="C153" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="D153" s="7" t="s">
-        <v>651</v>
-      </c>
-      <c r="E153" s="7" t="s">
-        <v>643</v>
-      </c>
-      <c r="F153" s="1" t="s">
-        <v>644</v>
-      </c>
-      <c r="G153" s="1" t="s">
-        <v>645</v>
-      </c>
+        <v>143</v>
+      </c>
+      <c r="D153" s="25" t="s">
+        <v>404</v>
+      </c>
+      <c r="E153" s="25"/>
+      <c r="F153" s="25"/>
+      <c r="G153" s="25"/>
+    </row>
+    <row r="154" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A154" s="1" t="s">
+        <v>318</v>
+      </c>
+      <c r="B154" s="1" t="s">
+        <v>320</v>
+      </c>
+      <c r="C154" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D154" s="25" t="s">
+        <v>412</v>
+      </c>
+      <c r="E154" s="25"/>
+      <c r="F154" s="25"/>
+      <c r="G154" s="25"/>
     </row>
     <row r="155" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A155" s="1" t="s">
-        <v>667</v>
+        <v>641</v>
       </c>
       <c r="B155" s="1" t="s">
-        <v>668</v>
+        <v>642</v>
       </c>
       <c r="C155" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="D155" s="1" t="s">
-        <v>680</v>
-      </c>
-      <c r="E155" s="1" t="s">
-        <v>681</v>
+      <c r="D155" s="7" t="s">
+        <v>651</v>
+      </c>
+      <c r="E155" s="7" t="s">
+        <v>643</v>
       </c>
       <c r="F155" s="1" t="s">
-        <v>682</v>
+        <v>644</v>
       </c>
       <c r="G155" s="1" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="156" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A156" s="1" t="s">
-        <v>323</v>
-      </c>
-      <c r="B156" s="1" t="s">
-        <v>325</v>
-      </c>
-      <c r="C156" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="D156" s="6" t="s">
-        <v>346</v>
-      </c>
-      <c r="E156" s="7" t="s">
-        <v>344</v>
-      </c>
-      <c r="F156" s="7" t="s">
-        <v>345</v>
-      </c>
-      <c r="G156" s="1" t="s">
-        <v>14</v>
+        <v>645</v>
       </c>
     </row>
     <row r="157" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A157" s="1" t="s">
-        <v>646</v>
+        <v>667</v>
       </c>
       <c r="B157" s="1" t="s">
-        <v>647</v>
+        <v>668</v>
       </c>
       <c r="C157" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="D157" s="7" t="s">
-        <v>648</v>
-      </c>
-      <c r="E157" s="7" t="s">
-        <v>649</v>
-      </c>
-      <c r="F157" s="7" t="s">
-        <v>650</v>
+      <c r="D157" s="1" t="s">
+        <v>680</v>
+      </c>
+      <c r="E157" s="1" t="s">
+        <v>681</v>
+      </c>
+      <c r="F157" s="1" t="s">
+        <v>682</v>
       </c>
       <c r="G157" s="1" t="s">
-        <v>645</v>
+        <v>14</v>
       </c>
     </row>
     <row r="158" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A158" s="1" t="s">
-        <v>655</v>
+        <v>323</v>
       </c>
       <c r="B158" s="1" t="s">
-        <v>652</v>
+        <v>325</v>
       </c>
       <c r="C158" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="D158" s="1" t="s">
-        <v>658</v>
-      </c>
-      <c r="E158" s="1" t="s">
-        <v>659</v>
-      </c>
-      <c r="F158" s="1" t="s">
-        <v>660</v>
+      <c r="D158" s="6" t="s">
+        <v>346</v>
+      </c>
+      <c r="E158" s="7" t="s">
+        <v>344</v>
+      </c>
+      <c r="F158" s="7" t="s">
+        <v>345</v>
       </c>
       <c r="G158" s="1" t="s">
         <v>14</v>
@@ -6767,45 +6806,45 @@
     </row>
     <row r="159" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A159" s="1" t="s">
-        <v>656</v>
+        <v>646</v>
       </c>
       <c r="B159" s="1" t="s">
-        <v>653</v>
+        <v>647</v>
       </c>
       <c r="C159" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="D159" s="1" t="s">
-        <v>661</v>
-      </c>
-      <c r="E159" s="1" t="s">
-        <v>662</v>
-      </c>
-      <c r="F159" s="1" t="s">
-        <v>663</v>
+      <c r="D159" s="7" t="s">
+        <v>648</v>
+      </c>
+      <c r="E159" s="7" t="s">
+        <v>649</v>
+      </c>
+      <c r="F159" s="7" t="s">
+        <v>650</v>
       </c>
       <c r="G159" s="1" t="s">
-        <v>14</v>
+        <v>645</v>
       </c>
     </row>
     <row r="160" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A160" s="1" t="s">
-        <v>657</v>
+        <v>655</v>
       </c>
       <c r="B160" s="1" t="s">
-        <v>654</v>
+        <v>652</v>
       </c>
       <c r="C160" s="1" t="s">
         <v>43</v>
       </c>
       <c r="D160" s="1" t="s">
-        <v>664</v>
+        <v>658</v>
       </c>
       <c r="E160" s="1" t="s">
-        <v>665</v>
+        <v>659</v>
       </c>
       <c r="F160" s="1" t="s">
-        <v>666</v>
+        <v>660</v>
       </c>
       <c r="G160" s="1" t="s">
         <v>14</v>
@@ -6813,22 +6852,22 @@
     </row>
     <row r="161" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A161" s="1" t="s">
-        <v>750</v>
+        <v>656</v>
       </c>
       <c r="B161" s="1" t="s">
-        <v>751</v>
+        <v>653</v>
       </c>
       <c r="C161" s="1" t="s">
         <v>43</v>
       </c>
       <c r="D161" s="1" t="s">
-        <v>754</v>
+        <v>661</v>
       </c>
       <c r="E161" s="1" t="s">
-        <v>753</v>
+        <v>662</v>
       </c>
       <c r="F161" s="1" t="s">
-        <v>752</v>
+        <v>663</v>
       </c>
       <c r="G161" s="1" t="s">
         <v>14</v>
@@ -6836,22 +6875,22 @@
     </row>
     <row r="162" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A162" s="1" t="s">
-        <v>829</v>
+        <v>657</v>
       </c>
       <c r="B162" s="1" t="s">
-        <v>830</v>
+        <v>654</v>
       </c>
       <c r="C162" s="1" t="s">
         <v>43</v>
       </c>
       <c r="D162" s="1" t="s">
-        <v>831</v>
+        <v>664</v>
       </c>
       <c r="E162" s="1" t="s">
-        <v>832</v>
+        <v>665</v>
       </c>
       <c r="F162" s="1" t="s">
-        <v>833</v>
+        <v>666</v>
       </c>
       <c r="G162" s="1" t="s">
         <v>14</v>
@@ -6859,192 +6898,281 @@
     </row>
     <row r="163" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A163" s="1" t="s">
-        <v>829</v>
+        <v>750</v>
       </c>
       <c r="B163" s="1" t="s">
-        <v>836</v>
+        <v>751</v>
       </c>
       <c r="C163" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="D163" s="15" t="s">
-        <v>834</v>
-      </c>
-      <c r="E163" s="15"/>
-      <c r="F163" s="15"/>
-      <c r="G163" s="15"/>
+      <c r="D163" s="1" t="s">
+        <v>754</v>
+      </c>
+      <c r="E163" s="1" t="s">
+        <v>753</v>
+      </c>
+      <c r="F163" s="1" t="s">
+        <v>752</v>
+      </c>
+      <c r="G163" s="1" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="164" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A164" s="1" t="s">
-        <v>837</v>
+        <v>829</v>
       </c>
       <c r="B164" s="1" t="s">
-        <v>838</v>
+        <v>830</v>
       </c>
       <c r="C164" s="1" t="s">
         <v>43</v>
       </c>
       <c r="D164" s="1" t="s">
-        <v>839</v>
+        <v>831</v>
       </c>
       <c r="E164" s="1" t="s">
-        <v>840</v>
+        <v>832</v>
       </c>
       <c r="F164" s="1" t="s">
-        <v>841</v>
+        <v>833</v>
       </c>
       <c r="G164" s="1" t="s">
         <v>14</v>
       </c>
     </row>
+    <row r="165" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A165" s="1" t="s">
+        <v>829</v>
+      </c>
+      <c r="B165" s="1" t="s">
+        <v>836</v>
+      </c>
+      <c r="C165" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D165" s="15" t="s">
+        <v>834</v>
+      </c>
+      <c r="E165" s="15"/>
+      <c r="F165" s="15"/>
+      <c r="G165" s="15"/>
+    </row>
     <row r="166" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A166" s="1" t="s">
-        <v>795</v>
+        <v>837</v>
       </c>
       <c r="B166" s="1" t="s">
-        <v>796</v>
+        <v>838</v>
       </c>
       <c r="C166" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="D166" s="24" t="s">
-        <v>805</v>
-      </c>
-      <c r="E166" s="24"/>
-      <c r="F166" s="24"/>
-      <c r="G166" s="24"/>
-    </row>
-    <row r="167" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A167" s="1" t="s">
-        <v>793</v>
-      </c>
-      <c r="B167" s="1" t="s">
-        <v>794</v>
-      </c>
-      <c r="C167" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="D167" s="24" t="s">
-        <v>806</v>
-      </c>
-      <c r="E167" s="24"/>
-      <c r="F167" s="24"/>
-      <c r="G167" s="24"/>
+      <c r="D166" s="1" t="s">
+        <v>839</v>
+      </c>
+      <c r="E166" s="1" t="s">
+        <v>840</v>
+      </c>
+      <c r="F166" s="1" t="s">
+        <v>841</v>
+      </c>
+      <c r="G166" s="1" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="168" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A168" s="1" t="s">
-        <v>797</v>
+        <v>795</v>
       </c>
       <c r="B168" s="1" t="s">
-        <v>798</v>
+        <v>796</v>
       </c>
       <c r="C168" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="D168" s="24" t="s">
+      <c r="D168" s="25" t="s">
+        <v>805</v>
+      </c>
+      <c r="E168" s="25"/>
+      <c r="F168" s="25"/>
+      <c r="G168" s="25"/>
+    </row>
+    <row r="169" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A169" s="1" t="s">
+        <v>793</v>
+      </c>
+      <c r="B169" s="1" t="s">
+        <v>794</v>
+      </c>
+      <c r="C169" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D169" s="25" t="s">
         <v>806</v>
       </c>
-      <c r="E168" s="24"/>
-      <c r="F168" s="24"/>
-      <c r="G168" s="24"/>
+      <c r="E169" s="25"/>
+      <c r="F169" s="25"/>
+      <c r="G169" s="25"/>
     </row>
     <row r="170" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A170" s="1" t="s">
-        <v>328</v>
+        <v>797</v>
       </c>
       <c r="B170" s="1" t="s">
-        <v>329</v>
+        <v>798</v>
       </c>
       <c r="C170" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="D170" s="30" t="s">
-        <v>343</v>
-      </c>
-      <c r="E170" s="30"/>
-      <c r="F170" s="30"/>
-      <c r="G170" s="30"/>
-    </row>
-    <row r="171" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A171" s="1" t="s">
-        <v>330</v>
-      </c>
-      <c r="B171" s="1" t="s">
-        <v>331</v>
-      </c>
-      <c r="C171" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="D171" s="6" t="s">
-        <v>348</v>
-      </c>
-      <c r="E171" s="7" t="s">
-        <v>349</v>
-      </c>
-      <c r="F171" s="1" t="s">
-        <v>347</v>
-      </c>
-      <c r="G171" s="1" t="s">
-        <v>14</v>
-      </c>
+      <c r="D170" s="25" t="s">
+        <v>806</v>
+      </c>
+      <c r="E170" s="25"/>
+      <c r="F170" s="25"/>
+      <c r="G170" s="25"/>
     </row>
     <row r="172" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A172" s="1" t="s">
-        <v>498</v>
+        <v>328</v>
       </c>
       <c r="B172" s="1" t="s">
-        <v>499</v>
+        <v>329</v>
       </c>
       <c r="C172" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="D172" s="7" t="s">
-        <v>503</v>
-      </c>
-      <c r="E172" s="1" t="s">
-        <v>502</v>
-      </c>
-      <c r="F172" s="1" t="s">
-        <v>501</v>
-      </c>
-      <c r="G172" s="1" t="s">
-        <v>500</v>
-      </c>
+      <c r="D172" s="26" t="s">
+        <v>343</v>
+      </c>
+      <c r="E172" s="26"/>
+      <c r="F172" s="26"/>
+      <c r="G172" s="26"/>
     </row>
     <row r="173" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A173" s="1" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="B173" s="1" t="s">
-        <v>367</v>
+        <v>331</v>
       </c>
       <c r="C173" s="1" t="s">
         <v>43</v>
       </c>
       <c r="D173" s="6" t="s">
-        <v>370</v>
+        <v>348</v>
       </c>
       <c r="E173" s="7" t="s">
-        <v>368</v>
-      </c>
-      <c r="F173" s="7" t="s">
-        <v>369</v>
+        <v>349</v>
+      </c>
+      <c r="F173" s="1" t="s">
+        <v>347</v>
       </c>
       <c r="G173" s="1" t="s">
         <v>14</v>
       </c>
     </row>
+    <row r="174" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A174" s="1" t="s">
+        <v>498</v>
+      </c>
+      <c r="B174" s="1" t="s">
+        <v>499</v>
+      </c>
+      <c r="C174" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D174" s="7" t="s">
+        <v>503</v>
+      </c>
+      <c r="E174" s="1" t="s">
+        <v>502</v>
+      </c>
+      <c r="F174" s="1" t="s">
+        <v>501</v>
+      </c>
+      <c r="G174" s="1" t="s">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="175" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A175" s="1" t="s">
+        <v>332</v>
+      </c>
+      <c r="B175" s="1" t="s">
+        <v>367</v>
+      </c>
+      <c r="C175" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D175" s="6" t="s">
+        <v>370</v>
+      </c>
+      <c r="E175" s="7" t="s">
+        <v>368</v>
+      </c>
+      <c r="F175" s="7" t="s">
+        <v>369</v>
+      </c>
+      <c r="G175" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="69">
+    <mergeCell ref="D168:G168"/>
+    <mergeCell ref="D169:G169"/>
+    <mergeCell ref="D170:G170"/>
+    <mergeCell ref="D87:G87"/>
+    <mergeCell ref="A7:C7"/>
+    <mergeCell ref="A8:C8"/>
+    <mergeCell ref="D12:G12"/>
+    <mergeCell ref="D7:E7"/>
+    <mergeCell ref="D8:E8"/>
+    <mergeCell ref="A9:C9"/>
+    <mergeCell ref="A10:C10"/>
+    <mergeCell ref="A12:B12"/>
+    <mergeCell ref="D52:G52"/>
+    <mergeCell ref="D27:G27"/>
+    <mergeCell ref="D28:G28"/>
+    <mergeCell ref="D29:G29"/>
+    <mergeCell ref="D15:G15"/>
+    <mergeCell ref="D17:G17"/>
+    <mergeCell ref="D46:G46"/>
+    <mergeCell ref="D83:G83"/>
+    <mergeCell ref="D85:G85"/>
+    <mergeCell ref="D82:G82"/>
+    <mergeCell ref="D35:G35"/>
+    <mergeCell ref="D67:G67"/>
+    <mergeCell ref="D26:G26"/>
+    <mergeCell ref="D32:G32"/>
+    <mergeCell ref="A4:C4"/>
+    <mergeCell ref="A6:C6"/>
+    <mergeCell ref="A5:C5"/>
+    <mergeCell ref="D5:E5"/>
+    <mergeCell ref="D6:E6"/>
+    <mergeCell ref="D4:E4"/>
+    <mergeCell ref="D14:G14"/>
+    <mergeCell ref="D25:G25"/>
+    <mergeCell ref="D172:G172"/>
+    <mergeCell ref="D154:G154"/>
+    <mergeCell ref="D142:G142"/>
+    <mergeCell ref="D71:G71"/>
+    <mergeCell ref="D132:G132"/>
+    <mergeCell ref="D131:G131"/>
     <mergeCell ref="D150:G150"/>
-    <mergeCell ref="D151:G151"/>
-    <mergeCell ref="D147:G147"/>
-    <mergeCell ref="D98:G98"/>
-    <mergeCell ref="D99:G99"/>
-    <mergeCell ref="D86:G86"/>
+    <mergeCell ref="D140:G140"/>
+    <mergeCell ref="D141:G141"/>
+    <mergeCell ref="D76:G76"/>
+    <mergeCell ref="D136:G136"/>
+    <mergeCell ref="D137:G137"/>
+    <mergeCell ref="D138:G138"/>
+    <mergeCell ref="D135:G135"/>
     <mergeCell ref="D88:G88"/>
+    <mergeCell ref="D90:G90"/>
     <mergeCell ref="D16:G16"/>
-    <mergeCell ref="D68:G68"/>
+    <mergeCell ref="D70:G70"/>
     <mergeCell ref="D18:G18"/>
     <mergeCell ref="D22:G22"/>
     <mergeCell ref="D23:G23"/>
@@ -7057,54 +7185,11 @@
     <mergeCell ref="D31:G31"/>
     <mergeCell ref="D33:G33"/>
     <mergeCell ref="D34:G34"/>
-    <mergeCell ref="D14:G14"/>
-    <mergeCell ref="D25:G25"/>
-    <mergeCell ref="D170:G170"/>
     <mergeCell ref="D152:G152"/>
-    <mergeCell ref="D140:G140"/>
-    <mergeCell ref="D69:G69"/>
-    <mergeCell ref="D130:G130"/>
-    <mergeCell ref="D129:G129"/>
-    <mergeCell ref="D148:G148"/>
-    <mergeCell ref="D138:G138"/>
-    <mergeCell ref="D139:G139"/>
-    <mergeCell ref="D74:G74"/>
-    <mergeCell ref="D134:G134"/>
-    <mergeCell ref="D135:G135"/>
-    <mergeCell ref="D136:G136"/>
-    <mergeCell ref="D133:G133"/>
-    <mergeCell ref="A4:C4"/>
-    <mergeCell ref="A6:C6"/>
-    <mergeCell ref="A5:C5"/>
-    <mergeCell ref="D5:E5"/>
-    <mergeCell ref="D6:E6"/>
-    <mergeCell ref="D4:E4"/>
-    <mergeCell ref="D15:G15"/>
-    <mergeCell ref="D17:G17"/>
-    <mergeCell ref="D46:G46"/>
-    <mergeCell ref="D81:G81"/>
-    <mergeCell ref="D83:G83"/>
-    <mergeCell ref="D80:G80"/>
-    <mergeCell ref="D35:G35"/>
-    <mergeCell ref="D65:G65"/>
-    <mergeCell ref="D26:G26"/>
-    <mergeCell ref="D32:G32"/>
-    <mergeCell ref="D166:G166"/>
-    <mergeCell ref="D167:G167"/>
-    <mergeCell ref="D168:G168"/>
-    <mergeCell ref="D85:G85"/>
-    <mergeCell ref="A7:C7"/>
-    <mergeCell ref="A8:C8"/>
-    <mergeCell ref="D12:G12"/>
-    <mergeCell ref="D7:E7"/>
-    <mergeCell ref="D8:E8"/>
-    <mergeCell ref="A9:C9"/>
-    <mergeCell ref="A10:C10"/>
-    <mergeCell ref="A12:B12"/>
-    <mergeCell ref="D52:G52"/>
-    <mergeCell ref="D27:G27"/>
-    <mergeCell ref="D28:G28"/>
-    <mergeCell ref="D29:G29"/>
+    <mergeCell ref="D153:G153"/>
+    <mergeCell ref="D149:G149"/>
+    <mergeCell ref="D100:G100"/>
+    <mergeCell ref="D101:G101"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -7138,86 +7223,86 @@
       <c r="H2" s="5"/>
     </row>
     <row r="4" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="24" t="s">
+      <c r="A4" s="25" t="s">
         <v>202</v>
       </c>
-      <c r="B4" s="24"/>
-      <c r="C4" s="24"/>
-      <c r="D4" s="33" t="s">
+      <c r="B4" s="25"/>
+      <c r="C4" s="25"/>
+      <c r="D4" s="30" t="s">
         <v>55</v>
       </c>
-      <c r="E4" s="33"/>
+      <c r="E4" s="30"/>
       <c r="F4" s="17" t="s">
         <v>56</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="24" t="s">
+      <c r="A5" s="25" t="s">
         <v>419</v>
       </c>
-      <c r="B5" s="24"/>
-      <c r="C5" s="24"/>
-      <c r="D5" s="31" t="s">
+      <c r="B5" s="25"/>
+      <c r="C5" s="25"/>
+      <c r="D5" s="28" t="s">
         <v>47</v>
       </c>
-      <c r="E5" s="31"/>
+      <c r="E5" s="28"/>
       <c r="F5" s="10" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="24"/>
-      <c r="B6" s="24"/>
-      <c r="C6" s="24"/>
-      <c r="D6" s="32" t="s">
+      <c r="A6" s="25"/>
+      <c r="B6" s="25"/>
+      <c r="C6" s="25"/>
+      <c r="D6" s="29" t="s">
         <v>350</v>
       </c>
-      <c r="E6" s="32"/>
+      <c r="E6" s="29"/>
       <c r="F6" s="13" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="25"/>
-      <c r="B7" s="25"/>
-      <c r="C7" s="37"/>
-      <c r="D7" s="27" t="s">
+      <c r="A7" s="31"/>
+      <c r="B7" s="31"/>
+      <c r="C7" s="36"/>
+      <c r="D7" s="33" t="s">
         <v>51</v>
       </c>
-      <c r="E7" s="27"/>
+      <c r="E7" s="33"/>
       <c r="F7" s="12" t="s">
         <v>52</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="25"/>
-      <c r="B8" s="25"/>
-      <c r="C8" s="25"/>
-      <c r="D8" s="28" t="s">
+      <c r="A8" s="31"/>
+      <c r="B8" s="31"/>
+      <c r="C8" s="31"/>
+      <c r="D8" s="34" t="s">
         <v>53</v>
       </c>
-      <c r="E8" s="28"/>
+      <c r="E8" s="34"/>
       <c r="F8" s="14" t="s">
         <v>54</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="24"/>
-      <c r="B9" s="24"/>
-      <c r="C9" s="24"/>
+      <c r="A9" s="25"/>
+      <c r="B9" s="25"/>
+      <c r="C9" s="25"/>
     </row>
     <row r="11" spans="1:8" ht="16.2" x14ac:dyDescent="0.4">
-      <c r="A11" s="29" t="s">
+      <c r="A11" s="35" t="s">
         <v>342</v>
       </c>
-      <c r="B11" s="29"/>
+      <c r="B11" s="35"/>
       <c r="C11" s="18"/>
-      <c r="D11" s="26" t="s">
+      <c r="D11" s="32" t="s">
         <v>577</v>
       </c>
-      <c r="E11" s="26"/>
-      <c r="F11" s="26"/>
-      <c r="G11" s="26"/>
+      <c r="E11" s="32"/>
+      <c r="F11" s="32"/>
+      <c r="G11" s="32"/>
       <c r="H11" s="5"/>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.35">
@@ -7236,10 +7321,10 @@
       <c r="E12" s="3" t="s">
         <v>352</v>
       </c>
-      <c r="F12" s="36" t="s">
+      <c r="F12" s="37" t="s">
         <v>353</v>
       </c>
-      <c r="G12" s="36"/>
+      <c r="G12" s="37"/>
       <c r="H12" s="2"/>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.35">
@@ -7252,12 +7337,12 @@
       <c r="C13" s="1" t="s">
         <v>180</v>
       </c>
-      <c r="D13" s="30" t="s">
+      <c r="D13" s="26" t="s">
         <v>178</v>
       </c>
-      <c r="E13" s="30"/>
-      <c r="F13" s="30"/>
-      <c r="G13" s="30"/>
+      <c r="E13" s="26"/>
+      <c r="F13" s="26"/>
+      <c r="G13" s="26"/>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A14" s="1" t="s">
@@ -7269,12 +7354,12 @@
       <c r="C14" s="1" t="s">
         <v>180</v>
       </c>
-      <c r="D14" s="30" t="s">
+      <c r="D14" s="26" t="s">
         <v>178</v>
       </c>
-      <c r="E14" s="30"/>
-      <c r="F14" s="30"/>
-      <c r="G14" s="30"/>
+      <c r="E14" s="26"/>
+      <c r="F14" s="26"/>
+      <c r="G14" s="26"/>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A15" s="1" t="s">
@@ -7286,12 +7371,12 @@
       <c r="C15" s="1" t="s">
         <v>401</v>
       </c>
-      <c r="D15" s="24" t="s">
+      <c r="D15" s="25" t="s">
         <v>406</v>
       </c>
-      <c r="E15" s="24"/>
-      <c r="F15" s="24"/>
-      <c r="G15" s="24"/>
+      <c r="E15" s="25"/>
+      <c r="F15" s="25"/>
+      <c r="G15" s="25"/>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A16" s="1" t="s">
@@ -7303,12 +7388,12 @@
       <c r="C16" s="1" t="s">
         <v>180</v>
       </c>
-      <c r="D16" s="34" t="s">
+      <c r="D16" s="27" t="s">
         <v>418</v>
       </c>
-      <c r="E16" s="34"/>
-      <c r="F16" s="34"/>
-      <c r="G16" s="34"/>
+      <c r="E16" s="27"/>
+      <c r="F16" s="27"/>
+      <c r="G16" s="27"/>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A17" s="1" t="s">
@@ -7320,12 +7405,12 @@
       <c r="C17" s="1" t="s">
         <v>143</v>
       </c>
-      <c r="D17" s="24" t="s">
+      <c r="D17" s="25" t="s">
         <v>589</v>
       </c>
-      <c r="E17" s="24"/>
-      <c r="F17" s="24"/>
-      <c r="G17" s="24"/>
+      <c r="E17" s="25"/>
+      <c r="F17" s="25"/>
+      <c r="G17" s="25"/>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A18" s="1" t="s">
@@ -7337,12 +7422,12 @@
       <c r="C18" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="D18" s="24" t="s">
+      <c r="D18" s="25" t="s">
         <v>581</v>
       </c>
-      <c r="E18" s="24"/>
-      <c r="F18" s="24"/>
-      <c r="G18" s="24"/>
+      <c r="E18" s="25"/>
+      <c r="F18" s="25"/>
+      <c r="G18" s="25"/>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A19" s="1" t="s">
@@ -7354,12 +7439,12 @@
       <c r="C19" s="1" t="s">
         <v>143</v>
       </c>
-      <c r="D19" s="24" t="s">
+      <c r="D19" s="25" t="s">
         <v>404</v>
       </c>
-      <c r="E19" s="24"/>
-      <c r="F19" s="24"/>
-      <c r="G19" s="24"/>
+      <c r="E19" s="25"/>
+      <c r="F19" s="25"/>
+      <c r="G19" s="25"/>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A20" s="1" t="s">
@@ -7371,12 +7456,12 @@
       <c r="C20" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="D20" s="30" t="s">
+      <c r="D20" s="26" t="s">
         <v>178</v>
       </c>
-      <c r="E20" s="30"/>
-      <c r="F20" s="30"/>
-      <c r="G20" s="30"/>
+      <c r="E20" s="26"/>
+      <c r="F20" s="26"/>
+      <c r="G20" s="26"/>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A21" s="1" t="s">
@@ -7388,12 +7473,12 @@
       <c r="C21" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="D21" s="34" t="s">
+      <c r="D21" s="27" t="s">
         <v>721</v>
       </c>
-      <c r="E21" s="34"/>
-      <c r="F21" s="34"/>
-      <c r="G21" s="34"/>
+      <c r="E21" s="27"/>
+      <c r="F21" s="27"/>
+      <c r="G21" s="27"/>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A22" s="1" t="s">
@@ -7405,12 +7490,12 @@
       <c r="C22" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="D22" s="24" t="s">
+      <c r="D22" s="25" t="s">
         <v>720</v>
       </c>
-      <c r="E22" s="24"/>
-      <c r="F22" s="24"/>
-      <c r="G22" s="24"/>
+      <c r="E22" s="25"/>
+      <c r="F22" s="25"/>
+      <c r="G22" s="25"/>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A23" s="1" t="s">
@@ -7422,12 +7507,12 @@
       <c r="C23" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="D23" s="24" t="s">
+      <c r="D23" s="25" t="s">
         <v>722</v>
       </c>
-      <c r="E23" s="24"/>
-      <c r="F23" s="24"/>
-      <c r="G23" s="24"/>
+      <c r="E23" s="25"/>
+      <c r="F23" s="25"/>
+      <c r="G23" s="25"/>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A24" s="1" t="s">
@@ -7439,12 +7524,12 @@
       <c r="C24" s="1" t="s">
         <v>143</v>
       </c>
-      <c r="D24" s="24" t="s">
+      <c r="D24" s="25" t="s">
         <v>404</v>
       </c>
-      <c r="E24" s="24"/>
-      <c r="F24" s="24"/>
-      <c r="G24" s="24"/>
+      <c r="E24" s="25"/>
+      <c r="F24" s="25"/>
+      <c r="G24" s="25"/>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A25" s="1" t="s">
@@ -7456,12 +7541,12 @@
       <c r="C25" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="D25" s="24" t="s">
+      <c r="D25" s="25" t="s">
         <v>823</v>
       </c>
-      <c r="E25" s="24"/>
-      <c r="F25" s="24"/>
-      <c r="G25" s="24"/>
+      <c r="E25" s="25"/>
+      <c r="F25" s="25"/>
+      <c r="G25" s="25"/>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A26" s="1" t="s">
@@ -7473,12 +7558,12 @@
       <c r="C26" s="1" t="s">
         <v>179</v>
       </c>
-      <c r="D26" s="30" t="s">
+      <c r="D26" s="26" t="s">
         <v>178</v>
       </c>
-      <c r="E26" s="30"/>
-      <c r="F26" s="30"/>
-      <c r="G26" s="30"/>
+      <c r="E26" s="26"/>
+      <c r="F26" s="26"/>
+      <c r="G26" s="26"/>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A27" s="1" t="s">
@@ -7490,12 +7575,12 @@
       <c r="C27" s="1" t="s">
         <v>179</v>
       </c>
-      <c r="D27" s="30" t="s">
+      <c r="D27" s="26" t="s">
         <v>182</v>
       </c>
-      <c r="E27" s="30"/>
-      <c r="F27" s="30"/>
-      <c r="G27" s="30"/>
+      <c r="E27" s="26"/>
+      <c r="F27" s="26"/>
+      <c r="G27" s="26"/>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A28" s="1" t="s">
@@ -7507,12 +7592,12 @@
       <c r="C28" s="1" t="s">
         <v>179</v>
       </c>
-      <c r="D28" s="24" t="s">
+      <c r="D28" s="25" t="s">
         <v>406</v>
       </c>
-      <c r="E28" s="24"/>
-      <c r="F28" s="24"/>
-      <c r="G28" s="24"/>
+      <c r="E28" s="25"/>
+      <c r="F28" s="25"/>
+      <c r="G28" s="25"/>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A29" s="1" t="s">
@@ -7524,12 +7609,12 @@
       <c r="C29" s="1" t="s">
         <v>179</v>
       </c>
-      <c r="D29" s="30" t="s">
+      <c r="D29" s="26" t="s">
         <v>178</v>
       </c>
-      <c r="E29" s="30"/>
-      <c r="F29" s="30"/>
-      <c r="G29" s="30"/>
+      <c r="E29" s="26"/>
+      <c r="F29" s="26"/>
+      <c r="G29" s="26"/>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A30" s="1" t="s">
@@ -7541,12 +7626,12 @@
       <c r="C30" s="1" t="s">
         <v>180</v>
       </c>
-      <c r="D30" s="24" t="s">
+      <c r="D30" s="25" t="s">
         <v>417</v>
       </c>
-      <c r="E30" s="24"/>
-      <c r="F30" s="24"/>
-      <c r="G30" s="24"/>
+      <c r="E30" s="25"/>
+      <c r="F30" s="25"/>
+      <c r="G30" s="25"/>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A31" s="1" t="s">
@@ -7558,12 +7643,12 @@
       <c r="C31" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="D31" s="24" t="s">
+      <c r="D31" s="25" t="s">
         <v>828</v>
       </c>
-      <c r="E31" s="24"/>
-      <c r="F31" s="24"/>
-      <c r="G31" s="24"/>
+      <c r="E31" s="25"/>
+      <c r="F31" s="25"/>
+      <c r="G31" s="25"/>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A32" s="1" t="s">
@@ -7575,12 +7660,12 @@
       <c r="C32" s="1" t="s">
         <v>181</v>
       </c>
-      <c r="D32" s="30" t="s">
+      <c r="D32" s="26" t="s">
         <v>182</v>
       </c>
-      <c r="E32" s="30"/>
-      <c r="F32" s="30"/>
-      <c r="G32" s="30"/>
+      <c r="E32" s="26"/>
+      <c r="F32" s="26"/>
+      <c r="G32" s="26"/>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A33" s="1" t="s">
@@ -7592,12 +7677,12 @@
       <c r="C33" s="1" t="s">
         <v>180</v>
       </c>
-      <c r="D33" s="24" t="s">
+      <c r="D33" s="25" t="s">
         <v>416</v>
       </c>
-      <c r="E33" s="24"/>
-      <c r="F33" s="24"/>
-      <c r="G33" s="24"/>
+      <c r="E33" s="25"/>
+      <c r="F33" s="25"/>
+      <c r="G33" s="25"/>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A34" s="1" t="s">
@@ -7609,12 +7694,12 @@
       <c r="C34" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="D34" s="30" t="s">
+      <c r="D34" s="26" t="s">
         <v>182</v>
       </c>
-      <c r="E34" s="30"/>
-      <c r="F34" s="30"/>
-      <c r="G34" s="30"/>
+      <c r="E34" s="26"/>
+      <c r="F34" s="26"/>
+      <c r="G34" s="26"/>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A36" s="1" t="s">
@@ -7692,12 +7777,12 @@
       <c r="C42" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="D42" s="35" t="s">
+      <c r="D42" s="38" t="s">
         <v>415</v>
       </c>
-      <c r="E42" s="35"/>
-      <c r="F42" s="35"/>
-      <c r="G42" s="35"/>
+      <c r="E42" s="38"/>
+      <c r="F42" s="38"/>
+      <c r="G42" s="38"/>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A43" s="16" t="s">
@@ -7742,12 +7827,12 @@
       <c r="C46" s="1" t="s">
         <v>143</v>
       </c>
-      <c r="D46" s="24" t="s">
+      <c r="D46" s="25" t="s">
         <v>404</v>
       </c>
-      <c r="E46" s="24"/>
-      <c r="F46" s="24"/>
-      <c r="G46" s="24"/>
+      <c r="E46" s="25"/>
+      <c r="F46" s="25"/>
+      <c r="G46" s="25"/>
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A47" s="16" t="s">
@@ -7971,12 +8056,12 @@
       <c r="C65" s="1" t="s">
         <v>398</v>
       </c>
-      <c r="D65" s="24" t="s">
+      <c r="D65" s="25" t="s">
         <v>406</v>
       </c>
-      <c r="E65" s="24"/>
-      <c r="F65" s="24"/>
-      <c r="G65" s="24"/>
+      <c r="E65" s="25"/>
+      <c r="F65" s="25"/>
+      <c r="G65" s="25"/>
     </row>
     <row r="67" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A67" s="1" t="s">
@@ -8243,12 +8328,12 @@
       <c r="C90" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="D90" s="24" t="s">
+      <c r="D90" s="25" t="s">
         <v>712</v>
       </c>
-      <c r="E90" s="24"/>
-      <c r="F90" s="24"/>
-      <c r="G90" s="24"/>
+      <c r="E90" s="25"/>
+      <c r="F90" s="25"/>
+      <c r="G90" s="25"/>
     </row>
     <row r="91" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A91" s="16" t="s">
@@ -8260,12 +8345,12 @@
       <c r="C91" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="D91" s="24" t="s">
+      <c r="D91" s="25" t="s">
         <v>711</v>
       </c>
-      <c r="E91" s="24"/>
-      <c r="F91" s="24"/>
-      <c r="G91" s="24"/>
+      <c r="E91" s="25"/>
+      <c r="F91" s="25"/>
+      <c r="G91" s="25"/>
     </row>
     <row r="92" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A92" s="16" t="s">
@@ -8277,12 +8362,12 @@
       <c r="C92" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="D92" s="30" t="s">
+      <c r="D92" s="26" t="s">
         <v>305</v>
       </c>
-      <c r="E92" s="30"/>
-      <c r="F92" s="30"/>
-      <c r="G92" s="30"/>
+      <c r="E92" s="26"/>
+      <c r="F92" s="26"/>
+      <c r="G92" s="26"/>
     </row>
     <row r="93" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A93" s="16" t="s">
@@ -8294,12 +8379,12 @@
       <c r="C93" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="D93" s="30" t="s">
+      <c r="D93" s="26" t="s">
         <v>305</v>
       </c>
-      <c r="E93" s="30"/>
-      <c r="F93" s="30"/>
-      <c r="G93" s="30"/>
+      <c r="E93" s="26"/>
+      <c r="F93" s="26"/>
+      <c r="G93" s="26"/>
     </row>
     <row r="94" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A94" s="16" t="s">
@@ -8311,12 +8396,12 @@
       <c r="C94" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="D94" s="24" t="s">
+      <c r="D94" s="25" t="s">
         <v>413</v>
       </c>
-      <c r="E94" s="24"/>
-      <c r="F94" s="24"/>
-      <c r="G94" s="24"/>
+      <c r="E94" s="25"/>
+      <c r="F94" s="25"/>
+      <c r="G94" s="25"/>
     </row>
     <row r="95" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A95" s="1" t="s">
@@ -8328,12 +8413,12 @@
       <c r="C95" s="1" t="s">
         <v>143</v>
       </c>
-      <c r="D95" s="24" t="s">
+      <c r="D95" s="25" t="s">
         <v>406</v>
       </c>
-      <c r="E95" s="24"/>
-      <c r="F95" s="24"/>
-      <c r="G95" s="24"/>
+      <c r="E95" s="25"/>
+      <c r="F95" s="25"/>
+      <c r="G95" s="25"/>
     </row>
     <row r="96" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A96" s="1" t="s">
@@ -8345,12 +8430,12 @@
       <c r="C96" s="1" t="s">
         <v>143</v>
       </c>
-      <c r="D96" s="24" t="s">
+      <c r="D96" s="25" t="s">
         <v>406</v>
       </c>
-      <c r="E96" s="24"/>
-      <c r="F96" s="24"/>
-      <c r="G96" s="24"/>
+      <c r="E96" s="25"/>
+      <c r="F96" s="25"/>
+      <c r="G96" s="25"/>
     </row>
     <row r="97" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A97" s="1" t="s">
@@ -8362,12 +8447,12 @@
       <c r="C97" s="1" t="s">
         <v>143</v>
       </c>
-      <c r="D97" s="24" t="s">
+      <c r="D97" s="25" t="s">
         <v>406</v>
       </c>
-      <c r="E97" s="24"/>
-      <c r="F97" s="24"/>
-      <c r="G97" s="24"/>
+      <c r="E97" s="25"/>
+      <c r="F97" s="25"/>
+      <c r="G97" s="25"/>
     </row>
     <row r="99" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A99" s="1" t="s">
@@ -8379,12 +8464,12 @@
       <c r="C99" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="D99" s="30" t="s">
+      <c r="D99" s="26" t="s">
         <v>305</v>
       </c>
-      <c r="E99" s="30"/>
-      <c r="F99" s="30"/>
-      <c r="G99" s="30"/>
+      <c r="E99" s="26"/>
+      <c r="F99" s="26"/>
+      <c r="G99" s="26"/>
     </row>
     <row r="100" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A100" s="1" t="s">
@@ -8396,12 +8481,12 @@
       <c r="C100" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="D100" s="30" t="s">
+      <c r="D100" s="26" t="s">
         <v>305</v>
       </c>
-      <c r="E100" s="30"/>
-      <c r="F100" s="30"/>
-      <c r="G100" s="30"/>
+      <c r="E100" s="26"/>
+      <c r="F100" s="26"/>
+      <c r="G100" s="26"/>
     </row>
     <row r="101" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A101" s="1" t="s">
@@ -8413,12 +8498,12 @@
       <c r="C101" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="D101" s="34" t="s">
+      <c r="D101" s="27" t="s">
         <v>414</v>
       </c>
-      <c r="E101" s="34"/>
-      <c r="F101" s="34"/>
-      <c r="G101" s="34"/>
+      <c r="E101" s="27"/>
+      <c r="F101" s="27"/>
+      <c r="G101" s="27"/>
     </row>
     <row r="102" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A102" s="1" t="s">
@@ -8430,12 +8515,12 @@
       <c r="C102" s="1" t="s">
         <v>304</v>
       </c>
-      <c r="D102" s="30" t="s">
+      <c r="D102" s="26" t="s">
         <v>305</v>
       </c>
-      <c r="E102" s="30"/>
-      <c r="F102" s="30"/>
-      <c r="G102" s="30"/>
+      <c r="E102" s="26"/>
+      <c r="F102" s="26"/>
+      <c r="G102" s="26"/>
     </row>
     <row r="103" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A103" s="1" t="s">
@@ -8447,12 +8532,12 @@
       <c r="C103" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="D103" s="30" t="s">
+      <c r="D103" s="26" t="s">
         <v>306</v>
       </c>
-      <c r="E103" s="30"/>
-      <c r="F103" s="30"/>
-      <c r="G103" s="30"/>
+      <c r="E103" s="26"/>
+      <c r="F103" s="26"/>
+      <c r="G103" s="26"/>
     </row>
     <row r="104" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A104" s="1" t="s">
@@ -8464,12 +8549,12 @@
       <c r="C104" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="D104" s="24" t="s">
+      <c r="D104" s="25" t="s">
         <v>766</v>
       </c>
-      <c r="E104" s="24"/>
-      <c r="F104" s="24"/>
-      <c r="G104" s="24"/>
+      <c r="E104" s="25"/>
+      <c r="F104" s="25"/>
+      <c r="G104" s="25"/>
     </row>
     <row r="105" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A105" s="1" t="s">
@@ -8481,12 +8566,12 @@
       <c r="C105" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="D105" s="24" t="s">
+      <c r="D105" s="25" t="s">
         <v>767</v>
       </c>
-      <c r="E105" s="24"/>
-      <c r="F105" s="24"/>
-      <c r="G105" s="24"/>
+      <c r="E105" s="25"/>
+      <c r="F105" s="25"/>
+      <c r="G105" s="25"/>
     </row>
     <row r="106" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A106" s="1" t="s">
@@ -8498,12 +8583,12 @@
       <c r="C106" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="D106" s="30" t="s">
+      <c r="D106" s="26" t="s">
         <v>305</v>
       </c>
-      <c r="E106" s="30"/>
-      <c r="F106" s="30"/>
-      <c r="G106" s="30"/>
+      <c r="E106" s="26"/>
+      <c r="F106" s="26"/>
+      <c r="G106" s="26"/>
     </row>
     <row r="108" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A108" s="1" t="s">
@@ -8515,12 +8600,12 @@
       <c r="C108" s="1" t="s">
         <v>143</v>
       </c>
-      <c r="D108" s="24" t="s">
+      <c r="D108" s="25" t="s">
         <v>786</v>
       </c>
-      <c r="E108" s="24"/>
-      <c r="F108" s="24"/>
-      <c r="G108" s="24"/>
+      <c r="E108" s="25"/>
+      <c r="F108" s="25"/>
+      <c r="G108" s="25"/>
     </row>
     <row r="109" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A109" s="1" t="s">
@@ -8532,12 +8617,12 @@
       <c r="C109" s="1" t="s">
         <v>669</v>
       </c>
-      <c r="D109" s="24" t="s">
+      <c r="D109" s="25" t="s">
         <v>404</v>
       </c>
-      <c r="E109" s="24"/>
-      <c r="F109" s="24"/>
-      <c r="G109" s="24"/>
+      <c r="E109" s="25"/>
+      <c r="F109" s="25"/>
+      <c r="G109" s="25"/>
     </row>
     <row r="110" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A110" s="1" t="s">
@@ -8549,12 +8634,12 @@
       <c r="C110" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="D110" s="24" t="s">
+      <c r="D110" s="25" t="s">
         <v>675</v>
       </c>
-      <c r="E110" s="24"/>
-      <c r="F110" s="24"/>
-      <c r="G110" s="24"/>
+      <c r="E110" s="25"/>
+      <c r="F110" s="25"/>
+      <c r="G110" s="25"/>
     </row>
     <row r="111" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A111" s="1" t="s">
@@ -8566,12 +8651,12 @@
       <c r="C111" s="1" t="s">
         <v>143</v>
       </c>
-      <c r="D111" s="24" t="s">
+      <c r="D111" s="25" t="s">
         <v>404</v>
       </c>
-      <c r="E111" s="24"/>
-      <c r="F111" s="24"/>
-      <c r="G111" s="24"/>
+      <c r="E111" s="25"/>
+      <c r="F111" s="25"/>
+      <c r="G111" s="25"/>
     </row>
     <row r="112" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A112" s="1" t="s">
@@ -8583,12 +8668,12 @@
       <c r="C112" s="1" t="s">
         <v>143</v>
       </c>
-      <c r="D112" s="24" t="s">
+      <c r="D112" s="25" t="s">
         <v>404</v>
       </c>
-      <c r="E112" s="24"/>
-      <c r="F112" s="24"/>
-      <c r="G112" s="24"/>
+      <c r="E112" s="25"/>
+      <c r="F112" s="25"/>
+      <c r="G112" s="25"/>
     </row>
     <row r="113" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A113" s="1" t="s">
@@ -8600,12 +8685,12 @@
       <c r="C113" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="D113" s="24" t="s">
+      <c r="D113" s="25" t="s">
         <v>412</v>
       </c>
-      <c r="E113" s="24"/>
-      <c r="F113" s="24"/>
-      <c r="G113" s="24"/>
+      <c r="E113" s="25"/>
+      <c r="F113" s="25"/>
+      <c r="G113" s="25"/>
     </row>
     <row r="114" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A114" s="1" t="s">
@@ -8617,12 +8702,12 @@
       <c r="C114" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="D114" s="24" t="s">
+      <c r="D114" s="25" t="s">
         <v>679</v>
       </c>
-      <c r="E114" s="24"/>
-      <c r="F114" s="24"/>
-      <c r="G114" s="24"/>
+      <c r="E114" s="25"/>
+      <c r="F114" s="25"/>
+      <c r="G114" s="25"/>
     </row>
     <row r="116" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A116" s="1" t="s">
@@ -8634,12 +8719,12 @@
       <c r="C116" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="D116" s="24" t="s">
+      <c r="D116" s="25" t="s">
         <v>683</v>
       </c>
-      <c r="E116" s="24"/>
-      <c r="F116" s="24"/>
-      <c r="G116" s="24"/>
+      <c r="E116" s="25"/>
+      <c r="F116" s="25"/>
+      <c r="G116" s="25"/>
     </row>
     <row r="117" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A117" s="1" t="s">
@@ -8697,12 +8782,12 @@
       <c r="C119" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="D119" s="24" t="s">
+      <c r="D119" s="25" t="s">
         <v>685</v>
       </c>
-      <c r="E119" s="24"/>
-      <c r="F119" s="24"/>
-      <c r="G119" s="24"/>
+      <c r="E119" s="25"/>
+      <c r="F119" s="25"/>
+      <c r="G119" s="25"/>
     </row>
     <row r="120" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A120" s="1" t="s">
@@ -8714,12 +8799,12 @@
       <c r="C120" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="D120" s="24" t="s">
+      <c r="D120" s="25" t="s">
         <v>684</v>
       </c>
-      <c r="E120" s="24"/>
-      <c r="F120" s="24"/>
-      <c r="G120" s="24"/>
+      <c r="E120" s="25"/>
+      <c r="F120" s="25"/>
+      <c r="G120" s="25"/>
     </row>
     <row r="121" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A121" s="1" t="s">
@@ -8731,12 +8816,12 @@
       <c r="C121" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="D121" s="24" t="s">
+      <c r="D121" s="25" t="s">
         <v>686</v>
       </c>
-      <c r="E121" s="24"/>
-      <c r="F121" s="24"/>
-      <c r="G121" s="24"/>
+      <c r="E121" s="25"/>
+      <c r="F121" s="25"/>
+      <c r="G121" s="25"/>
     </row>
     <row r="122" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A122" s="1" t="s">
@@ -8748,12 +8833,12 @@
       <c r="C122" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="D122" s="24" t="s">
+      <c r="D122" s="25" t="s">
         <v>755</v>
       </c>
-      <c r="E122" s="24"/>
-      <c r="F122" s="24"/>
-      <c r="G122" s="24"/>
+      <c r="E122" s="25"/>
+      <c r="F122" s="25"/>
+      <c r="G122" s="25"/>
     </row>
     <row r="123" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A123" s="1" t="s">
@@ -8765,12 +8850,12 @@
       <c r="C123" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="D123" s="24" t="s">
+      <c r="D123" s="25" t="s">
         <v>835</v>
       </c>
-      <c r="E123" s="24"/>
-      <c r="F123" s="24"/>
-      <c r="G123" s="24"/>
+      <c r="E123" s="25"/>
+      <c r="F123" s="25"/>
+      <c r="G123" s="25"/>
     </row>
     <row r="124" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A124" s="1" t="s">
@@ -8799,12 +8884,12 @@
       <c r="C125" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="D125" s="24" t="s">
+      <c r="D125" s="25" t="s">
         <v>842</v>
       </c>
-      <c r="E125" s="24"/>
-      <c r="F125" s="24"/>
-      <c r="G125" s="24"/>
+      <c r="E125" s="25"/>
+      <c r="F125" s="25"/>
+      <c r="G125" s="25"/>
     </row>
     <row r="127" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A127" s="1" t="s">
@@ -8816,12 +8901,12 @@
       <c r="C127" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="D127" s="24" t="s">
+      <c r="D127" s="25" t="s">
         <v>804</v>
       </c>
-      <c r="E127" s="24"/>
-      <c r="F127" s="24"/>
-      <c r="G127" s="24"/>
+      <c r="E127" s="25"/>
+      <c r="F127" s="25"/>
+      <c r="G127" s="25"/>
     </row>
     <row r="128" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A128" s="1" t="s">
@@ -8833,12 +8918,12 @@
       <c r="C128" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="D128" s="34" t="s">
+      <c r="D128" s="27" t="s">
         <v>803</v>
       </c>
-      <c r="E128" s="34"/>
-      <c r="F128" s="34"/>
-      <c r="G128" s="34"/>
+      <c r="E128" s="27"/>
+      <c r="F128" s="27"/>
+      <c r="G128" s="27"/>
     </row>
     <row r="129" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A129" s="1" t="s">
@@ -8850,12 +8935,12 @@
       <c r="C129" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="D129" s="34" t="s">
+      <c r="D129" s="27" t="s">
         <v>802</v>
       </c>
-      <c r="E129" s="34"/>
-      <c r="F129" s="34"/>
-      <c r="G129" s="34"/>
+      <c r="E129" s="27"/>
+      <c r="F129" s="27"/>
+      <c r="G129" s="27"/>
     </row>
     <row r="131" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A131" s="1" t="s">
@@ -8927,32 +9012,36 @@
     </row>
   </sheetData>
   <mergeCells count="72">
-    <mergeCell ref="D103:G103"/>
-    <mergeCell ref="D23:G23"/>
-    <mergeCell ref="D21:G21"/>
-    <mergeCell ref="D22:G22"/>
-    <mergeCell ref="D119:G119"/>
-    <mergeCell ref="D32:G32"/>
-    <mergeCell ref="D95:G95"/>
-    <mergeCell ref="D96:G96"/>
-    <mergeCell ref="D33:G33"/>
-    <mergeCell ref="D101:G101"/>
-    <mergeCell ref="D25:G25"/>
-    <mergeCell ref="D31:G31"/>
-    <mergeCell ref="D100:G100"/>
-    <mergeCell ref="D24:G24"/>
-    <mergeCell ref="D111:G111"/>
-    <mergeCell ref="A4:C4"/>
-    <mergeCell ref="D4:E4"/>
-    <mergeCell ref="A5:C5"/>
-    <mergeCell ref="D5:E5"/>
-    <mergeCell ref="A6:C6"/>
-    <mergeCell ref="D6:E6"/>
-    <mergeCell ref="A7:C7"/>
-    <mergeCell ref="D7:E7"/>
-    <mergeCell ref="A8:C8"/>
-    <mergeCell ref="D8:E8"/>
-    <mergeCell ref="A9:C9"/>
+    <mergeCell ref="D127:G127"/>
+    <mergeCell ref="D128:G128"/>
+    <mergeCell ref="D129:G129"/>
+    <mergeCell ref="D122:G122"/>
+    <mergeCell ref="D104:G104"/>
+    <mergeCell ref="D105:G105"/>
+    <mergeCell ref="D106:G106"/>
+    <mergeCell ref="D112:G112"/>
+    <mergeCell ref="D108:G108"/>
+    <mergeCell ref="D121:G121"/>
+    <mergeCell ref="D109:G109"/>
+    <mergeCell ref="D110:G110"/>
+    <mergeCell ref="D114:G114"/>
+    <mergeCell ref="D120:G120"/>
+    <mergeCell ref="D123:G123"/>
+    <mergeCell ref="D125:G125"/>
+    <mergeCell ref="D17:G17"/>
+    <mergeCell ref="D18:G18"/>
+    <mergeCell ref="D65:G65"/>
+    <mergeCell ref="D97:G97"/>
+    <mergeCell ref="D94:G94"/>
+    <mergeCell ref="D28:G28"/>
+    <mergeCell ref="D29:G29"/>
+    <mergeCell ref="D42:G42"/>
+    <mergeCell ref="D34:G34"/>
+    <mergeCell ref="D46:G46"/>
+    <mergeCell ref="D26:G26"/>
+    <mergeCell ref="D27:G27"/>
+    <mergeCell ref="D19:G19"/>
+    <mergeCell ref="D20:G20"/>
     <mergeCell ref="A11:B11"/>
     <mergeCell ref="D99:G99"/>
     <mergeCell ref="D102:G102"/>
@@ -8969,36 +9058,32 @@
     <mergeCell ref="D93:G93"/>
     <mergeCell ref="D91:G91"/>
     <mergeCell ref="D90:G90"/>
-    <mergeCell ref="D17:G17"/>
-    <mergeCell ref="D18:G18"/>
-    <mergeCell ref="D65:G65"/>
-    <mergeCell ref="D97:G97"/>
-    <mergeCell ref="D94:G94"/>
-    <mergeCell ref="D28:G28"/>
-    <mergeCell ref="D29:G29"/>
-    <mergeCell ref="D42:G42"/>
-    <mergeCell ref="D34:G34"/>
-    <mergeCell ref="D46:G46"/>
-    <mergeCell ref="D26:G26"/>
-    <mergeCell ref="D27:G27"/>
-    <mergeCell ref="D19:G19"/>
-    <mergeCell ref="D20:G20"/>
-    <mergeCell ref="D127:G127"/>
-    <mergeCell ref="D128:G128"/>
-    <mergeCell ref="D129:G129"/>
-    <mergeCell ref="D122:G122"/>
-    <mergeCell ref="D104:G104"/>
-    <mergeCell ref="D105:G105"/>
-    <mergeCell ref="D106:G106"/>
-    <mergeCell ref="D112:G112"/>
-    <mergeCell ref="D108:G108"/>
-    <mergeCell ref="D121:G121"/>
-    <mergeCell ref="D109:G109"/>
-    <mergeCell ref="D110:G110"/>
-    <mergeCell ref="D114:G114"/>
-    <mergeCell ref="D120:G120"/>
-    <mergeCell ref="D123:G123"/>
-    <mergeCell ref="D125:G125"/>
+    <mergeCell ref="A7:C7"/>
+    <mergeCell ref="D7:E7"/>
+    <mergeCell ref="A8:C8"/>
+    <mergeCell ref="D8:E8"/>
+    <mergeCell ref="A9:C9"/>
+    <mergeCell ref="A4:C4"/>
+    <mergeCell ref="D4:E4"/>
+    <mergeCell ref="A5:C5"/>
+    <mergeCell ref="D5:E5"/>
+    <mergeCell ref="A6:C6"/>
+    <mergeCell ref="D6:E6"/>
+    <mergeCell ref="D103:G103"/>
+    <mergeCell ref="D23:G23"/>
+    <mergeCell ref="D21:G21"/>
+    <mergeCell ref="D22:G22"/>
+    <mergeCell ref="D119:G119"/>
+    <mergeCell ref="D32:G32"/>
+    <mergeCell ref="D95:G95"/>
+    <mergeCell ref="D96:G96"/>
+    <mergeCell ref="D33:G33"/>
+    <mergeCell ref="D101:G101"/>
+    <mergeCell ref="D25:G25"/>
+    <mergeCell ref="D31:G31"/>
+    <mergeCell ref="D100:G100"/>
+    <mergeCell ref="D24:G24"/>
+    <mergeCell ref="D111:G111"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -9032,86 +9117,86 @@
       <c r="H2" s="5"/>
     </row>
     <row r="4" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="24" t="s">
+      <c r="A4" s="25" t="s">
         <v>202</v>
       </c>
-      <c r="B4" s="24"/>
-      <c r="C4" s="24"/>
-      <c r="D4" s="33" t="s">
+      <c r="B4" s="25"/>
+      <c r="C4" s="25"/>
+      <c r="D4" s="30" t="s">
         <v>55</v>
       </c>
-      <c r="E4" s="33"/>
+      <c r="E4" s="30"/>
       <c r="F4" s="20" t="s">
         <v>56</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="24" t="s">
+      <c r="A5" s="25" t="s">
         <v>420</v>
       </c>
-      <c r="B5" s="24"/>
-      <c r="C5" s="24"/>
-      <c r="D5" s="31" t="s">
+      <c r="B5" s="25"/>
+      <c r="C5" s="25"/>
+      <c r="D5" s="28" t="s">
         <v>47</v>
       </c>
-      <c r="E5" s="31"/>
+      <c r="E5" s="28"/>
       <c r="F5" s="10" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="24"/>
-      <c r="B6" s="24"/>
-      <c r="C6" s="24"/>
-      <c r="D6" s="32" t="s">
+      <c r="A6" s="25"/>
+      <c r="B6" s="25"/>
+      <c r="C6" s="25"/>
+      <c r="D6" s="29" t="s">
         <v>350</v>
       </c>
-      <c r="E6" s="32"/>
+      <c r="E6" s="29"/>
       <c r="F6" s="13" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="25"/>
-      <c r="B7" s="25"/>
-      <c r="C7" s="37"/>
-      <c r="D7" s="27" t="s">
+      <c r="A7" s="31"/>
+      <c r="B7" s="31"/>
+      <c r="C7" s="36"/>
+      <c r="D7" s="33" t="s">
         <v>51</v>
       </c>
-      <c r="E7" s="27"/>
+      <c r="E7" s="33"/>
       <c r="F7" s="12" t="s">
         <v>52</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="25"/>
-      <c r="B8" s="25"/>
-      <c r="C8" s="25"/>
-      <c r="D8" s="28" t="s">
+      <c r="A8" s="31"/>
+      <c r="B8" s="31"/>
+      <c r="C8" s="31"/>
+      <c r="D8" s="34" t="s">
         <v>53</v>
       </c>
-      <c r="E8" s="28"/>
+      <c r="E8" s="34"/>
       <c r="F8" s="14" t="s">
         <v>54</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="24"/>
-      <c r="B9" s="24"/>
-      <c r="C9" s="24"/>
+      <c r="A9" s="25"/>
+      <c r="B9" s="25"/>
+      <c r="C9" s="25"/>
     </row>
     <row r="11" spans="1:8" ht="16.2" x14ac:dyDescent="0.4">
-      <c r="A11" s="29" t="s">
+      <c r="A11" s="35" t="s">
         <v>484</v>
       </c>
-      <c r="B11" s="29"/>
+      <c r="B11" s="35"/>
       <c r="C11" s="21"/>
-      <c r="D11" s="26" t="s">
+      <c r="D11" s="32" t="s">
         <v>578</v>
       </c>
-      <c r="E11" s="26"/>
-      <c r="F11" s="26"/>
-      <c r="G11" s="26"/>
+      <c r="E11" s="32"/>
+      <c r="F11" s="32"/>
+      <c r="G11" s="32"/>
       <c r="H11" s="5"/>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.35">
@@ -9148,12 +9233,12 @@
       <c r="C13" s="1" t="s">
         <v>180</v>
       </c>
-      <c r="D13" s="30" t="s">
+      <c r="D13" s="26" t="s">
         <v>178</v>
       </c>
-      <c r="E13" s="30"/>
-      <c r="F13" s="30"/>
-      <c r="G13" s="30"/>
+      <c r="E13" s="26"/>
+      <c r="F13" s="26"/>
+      <c r="G13" s="26"/>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A14" s="1" t="s">
@@ -9165,12 +9250,12 @@
       <c r="C14" s="1" t="s">
         <v>180</v>
       </c>
-      <c r="D14" s="30" t="s">
+      <c r="D14" s="26" t="s">
         <v>178</v>
       </c>
-      <c r="E14" s="30"/>
-      <c r="F14" s="30"/>
-      <c r="G14" s="30"/>
+      <c r="E14" s="26"/>
+      <c r="F14" s="26"/>
+      <c r="G14" s="26"/>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A15" s="1" t="s">
@@ -9182,12 +9267,12 @@
       <c r="C15" s="1" t="s">
         <v>143</v>
       </c>
-      <c r="D15" s="24" t="s">
+      <c r="D15" s="25" t="s">
         <v>406</v>
       </c>
-      <c r="E15" s="24"/>
-      <c r="F15" s="24"/>
-      <c r="G15" s="24"/>
+      <c r="E15" s="25"/>
+      <c r="F15" s="25"/>
+      <c r="G15" s="25"/>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A16" s="1" t="s">
@@ -9199,12 +9284,12 @@
       <c r="C16" s="1" t="s">
         <v>180</v>
       </c>
-      <c r="D16" s="34" t="s">
+      <c r="D16" s="27" t="s">
         <v>418</v>
       </c>
-      <c r="E16" s="34"/>
-      <c r="F16" s="34"/>
-      <c r="G16" s="34"/>
+      <c r="E16" s="27"/>
+      <c r="F16" s="27"/>
+      <c r="G16" s="27"/>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A17" s="1" t="s">
@@ -9216,12 +9301,12 @@
       <c r="C17" s="1" t="s">
         <v>143</v>
       </c>
-      <c r="D17" s="24" t="s">
+      <c r="D17" s="25" t="s">
         <v>589</v>
       </c>
-      <c r="E17" s="24"/>
-      <c r="F17" s="24"/>
-      <c r="G17" s="24"/>
+      <c r="E17" s="25"/>
+      <c r="F17" s="25"/>
+      <c r="G17" s="25"/>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A18" s="1" t="s">
@@ -9233,12 +9318,12 @@
       <c r="C18" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="D18" s="24" t="s">
+      <c r="D18" s="25" t="s">
         <v>581</v>
       </c>
-      <c r="E18" s="24"/>
-      <c r="F18" s="24"/>
-      <c r="G18" s="24"/>
+      <c r="E18" s="25"/>
+      <c r="F18" s="25"/>
+      <c r="G18" s="25"/>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A19" s="1" t="s">
@@ -9250,12 +9335,12 @@
       <c r="C19" s="1" t="s">
         <v>143</v>
       </c>
-      <c r="D19" s="24" t="s">
+      <c r="D19" s="25" t="s">
         <v>404</v>
       </c>
-      <c r="E19" s="24"/>
-      <c r="F19" s="24"/>
-      <c r="G19" s="24"/>
+      <c r="E19" s="25"/>
+      <c r="F19" s="25"/>
+      <c r="G19" s="25"/>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A20" s="1" t="s">
@@ -9267,12 +9352,12 @@
       <c r="C20" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="D20" s="30" t="s">
+      <c r="D20" s="26" t="s">
         <v>178</v>
       </c>
-      <c r="E20" s="30"/>
-      <c r="F20" s="30"/>
-      <c r="G20" s="30"/>
+      <c r="E20" s="26"/>
+      <c r="F20" s="26"/>
+      <c r="G20" s="26"/>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A21" s="1" t="s">
@@ -9284,12 +9369,12 @@
       <c r="C21" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="D21" s="24" t="s">
+      <c r="D21" s="25" t="s">
         <v>740</v>
       </c>
-      <c r="E21" s="24"/>
-      <c r="F21" s="24"/>
-      <c r="G21" s="24"/>
+      <c r="E21" s="25"/>
+      <c r="F21" s="25"/>
+      <c r="G21" s="25"/>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A22" s="1" t="s">
@@ -9301,12 +9386,12 @@
       <c r="C22" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="D22" s="24" t="s">
+      <c r="D22" s="25" t="s">
         <v>739</v>
       </c>
-      <c r="E22" s="24"/>
-      <c r="F22" s="24"/>
-      <c r="G22" s="24"/>
+      <c r="E22" s="25"/>
+      <c r="F22" s="25"/>
+      <c r="G22" s="25"/>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A23" s="1" t="s">
@@ -9318,12 +9403,12 @@
       <c r="C23" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="D23" s="24" t="s">
+      <c r="D23" s="25" t="s">
         <v>738</v>
       </c>
-      <c r="E23" s="24"/>
-      <c r="F23" s="24"/>
-      <c r="G23" s="24"/>
+      <c r="E23" s="25"/>
+      <c r="F23" s="25"/>
+      <c r="G23" s="25"/>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A24" s="1" t="s">
@@ -9335,12 +9420,12 @@
       <c r="C24" s="1" t="s">
         <v>143</v>
       </c>
-      <c r="D24" s="24" t="s">
+      <c r="D24" s="25" t="s">
         <v>404</v>
       </c>
-      <c r="E24" s="24"/>
-      <c r="F24" s="24"/>
-      <c r="G24" s="24"/>
+      <c r="E24" s="25"/>
+      <c r="F24" s="25"/>
+      <c r="G24" s="25"/>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A25" s="1" t="s">
@@ -9352,12 +9437,12 @@
       <c r="C25" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="D25" s="24" t="s">
+      <c r="D25" s="25" t="s">
         <v>823</v>
       </c>
-      <c r="E25" s="24"/>
-      <c r="F25" s="24"/>
-      <c r="G25" s="24"/>
+      <c r="E25" s="25"/>
+      <c r="F25" s="25"/>
+      <c r="G25" s="25"/>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A26" s="1" t="s">
@@ -9369,12 +9454,12 @@
       <c r="C26" s="1" t="s">
         <v>143</v>
       </c>
-      <c r="D26" s="30" t="s">
+      <c r="D26" s="26" t="s">
         <v>178</v>
       </c>
-      <c r="E26" s="30"/>
-      <c r="F26" s="30"/>
-      <c r="G26" s="30"/>
+      <c r="E26" s="26"/>
+      <c r="F26" s="26"/>
+      <c r="G26" s="26"/>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A27" s="1" t="s">
@@ -9386,12 +9471,12 @@
       <c r="C27" s="1" t="s">
         <v>143</v>
       </c>
-      <c r="D27" s="30" t="s">
+      <c r="D27" s="26" t="s">
         <v>182</v>
       </c>
-      <c r="E27" s="30"/>
-      <c r="F27" s="30"/>
-      <c r="G27" s="30"/>
+      <c r="E27" s="26"/>
+      <c r="F27" s="26"/>
+      <c r="G27" s="26"/>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A28" s="1" t="s">
@@ -9403,12 +9488,12 @@
       <c r="C28" s="1" t="s">
         <v>143</v>
       </c>
-      <c r="D28" s="24" t="s">
+      <c r="D28" s="25" t="s">
         <v>406</v>
       </c>
-      <c r="E28" s="24"/>
-      <c r="F28" s="24"/>
-      <c r="G28" s="24"/>
+      <c r="E28" s="25"/>
+      <c r="F28" s="25"/>
+      <c r="G28" s="25"/>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A29" s="1" t="s">
@@ -9420,12 +9505,12 @@
       <c r="C29" s="1" t="s">
         <v>143</v>
       </c>
-      <c r="D29" s="30" t="s">
+      <c r="D29" s="26" t="s">
         <v>178</v>
       </c>
-      <c r="E29" s="30"/>
-      <c r="F29" s="30"/>
-      <c r="G29" s="30"/>
+      <c r="E29" s="26"/>
+      <c r="F29" s="26"/>
+      <c r="G29" s="26"/>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A30" s="1" t="s">
@@ -9437,12 +9522,12 @@
       <c r="C30" s="1" t="s">
         <v>180</v>
       </c>
-      <c r="D30" s="30" t="s">
+      <c r="D30" s="26" t="s">
         <v>421</v>
       </c>
-      <c r="E30" s="30"/>
-      <c r="F30" s="30"/>
-      <c r="G30" s="30"/>
+      <c r="E30" s="26"/>
+      <c r="F30" s="26"/>
+      <c r="G30" s="26"/>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A31" s="1" t="s">
@@ -9454,12 +9539,12 @@
       <c r="C31" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="D31" s="24" t="s">
+      <c r="D31" s="25" t="s">
         <v>822</v>
       </c>
-      <c r="E31" s="24"/>
-      <c r="F31" s="24"/>
-      <c r="G31" s="24"/>
+      <c r="E31" s="25"/>
+      <c r="F31" s="25"/>
+      <c r="G31" s="25"/>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A32" s="1" t="s">
@@ -9471,12 +9556,12 @@
       <c r="C32" s="1" t="s">
         <v>181</v>
       </c>
-      <c r="D32" s="30" t="s">
+      <c r="D32" s="26" t="s">
         <v>182</v>
       </c>
-      <c r="E32" s="30"/>
-      <c r="F32" s="30"/>
-      <c r="G32" s="30"/>
+      <c r="E32" s="26"/>
+      <c r="F32" s="26"/>
+      <c r="G32" s="26"/>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A33" s="1" t="s">
@@ -9488,12 +9573,12 @@
       <c r="C33" s="1" t="s">
         <v>180</v>
       </c>
-      <c r="D33" s="24" t="s">
+      <c r="D33" s="25" t="s">
         <v>416</v>
       </c>
-      <c r="E33" s="24"/>
-      <c r="F33" s="24"/>
-      <c r="G33" s="24"/>
+      <c r="E33" s="25"/>
+      <c r="F33" s="25"/>
+      <c r="G33" s="25"/>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A34" s="1" t="s">
@@ -9505,12 +9590,12 @@
       <c r="C34" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="D34" s="30" t="s">
+      <c r="D34" s="26" t="s">
         <v>182</v>
       </c>
-      <c r="E34" s="30"/>
-      <c r="F34" s="30"/>
-      <c r="G34" s="30"/>
+      <c r="E34" s="26"/>
+      <c r="F34" s="26"/>
+      <c r="G34" s="26"/>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A36" s="1" t="s">
@@ -9610,12 +9695,12 @@
       <c r="C44" s="1" t="s">
         <v>143</v>
       </c>
-      <c r="D44" s="30" t="s">
+      <c r="D44" s="26" t="s">
         <v>421</v>
       </c>
-      <c r="E44" s="30"/>
-      <c r="F44" s="30"/>
-      <c r="G44" s="30"/>
+      <c r="E44" s="26"/>
+      <c r="F44" s="26"/>
+      <c r="G44" s="26"/>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A46" s="1" t="s">
@@ -9627,12 +9712,12 @@
       <c r="C46" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="D46" s="30" t="s">
+      <c r="D46" s="26" t="s">
         <v>421</v>
       </c>
-      <c r="E46" s="30"/>
-      <c r="F46" s="30"/>
-      <c r="G46" s="30"/>
+      <c r="E46" s="26"/>
+      <c r="F46" s="26"/>
+      <c r="G46" s="26"/>
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A47" s="1" t="s">
@@ -9644,12 +9729,12 @@
       <c r="C47" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="D47" s="30" t="s">
+      <c r="D47" s="26" t="s">
         <v>421</v>
       </c>
-      <c r="E47" s="30"/>
-      <c r="F47" s="30"/>
-      <c r="G47" s="30"/>
+      <c r="E47" s="26"/>
+      <c r="F47" s="26"/>
+      <c r="G47" s="26"/>
     </row>
     <row r="48" spans="1:8" ht="15.6" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A48" s="16" t="s">
@@ -9661,12 +9746,12 @@
       <c r="C48" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="D48" s="30" t="s">
+      <c r="D48" s="26" t="s">
         <v>421</v>
       </c>
-      <c r="E48" s="30"/>
-      <c r="F48" s="30"/>
-      <c r="G48" s="30"/>
+      <c r="E48" s="26"/>
+      <c r="F48" s="26"/>
+      <c r="G48" s="26"/>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A49" s="16" t="s">
@@ -9701,12 +9786,12 @@
       <c r="C50" s="1" t="s">
         <v>143</v>
       </c>
-      <c r="D50" s="24" t="s">
+      <c r="D50" s="25" t="s">
         <v>406</v>
       </c>
-      <c r="E50" s="24"/>
-      <c r="F50" s="24"/>
-      <c r="G50" s="24"/>
+      <c r="E50" s="25"/>
+      <c r="F50" s="25"/>
+      <c r="G50" s="25"/>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A51" s="1" t="s">
@@ -9718,12 +9803,12 @@
       <c r="C51" s="1" t="s">
         <v>143</v>
       </c>
-      <c r="D51" s="24" t="s">
+      <c r="D51" s="25" t="s">
         <v>406</v>
       </c>
-      <c r="E51" s="24"/>
-      <c r="F51" s="24"/>
-      <c r="G51" s="24"/>
+      <c r="E51" s="25"/>
+      <c r="F51" s="25"/>
+      <c r="G51" s="25"/>
     </row>
     <row r="52" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A52" s="1" t="s">
@@ -9735,12 +9820,12 @@
       <c r="C52" s="1" t="s">
         <v>143</v>
       </c>
-      <c r="D52" s="24" t="s">
+      <c r="D52" s="25" t="s">
         <v>406</v>
       </c>
-      <c r="E52" s="24"/>
-      <c r="F52" s="24"/>
-      <c r="G52" s="24"/>
+      <c r="E52" s="25"/>
+      <c r="F52" s="25"/>
+      <c r="G52" s="25"/>
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A54" s="1" t="s">
@@ -9752,12 +9837,12 @@
       <c r="C54" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="D54" s="30" t="s">
+      <c r="D54" s="26" t="s">
         <v>422</v>
       </c>
-      <c r="E54" s="30"/>
-      <c r="F54" s="30"/>
-      <c r="G54" s="30"/>
+      <c r="E54" s="26"/>
+      <c r="F54" s="26"/>
+      <c r="G54" s="26"/>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A55" s="1" t="s">
@@ -9769,12 +9854,12 @@
       <c r="C55" s="1" t="s">
         <v>180</v>
       </c>
-      <c r="D55" s="30" t="s">
+      <c r="D55" s="26" t="s">
         <v>305</v>
       </c>
-      <c r="E55" s="30"/>
-      <c r="F55" s="30"/>
-      <c r="G55" s="30"/>
+      <c r="E55" s="26"/>
+      <c r="F55" s="26"/>
+      <c r="G55" s="26"/>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A56" s="1" t="s">
@@ -9786,12 +9871,12 @@
       <c r="C56" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="D56" s="30" t="s">
+      <c r="D56" s="26" t="s">
         <v>305</v>
       </c>
-      <c r="E56" s="30"/>
-      <c r="F56" s="30"/>
-      <c r="G56" s="30"/>
+      <c r="E56" s="26"/>
+      <c r="F56" s="26"/>
+      <c r="G56" s="26"/>
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A58" s="1" t="s">
@@ -9803,12 +9888,12 @@
       <c r="C58" s="1" t="s">
         <v>143</v>
       </c>
-      <c r="D58" s="24" t="s">
+      <c r="D58" s="25" t="s">
         <v>786</v>
       </c>
-      <c r="E58" s="24"/>
-      <c r="F58" s="24"/>
-      <c r="G58" s="24"/>
+      <c r="E58" s="25"/>
+      <c r="F58" s="25"/>
+      <c r="G58" s="25"/>
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A59" s="1" t="s">
@@ -9820,12 +9905,12 @@
       <c r="C59" s="1" t="s">
         <v>143</v>
       </c>
-      <c r="D59" s="24" t="s">
+      <c r="D59" s="25" t="s">
         <v>404</v>
       </c>
-      <c r="E59" s="24"/>
-      <c r="F59" s="24"/>
-      <c r="G59" s="24"/>
+      <c r="E59" s="25"/>
+      <c r="F59" s="25"/>
+      <c r="G59" s="25"/>
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A60" s="1" t="s">
@@ -9837,12 +9922,12 @@
       <c r="C60" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="D60" s="30" t="s">
+      <c r="D60" s="26" t="s">
         <v>421</v>
       </c>
-      <c r="E60" s="30"/>
-      <c r="F60" s="30"/>
-      <c r="G60" s="30"/>
+      <c r="E60" s="26"/>
+      <c r="F60" s="26"/>
+      <c r="G60" s="26"/>
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A61" s="1" t="s">
@@ -9854,12 +9939,12 @@
       <c r="C61" s="1" t="s">
         <v>143</v>
       </c>
-      <c r="D61" s="24" t="s">
+      <c r="D61" s="25" t="s">
         <v>404</v>
       </c>
-      <c r="E61" s="24"/>
-      <c r="F61" s="24"/>
-      <c r="G61" s="24"/>
+      <c r="E61" s="25"/>
+      <c r="F61" s="25"/>
+      <c r="G61" s="25"/>
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A62" s="1" t="s">
@@ -9871,12 +9956,12 @@
       <c r="C62" s="1" t="s">
         <v>143</v>
       </c>
-      <c r="D62" s="24" t="s">
+      <c r="D62" s="25" t="s">
         <v>404</v>
       </c>
-      <c r="E62" s="24"/>
-      <c r="F62" s="24"/>
-      <c r="G62" s="24"/>
+      <c r="E62" s="25"/>
+      <c r="F62" s="25"/>
+      <c r="G62" s="25"/>
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A63" s="1" t="s">
@@ -9888,12 +9973,12 @@
       <c r="C63" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="D63" s="30" t="s">
+      <c r="D63" s="26" t="s">
         <v>421</v>
       </c>
-      <c r="E63" s="30"/>
-      <c r="F63" s="30"/>
-      <c r="G63" s="30"/>
+      <c r="E63" s="26"/>
+      <c r="F63" s="26"/>
+      <c r="G63" s="26"/>
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A64" s="1" t="s">
@@ -9905,12 +9990,12 @@
       <c r="C64" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="D64" s="30" t="s">
+      <c r="D64" s="26" t="s">
         <v>421</v>
       </c>
-      <c r="E64" s="30"/>
-      <c r="F64" s="30"/>
-      <c r="G64" s="30"/>
+      <c r="E64" s="26"/>
+      <c r="F64" s="26"/>
+      <c r="G64" s="26"/>
     </row>
     <row r="66" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A66" s="1" t="s">
@@ -9922,12 +10007,12 @@
       <c r="C66" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="D66" s="30" t="s">
+      <c r="D66" s="26" t="s">
         <v>421</v>
       </c>
-      <c r="E66" s="30"/>
-      <c r="F66" s="30"/>
-      <c r="G66" s="30"/>
+      <c r="E66" s="26"/>
+      <c r="F66" s="26"/>
+      <c r="G66" s="26"/>
     </row>
     <row r="67" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A67" s="1" t="s">
@@ -9939,12 +10024,12 @@
       <c r="C67" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="D67" s="30" t="s">
+      <c r="D67" s="26" t="s">
         <v>421</v>
       </c>
-      <c r="E67" s="30"/>
-      <c r="F67" s="30"/>
-      <c r="G67" s="30"/>
+      <c r="E67" s="26"/>
+      <c r="F67" s="26"/>
+      <c r="G67" s="26"/>
     </row>
     <row r="69" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A69" s="1" t="s">
@@ -9956,12 +10041,12 @@
       <c r="C69" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="D69" s="24" t="s">
+      <c r="D69" s="25" t="s">
         <v>404</v>
       </c>
-      <c r="E69" s="24"/>
-      <c r="F69" s="24"/>
-      <c r="G69" s="24"/>
+      <c r="E69" s="25"/>
+      <c r="F69" s="25"/>
+      <c r="G69" s="25"/>
     </row>
     <row r="70" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A70" s="1" t="s">
@@ -9973,12 +10058,12 @@
       <c r="C70" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="D70" s="24" t="s">
+      <c r="D70" s="25" t="s">
         <v>799</v>
       </c>
-      <c r="E70" s="24"/>
-      <c r="F70" s="24"/>
-      <c r="G70" s="24"/>
+      <c r="E70" s="25"/>
+      <c r="F70" s="25"/>
+      <c r="G70" s="25"/>
     </row>
     <row r="71" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A71" s="1" t="s">
@@ -9990,12 +10075,12 @@
       <c r="C71" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="D71" s="24" t="s">
+      <c r="D71" s="25" t="s">
         <v>800</v>
       </c>
-      <c r="E71" s="24"/>
-      <c r="F71" s="24"/>
-      <c r="G71" s="24"/>
+      <c r="E71" s="25"/>
+      <c r="F71" s="25"/>
+      <c r="G71" s="25"/>
     </row>
     <row r="72" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A72" s="1" t="s">
@@ -10007,12 +10092,12 @@
       <c r="C72" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="D72" s="34" t="s">
+      <c r="D72" s="27" t="s">
         <v>801</v>
       </c>
-      <c r="E72" s="34"/>
-      <c r="F72" s="34"/>
-      <c r="G72" s="34"/>
+      <c r="E72" s="27"/>
+      <c r="F72" s="27"/>
+      <c r="G72" s="27"/>
     </row>
     <row r="73" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A73" s="1" t="s">
@@ -10024,12 +10109,12 @@
       <c r="C73" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="D73" s="24" t="s">
+      <c r="D73" s="25" t="s">
         <v>599</v>
       </c>
-      <c r="E73" s="24"/>
-      <c r="F73" s="24"/>
-      <c r="G73" s="24"/>
+      <c r="E73" s="25"/>
+      <c r="F73" s="25"/>
+      <c r="G73" s="25"/>
     </row>
     <row r="74" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A74" s="1" t="s">
@@ -10041,12 +10126,12 @@
       <c r="C74" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="D74" s="24" t="s">
+      <c r="D74" s="25" t="s">
         <v>598</v>
       </c>
-      <c r="E74" s="24"/>
-      <c r="F74" s="24"/>
-      <c r="G74" s="24"/>
+      <c r="E74" s="25"/>
+      <c r="F74" s="25"/>
+      <c r="G74" s="25"/>
     </row>
     <row r="75" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A75" s="1" t="s">
@@ -10058,12 +10143,12 @@
       <c r="C75" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="D75" s="24" t="s">
+      <c r="D75" s="25" t="s">
         <v>596</v>
       </c>
-      <c r="E75" s="24"/>
-      <c r="F75" s="24"/>
-      <c r="G75" s="24"/>
+      <c r="E75" s="25"/>
+      <c r="F75" s="25"/>
+      <c r="G75" s="25"/>
     </row>
     <row r="76" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A76" s="1" t="s">
@@ -10075,12 +10160,12 @@
       <c r="C76" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="D76" s="24" t="s">
+      <c r="D76" s="25" t="s">
         <v>597</v>
       </c>
-      <c r="E76" s="24"/>
-      <c r="F76" s="24"/>
-      <c r="G76" s="24"/>
+      <c r="E76" s="25"/>
+      <c r="F76" s="25"/>
+      <c r="G76" s="25"/>
     </row>
     <row r="77" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A77" s="1" t="s">
@@ -10092,12 +10177,12 @@
       <c r="C77" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="D77" s="24" t="s">
+      <c r="D77" s="25" t="s">
         <v>600</v>
       </c>
-      <c r="E77" s="24"/>
-      <c r="F77" s="24"/>
-      <c r="G77" s="24"/>
+      <c r="E77" s="25"/>
+      <c r="F77" s="25"/>
+      <c r="G77" s="25"/>
     </row>
     <row r="79" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A79" s="1" t="s">
@@ -10109,12 +10194,12 @@
       <c r="C79" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="D79" s="34" t="s">
+      <c r="D79" s="27" t="s">
         <v>735</v>
       </c>
-      <c r="E79" s="34"/>
-      <c r="F79" s="34"/>
-      <c r="G79" s="34"/>
+      <c r="E79" s="27"/>
+      <c r="F79" s="27"/>
+      <c r="G79" s="27"/>
     </row>
     <row r="80" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A80" s="1" t="s">
@@ -10181,12 +10266,12 @@
       <c r="C85" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="D85" s="24" t="s">
+      <c r="D85" s="25" t="s">
         <v>592</v>
       </c>
-      <c r="E85" s="24"/>
-      <c r="F85" s="24"/>
-      <c r="G85" s="24"/>
+      <c r="E85" s="25"/>
+      <c r="F85" s="25"/>
+      <c r="G85" s="25"/>
     </row>
     <row r="86" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A86" s="1" t="s">
@@ -10198,12 +10283,12 @@
       <c r="C86" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="D86" s="24" t="s">
+      <c r="D86" s="25" t="s">
         <v>595</v>
       </c>
-      <c r="E86" s="24"/>
-      <c r="F86" s="24"/>
-      <c r="G86" s="24"/>
+      <c r="E86" s="25"/>
+      <c r="F86" s="25"/>
+      <c r="G86" s="25"/>
     </row>
     <row r="87" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A87" s="1" t="s">
@@ -10259,12 +10344,12 @@
       <c r="C91" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="D91" s="24" t="s">
+      <c r="D91" s="25" t="s">
         <v>584</v>
       </c>
-      <c r="E91" s="24"/>
-      <c r="F91" s="24"/>
-      <c r="G91" s="24"/>
+      <c r="E91" s="25"/>
+      <c r="F91" s="25"/>
+      <c r="G91" s="25"/>
     </row>
     <row r="92" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A92" s="1" t="s">
@@ -10276,12 +10361,12 @@
       <c r="C92" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="D92" s="24" t="s">
+      <c r="D92" s="25" t="s">
         <v>585</v>
       </c>
-      <c r="E92" s="24"/>
-      <c r="F92" s="24"/>
-      <c r="G92" s="24"/>
+      <c r="E92" s="25"/>
+      <c r="F92" s="25"/>
+      <c r="G92" s="25"/>
     </row>
     <row r="93" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A93" s="1" t="s">
@@ -10293,12 +10378,12 @@
       <c r="C93" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="D93" s="24" t="s">
+      <c r="D93" s="25" t="s">
         <v>586</v>
       </c>
-      <c r="E93" s="24"/>
-      <c r="F93" s="24"/>
-      <c r="G93" s="24"/>
+      <c r="E93" s="25"/>
+      <c r="F93" s="25"/>
+      <c r="G93" s="25"/>
     </row>
     <row r="94" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A94" s="1" t="s">
@@ -10310,12 +10395,12 @@
       <c r="C94" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="D94" s="24" t="s">
+      <c r="D94" s="25" t="s">
         <v>585</v>
       </c>
-      <c r="E94" s="24"/>
-      <c r="F94" s="24"/>
-      <c r="G94" s="24"/>
+      <c r="E94" s="25"/>
+      <c r="F94" s="25"/>
+      <c r="G94" s="25"/>
     </row>
     <row r="95" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A95" s="1" t="s">
@@ -10327,12 +10412,12 @@
       <c r="C95" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="D95" s="24" t="s">
+      <c r="D95" s="25" t="s">
         <v>781</v>
       </c>
-      <c r="E95" s="24"/>
-      <c r="F95" s="24"/>
-      <c r="G95" s="24"/>
+      <c r="E95" s="25"/>
+      <c r="F95" s="25"/>
+      <c r="G95" s="25"/>
     </row>
     <row r="96" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A96" s="1" t="s">
@@ -10344,12 +10429,12 @@
       <c r="C96" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="D96" s="24" t="s">
+      <c r="D96" s="25" t="s">
         <v>780</v>
       </c>
-      <c r="E96" s="24"/>
-      <c r="F96" s="24"/>
-      <c r="G96" s="24"/>
+      <c r="E96" s="25"/>
+      <c r="F96" s="25"/>
+      <c r="G96" s="25"/>
     </row>
     <row r="97" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A97" s="1" t="s">
@@ -10361,12 +10446,12 @@
       <c r="C97" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="D97" s="24" t="s">
+      <c r="D97" s="25" t="s">
         <v>819</v>
       </c>
-      <c r="E97" s="24"/>
-      <c r="F97" s="24"/>
-      <c r="G97" s="24"/>
+      <c r="E97" s="25"/>
+      <c r="F97" s="25"/>
+      <c r="G97" s="25"/>
     </row>
     <row r="99" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A99" s="1" t="s">
@@ -10433,12 +10518,12 @@
       <c r="C104" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="D104" s="24" t="s">
+      <c r="D104" s="25" t="s">
         <v>404</v>
       </c>
-      <c r="E104" s="24"/>
-      <c r="F104" s="24"/>
-      <c r="G104" s="24"/>
+      <c r="E104" s="25"/>
+      <c r="F104" s="25"/>
+      <c r="G104" s="25"/>
     </row>
     <row r="105" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A105" s="1" t="s">
@@ -10450,12 +10535,12 @@
       <c r="C105" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="D105" s="34" t="s">
+      <c r="D105" s="27" t="s">
         <v>808</v>
       </c>
-      <c r="E105" s="34"/>
-      <c r="F105" s="34"/>
-      <c r="G105" s="34"/>
+      <c r="E105" s="27"/>
+      <c r="F105" s="27"/>
+      <c r="G105" s="27"/>
     </row>
     <row r="107" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A107" s="1" t="s">
@@ -10467,16 +10552,16 @@
       <c r="C107" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="D107" s="35" t="s">
+      <c r="D107" s="38" t="s">
         <v>494</v>
       </c>
-      <c r="E107" s="35" t="s">
+      <c r="E107" s="38" t="s">
         <v>493</v>
       </c>
-      <c r="F107" s="35" t="s">
+      <c r="F107" s="38" t="s">
         <v>309</v>
       </c>
-      <c r="G107" s="35" t="s">
+      <c r="G107" s="38" t="s">
         <v>489</v>
       </c>
     </row>
@@ -10501,12 +10586,12 @@
       <c r="C109" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="D109" s="24" t="s">
+      <c r="D109" s="25" t="s">
         <v>599</v>
       </c>
-      <c r="E109" s="24"/>
-      <c r="F109" s="24"/>
-      <c r="G109" s="24"/>
+      <c r="E109" s="25"/>
+      <c r="F109" s="25"/>
+      <c r="G109" s="25"/>
     </row>
     <row r="110" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A110" s="16" t="s">
@@ -10518,12 +10603,12 @@
       <c r="C110" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="D110" s="24" t="s">
+      <c r="D110" s="25" t="s">
         <v>598</v>
       </c>
-      <c r="E110" s="24"/>
-      <c r="F110" s="24"/>
-      <c r="G110" s="24"/>
+      <c r="E110" s="25"/>
+      <c r="F110" s="25"/>
+      <c r="G110" s="25"/>
     </row>
     <row r="111" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A111" s="16" t="s">
@@ -10535,12 +10620,12 @@
       <c r="C111" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="D111" s="24" t="s">
+      <c r="D111" s="25" t="s">
         <v>596</v>
       </c>
-      <c r="E111" s="24"/>
-      <c r="F111" s="24"/>
-      <c r="G111" s="24"/>
+      <c r="E111" s="25"/>
+      <c r="F111" s="25"/>
+      <c r="G111" s="25"/>
     </row>
     <row r="112" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A112" s="16" t="s">
@@ -10552,12 +10637,12 @@
       <c r="C112" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="D112" s="24" t="s">
+      <c r="D112" s="25" t="s">
         <v>597</v>
       </c>
-      <c r="E112" s="24"/>
-      <c r="F112" s="24"/>
-      <c r="G112" s="24"/>
+      <c r="E112" s="25"/>
+      <c r="F112" s="25"/>
+      <c r="G112" s="25"/>
     </row>
     <row r="113" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A113" s="16" t="s">
@@ -10580,12 +10665,12 @@
       <c r="C114" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="D114" s="24" t="s">
+      <c r="D114" s="25" t="s">
         <v>588</v>
       </c>
-      <c r="E114" s="24"/>
-      <c r="F114" s="24"/>
-      <c r="G114" s="24"/>
+      <c r="E114" s="25"/>
+      <c r="F114" s="25"/>
+      <c r="G114" s="25"/>
     </row>
     <row r="115" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A115" s="16" t="s">
@@ -10619,12 +10704,12 @@
       <c r="C118" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="D118" s="24" t="s">
+      <c r="D118" s="25" t="s">
         <v>807</v>
       </c>
-      <c r="E118" s="24"/>
-      <c r="F118" s="24"/>
-      <c r="G118" s="24"/>
+      <c r="E118" s="25"/>
+      <c r="F118" s="25"/>
+      <c r="G118" s="25"/>
     </row>
     <row r="119" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A119" s="1" t="s">
@@ -10639,31 +10724,47 @@
     </row>
   </sheetData>
   <mergeCells count="82">
-    <mergeCell ref="D114:G114"/>
-    <mergeCell ref="D92:G92"/>
-    <mergeCell ref="D93:G93"/>
-    <mergeCell ref="D104:G104"/>
-    <mergeCell ref="D107:G107"/>
-    <mergeCell ref="D109:G109"/>
-    <mergeCell ref="D110:G110"/>
-    <mergeCell ref="D111:G111"/>
-    <mergeCell ref="D112:G112"/>
-    <mergeCell ref="D94:G94"/>
-    <mergeCell ref="D95:G95"/>
-    <mergeCell ref="D96:G96"/>
-    <mergeCell ref="D97:G97"/>
-    <mergeCell ref="D59:G59"/>
-    <mergeCell ref="D58:G58"/>
-    <mergeCell ref="D69:G69"/>
-    <mergeCell ref="D48:G48"/>
-    <mergeCell ref="D50:G50"/>
-    <mergeCell ref="D51:G51"/>
-    <mergeCell ref="D52:G52"/>
-    <mergeCell ref="D54:G54"/>
-    <mergeCell ref="D61:G61"/>
-    <mergeCell ref="D62:G62"/>
-    <mergeCell ref="D64:G64"/>
-    <mergeCell ref="D60:G60"/>
+    <mergeCell ref="D118:G118"/>
+    <mergeCell ref="D105:G105"/>
+    <mergeCell ref="A11:B11"/>
+    <mergeCell ref="D11:G11"/>
+    <mergeCell ref="D24:G24"/>
+    <mergeCell ref="D70:G70"/>
+    <mergeCell ref="D71:G71"/>
+    <mergeCell ref="D91:G91"/>
+    <mergeCell ref="D13:G13"/>
+    <mergeCell ref="D14:G14"/>
+    <mergeCell ref="D15:G15"/>
+    <mergeCell ref="D16:G16"/>
+    <mergeCell ref="D26:G26"/>
+    <mergeCell ref="D17:G17"/>
+    <mergeCell ref="D18:G18"/>
+    <mergeCell ref="D19:G19"/>
+    <mergeCell ref="A7:C7"/>
+    <mergeCell ref="D7:E7"/>
+    <mergeCell ref="A8:C8"/>
+    <mergeCell ref="D8:E8"/>
+    <mergeCell ref="A9:C9"/>
+    <mergeCell ref="A4:C4"/>
+    <mergeCell ref="D4:E4"/>
+    <mergeCell ref="A5:C5"/>
+    <mergeCell ref="D5:E5"/>
+    <mergeCell ref="A6:C6"/>
+    <mergeCell ref="D6:E6"/>
+    <mergeCell ref="D20:G20"/>
+    <mergeCell ref="D27:G27"/>
+    <mergeCell ref="D28:G28"/>
+    <mergeCell ref="D29:G29"/>
+    <mergeCell ref="D30:G30"/>
+    <mergeCell ref="D25:G25"/>
+    <mergeCell ref="D73:G73"/>
+    <mergeCell ref="D23:G23"/>
+    <mergeCell ref="D22:G22"/>
+    <mergeCell ref="D21:G21"/>
+    <mergeCell ref="D34:G34"/>
+    <mergeCell ref="D32:G32"/>
+    <mergeCell ref="D33:G33"/>
+    <mergeCell ref="D31:G31"/>
     <mergeCell ref="D72:G72"/>
     <mergeCell ref="D86:G86"/>
     <mergeCell ref="D67:G67"/>
@@ -10680,47 +10781,31 @@
     <mergeCell ref="D55:G55"/>
     <mergeCell ref="D56:G56"/>
     <mergeCell ref="D63:G63"/>
-    <mergeCell ref="D73:G73"/>
-    <mergeCell ref="D23:G23"/>
-    <mergeCell ref="D22:G22"/>
-    <mergeCell ref="D21:G21"/>
-    <mergeCell ref="D34:G34"/>
-    <mergeCell ref="D20:G20"/>
-    <mergeCell ref="D27:G27"/>
-    <mergeCell ref="D28:G28"/>
-    <mergeCell ref="D29:G29"/>
-    <mergeCell ref="D30:G30"/>
-    <mergeCell ref="D32:G32"/>
-    <mergeCell ref="D33:G33"/>
-    <mergeCell ref="D31:G31"/>
-    <mergeCell ref="D25:G25"/>
-    <mergeCell ref="A4:C4"/>
-    <mergeCell ref="D4:E4"/>
-    <mergeCell ref="A5:C5"/>
-    <mergeCell ref="D5:E5"/>
-    <mergeCell ref="A6:C6"/>
-    <mergeCell ref="D6:E6"/>
-    <mergeCell ref="A7:C7"/>
-    <mergeCell ref="D7:E7"/>
-    <mergeCell ref="A8:C8"/>
-    <mergeCell ref="D8:E8"/>
-    <mergeCell ref="A9:C9"/>
-    <mergeCell ref="D118:G118"/>
-    <mergeCell ref="D105:G105"/>
-    <mergeCell ref="A11:B11"/>
-    <mergeCell ref="D11:G11"/>
-    <mergeCell ref="D24:G24"/>
-    <mergeCell ref="D70:G70"/>
-    <mergeCell ref="D71:G71"/>
-    <mergeCell ref="D91:G91"/>
-    <mergeCell ref="D13:G13"/>
-    <mergeCell ref="D14:G14"/>
-    <mergeCell ref="D15:G15"/>
-    <mergeCell ref="D16:G16"/>
-    <mergeCell ref="D26:G26"/>
-    <mergeCell ref="D17:G17"/>
-    <mergeCell ref="D18:G18"/>
-    <mergeCell ref="D19:G19"/>
+    <mergeCell ref="D59:G59"/>
+    <mergeCell ref="D58:G58"/>
+    <mergeCell ref="D69:G69"/>
+    <mergeCell ref="D48:G48"/>
+    <mergeCell ref="D50:G50"/>
+    <mergeCell ref="D51:G51"/>
+    <mergeCell ref="D52:G52"/>
+    <mergeCell ref="D54:G54"/>
+    <mergeCell ref="D61:G61"/>
+    <mergeCell ref="D62:G62"/>
+    <mergeCell ref="D64:G64"/>
+    <mergeCell ref="D60:G60"/>
+    <mergeCell ref="D114:G114"/>
+    <mergeCell ref="D92:G92"/>
+    <mergeCell ref="D93:G93"/>
+    <mergeCell ref="D104:G104"/>
+    <mergeCell ref="D107:G107"/>
+    <mergeCell ref="D109:G109"/>
+    <mergeCell ref="D110:G110"/>
+    <mergeCell ref="D111:G111"/>
+    <mergeCell ref="D112:G112"/>
+    <mergeCell ref="D94:G94"/>
+    <mergeCell ref="D95:G95"/>
+    <mergeCell ref="D96:G96"/>
+    <mergeCell ref="D97:G97"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
